--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC19" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Netherland" displayName="AveragesTable_Netherland" ref="A1:EC19" headerRowCount="1">
   <autoFilter ref="A1:EC19"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -5018,13 +5018,13 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="H11" t="n">
-        <v>91.33</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -5033,67 +5033,67 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="L11" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="M11" t="n">
-        <v>48.33</v>
+        <v>42.86</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>10.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>13.29</v>
       </c>
       <c r="R11" t="n">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="U11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>48.67</v>
+        <v>48.43</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.33</v>
+        <v>13.71</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.67</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.67</v>
+        <v>4.43</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.33</v>
+        <v>18.86</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF11" t="n">
         <v>0.17</v>
@@ -5177,70 +5177,70 @@
         <v>1.83</v>
       </c>
       <c r="BG11" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.58</v>
+        <v>8.77</v>
       </c>
       <c r="BI11" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="BO11" t="n">
         <v>1.08</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.08</v>
+        <v>4.15</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.5</v>
+        <v>4.62</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BT11" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV11" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX11" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.68</v>
+        <v>3.31</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.59</v>
+        <v>3.32</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.09</v>
+        <v>4.21</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.21</v>
+        <v>4.37</v>
       </c>
       <c r="CC11" t="n">
         <v>6.05</v>
@@ -5249,43 +5249,43 @@
         <v>6.41</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL11" t="n">
         <v>1.86</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
@@ -5315,64 +5315,64 @@
         <v>2.42</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="DE11" t="n">
         <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DG11" t="n">
         <v>2</v>
       </c>
       <c r="DH11" t="n">
-        <v>90.58</v>
+        <v>84.38</v>
       </c>
       <c r="DI11" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DM11" t="n">
-        <v>41.66</v>
+        <v>39.23</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.75</v>
+        <v>11.69</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.66</v>
+        <v>12.85</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.84</v>
+        <v>7.77</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
@@ -5381,25 +5381,25 @@
         <v>47.08</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DX11" t="n">
-        <v>12</v>
+        <v>12.31</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.08</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.08</v>
+        <v>20.23</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="12">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0.33</v>
@@ -6305,52 +6305,52 @@
         <v>0.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="AI14" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.17</v>
+        <v>5.14</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN14" t="n">
-        <v>53.83</v>
+        <v>47.57</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11</v>
+        <v>11.57</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.17</v>
+        <v>8.57</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>55.5</v>
+        <v>55.14</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.83</v>
+        <v>14.86</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.67</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.17</v>
+        <v>6.71</v>
       </c>
       <c r="BD14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="BF14" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.75</v>
+        <v>4.46</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.75</v>
+        <v>10.77</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.75</v>
+        <v>4.46</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.5</v>
+        <v>6.46</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="BT14" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BU14" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BV14" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BW14" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BX14" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BY14" t="n">
         <v>1.24</v>
@@ -6446,46 +6446,46 @@
         <v>1.24</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.11</v>
+        <v>6.08</v>
       </c>
       <c r="CB14" t="n">
-        <v>6.71</v>
+        <v>6.68</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CF14" t="n">
         <v>1.91</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.53</v>
+        <v>4.51</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.56</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CO14" t="n">
         <v>1.06</v>
@@ -6494,7 +6494,7 @@
         <v>1.33</v>
       </c>
       <c r="CQ14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
@@ -6505,69 +6505,69 @@
         <v>1.95</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="DB14" t="n">
         <v>1.11</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DF14" t="n">
         <v>1</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="DH14" t="n">
-        <v>114.16</v>
+        <v>106.23</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.42</v>
+        <v>6.31</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM14" t="n">
-        <v>59.5</v>
+        <v>55.69</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.58</v>
+        <v>10.92</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.83</v>
+        <v>9</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.75</v>
+        <v>7.15</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6579,28 +6579,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.84</v>
+        <v>59.31</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>18.75</v>
+        <v>18</v>
       </c>
       <c r="DY14" t="n">
-        <v>11.34</v>
+        <v>10.84</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7.42</v>
+        <v>7.15</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.34</v>
+        <v>17.54</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>0.33</v>
@@ -1469,139 +1469,139 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>97.83</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.67</v>
+        <v>3.14</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>49.5</v>
+        <v>46.57</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
         <v>3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>12.14</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.17</v>
+        <v>10</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>54.83</v>
+        <v>54.57</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA2" t="n">
-        <v>18.17</v>
+        <v>16.86</v>
       </c>
       <c r="BB2" t="n">
-        <v>11.83</v>
+        <v>10.71</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.33</v>
+        <v>6.14</v>
       </c>
       <c r="BD2" t="n">
-        <v>13</v>
+        <v>14.29</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.42</v>
+        <v>10.62</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BM2" t="n">
         <v>1</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BO2" t="n">
         <v>2</v>
       </c>
       <c r="BP2" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.42</v>
+        <v>5.46</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT2" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BV2" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BW2" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX2" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BY2" t="n">
         <v>1.84</v>
@@ -1610,16 +1610,16 @@
         <v>1.94</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.46</v>
+        <v>4.42</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.6</v>
+        <v>4.54</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="CD2" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="CE2" t="n">
         <v>1.24</v>
@@ -1628,16 +1628,16 @@
         <v>2.17</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CH2" t="n">
         <v>1.63</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CK2" t="n">
         <v>1.44</v>
@@ -1646,7 +1646,7 @@
         <v>1.85</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN2" t="n">
         <v>2.01</v>
@@ -1658,7 +1658,7 @@
         <v>1.51</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CR2" t="n">
         <v>1.33</v>
@@ -1673,16 +1673,16 @@
         <v>1.69</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CX2" t="n">
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.46</v>
@@ -1694,85 +1694,85 @@
         <v>1.16</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="DH2" t="n">
-        <v>102.5</v>
+        <v>102</v>
       </c>
       <c r="DI2" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.83</v>
+        <v>2.61</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.17</v>
+        <v>6.08</v>
       </c>
       <c r="DL2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.58</v>
+        <v>49.85</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="DO2" t="n">
         <v>3</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.08</v>
+        <v>10.54</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.5</v>
+        <v>10.38</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.66</v>
+        <v>7.77</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.5</v>
+        <v>54.39</v>
       </c>
       <c r="DW2" t="n">
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>17.5</v>
+        <v>16.85</v>
       </c>
       <c r="DY2" t="n">
-        <v>11.08</v>
+        <v>10.53</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6.42</v>
+        <v>6.31</v>
       </c>
       <c r="EA2" t="n">
-        <v>15.58</v>
+        <v>16.08</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F3" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G3" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="H3" t="n">
-        <v>106.33</v>
+        <v>111.29</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J3" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="K3" t="n">
-        <v>6.17</v>
+        <v>6.57</v>
       </c>
       <c r="L3" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>54.5</v>
+        <v>60.71</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="O3" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="P3" t="n">
-        <v>11.17</v>
+        <v>10.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.17</v>
+        <v>14</v>
       </c>
       <c r="R3" t="n">
-        <v>5.83</v>
+        <v>5.57</v>
       </c>
       <c r="S3" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>59.33</v>
+        <v>60</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.33</v>
+        <v>15.29</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.83</v>
+        <v>9</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.67</v>
+        <v>18.86</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AF3" t="n">
         <v>0.17</v>
@@ -1953,37 +1953,37 @@
         <v>2.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.75</v>
+        <v>10.77</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.42</v>
+        <v>5.46</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.33</v>
+        <v>5.31</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,31 +1992,31 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU3" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV3" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX3" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.96</v>
+        <v>5.01</v>
       </c>
       <c r="CB3" t="n">
-        <v>5.11</v>
+        <v>5.18</v>
       </c>
       <c r="CC3" t="n">
         <v>2.39</v>
@@ -2025,19 +2025,19 @@
         <v>2.58</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
       <c r="CH3" t="n">
         <v>1.69</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.64</v>
@@ -2046,13 +2046,13 @@
         <v>1.49</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CO3" t="n">
         <v>1.13</v>
@@ -2061,19 +2061,19 @@
         <v>1.46</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="CT3" t="n">
         <v>3.32</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CV3" t="n">
         <v>2.36</v>
@@ -2085,34 +2085,34 @@
         <v>1.52</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.45</v>
       </c>
       <c r="DA3" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DB3" t="n">
         <v>1.15</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.16</v>
+        <v>103.31</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.08</v>
@@ -2121,28 +2121,28 @@
         <v>1.92</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.58</v>
+        <v>5.85</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.59</v>
+        <v>0.77</v>
       </c>
       <c r="DM3" t="n">
-        <v>52.25</v>
+        <v>55.77</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.58</v>
+        <v>11</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.25</v>
+        <v>13.23</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.25</v>
+        <v>6.08</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.33</v>
+        <v>57.84</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.75</v>
+        <v>14.77</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.58</v>
+        <v>8.69</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.16</v>
+        <v>6.08</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.67</v>
+        <v>17.39</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="EC3" t="n">
         <v>1.92</v>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0.5</v>
@@ -2275,115 +2275,115 @@
         <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AI4" t="n">
-        <v>90.17</v>
+        <v>89</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.67</v>
+        <v>4.29</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AN4" t="n">
-        <v>43.83</v>
+        <v>43.86</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.33</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.33</v>
+        <v>7.71</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.5</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AU4" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>45.67</v>
+        <v>44.29</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.83</v>
+        <v>12.14</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.17</v>
+        <v>7.57</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.67</v>
+        <v>4.57</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.5</v>
+        <v>17.43</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.67</v>
+        <v>9.77</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL4" t="n">
         <v>0.92</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="BQ4" t="n">
         <v>5</v>
@@ -2392,22 +2392,22 @@
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT4" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV4" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY4" t="n">
         <v>3.85</v>
@@ -2416,37 +2416,37 @@
         <v>3.95</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.07</v>
+        <v>4.19</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.17</v>
+        <v>4.31</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.24</v>
+        <v>4.69</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.57</v>
+        <v>3.66</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.56</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL4" t="n">
         <v>1.72</v>
@@ -2461,91 +2461,91 @@
         <v>1.16</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CR4" t="n">
         <v>1.34</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="CT4" t="n">
         <v>3.31</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX4" t="n">
         <v>1.5</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.48</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="DH4" t="n">
-        <v>91.84</v>
+        <v>91.08</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.5</v>
+        <v>4.31</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.5</v>
+        <v>40.77</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.75</v>
+        <v>13.69</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.33</v>
+        <v>8.92</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.17</v>
+        <v>9</v>
       </c>
       <c r="DS4" t="n">
         <v>0.08</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.67</v>
+        <v>44</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.58</v>
+        <v>12.23</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.25</v>
+        <v>7.92</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.34</v>
+        <v>4.31</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.42</v>
+        <v>17.85</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="5">
@@ -2588,61 +2588,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="G5" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="H5" t="n">
-        <v>99.33</v>
+        <v>100.29</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>7.83</v>
+        <v>7.71</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>59.33</v>
+        <v>58.29</v>
       </c>
       <c r="N5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="O5" t="n">
-        <v>4.67</v>
+        <v>4.57</v>
       </c>
       <c r="P5" t="n">
-        <v>8.17</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.67</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>7.33</v>
+        <v>6.86</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="T5" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>53.5</v>
+        <v>53.71</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.83</v>
+        <v>19.71</v>
       </c>
       <c r="AA5" t="n">
-        <v>13.33</v>
+        <v>13.43</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.17</v>
+        <v>20.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AF5" t="n">
         <v>0.17</v>
@@ -2759,67 +2759,67 @@
         <v>2.17</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.58</v>
+        <v>3.77</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.58</v>
+        <v>10.77</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.58</v>
+        <v>3.77</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.08</v>
+        <v>5.23</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT5" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU5" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BV5" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BW5" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BZ5" t="n">
         <v>1.48</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>1.49</v>
-      </c>
       <c r="CA5" t="n">
-        <v>4.96</v>
+        <v>4.98</v>
       </c>
       <c r="CB5" t="n">
         <v>5.28</v>
@@ -2834,19 +2834,19 @@
         <v>1.24</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.79</v>
+        <v>3.84</v>
       </c>
       <c r="CH5" t="n">
         <v>1.66</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK5" t="n">
         <v>1.43</v>
@@ -2861,94 +2861,94 @@
         <v>2.01</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CR5" t="n">
         <v>1.33</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CT5" t="n">
         <v>3.32</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CX5" t="n">
         <v>1.54</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.42</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DB5" t="n">
         <v>1.17</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF5" t="n">
         <v>1</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="DH5" t="n">
-        <v>100.25</v>
+        <v>100.7</v>
       </c>
       <c r="DI5" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.66</v>
+        <v>7.61</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM5" t="n">
-        <v>57.33</v>
+        <v>56.92</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DO5" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="DP5" t="n">
-        <v>8.75</v>
+        <v>8.69</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.67</v>
+        <v>10.85</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.08</v>
+        <v>6.85</v>
       </c>
       <c r="DS5" t="n">
         <v>0.08</v>
@@ -2963,25 +2963,25 @@
         <v>54.92</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX5" t="n">
-        <v>19.08</v>
+        <v>19.07</v>
       </c>
       <c r="DY5" t="n">
-        <v>12.08</v>
+        <v>12.23</v>
       </c>
       <c r="DZ5" t="n">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.08</v>
+        <v>19.38</v>
       </c>
       <c r="EB5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0.33</v>
@@ -3081,52 +3081,52 @@
         <v>2.67</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AI6" t="n">
-        <v>87.83</v>
+        <v>89.86</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14</v>
+        <v>13.57</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.83</v>
+        <v>10.57</v>
       </c>
       <c r="AS6" t="n">
-        <v>9</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.67</v>
+        <v>45.57</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.33</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.33</v>
+        <v>5.29</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>4.43</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.33</v>
+        <v>19</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.42</v>
+        <v>10.54</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BJ6" t="n">
         <v>1.08</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.25</v>
+        <v>5.46</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU6" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV6" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX6" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY6" t="n">
         <v>2.93</v>
@@ -3222,28 +3222,28 @@
         <v>2.85</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="CC6" t="n">
-        <v>7.02</v>
+        <v>6.55</v>
       </c>
       <c r="CD6" t="n">
-        <v>7.86</v>
+        <v>7.35</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI6" t="n">
         <v>2.15</v>
@@ -3252,25 +3252,25 @@
         <v>1.67</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
@@ -3285,7 +3285,7 @@
         <v>1.59</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW6" t="n">
         <v>1.7</v>
@@ -3294,76 +3294,76 @@
         <v>1.5</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.5</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="DB6" t="n">
         <v>1.24</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DH6" t="n">
-        <v>91</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DM6" t="n">
-        <v>37.66</v>
+        <v>37.46</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.66</v>
+        <v>13.46</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.08</v>
+        <v>10</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.75</v>
+        <v>7.69</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.5</v>
+        <v>46.84</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
@@ -3372,19 +3372,19 @@
         <v>12</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.75</v>
+        <v>7.54</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.75</v>
+        <v>18.16</v>
       </c>
       <c r="EB6" t="n">
         <v>1.34</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0.33</v>
@@ -3484,52 +3484,52 @@
         <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AI7" t="n">
-        <v>93.83</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN7" t="n">
-        <v>45.17</v>
+        <v>44.57</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>8.57</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.83</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>51.5</v>
+        <v>51.86</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.33</v>
+        <v>9.57</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.17</v>
+        <v>5.57</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.83</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.42</v>
+        <v>11.23</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.92</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.58</v>
+        <v>6.46</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.33</v>
+        <v>15.38</v>
       </c>
       <c r="BX7" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY7" t="n">
         <v>3.04</v>
@@ -3625,46 +3625,46 @@
         <v>3.14</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.13</v>
+        <v>4.09</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.5</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CO7" t="n">
         <v>1.14</v>
@@ -3673,19 +3673,19 @@
         <v>1.55</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CR7" t="n">
         <v>1.34</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CT7" t="n">
         <v>3.31</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CV7" t="n">
         <v>2.67</v>
@@ -3697,64 +3697,64 @@
         <v>1.44</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.63</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="DH7" t="n">
-        <v>93.58</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.75</v>
+        <v>5.54</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DM7" t="n">
-        <v>48.08</v>
+        <v>47.54</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="DP7" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="DR7" t="n">
         <v>9</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>9.33</v>
       </c>
       <c r="DS7" t="n">
         <v>0.08</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.42</v>
+        <v>51.62</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.75</v>
+        <v>18</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="G8" t="n">
-        <v>2.83</v>
+        <v>3.29</v>
       </c>
       <c r="H8" t="n">
-        <v>104.83</v>
+        <v>115.43</v>
       </c>
       <c r="I8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J8" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>6.57</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="M8" t="n">
-        <v>40.5</v>
+        <v>49.57</v>
       </c>
       <c r="N8" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O8" t="n">
-        <v>2.67</v>
+        <v>3.29</v>
       </c>
       <c r="P8" t="n">
-        <v>10.83</v>
+        <v>10.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.67</v>
+        <v>10.43</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>6.29</v>
       </c>
       <c r="S8" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="U8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>54</v>
+        <v>55.43</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.83</v>
+        <v>17.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.17</v>
+        <v>11.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.67</v>
+        <v>5.86</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.67</v>
+        <v>22.29</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
         <v>0.17</v>
@@ -3968,70 +3968,70 @@
         <v>1.83</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="BH8" t="n">
-        <v>10</v>
+        <v>10.23</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.17</v>
+        <v>5.23</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU8" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV8" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.17</v>
+        <v>4.19</v>
       </c>
       <c r="CC8" t="n">
         <v>6.01</v>
@@ -4043,7 +4043,7 @@
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CG8" t="n">
         <v>3.17</v>
@@ -4061,10 +4061,10 @@
         <v>1.56</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CN8" t="n">
         <v>1.81</v>
@@ -4073,19 +4073,19 @@
         <v>1.24</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="CU8" t="n">
         <v>1.51</v>
@@ -4112,52 +4112,52 @@
         <v>1.25</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.42</v>
+        <v>2.69</v>
       </c>
       <c r="DH8" t="n">
-        <v>99.92</v>
+        <v>106</v>
       </c>
       <c r="DI8" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.84</v>
+        <v>5.46</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DM8" t="n">
-        <v>38.75</v>
+        <v>43.77</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.42</v>
+        <v>2.77</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.66</v>
+        <v>11.62</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.92</v>
+        <v>10.77</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.42</v>
+        <v>7</v>
       </c>
       <c r="DS8" t="n">
         <v>0.08</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.08</v>
+        <v>50.23</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.66</v>
+        <v>15.62</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.75</v>
+        <v>9.15</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.92</v>
+        <v>6.46</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.25</v>
+        <v>21.62</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="EC8" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="G9" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="H9" t="n">
-        <v>108.17</v>
+        <v>108.71</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="L9" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="M9" t="n">
-        <v>60.17</v>
+        <v>59.43</v>
       </c>
       <c r="N9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="O9" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="P9" t="n">
-        <v>8.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.33</v>
+        <v>12</v>
       </c>
       <c r="R9" t="n">
-        <v>6.33</v>
+        <v>6.29</v>
       </c>
       <c r="S9" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="U9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>54.83</v>
+        <v>53.71</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.33</v>
+        <v>17</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.33</v>
+        <v>11.43</v>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>5.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.33</v>
+        <v>15.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,19 +4371,19 @@
         <v>1.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.5</v>
+        <v>10.69</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL9" t="n">
         <v>1.08</v>
@@ -4395,46 +4395,46 @@
         <v>2</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.92</v>
+        <v>5.08</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT9" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU9" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BV9" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX9" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="CA9" t="n">
         <v>3.9</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="CC9" t="n">
         <v>3.98</v>
@@ -4443,31 +4443,31 @@
         <v>4.41</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CI9" t="n">
         <v>2.33</v>
       </c>
-      <c r="CG9" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>2.3</v>
-      </c>
       <c r="CJ9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CN9" t="n">
         <v>2.02</v>
@@ -4476,28 +4476,28 @@
         <v>1.18</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CT9" t="n">
         <v>3.24</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CX9" t="n">
         <v>1.51</v>
@@ -4515,85 +4515,85 @@
         <v>1.19</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="DE9" t="n">
         <v>0.08</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="DH9" t="n">
-        <v>102</v>
+        <v>102.77</v>
       </c>
       <c r="DI9" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>6</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>7</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="EB9" t="n">
         <v>1.75</v>
       </c>
-      <c r="DK9" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>51</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DT9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>52.83</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>15.42</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="EA9" t="n">
-        <v>18.16</v>
-      </c>
-      <c r="EB9" t="n">
-        <v>1.7</v>
-      </c>
       <c r="EC9" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="H10" t="n">
-        <v>87.59999999999999</v>
+        <v>87.33</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.2</v>
+        <v>11.83</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="T10" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>42.4</v>
+        <v>43</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.4</v>
+        <v>15.67</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.6</v>
+        <v>6.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>13.8</v>
+        <v>13.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,37 +4774,37 @@
         <v>1.86</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.17</v>
+        <v>4.31</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.67</v>
+        <v>10.54</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.17</v>
+        <v>4.31</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.17</v>
+        <v>5.15</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4813,31 +4813,31 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BU10" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BV10" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BW10" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY10" t="n">
-        <v>4.09</v>
+        <v>3.8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.26</v>
+        <v>3.98</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.34</v>
+        <v>4.27</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.5</v>
+        <v>4.42</v>
       </c>
       <c r="CC10" t="n">
         <v>5.41</v>
@@ -4852,34 +4852,34 @@
         <v>2.32</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CH10" t="n">
         <v>1.56</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CO10" t="n">
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CQ10" t="n">
         <v>2.53</v>
@@ -4897,22 +4897,22 @@
         <v>1.62</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX10" t="n">
         <v>1.46</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.59</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="DB10" t="n">
         <v>1.19</v>
@@ -4924,46 +4924,46 @@
         <v>2.56</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DH10" t="n">
-        <v>87.25</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.41</v>
+        <v>4.53</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.58</v>
+        <v>41.15</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.75</v>
+        <v>12.23</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.25</v>
+        <v>10.61</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.67</v>
+        <v>7.23</v>
       </c>
       <c r="DS10" t="n">
         <v>0.08</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.58</v>
+        <v>43.77</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.33</v>
+        <v>12.15</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.58</v>
+        <v>7.77</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.75</v>
+        <v>4.39</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.67</v>
+        <v>17.38</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="11">
@@ -5234,13 +5234,13 @@
         <v>3.31</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.32</v>
+        <v>3.43</v>
       </c>
       <c r="CA11" t="n">
         <v>4.21</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="CC11" t="n">
         <v>6.05</v>
@@ -5303,7 +5303,7 @@
         <v>2.22</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX11" t="n">
         <v>1.54</v>
@@ -5321,10 +5321,10 @@
         <v>1.21</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="DE11" t="n">
         <v>0.08</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0.17</v>
@@ -5499,34 +5499,34 @@
         <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AI12" t="n">
-        <v>109.33</v>
+        <v>104.71</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN12" t="n">
-        <v>64</v>
+        <v>58.71</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP12" t="n">
         <v>2</v>
@@ -5535,16 +5535,16 @@
         <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.17</v>
+        <v>5.71</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>62.67</v>
+        <v>60.14</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA12" t="n">
-        <v>15.5</v>
+        <v>16.43</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.33</v>
+        <v>9.43</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.17</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
-        <v>22.33</v>
+        <v>21.71</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.08</v>
+        <v>4.23</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.92</v>
+        <v>9.23</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.08</v>
+        <v>4.23</v>
       </c>
       <c r="BJ12" t="n">
         <v>0.92</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BM12" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.33</v>
+        <v>4.46</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.58</v>
+        <v>4.77</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT12" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BU12" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BV12" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BW12" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY12" t="n">
         <v>2.49</v>
@@ -5640,31 +5640,31 @@
         <v>2.74</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.81</v>
+        <v>3.92</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.96</v>
+        <v>4.06</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.54</v>
+        <v>3.15</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="CE12" t="n">
         <v>1.26</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.51</v>
@@ -5676,37 +5676,37 @@
         <v>1.73</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CR12" t="n">
         <v>1.34</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CT12" t="n">
         <v>3.34</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CX12" t="n">
         <v>1.49</v>
@@ -5718,91 +5718,91 @@
         <v>2.5</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF12" t="n">
         <v>1</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="DH12" t="n">
-        <v>107.66</v>
+        <v>105.31</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.16</v>
+        <v>5.23</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM12" t="n">
-        <v>54.34</v>
+        <v>52.23</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DO12" t="n">
         <v>2.08</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.58</v>
+        <v>12.62</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.84</v>
+        <v>13.39</v>
       </c>
       <c r="DR12" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>58.75</v>
+        <v>57.69</v>
       </c>
       <c r="DW12" t="n">
         <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.16</v>
+        <v>15.69</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.75</v>
+        <v>8.85</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.42</v>
+        <v>6.85</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.25</v>
+        <v>21</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0.17</v>
@@ -5902,52 +5902,52 @@
         <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>79.83</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN13" t="n">
-        <v>33.33</v>
+        <v>31.57</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.33</v>
+        <v>10.14</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.5</v>
+        <v>13.14</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.67</v>
+        <v>10.57</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>47.17</v>
+        <v>45.57</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.67</v>
+        <v>9</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.5</v>
+        <v>5.86</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="BD13" t="n">
-        <v>14.67</v>
+        <v>14.71</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.75</v>
+        <v>8.15</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BO13" t="n">
         <v>2</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.83</v>
+        <v>4.08</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.92</v>
+        <v>4.08</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT13" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU13" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BV13" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY13" t="n">
         <v>3.57</v>
@@ -6043,46 +6043,46 @@
         <v>3.8</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.66</v>
+        <v>4.95</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.19</v>
+        <v>5.49</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF13" t="n">
         <v>2.35</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CH13" t="n">
         <v>1.55</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CO13" t="n">
         <v>1.17</v>
@@ -6097,82 +6097,82 @@
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CT13" t="n">
         <v>3.34</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="DB13" t="n">
         <v>1.19</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="DH13" t="n">
-        <v>78.25</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="DK13" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DM13" t="n">
-        <v>34.08</v>
+        <v>33.07</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.08</v>
+        <v>10</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.42</v>
+        <v>12.3</v>
       </c>
       <c r="DR13" t="n">
-        <v>11.08</v>
+        <v>11</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>41.75</v>
+        <v>41.31</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DX13" t="n">
-        <v>8.67</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.92</v>
+        <v>5.62</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="EA13" t="n">
-        <v>16</v>
+        <v>15.92</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="14">
@@ -6449,13 +6449,13 @@
         <v>6.08</v>
       </c>
       <c r="CB14" t="n">
-        <v>6.68</v>
+        <v>6.71</v>
       </c>
       <c r="CC14" t="n">
         <v>1.74</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CE14" t="n">
         <v>1.17</v>
@@ -6508,7 +6508,7 @@
         <v>2.52</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
@@ -6522,10 +6522,10 @@
         <v>1.11</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DE14" t="n">
         <v>0.31</v>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -6622,82 +6622,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="H15" t="n">
-        <v>85.17</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="K15" t="n">
-        <v>4.17</v>
+        <v>4.57</v>
       </c>
       <c r="L15" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="M15" t="n">
-        <v>40.33</v>
+        <v>43.71</v>
       </c>
       <c r="N15" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O15" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="P15" t="n">
-        <v>7.5</v>
+        <v>7.71</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.83</v>
+        <v>10</v>
       </c>
       <c r="R15" t="n">
-        <v>10.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="T15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="U15" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V15" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>41.67</v>
+        <v>44.43</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.17</v>
+        <v>11.43</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.33</v>
+        <v>7.57</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="AC15" t="n">
-        <v>14.83</v>
+        <v>14.43</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6781,70 +6781,70 @@
         <v>2.17</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.83</v>
+        <v>10.92</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BN15" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.17</v>
+        <v>6.31</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT15" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV15" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW15" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BX15" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="CC15" t="n">
         <v>4.51</v>
@@ -6856,40 +6856,40 @@
         <v>1.28</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL15" t="n">
         <v>1.74</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CN15" t="n">
         <v>2.14</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
@@ -6904,27 +6904,27 @@
         <v>1.63</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CZ15" t="inlineStr"/>
       <c r="DA15" t="n">
         <v>2.2</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
@@ -6933,40 +6933,40 @@
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="DH15" t="n">
-        <v>86</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DM15" t="n">
-        <v>40.5</v>
+        <v>42.31</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="DP15" t="n">
-        <v>8.25</v>
+        <v>8.31</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9.67</v>
+        <v>9.77</v>
       </c>
       <c r="DR15" t="n">
-        <v>10</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DS15" t="n">
         <v>0.16</v>
@@ -6978,28 +6978,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.17</v>
+        <v>44.54</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.25</v>
+        <v>12.31</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.33</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.92</v>
       </c>
       <c r="EA15" t="n">
-        <v>14.08</v>
+        <v>13.92</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="16">
@@ -7009,61 +7009,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>3.83</v>
+        <v>3.43</v>
       </c>
       <c r="H16" t="n">
-        <v>85.17</v>
+        <v>86</v>
       </c>
       <c r="I16" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="J16" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="K16" t="n">
-        <v>6.33</v>
+        <v>5.57</v>
       </c>
       <c r="L16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M16" t="n">
-        <v>50.17</v>
+        <v>47.71</v>
       </c>
       <c r="N16" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="P16" t="n">
-        <v>11.17</v>
+        <v>11</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.17</v>
+        <v>11.86</v>
       </c>
       <c r="R16" t="n">
-        <v>7</v>
+        <v>7.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7075,28 +7075,28 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>48</v>
+        <v>47.14</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.67</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.33</v>
+        <v>6.71</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.5</v>
+        <v>19.71</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7180,70 +7180,70 @@
         <v>1.67</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.58</v>
+        <v>11.38</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.75</v>
+        <v>5.69</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.83</v>
+        <v>5.69</v>
       </c>
       <c r="BR16" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS16" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU16" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV16" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.96</v>
+        <v>4.85</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.19</v>
+        <v>5.09</v>
       </c>
       <c r="CC16" t="n">
         <v>11.17</v>
@@ -7255,13 +7255,13 @@
         <v>1.26</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CI16" t="n">
         <v>2.19</v>
@@ -7276,34 +7276,34 @@
         <v>1.73</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CN16" t="n">
         <v>2.1</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW16" t="n">
         <v>1.67</v>
@@ -7324,52 +7324,52 @@
         <v>1.19</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="DE16" t="n">
         <v>0.16</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>81.5</v>
+        <v>82.23</v>
       </c>
       <c r="DI16" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
         <v>1.84</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DM16" t="n">
-        <v>42.67</v>
+        <v>41.92</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.92</v>
+        <v>10.85</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.84</v>
+        <v>10.77</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.5</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
@@ -7381,28 +7381,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44</v>
+        <v>43.84</v>
       </c>
       <c r="DW16" t="n">
         <v>0.08</v>
       </c>
       <c r="DX16" t="n">
-        <v>14.16</v>
+        <v>13.84</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.83</v>
+        <v>8.69</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.33</v>
+        <v>5.15</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.42</v>
+        <v>18.61</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="17">
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>0.17</v>
@@ -7505,136 +7505,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AI17" t="n">
-        <v>94.17</v>
+        <v>91.14</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AL17" t="n">
         <v>4</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN17" t="n">
-        <v>49.67</v>
+        <v>51.14</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>13.71</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.67</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.5</v>
+        <v>7.43</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>52</v>
+        <v>51.43</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>15.83</v>
+        <v>16.14</v>
       </c>
       <c r="BB17" t="n">
-        <v>10</v>
+        <v>10.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.83</v>
+        <v>5.86</v>
       </c>
       <c r="BD17" t="n">
-        <v>22.5</v>
+        <v>21.14</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.42</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL17" t="n">
         <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BN17" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.08</v>
+        <v>4.77</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.33</v>
+        <v>3.62</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT17" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU17" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV17" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BW17" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY17" t="n">
         <v>2.17</v>
@@ -7643,25 +7643,25 @@
         <v>2.2</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF17" t="n">
         <v>2.34</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="CH17" t="n">
         <v>1.58</v>
@@ -7673,25 +7673,25 @@
         <v>1.64</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM17" t="n">
         <v>2.52</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO17" t="n">
         <v>1.19</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CR17" t="n">
         <v>1.35</v>
@@ -7736,76 +7736,76 @@
         <v>0.08</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DH17" t="n">
-        <v>110.5</v>
+        <v>107.61</v>
       </c>
       <c r="DI17" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DK17" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM17" t="n">
-        <v>58.84</v>
+        <v>58.92</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.92</v>
+        <v>12.84</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.67</v>
+        <v>10.23</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.5</v>
+        <v>6.54</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>55.34</v>
+        <v>54.77</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX17" t="n">
         <v>18</v>
       </c>
       <c r="DY17" t="n">
-        <v>11.66</v>
+        <v>11.69</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.33</v>
+        <v>6.31</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.67</v>
+        <v>21</v>
       </c>
       <c r="EB17" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="18">
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7908,49 +7908,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
         <v>3</v>
       </c>
       <c r="AI18" t="n">
-        <v>109.2</v>
+        <v>111.5</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.8</v>
+        <v>5.33</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="AN18" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.4</v>
+        <v>10.33</v>
       </c>
       <c r="AR18" t="n">
-        <v>9</v>
+        <v>9.17</v>
       </c>
       <c r="AS18" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="AT18" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7962,82 +7962,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>53.2</v>
+        <v>54</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.2</v>
+        <v>13.83</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="BD18" t="n">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.33</v>
+        <v>9.31</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN18" t="n">
         <v>1.92</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BP18" t="n">
         <v>5.08</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT18" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU18" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BV18" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY18" t="n">
         <v>1.81</v>
@@ -8046,67 +8046,67 @@
         <v>1.86</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="CD18" t="n">
-        <v>4.02</v>
+        <v>3.68</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF18" t="n">
         <v>2.34</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CH18" t="n">
         <v>1.53</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.66</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CO18" t="n">
         <v>1.19</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CQ18" t="n">
         <v>2.69</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV18" t="n">
         <v>2.24</v>
@@ -8118,64 +8118,64 @@
         <v>1.48</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.54</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DB18" t="n">
         <v>1.22</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DH18" t="n">
-        <v>101.91</v>
+        <v>103.54</v>
       </c>
       <c r="DI18" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.09</v>
+        <v>5.31</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="DM18" t="n">
-        <v>38.25</v>
+        <v>39.92</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.75</v>
+        <v>10.69</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.84</v>
+        <v>11.7</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.08</v>
+        <v>7.31</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8187,28 +8187,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.17</v>
+        <v>49.85</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.75</v>
+        <v>14.92</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.42</v>
+        <v>9.77</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.34</v>
+        <v>5.15</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.17</v>
+        <v>20.08</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="19">
@@ -8218,61 +8218,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="G19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H19" t="n">
+        <v>84.14</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M19" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="n">
-        <v>85.17</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="M19" t="n">
-        <v>40.83</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.33</v>
-      </c>
       <c r="P19" t="n">
-        <v>10.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>12.86</v>
       </c>
       <c r="R19" t="n">
-        <v>10.67</v>
+        <v>11.14</v>
       </c>
       <c r="S19" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8284,28 +8284,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>43.17</v>
+        <v>44.43</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.17</v>
+        <v>12</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.33</v>
+        <v>7.29</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="AC19" t="n">
-        <v>11.33</v>
+        <v>12</v>
       </c>
       <c r="AD19" t="n">
         <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8389,49 +8389,49 @@
         <v>0.83</v>
       </c>
       <c r="BG19" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.25</v>
+        <v>10.08</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.67</v>
+        <v>5.31</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.58</v>
+        <v>4.77</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT19" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BU19" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8440,19 +8440,19 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BY19" t="n">
-        <v>4.02</v>
+        <v>4.14</v>
       </c>
       <c r="BZ19" t="n">
-        <v>4.17</v>
+        <v>4.26</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.69</v>
+        <v>4.63</v>
       </c>
       <c r="CB19" t="n">
-        <v>5.04</v>
+        <v>4.96</v>
       </c>
       <c r="CC19" t="n">
         <v>6.36</v>
@@ -8464,16 +8464,16 @@
         <v>1.24</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CG19" t="n">
         <v>3.71</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.61</v>
@@ -8482,19 +8482,19 @@
         <v>1.38</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CO19" t="n">
         <v>1.15</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ19" t="n">
         <v>2.28</v>
@@ -8503,13 +8503,13 @@
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CT19" t="n">
         <v>3.34</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CV19" t="n">
         <v>2.39</v>
@@ -8521,64 +8521,64 @@
         <v>1.51</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.44</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="DE19" t="n">
         <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="DH19" t="n">
-        <v>83.75</v>
+        <v>83.3</v>
       </c>
       <c r="DI19" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM19" t="n">
-        <v>37.08</v>
+        <v>38.46</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DP19" t="n">
-        <v>10.5</v>
+        <v>10.07</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.5</v>
+        <v>11.54</v>
       </c>
       <c r="DR19" t="n">
-        <v>10.5</v>
+        <v>10.77</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8590,28 +8590,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.08</v>
+        <v>45.62</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.58</v>
+        <v>10.62</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.92</v>
+        <v>6.93</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="EA19" t="n">
-        <v>14.33</v>
+        <v>14.46</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0.14</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="AI9" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.67</v>
+        <v>6.14</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AN9" t="n">
-        <v>41.83</v>
+        <v>43.86</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>13.86</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.17</v>
+        <v>10.29</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.83</v>
+        <v>7.57</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>50.83</v>
+        <v>51.71</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA9" t="n">
-        <v>14.5</v>
+        <v>15.14</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.17</v>
+        <v>9.57</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.33</v>
+        <v>5.57</v>
       </c>
       <c r="BD9" t="n">
-        <v>20</v>
+        <v>19.43</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.69</v>
+        <v>10.79</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BN9" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.08</v>
+        <v>5.21</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.54</v>
+        <v>5.5</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT9" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV9" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX9" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BY9" t="n">
         <v>2.19</v>
@@ -4431,61 +4431,61 @@
         <v>2.11</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="CB9" t="n">
         <v>4.04</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.41</v>
+        <v>4.05</v>
       </c>
       <c r="CE9" t="n">
         <v>1.28</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CH9" t="n">
         <v>1.58</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CO9" t="n">
         <v>1.18</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CT9" t="n">
         <v>3.24</v>
@@ -4494,19 +4494,19 @@
         <v>1.61</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY9" t="n">
         <v>1.77</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DA9" t="n">
         <v>2.04</v>
@@ -4518,82 +4518,82 @@
         <v>1.62</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.92</v>
+        <v>3.07</v>
       </c>
       <c r="DH9" t="n">
-        <v>102.77</v>
+        <v>102.35</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="DK9" t="n">
-        <v>6</v>
+        <v>6.21</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="DM9" t="n">
-        <v>51.31</v>
+        <v>51.64</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DO9" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.77</v>
+        <v>11.36</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.16</v>
+        <v>11.14</v>
       </c>
       <c r="DR9" t="n">
-        <v>7</v>
+        <v>6.93</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.38</v>
+        <v>52.71</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.85</v>
+        <v>16.07</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.39</v>
+        <v>10.5</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.46</v>
+        <v>5.57</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.61</v>
+        <v>17.5</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="10">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F13" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="H13" t="n">
-        <v>76.67</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J13" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="M13" t="n">
-        <v>34.83</v>
+        <v>34.29</v>
       </c>
       <c r="N13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="P13" t="n">
-        <v>9.83</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.33</v>
+        <v>12.43</v>
       </c>
       <c r="R13" t="n">
-        <v>11.5</v>
+        <v>11.14</v>
       </c>
       <c r="S13" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T13" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>36.33</v>
+        <v>37.29</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.67</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.33</v>
+        <v>5.57</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.33</v>
+        <v>17.29</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AF13" t="n">
         <v>0.29</v>
@@ -5983,70 +5983,70 @@
         <v>2.29</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.15</v>
+        <v>8.43</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="BO13" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.08</v>
+        <v>4.29</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.08</v>
+        <v>4.14</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU13" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BV13" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX13" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="CC13" t="n">
         <v>4.95</v>
@@ -6055,19 +6055,19 @@
         <v>5.49</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CH13" t="n">
         <v>1.55</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.6</v>
@@ -6076,10 +6076,10 @@
         <v>1.44</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CN13" t="n">
         <v>2.01</v>
@@ -6088,37 +6088,37 @@
         <v>1.17</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CT13" t="n">
         <v>3.34</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DA13" t="n">
         <v>2</v>
@@ -6127,52 +6127,52 @@
         <v>1.19</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="DH13" t="n">
-        <v>75.54000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="DK13" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="DM13" t="n">
-        <v>33.07</v>
+        <v>32.93</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="DP13" t="n">
-        <v>10</v>
+        <v>10.07</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.3</v>
+        <v>12.78</v>
       </c>
       <c r="DR13" t="n">
-        <v>11</v>
+        <v>10.86</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>41.31</v>
+        <v>41.43</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DX13" t="n">
-        <v>8.390000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.62</v>
+        <v>5.72</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="EA13" t="n">
-        <v>15.92</v>
+        <v>16</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0.33</v>
@@ -1469,139 +1469,139 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AH2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AI2" t="n">
-        <v>97.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AL2" t="n">
-        <v>6</v>
+        <v>5.62</v>
       </c>
       <c r="AM2" t="n">
         <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.57</v>
+        <v>45.88</v>
       </c>
       <c r="AO2" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP2" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.14</v>
+        <v>11.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="AS2" t="n">
         <v>8</v>
       </c>
       <c r="AT2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>53.88</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>1.14</v>
       </c>
-      <c r="AU2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>54.57</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>16.86</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1.23</v>
-      </c>
       <c r="BK2" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM2" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BO2" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.15</v>
+        <v>4.93</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.46</v>
+        <v>5.29</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BV2" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX2" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY2" t="n">
         <v>1.84</v>
@@ -1610,85 +1610,85 @@
         <v>1.94</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.54</v>
+        <v>4.49</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="CE2" t="n">
         <v>1.24</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="CH2" t="n">
         <v>1.63</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK2" t="n">
         <v>1.44</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP2" t="n">
         <v>1.51</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CR2" t="n">
         <v>1.33</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CT2" t="n">
         <v>3.32</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CX2" t="n">
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="DB2" t="n">
         <v>1.16</v>
@@ -1700,79 +1700,79 @@
         <v>2.31</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DH2" t="n">
-        <v>102</v>
+        <v>103.07</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.61</v>
+        <v>2.71</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.08</v>
+        <v>5.86</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.85</v>
+        <v>49.22</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="DO2" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.54</v>
+        <v>10.43</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.38</v>
+        <v>10.5</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.77</v>
+        <v>7.79</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.39</v>
+        <v>54</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.85</v>
+        <v>16.14</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.53</v>
+        <v>10.21</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6.31</v>
+        <v>5.93</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.08</v>
+        <v>16.43</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="3">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="F4" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="G4" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="H4" t="n">
-        <v>93.5</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="K4" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M4" t="n">
-        <v>37.17</v>
+        <v>34.71</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="O4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="P4" t="n">
-        <v>12.17</v>
+        <v>13.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.33</v>
+        <v>10.43</v>
       </c>
       <c r="R4" t="n">
-        <v>9.83</v>
+        <v>10.14</v>
       </c>
       <c r="S4" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>43.67</v>
+        <v>43.57</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.33</v>
+        <v>11.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.33</v>
+        <v>7.71</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="AC4" t="n">
-        <v>18.33</v>
+        <v>18</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AF4" t="n">
         <v>0.14</v>
@@ -2356,34 +2356,34 @@
         <v>1.57</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.77</v>
+        <v>9.57</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.77</v>
+        <v>4.57</v>
       </c>
       <c r="BQ4" t="n">
         <v>5</v>
@@ -2392,34 +2392,34 @@
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV4" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.85</v>
+        <v>3.64</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.95</v>
+        <v>3.74</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="CC4" t="n">
         <v>4.69</v>
@@ -2428,157 +2428,157 @@
         <v>5</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.56</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL4" t="n">
         <v>1.72</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CO4" t="n">
         <v>1.16</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CX4" t="n">
         <v>1.5</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="DC4" t="n">
         <v>1.58</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="DH4" t="n">
-        <v>91.08</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.31</v>
+        <v>4.08</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.77</v>
+        <v>39.29</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.69</v>
+        <v>14.28</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.92</v>
+        <v>9.07</v>
       </c>
       <c r="DR4" t="n">
-        <v>9</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44</v>
+        <v>43.93</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.23</v>
+        <v>11.78</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.92</v>
+        <v>7.64</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.31</v>
+        <v>4.14</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.85</v>
+        <v>17.72</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0.14</v>
@@ -2678,139 +2678,139 @@
         <v>0.71</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.83</v>
+        <v>3.43</v>
       </c>
       <c r="AI5" t="n">
-        <v>101.17</v>
+        <v>104</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AL5" t="n">
-        <v>7.5</v>
+        <v>7.14</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AN5" t="n">
-        <v>55.33</v>
+        <v>56</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.67</v>
+        <v>10.29</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.83</v>
+        <v>7.14</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>56.33</v>
+        <v>55.71</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA5" t="n">
-        <v>18.33</v>
+        <v>17.29</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.83</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.5</v>
+        <v>7.43</v>
       </c>
       <c r="BD5" t="n">
-        <v>18</v>
+        <v>19.14</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.77</v>
+        <v>3.71</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.77</v>
+        <v>10.57</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.77</v>
+        <v>3.71</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.54</v>
+        <v>5.43</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.23</v>
+        <v>5.14</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BV5" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BW5" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BX5" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY5" t="n">
         <v>1.47</v>
@@ -2819,16 +2819,16 @@
         <v>1.48</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.98</v>
+        <v>4.96</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.28</v>
+        <v>5.23</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="CE5" t="n">
         <v>1.24</v>
@@ -2837,7 +2837,7 @@
         <v>2.16</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="CH5" t="n">
         <v>1.66</v>
@@ -2846,19 +2846,19 @@
         <v>2.22</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CO5" t="n">
         <v>1.14</v>
@@ -2873,7 +2873,7 @@
         <v>1.33</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CT5" t="n">
         <v>3.32</v>
@@ -2882,106 +2882,106 @@
         <v>1.75</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX5" t="n">
         <v>1.54</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.42</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DC5" t="n">
         <v>1.51</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.46</v>
+        <v>3.28</v>
       </c>
       <c r="DH5" t="n">
-        <v>100.7</v>
+        <v>102.15</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.61</v>
+        <v>7.42</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="DM5" t="n">
-        <v>56.92</v>
+        <v>57.14</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DO5" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="DP5" t="n">
-        <v>8.69</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.85</v>
+        <v>10.64</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.92</v>
+        <v>54.71</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX5" t="n">
-        <v>19.07</v>
+        <v>18.5</v>
       </c>
       <c r="DY5" t="n">
-        <v>12.23</v>
+        <v>11.64</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.85</v>
+        <v>6.86</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.38</v>
+        <v>19.86</v>
       </c>
       <c r="EB5" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="H6" t="n">
-        <v>94.17</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>5.86</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="M6" t="n">
-        <v>43.83</v>
+        <v>44.86</v>
       </c>
       <c r="N6" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>3.43</v>
       </c>
       <c r="P6" t="n">
-        <v>13.33</v>
+        <v>14.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.33</v>
+        <v>11.14</v>
       </c>
       <c r="R6" t="n">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="U6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>48.33</v>
+        <v>49.57</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.67</v>
+        <v>15.86</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.17</v>
+        <v>11.29</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.17</v>
+        <v>17.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AF6" t="n">
         <v>0.14</v>
@@ -3162,70 +3162,70 @@
         <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.54</v>
+        <v>10.79</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BP6" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.46</v>
+        <v>5.57</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV6" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX6" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.93</v>
+        <v>2.78</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.18</v>
+        <v>4.12</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="CC6" t="n">
         <v>6.55</v>
@@ -3240,7 +3240,7 @@
         <v>2.46</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CH6" t="n">
         <v>1.54</v>
@@ -3252,16 +3252,16 @@
         <v>1.67</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
@@ -3270,7 +3270,7 @@
         <v>1.7</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
@@ -3285,10 +3285,10 @@
         <v>1.59</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CX6" t="n">
         <v>1.5</v>
@@ -3309,82 +3309,82 @@
         <v>1.74</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="DH6" t="n">
-        <v>91.84999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="DK6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="DM6" t="n">
-        <v>37.46</v>
+        <v>38.43</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.46</v>
+        <v>13.86</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10</v>
+        <v>10.86</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.69</v>
+        <v>7.57</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.84</v>
+        <v>47.57</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>12</v>
+        <v>12.78</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.54</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.16</v>
+        <v>18.07</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F7" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="G7" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="H7" t="n">
-        <v>93.33</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="K7" t="n">
-        <v>7.33</v>
+        <v>6.86</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>51</v>
+        <v>52.29</v>
       </c>
       <c r="N7" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
         <v>9</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.17</v>
+        <v>11.29</v>
       </c>
       <c r="R7" t="n">
-        <v>8.83</v>
+        <v>8.57</v>
       </c>
       <c r="S7" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="U7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.33</v>
+        <v>52.43</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.67</v>
+        <v>12.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.83</v>
+        <v>6.57</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.83</v>
+        <v>5.86</v>
       </c>
       <c r="AC7" t="n">
-        <v>15.67</v>
+        <v>16.29</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
         <v>0.14</v>
@@ -3565,70 +3565,70 @@
         <v>1.43</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.23</v>
+        <v>10.93</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.62</v>
+        <v>4.64</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.46</v>
+        <v>6.14</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT7" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BV7" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW7" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX7" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="BZ7" t="n">
         <v>3.14</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.27</v>
+        <v>4.21</v>
       </c>
       <c r="CC7" t="n">
         <v>3.6</v>
@@ -3640,16 +3640,16 @@
         <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.74</v>
+        <v>3.69</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.5</v>
@@ -3658,10 +3658,10 @@
         <v>1.34</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CM7" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CN7" t="n">
         <v>2.22</v>
@@ -3670,10 +3670,10 @@
         <v>1.14</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="CR7" t="n">
         <v>1.34</v>
@@ -3688,10 +3688,10 @@
         <v>1.7</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CX7" t="n">
         <v>1.44</v>
@@ -3709,85 +3709,85 @@
         <v>1.17</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="DH7" t="n">
-        <v>95.45999999999999</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.54</v>
+        <v>5.43</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DM7" t="n">
-        <v>47.54</v>
+        <v>48.43</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.460000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.77</v>
+        <v>9.93</v>
       </c>
       <c r="DR7" t="n">
-        <v>9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.62</v>
+        <v>52.14</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
         <v>11</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.15</v>
+        <v>6.07</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.84</v>
+        <v>4.93</v>
       </c>
       <c r="EA7" t="n">
-        <v>18</v>
+        <v>18.14</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="8">
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>51.71</v>
+        <v>51.57</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.14</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.71</v>
+        <v>52.64</v>
       </c>
       <c r="DW9" t="n">
         <v>0.14</v>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0.33</v>
@@ -4696,115 +4696,115 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>84.88</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>38.62</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BL10" t="n">
         <v>1.43</v>
       </c>
-      <c r="AH10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>87</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>39.57</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>13.29</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>44.43</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>10.54</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1.54</v>
-      </c>
       <c r="BM10" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="BO10" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.38</v>
+        <v>5.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.15</v>
+        <v>5.29</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4813,19 +4813,19 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>92.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BU10" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV10" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW10" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BX10" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY10" t="n">
         <v>3.8</v>
@@ -4834,25 +4834,25 @@
         <v>3.98</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.41</v>
+        <v>5.15</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.65</v>
+        <v>6.28</v>
       </c>
       <c r="CE10" t="n">
         <v>1.28</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CH10" t="n">
         <v>1.56</v>
@@ -4864,25 +4864,25 @@
         <v>1.64</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CO10" t="n">
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CR10" t="n">
         <v>1.34</v>
@@ -4897,10 +4897,10 @@
         <v>1.62</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX10" t="n">
         <v>1.46</v>
@@ -4915,88 +4915,88 @@
         <v>2.17</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DD10" t="n">
         <v>2.56</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DG10" t="n">
         <v>2</v>
       </c>
       <c r="DH10" t="n">
-        <v>87.15000000000001</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.53</v>
+        <v>4.43</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM10" t="n">
-        <v>41.15</v>
+        <v>40.5</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.23</v>
+        <v>12.93</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.61</v>
+        <v>11.21</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.23</v>
+        <v>7.64</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.77</v>
+        <v>43.71</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.15</v>
+        <v>11.72</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.77</v>
+        <v>7.43</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.39</v>
+        <v>4.29</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.38</v>
+        <v>17.36</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5096,139 +5096,139 @@
         <v>1.71</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>89.83</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.33</v>
+        <v>4.57</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN11" t="n">
-        <v>35</v>
+        <v>36.86</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.5</v>
+        <v>13.29</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.33</v>
+        <v>13.71</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.17</v>
+        <v>8.57</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>45.5</v>
+        <v>47.14</v>
       </c>
       <c r="AZ11" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BK11" t="n">
         <v>0.5</v>
       </c>
-      <c r="BA11" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>21.83</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>8.77</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.54</v>
-      </c>
       <c r="BL11" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.62</v>
+        <v>4.64</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU11" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX11" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY11" t="n">
         <v>3.31</v>
@@ -5237,34 +5237,34 @@
         <v>3.43</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.21</v>
+        <v>4.16</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="CC11" t="n">
-        <v>6.05</v>
+        <v>5.58</v>
       </c>
       <c r="CD11" t="n">
-        <v>6.41</v>
+        <v>5.89</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CH11" t="n">
         <v>1.53</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK11" t="n">
         <v>1.47</v>
@@ -5273,10 +5273,10 @@
         <v>1.86</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO11" t="n">
         <v>1.19</v>
@@ -5291,31 +5291,31 @@
         <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY11" t="n">
         <v>1.82</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB11" t="n">
         <v>1.21</v>
@@ -5327,79 +5327,79 @@
         <v>2.68</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="DH11" t="n">
-        <v>84.38</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.53</v>
+        <v>4.64</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM11" t="n">
-        <v>39.23</v>
+        <v>39.86</v>
       </c>
       <c r="DN11" t="n">
         <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.69</v>
+        <v>11.72</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.85</v>
+        <v>13.5</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.77</v>
+        <v>7.57</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>47.08</v>
+        <v>47.78</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.31</v>
+        <v>13</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.460000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.23</v>
+        <v>21</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="G12" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="H12" t="n">
-        <v>106</v>
+        <v>107.43</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="K12" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M12" t="n">
-        <v>44.67</v>
+        <v>45.29</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="P12" t="n">
-        <v>12.17</v>
+        <v>11.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>16.17</v>
+        <v>15.57</v>
       </c>
       <c r="R12" t="n">
-        <v>4.17</v>
+        <v>4.86</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="T12" t="n">
         <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="V12" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>54.83</v>
+        <v>54.43</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.83</v>
+        <v>15.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.17</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.67</v>
+        <v>6.71</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.17</v>
+        <v>20.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
         <v>0.14</v>
@@ -5580,70 +5580,70 @@
         <v>1.71</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.23</v>
+        <v>4.21</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.23</v>
+        <v>9.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.23</v>
+        <v>4.21</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.77</v>
+        <v>5.07</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT12" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BU12" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BV12" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BW12" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BX12" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
       <c r="CC12" t="n">
         <v>3.15</v>
@@ -5652,40 +5652,40 @@
         <v>3.12</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.51</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CQ12" t="n">
         <v>2.34</v>
@@ -5694,7 +5694,7 @@
         <v>1.34</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CT12" t="n">
         <v>3.34</v>
@@ -5703,7 +5703,7 @@
         <v>1.7</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CW12" t="n">
         <v>1.5</v>
@@ -5712,13 +5712,13 @@
         <v>1.49</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.5</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="DB12" t="n">
         <v>1.16</v>
@@ -5727,82 +5727,82 @@
         <v>1.53</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DF12" t="n">
         <v>1</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="DH12" t="n">
-        <v>105.31</v>
+        <v>106.07</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.23</v>
+        <v>5.36</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DM12" t="n">
-        <v>52.23</v>
+        <v>52</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.62</v>
+        <v>12.36</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.39</v>
+        <v>13.28</v>
       </c>
       <c r="DR12" t="n">
-        <v>5</v>
+        <v>5.29</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.69</v>
+        <v>57.28</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.69</v>
+        <v>15.93</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.85</v>
+        <v>9.07</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.85</v>
+        <v>6.86</v>
       </c>
       <c r="EA12" t="n">
-        <v>21</v>
+        <v>20.93</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="13">
@@ -5878,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>37.29</v>
+        <v>37.43</v>
       </c>
       <c r="Y13" t="n">
         <v>0.29</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>41.43</v>
+        <v>41.5</v>
       </c>
       <c r="DW13" t="n">
         <v>0.29</v>
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="F14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="H14" t="n">
-        <v>119.33</v>
+        <v>121.57</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="J14" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="K14" t="n">
-        <v>7.67</v>
+        <v>7.29</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="M14" t="n">
-        <v>65.17</v>
+        <v>69.14</v>
       </c>
       <c r="N14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="O14" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="P14" t="n">
-        <v>10.17</v>
+        <v>10.43</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.5</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="S14" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="T14" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>64.17</v>
+        <v>63.86</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.67</v>
+        <v>21.29</v>
       </c>
       <c r="AA14" t="n">
-        <v>14</v>
+        <v>13.57</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.67</v>
+        <v>7.71</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.17</v>
+        <v>18.14</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AF14" t="n">
         <v>0.29</v>
@@ -6386,70 +6386,70 @@
         <v>1.86</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.46</v>
+        <v>4.36</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.77</v>
+        <v>10.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.46</v>
+        <v>4.36</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.31</v>
+        <v>4.43</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.46</v>
+        <v>6.07</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT14" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BU14" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BV14" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BW14" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BX14" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.08</v>
+        <v>6.57</v>
       </c>
       <c r="CB14" t="n">
-        <v>6.71</v>
+        <v>7.14</v>
       </c>
       <c r="CC14" t="n">
         <v>1.74</v>
@@ -6458,116 +6458,116 @@
         <v>1.72</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.51</v>
+        <v>4.55</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="CO14" t="n">
         <v>1.06</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="CQ14" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="DB14" t="n">
         <v>1.11</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DF14" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="DH14" t="n">
-        <v>106.23</v>
+        <v>108.28</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.31</v>
+        <v>6.21</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DM14" t="n">
-        <v>55.69</v>
+        <v>58.36</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.61</v>
+        <v>2.71</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.92</v>
+        <v>11</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.15</v>
+        <v>7.22</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6579,28 +6579,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.31</v>
+        <v>59.5</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>18</v>
+        <v>18.08</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.84</v>
+        <v>10.86</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7.15</v>
+        <v>7.21</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.54</v>
+        <v>17.57</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="15">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6703,49 +6703,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AI15" t="n">
-        <v>86.83</v>
+        <v>85.14</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN15" t="n">
-        <v>40.67</v>
+        <v>41.57</v>
       </c>
       <c r="AO15" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9</v>
+        <v>9.57</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.5</v>
+        <v>9.57</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6757,82 +6757,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>44.67</v>
+        <v>45.14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.33</v>
+        <v>13.29</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BD15" t="n">
-        <v>13.33</v>
+        <v>14.29</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.92</v>
+        <v>11.07</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.31</v>
+        <v>6.5</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU15" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV15" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW15" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BX15" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BY15" t="n">
         <v>3.05</v>
@@ -6841,31 +6841,31 @@
         <v>3.15</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.95</v>
+        <v>3.99</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.14</v>
+        <v>4.16</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.51</v>
+        <v>4.56</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.93</v>
+        <v>4.97</v>
       </c>
       <c r="CE15" t="n">
         <v>1.28</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.59</v>
@@ -6874,132 +6874,132 @@
         <v>1.35</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CT15" t="n">
         <v>3.25</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CW15" t="n">
         <v>1.58</v>
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ15" t="inlineStr"/>
       <c r="DA15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DB15" t="n">
         <v>1.19</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="DH15" t="n">
-        <v>90.84999999999999</v>
+        <v>89.72</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.15</v>
+        <v>4.28</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM15" t="n">
-        <v>42.31</v>
+        <v>42.64</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="DP15" t="n">
-        <v>8.31</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9.77</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.609999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.54</v>
+        <v>44.78</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.31</v>
+        <v>12.36</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.380000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="EA15" t="n">
-        <v>13.92</v>
+        <v>14.36</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="16">
@@ -7009,61 +7009,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="G16" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="H16" t="n">
-        <v>86</v>
+        <v>86.62</v>
       </c>
       <c r="I16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J16" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="K16" t="n">
-        <v>5.57</v>
+        <v>5.25</v>
       </c>
       <c r="L16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M16" t="n">
-        <v>47.71</v>
+        <v>48.38</v>
       </c>
       <c r="N16" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O16" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="P16" t="n">
-        <v>11</v>
+        <v>10.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.86</v>
+        <v>11.38</v>
       </c>
       <c r="R16" t="n">
-        <v>7.43</v>
+        <v>7</v>
       </c>
       <c r="S16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="T16" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7075,28 +7075,28 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>47.14</v>
+        <v>47.25</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.289999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.71</v>
+        <v>6.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.71</v>
+        <v>19.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7180,70 +7180,70 @@
         <v>1.67</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.38</v>
+        <v>11.14</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.69</v>
+        <v>5.57</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.69</v>
+        <v>5.57</v>
       </c>
       <c r="BR16" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS16" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV16" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX16" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.68</v>
+        <v>2.99</v>
       </c>
       <c r="CA16" t="n">
         <v>4.85</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="CC16" t="n">
         <v>11.17</v>
@@ -7258,16 +7258,16 @@
         <v>2.27</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="CH16" t="n">
         <v>1.61</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK16" t="n">
         <v>1.38</v>
@@ -7276,100 +7276,100 @@
         <v>1.73</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="CT16" t="n">
         <v>3.3</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.37</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DB16" t="n">
         <v>1.19</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="DG16" t="n">
         <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>82.23</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.92</v>
+        <v>42.72</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.85</v>
+        <v>10.64</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.77</v>
+        <v>10.57</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.619999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
@@ -7381,28 +7381,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.84</v>
+        <v>44.14</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.84</v>
+        <v>13.71</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.69</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.15</v>
+        <v>4.92</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.61</v>
+        <v>18.5</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="17">
@@ -7412,94 +7412,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="G17" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="H17" t="n">
-        <v>126.83</v>
+        <v>123.14</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>5.43</v>
       </c>
       <c r="L17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M17" t="n">
-        <v>68</v>
+        <v>64.14</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O17" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>11.83</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.67</v>
+        <v>10.43</v>
       </c>
       <c r="R17" t="n">
-        <v>5.5</v>
+        <v>6.29</v>
       </c>
       <c r="S17" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>58.67</v>
+        <v>57.57</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.17</v>
+        <v>18.29</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.33</v>
+        <v>12.14</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.83</v>
+        <v>6.14</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.83</v>
+        <v>20.43</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7583,70 +7583,70 @@
         <v>2.29</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.380000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
         <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BN17" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.77</v>
+        <v>4.57</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV17" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW17" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX17" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="BZ17" t="n">
         <v>2.2</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="CC17" t="n">
         <v>2.19</v>
@@ -7658,31 +7658,31 @@
         <v>1.26</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CH17" t="n">
         <v>1.58</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO17" t="n">
         <v>1.19</v>
@@ -7697,7 +7697,7 @@
         <v>1.35</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CT17" t="n">
         <v>3.32</v>
@@ -7706,106 +7706,106 @@
         <v>1.58</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB17" t="n">
         <v>1.2</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="DH17" t="n">
-        <v>107.61</v>
+        <v>107.14</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ17" t="n">
         <v>2</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.92</v>
+        <v>4.71</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM17" t="n">
-        <v>58.92</v>
+        <v>57.64</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.84</v>
+        <v>12.86</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.23</v>
+        <v>10.14</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.54</v>
+        <v>6.86</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.77</v>
+        <v>54.5</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX17" t="n">
-        <v>18</v>
+        <v>17.22</v>
       </c>
       <c r="DY17" t="n">
-        <v>11.69</v>
+        <v>11.22</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.31</v>
+        <v>6</v>
       </c>
       <c r="EA17" t="n">
-        <v>21</v>
+        <v>20.78</v>
       </c>
       <c r="EB17" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="18">
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7908,49 +7908,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="AI18" t="n">
-        <v>111.5</v>
+        <v>108.86</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AN18" t="n">
-        <v>45</v>
+        <v>43.43</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.33</v>
+        <v>10.57</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.17</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7962,82 +7962,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>54</v>
+        <v>52.14</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.83</v>
+        <v>14.29</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.33</v>
+        <v>4.86</v>
       </c>
       <c r="BD18" t="n">
-        <v>21</v>
+        <v>21.14</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.31</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.23</v>
+        <v>4.07</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU18" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BV18" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY18" t="n">
         <v>1.81</v>
@@ -8046,55 +8046,55 @@
         <v>1.86</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="CE18" t="n">
         <v>1.31</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI18" t="n">
         <v>2.17</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CK18" t="n">
         <v>1.42</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8118,22 +8118,22 @@
         <v>1.48</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.54</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="DB18" t="n">
         <v>1.22</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
@@ -8142,40 +8142,40 @@
         <v>0.92</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="DH18" t="n">
-        <v>103.54</v>
+        <v>102.78</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.31</v>
+        <v>5.14</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.92</v>
+        <v>39.5</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DO18" t="n">
         <v>3</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.69</v>
+        <v>10.78</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8187,28 +8187,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.85</v>
+        <v>49.22</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.92</v>
+        <v>15.08</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.77</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.15</v>
+        <v>5.36</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.08</v>
+        <v>20.22</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="19">
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>0.14</v>
@@ -8311,49 +8311,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AI19" t="n">
-        <v>82.33</v>
+        <v>79</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN19" t="n">
-        <v>33.33</v>
+        <v>33.43</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.5</v>
+        <v>9.57</v>
       </c>
       <c r="AR19" t="n">
-        <v>10</v>
+        <v>10.29</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.33</v>
+        <v>10.14</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8365,73 +8365,73 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>47</v>
+        <v>45.71</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.5</v>
+        <v>6.71</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BD19" t="n">
-        <v>17.33</v>
+        <v>16.71</v>
       </c>
       <c r="BE19" t="n">
         <v>0.99</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.08</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.77</v>
+        <v>4.5</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT19" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8440,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY19" t="n">
         <v>4.14</v>
@@ -8449,136 +8449,136 @@
         <v>4.26</v>
       </c>
       <c r="CA19" t="n">
-        <v>4.63</v>
+        <v>5.23</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.96</v>
+        <v>5.52</v>
       </c>
       <c r="CC19" t="n">
-        <v>6.36</v>
+        <v>8.16</v>
       </c>
       <c r="CD19" t="n">
-        <v>7.95</v>
+        <v>9.18</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.71</v>
+        <v>3.81</v>
       </c>
       <c r="CH19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="CJ19" t="n">
         <v>1.62</v>
       </c>
-      <c r="CI19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CJ19" t="n">
-        <v>1.61</v>
-      </c>
       <c r="CK19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="CT19" t="n">
         <v>3.34</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX19" t="n">
         <v>1.51</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.44</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="DB19" t="n">
         <v>1.17</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="DH19" t="n">
-        <v>83.3</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM19" t="n">
-        <v>38.46</v>
+        <v>38.14</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DP19" t="n">
-        <v>10.07</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.54</v>
+        <v>11.58</v>
       </c>
       <c r="DR19" t="n">
-        <v>10.77</v>
+        <v>10.64</v>
       </c>
       <c r="DS19" t="n">
         <v>0</v>
@@ -8590,28 +8590,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.62</v>
+        <v>45.07</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.62</v>
+        <v>10.57</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.93</v>
+        <v>7</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.69</v>
+        <v>3.57</v>
       </c>
       <c r="EA19" t="n">
-        <v>14.46</v>
+        <v>14.36</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="EC19" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F3" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="G3" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>111.29</v>
+        <v>107.88</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J3" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="K3" t="n">
-        <v>6.57</v>
+        <v>6.12</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="M3" t="n">
-        <v>60.71</v>
+        <v>59.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="P3" t="n">
-        <v>10.14</v>
+        <v>10.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="R3" t="n">
-        <v>5.57</v>
+        <v>5.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="T3" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>60</v>
+        <v>58.62</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.29</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.29</v>
+        <v>6.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.86</v>
+        <v>17.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF3" t="n">
         <v>0.17</v>
@@ -1953,37 +1953,37 @@
         <v>2.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.77</v>
+        <v>10.57</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="BJ3" t="n">
         <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.46</v>
+        <v>5.36</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.31</v>
+        <v>5.21</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,31 +1992,31 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU3" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV3" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX3" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.01</v>
+        <v>4.9</v>
       </c>
       <c r="CB3" t="n">
-        <v>5.18</v>
+        <v>5.08</v>
       </c>
       <c r="CC3" t="n">
         <v>2.39</v>
@@ -2025,31 +2025,31 @@
         <v>2.58</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.64</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CN3" t="n">
         <v>1.94</v>
@@ -2058,10 +2058,10 @@
         <v>1.13</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
@@ -2082,13 +2082,13 @@
         <v>1.66</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA3" t="n">
         <v>2.01</v>
@@ -2103,79 +2103,79 @@
         <v>2.22</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="DH3" t="n">
-        <v>103.31</v>
+        <v>101.93</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.85</v>
+        <v>5.64</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DM3" t="n">
-        <v>55.77</v>
+        <v>55.43</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="DP3" t="n">
-        <v>11</v>
+        <v>11.21</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.23</v>
+        <v>13</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.08</v>
+        <v>6</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.84</v>
+        <v>57.21</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.77</v>
+        <v>14.64</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.69</v>
+        <v>8.57</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.39</v>
+        <v>16.93</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="4">
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>55.71</v>
+        <v>55.57</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.14</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.71</v>
+        <v>54.64</v>
       </c>
       <c r="DW5" t="n">
         <v>0.14</v>
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0.14</v>
@@ -3887,52 +3887,52 @@
         <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH8" t="n">
         <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>95</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.17</v>
+        <v>4.29</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN8" t="n">
-        <v>37</v>
+        <v>38.29</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.5</v>
+        <v>12.14</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.17</v>
+        <v>11.57</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
         <v>2</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>44.17</v>
+        <v>45.14</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.33</v>
+        <v>6.86</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.17</v>
+        <v>7.14</v>
       </c>
       <c r="BD8" t="n">
-        <v>20.83</v>
+        <v>20.86</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.23</v>
+        <v>10.07</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP8" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.23</v>
+        <v>5.14</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV8" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX8" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>2.18</v>
@@ -4028,34 +4028,34 @@
         <v>2.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.19</v>
+        <v>4.16</v>
       </c>
       <c r="CC8" t="n">
-        <v>6.01</v>
+        <v>5.67</v>
       </c>
       <c r="CD8" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF8" t="n">
         <v>2.51</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="CH8" t="n">
         <v>1.49</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK8" t="n">
         <v>1.56</v>
@@ -4067,16 +4067,16 @@
         <v>2.31</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP8" t="n">
         <v>1.75</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4091,22 +4091,22 @@
         <v>1.51</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB8" t="n">
         <v>1.25</v>
@@ -4118,79 +4118,79 @@
         <v>2.98</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="DH8" t="n">
-        <v>106</v>
+        <v>106.5</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.46</v>
+        <v>5.43</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM8" t="n">
-        <v>43.77</v>
+        <v>43.93</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.62</v>
+        <v>11.5</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.77</v>
+        <v>11</v>
       </c>
       <c r="DR8" t="n">
-        <v>7</v>
+        <v>7.14</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.23</v>
+        <v>50.28</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.62</v>
+        <v>15.72</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.15</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.46</v>
+        <v>6.5</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.62</v>
+        <v>21.57</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="9">
@@ -7075,7 +7075,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>47.25</v>
+        <v>47.38</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -7381,7 +7381,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.14</v>
+        <v>44.22</v>
       </c>
       <c r="DW16" t="n">
         <v>0.07000000000000001</v>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>58.62</v>
+        <v>58.5</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.21</v>
+        <v>57.14</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F4" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="G4" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="H4" t="n">
-        <v>91.70999999999999</v>
+        <v>92.12</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="K4" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M4" t="n">
-        <v>34.71</v>
+        <v>33.12</v>
       </c>
       <c r="N4" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="O4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="P4" t="n">
-        <v>13.57</v>
+        <v>13.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.43</v>
+        <v>10.25</v>
       </c>
       <c r="R4" t="n">
-        <v>10.14</v>
+        <v>10.25</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="T4" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="U4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>43.57</v>
+        <v>43.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.43</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.71</v>
+        <v>8</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.71</v>
+        <v>4</v>
       </c>
       <c r="AC4" t="n">
-        <v>18</v>
+        <v>17.12</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AF4" t="n">
         <v>0.14</v>
@@ -2356,70 +2356,70 @@
         <v>1.57</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.57</v>
+        <v>9.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.57</v>
+        <v>4.53</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT4" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU4" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV4" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.64</v>
+        <v>3.56</v>
       </c>
       <c r="BZ4" t="n">
         <v>3.74</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="CC4" t="n">
         <v>4.69</v>
@@ -2428,157 +2428,157 @@
         <v>5</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK4" t="n">
         <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX4" t="n">
         <v>1.5</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DB4" t="n">
         <v>1.18</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF4" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="DH4" t="n">
-        <v>90.34999999999999</v>
+        <v>90.66</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.08</v>
+        <v>4.14</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM4" t="n">
-        <v>39.29</v>
+        <v>38.13</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO4" t="n">
         <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>14.28</v>
+        <v>14</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.07</v>
+        <v>9.06</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.220000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.93</v>
+        <v>44.07</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.78</v>
+        <v>12.07</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.64</v>
+        <v>7.8</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.14</v>
+        <v>4.27</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.72</v>
+        <v>17.26</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="5">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0.14</v>
@@ -3887,139 +3887,139 @@
         <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AI8" t="n">
-        <v>97.56999999999999</v>
+        <v>99.25</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>38.29</v>
+        <v>39.25</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.14</v>
+        <v>11.75</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.57</v>
+        <v>11.25</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>7.88</v>
       </c>
       <c r="AT8" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>45.14</v>
+        <v>46.38</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA8" t="n">
-        <v>14</v>
+        <v>14.75</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.86</v>
+        <v>7.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.14</v>
+        <v>7.25</v>
       </c>
       <c r="BD8" t="n">
-        <v>20.86</v>
+        <v>20.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="BH8" t="n">
         <v>10.07</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.93</v>
+        <v>4.87</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV8" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY8" t="n">
         <v>2.18</v>
@@ -4028,19 +4028,19 @@
         <v>2.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.16</v>
+        <v>4.12</v>
       </c>
       <c r="CC8" t="n">
-        <v>5.67</v>
+        <v>5.19</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.67</v>
+        <v>5.22</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF8" t="n">
         <v>2.51</v>
@@ -4052,19 +4052,19 @@
         <v>1.49</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.72</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN8" t="n">
         <v>1.82</v>
@@ -4073,7 +4073,7 @@
         <v>1.23</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ8" t="n">
         <v>2.82</v>
@@ -4082,10 +4082,10 @@
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CU8" t="n">
         <v>1.51</v>
@@ -4097,16 +4097,16 @@
         <v>1.78</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB8" t="n">
         <v>1.25</v>
@@ -4115,82 +4115,82 @@
         <v>1.82</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="DH8" t="n">
-        <v>106.5</v>
+        <v>106.8</v>
       </c>
       <c r="DI8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.43</v>
+        <v>5.4</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM8" t="n">
-        <v>43.93</v>
+        <v>44.07</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.5</v>
+        <v>11.33</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11</v>
+        <v>10.87</v>
       </c>
       <c r="DR8" t="n">
         <v>7.14</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.28</v>
+        <v>50.6</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.72</v>
+        <v>16</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.220000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.57</v>
+        <v>21.47</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1379,91 +1379,91 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F2" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="G2" t="n">
-        <v>3.17</v>
+        <v>3.86</v>
       </c>
       <c r="H2" t="n">
-        <v>107.17</v>
+        <v>105.29</v>
       </c>
       <c r="I2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>6.17</v>
+        <v>6.86</v>
       </c>
       <c r="L2" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="M2" t="n">
-        <v>53.67</v>
+        <v>53.14</v>
       </c>
       <c r="N2" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>8.67</v>
+        <v>8.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.83</v>
+        <v>10.43</v>
       </c>
       <c r="R2" t="n">
-        <v>7.5</v>
+        <v>7.14</v>
       </c>
       <c r="S2" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="T2" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>54.17</v>
+        <v>53.43</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.83</v>
+        <v>17.71</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.33</v>
+        <v>11.14</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.17</v>
+        <v>17.71</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -1550,70 +1550,70 @@
         <v>3.12</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.21</v>
+        <v>10.53</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BM2" t="n">
         <v>0.93</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.93</v>
+        <v>4.87</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.29</v>
+        <v>5.67</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT2" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.36</v>
+        <v>4.43</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.49</v>
+        <v>4.57</v>
       </c>
       <c r="CC2" t="n">
         <v>2.15</v>
@@ -1625,55 +1625,55 @@
         <v>1.24</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.56</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="CN2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CR2" t="n">
         <v>1.33</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="CT2" t="n">
         <v>3.32</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CW2" t="n">
         <v>1.6</v>
@@ -1682,97 +1682,97 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.44</v>
       </c>
       <c r="DA2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DB2" t="n">
         <v>1.16</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="DG2" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="DH2" t="n">
-        <v>103.07</v>
+        <v>102.47</v>
       </c>
       <c r="DI2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.86</v>
+        <v>6.2</v>
       </c>
       <c r="DL2" t="n">
         <v>0.93</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.22</v>
+        <v>49.27</v>
       </c>
       <c r="DN2" t="n">
         <v>1.07</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.43</v>
+        <v>10.27</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.79</v>
+        <v>7.6</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54</v>
+        <v>53.67</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.14</v>
+        <v>16.6</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.21</v>
+        <v>10.6</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.43</v>
+        <v>16.33</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0.12</v>
@@ -1872,118 +1872,118 @@
         <v>1.38</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AI3" t="n">
-        <v>94</v>
+        <v>96.14</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AL3" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN3" t="n">
-        <v>50</v>
+        <v>49.71</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>11.57</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.33</v>
+        <v>12.43</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.67</v>
+        <v>7.71</v>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>55.33</v>
+        <v>56.57</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BA3" t="n">
-        <v>14.17</v>
+        <v>14</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.33</v>
+        <v>8.43</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.83</v>
+        <v>5.57</v>
       </c>
       <c r="BD3" t="n">
-        <v>15.67</v>
+        <v>15.71</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.57</v>
+        <v>10.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="BJ3" t="n">
         <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.36</v>
+        <v>5.2</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,19 +1992,19 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU3" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV3" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX3" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY3" t="n">
         <v>1.47</v>
@@ -2013,28 +2013,28 @@
         <v>1.5</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.9</v>
+        <v>4.81</v>
       </c>
       <c r="CB3" t="n">
-        <v>5.08</v>
+        <v>4.99</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="CE3" t="n">
         <v>1.24</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI3" t="n">
         <v>2.27</v>
@@ -2046,10 +2046,10 @@
         <v>1.5</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CN3" t="n">
         <v>1.94</v>
@@ -2061,25 +2061,25 @@
         <v>1.49</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="CT3" t="n">
         <v>3.32</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CV3" t="n">
         <v>2.36</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX3" t="n">
         <v>1.51</v>
@@ -2091,58 +2091,58 @@
         <v>2.46</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.93</v>
+        <v>102.4</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.64</v>
+        <v>5.53</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="DM3" t="n">
-        <v>55.43</v>
+        <v>54.93</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.21</v>
+        <v>11.06</v>
       </c>
       <c r="DQ3" t="n">
         <v>13</v>
       </c>
       <c r="DR3" t="n">
-        <v>6</v>
+        <v>6.53</v>
       </c>
       <c r="DS3" t="n">
         <v>0.07000000000000001</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.14</v>
+        <v>57.6</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.64</v>
+        <v>14.53</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.57</v>
+        <v>8.6</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.07</v>
+        <v>5.93</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.93</v>
+        <v>16.87</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="4">
@@ -2473,7 +2473,7 @@
         <v>2.38</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CU4" t="n">
         <v>1.64</v>
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F5" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="G5" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="H5" t="n">
-        <v>100.29</v>
+        <v>100.5</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>7.71</v>
+        <v>7.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="M5" t="n">
-        <v>58.29</v>
+        <v>55.38</v>
       </c>
       <c r="N5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="O5" t="n">
-        <v>4.57</v>
+        <v>4.25</v>
       </c>
       <c r="P5" t="n">
-        <v>8.140000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="Q5" t="n">
         <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>6.86</v>
+        <v>6.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>53.71</v>
+        <v>54.12</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.71</v>
+        <v>20.38</v>
       </c>
       <c r="AA5" t="n">
-        <v>13.43</v>
+        <v>13.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.29</v>
+        <v>7</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.57</v>
+        <v>18.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AF5" t="n">
         <v>0.14</v>
@@ -2759,70 +2759,70 @@
         <v>2.29</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.71</v>
+        <v>3.93</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.57</v>
+        <v>10.67</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.71</v>
+        <v>3.93</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.71</v>
+        <v>0.93</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.43</v>
+        <v>5.27</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.14</v>
+        <v>5.4</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BW5" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BX5" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.96</v>
+        <v>5.13</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.23</v>
+        <v>5.51</v>
       </c>
       <c r="CC5" t="n">
         <v>1.76</v>
@@ -2831,157 +2831,157 @@
         <v>1.79</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK5" t="n">
         <v>1.42</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM5" t="n">
         <v>2.64</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CR5" t="n">
         <v>1.33</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CT5" t="n">
         <v>3.32</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX5" t="n">
         <v>1.54</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.42</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB5" t="n">
         <v>1.16</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.28</v>
+        <v>3.47</v>
       </c>
       <c r="DH5" t="n">
-        <v>102.15</v>
+        <v>102.13</v>
       </c>
       <c r="DI5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.42</v>
+        <v>7.47</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="DM5" t="n">
-        <v>57.14</v>
+        <v>55.67</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DO5" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="DP5" t="n">
-        <v>8.640000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.64</v>
+        <v>10.67</v>
       </c>
       <c r="DR5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.64</v>
+        <v>54.8</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX5" t="n">
-        <v>18.5</v>
+        <v>18.94</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.64</v>
+        <v>11.74</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.86</v>
+        <v>7.2</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.86</v>
+        <v>19</v>
       </c>
       <c r="EB5" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="G6" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="H6" t="n">
-        <v>92.29000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>5.86</v>
+        <v>5.62</v>
       </c>
       <c r="L6" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="M6" t="n">
-        <v>44.86</v>
+        <v>45.38</v>
       </c>
       <c r="N6" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O6" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="P6" t="n">
-        <v>14.14</v>
+        <v>14</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="R6" t="n">
-        <v>6.43</v>
+        <v>6.25</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.57</v>
+        <v>47.88</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.86</v>
+        <v>17</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.29</v>
+        <v>12.12</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.57</v>
+        <v>4.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.14</v>
+        <v>16.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AF6" t="n">
         <v>0.14</v>
@@ -3162,70 +3162,70 @@
         <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.79</v>
+        <v>10.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="BJ6" t="n">
         <v>1.07</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.57</v>
+        <v>5.53</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV6" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX6" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.35</v>
+        <v>4.31</v>
       </c>
       <c r="CC6" t="n">
         <v>6.55</v>
@@ -3243,31 +3243,31 @@
         <v>3.29</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CQ6" t="n">
         <v>2.66</v>
@@ -3285,7 +3285,7 @@
         <v>1.59</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CW6" t="n">
         <v>1.69</v>
@@ -3294,97 +3294,97 @@
         <v>1.5</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.5</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="DB6" t="n">
         <v>1.24</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DD6" t="n">
         <v>2.78</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DH6" t="n">
-        <v>91.08</v>
+        <v>90.2</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.43</v>
+        <v>39.14</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.86</v>
+        <v>13.8</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.86</v>
+        <v>10.74</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.57</v>
+        <v>7.4</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.57</v>
+        <v>46.8</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.78</v>
+        <v>13.6</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.07</v>
+        <v>17.6</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0.29</v>
@@ -3484,52 +3484,52 @@
         <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>97.29000000000001</v>
+        <v>97.62</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AL7" t="n">
         <v>4</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>44.57</v>
+        <v>42.75</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.859999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.57</v>
+        <v>8.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.140000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>51.86</v>
+        <v>51.75</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.57</v>
+        <v>9.75</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.57</v>
+        <v>5.38</v>
       </c>
       <c r="BC7" t="n">
-        <v>4</v>
+        <v>4.38</v>
       </c>
       <c r="BD7" t="n">
-        <v>20</v>
+        <v>19.88</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.93</v>
+        <v>11.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.14</v>
+        <v>6.47</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BV7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
         <v>2.96</v>
@@ -3625,40 +3625,40 @@
         <v>3.14</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.21</v>
+        <v>4.32</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.6</v>
+        <v>4.01</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.75</v>
+        <v>4.36</v>
       </c>
       <c r="CE7" t="n">
         <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CK7" t="n">
         <v>1.34</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CM7" t="n">
         <v>3.01</v>
@@ -3670,34 +3670,34 @@
         <v>1.14</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CR7" t="n">
         <v>1.34</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="CT7" t="n">
         <v>3.31</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CX7" t="n">
         <v>1.44</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.63</v>
@@ -3709,49 +3709,49 @@
         <v>1.17</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="DH7" t="n">
-        <v>96.29000000000001</v>
+        <v>96.53</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.43</v>
+        <v>5.33</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM7" t="n">
-        <v>48.43</v>
+        <v>47.2</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.43</v>
+        <v>9.33</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.93</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DR7" t="n">
         <v>8.859999999999999</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.14</v>
+        <v>52.07</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX7" t="n">
         <v>11</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.07</v>
+        <v>5.94</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.93</v>
+        <v>5.07</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.14</v>
+        <v>18.2</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="8">
@@ -4085,7 +4085,7 @@
         <v>2.73</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CU8" t="n">
         <v>1.51</v>
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F9" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="G9" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="H9" t="n">
-        <v>108.71</v>
+        <v>104.25</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="K9" t="n">
-        <v>6.29</v>
+        <v>6.38</v>
       </c>
       <c r="L9" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="M9" t="n">
-        <v>59.43</v>
+        <v>58</v>
       </c>
       <c r="N9" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>8.859999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>11.12</v>
       </c>
       <c r="R9" t="n">
-        <v>6.29</v>
+        <v>6.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="T9" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="U9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>53.71</v>
+        <v>51.75</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>17</v>
+        <v>16.38</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.43</v>
+        <v>11.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.57</v>
+        <v>5.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.57</v>
+        <v>15.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>1.71</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.79</v>
+        <v>10.73</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="BJ9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BL9" t="n">
         <v>0.93</v>
       </c>
-      <c r="BK9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1</v>
-      </c>
       <c r="BM9" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.21</v>
+        <v>5.13</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT9" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV9" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX9" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.91</v>
+        <v>3.93</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="CC9" t="n">
         <v>3.68</v>
@@ -4443,157 +4443,157 @@
         <v>4.05</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL9" t="n">
         <v>1.82</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="CT9" t="n">
         <v>3.24</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.48</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="DH9" t="n">
-        <v>102.35</v>
+        <v>100.4</v>
       </c>
       <c r="DI9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.21</v>
+        <v>6.27</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="DM9" t="n">
-        <v>51.64</v>
+        <v>51.4</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DO9" t="n">
         <v>3.07</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.36</v>
+        <v>11.47</v>
       </c>
       <c r="DQ9" t="n">
-        <v>11.14</v>
+        <v>10.73</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.93</v>
+        <v>6.87</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.64</v>
+        <v>51.67</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX9" t="n">
-        <v>16.07</v>
+        <v>15.8</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.57</v>
+        <v>5.4</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="G10" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="H10" t="n">
-        <v>87.33</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="K10" t="n">
-        <v>4.33</v>
+        <v>4.57</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="M10" t="n">
-        <v>43</v>
+        <v>43.14</v>
       </c>
       <c r="N10" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="O10" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="P10" t="n">
-        <v>11</v>
+        <v>11.57</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.83</v>
+        <v>11.86</v>
       </c>
       <c r="R10" t="n">
         <v>7</v>
       </c>
       <c r="S10" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="T10" t="n">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="U10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>43</v>
+        <v>43.43</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.67</v>
+        <v>15.57</v>
       </c>
       <c r="AA10" t="n">
         <v>9</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.67</v>
+        <v>6.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>13.83</v>
+        <v>15.86</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,37 +4774,37 @@
         <v>2.25</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.79</v>
+        <v>10.87</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.29</v>
+        <v>5.4</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4813,31 +4813,31 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BU10" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV10" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW10" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BX10" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.98</v>
+        <v>3.76</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="CC10" t="n">
         <v>5.15</v>
@@ -4858,7 +4858,7 @@
         <v>1.56</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.64</v>
@@ -4870,10 +4870,10 @@
         <v>1.68</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CO10" t="n">
         <v>1.18</v>
@@ -4888,16 +4888,16 @@
         <v>1.34</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CT10" t="n">
         <v>3.36</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CW10" t="n">
         <v>1.66</v>
@@ -4906,16 +4906,16 @@
         <v>1.46</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.59</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC10" t="n">
         <v>1.64</v>
@@ -4927,43 +4927,43 @@
         <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="DG10" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DH10" t="n">
-        <v>85.93000000000001</v>
+        <v>86.47</v>
       </c>
       <c r="DI10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.43</v>
+        <v>4.53</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.5</v>
+        <v>40.73</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.93</v>
+        <v>13.07</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.21</v>
+        <v>11.27</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.64</v>
+        <v>7.6</v>
       </c>
       <c r="DS10" t="n">
         <v>0.07000000000000001</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.71</v>
+        <v>43.87</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.72</v>
+        <v>11.93</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.43</v>
+        <v>7.53</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.29</v>
+        <v>4.4</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.36</v>
+        <v>18.07</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5096,109 +5096,109 @@
         <v>1.71</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG11" t="n">
         <v>1</v>
       </c>
       <c r="AH11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AT11" t="n">
         <v>2</v>
       </c>
-      <c r="AI11" t="n">
-        <v>94.70999999999999</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>36.86</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>13.29</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>13.71</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AU11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BL11" t="n">
         <v>1</v>
       </c>
-      <c r="AV11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>23.14</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1.07</v>
-      </c>
       <c r="BM11" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BO11" t="n">
         <v>1.07</v>
@@ -5207,28 +5207,28 @@
         <v>4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.64</v>
+        <v>5.07</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU11" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX11" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY11" t="n">
         <v>3.31</v>
@@ -5237,16 +5237,16 @@
         <v>3.43</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.16</v>
+        <v>4.11</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.58</v>
+        <v>5.26</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.89</v>
+        <v>5.53</v>
       </c>
       <c r="CE11" t="n">
         <v>1.29</v>
@@ -5255,13 +5255,13 @@
         <v>2.42</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CH11" t="n">
         <v>1.53</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.67</v>
@@ -5273,7 +5273,7 @@
         <v>1.86</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CN11" t="n">
         <v>1.93</v>
@@ -5285,19 +5285,19 @@
         <v>1.68</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV11" t="n">
         <v>2.25</v>
@@ -5309,97 +5309,97 @@
         <v>1.53</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.44</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB11" t="n">
         <v>1.21</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF11" t="n">
         <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.22</v>
+        <v>2.73</v>
       </c>
       <c r="DH11" t="n">
-        <v>87.20999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.64</v>
+        <v>5.26</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM11" t="n">
-        <v>39.86</v>
+        <v>42.53</v>
       </c>
       <c r="DN11" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.72</v>
+        <v>11.6</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.5</v>
+        <v>13.34</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.57</v>
+        <v>7.47</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>47.78</v>
+        <v>48.53</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX11" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.220000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.78</v>
+        <v>4.14</v>
       </c>
       <c r="EA11" t="n">
-        <v>21</v>
+        <v>20.93</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0.29</v>
@@ -5499,52 +5499,52 @@
         <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AI12" t="n">
-        <v>104.71</v>
+        <v>103</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.71</v>
+        <v>5.12</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.71</v>
+        <v>58.62</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="AP12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.71</v>
+        <v>6</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>60.14</v>
+        <v>59.75</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA12" t="n">
-        <v>16.43</v>
+        <v>16.38</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.43</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BC12" t="n">
         <v>7</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.71</v>
+        <v>22.38</v>
       </c>
       <c r="BE12" t="n">
         <v>1.95</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.21</v>
+        <v>4.27</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.5</v>
+        <v>9.67</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.21</v>
+        <v>4.27</v>
       </c>
       <c r="BJ12" t="n">
         <v>1</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.43</v>
+        <v>4.67</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BU12" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BW12" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BX12" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY12" t="n">
         <v>2.35</v>
@@ -5643,28 +5643,28 @@
         <v>3.96</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.08</v>
+        <v>4.11</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="CE12" t="n">
         <v>1.25</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.51</v>
@@ -5679,31 +5679,31 @@
         <v>2.75</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO12" t="n">
         <v>1.15</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CR12" t="n">
         <v>1.34</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CT12" t="n">
         <v>3.34</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CW12" t="n">
         <v>1.5</v>
@@ -5718,76 +5718,76 @@
         <v>2.5</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DB12" t="n">
         <v>1.16</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF12" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="DH12" t="n">
-        <v>106.07</v>
+        <v>105.07</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.36</v>
+        <v>5.53</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DM12" t="n">
-        <v>52</v>
+        <v>52.4</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.36</v>
+        <v>12.66</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.28</v>
+        <v>12.87</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.29</v>
+        <v>5.47</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.28</v>
+        <v>57.27</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.93</v>
+        <v>15.94</v>
       </c>
       <c r="DY12" t="n">
         <v>9.07</v>
@@ -5796,13 +5796,13 @@
         <v>6.86</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.93</v>
+        <v>21.33</v>
       </c>
       <c r="EB12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="EC12" t="n">
         <v>1.86</v>
-      </c>
-      <c r="EC12" t="n">
-        <v>1.64</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0.14</v>
@@ -5902,52 +5902,52 @@
         <v>1.71</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>74.56999999999999</v>
+        <v>71.88</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN13" t="n">
-        <v>31.57</v>
+        <v>28.75</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.14</v>
+        <v>10.38</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.14</v>
+        <v>13.62</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.57</v>
+        <v>10.88</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>45.57</v>
+        <v>45.25</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.86</v>
+        <v>5.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="BD13" t="n">
-        <v>14.71</v>
+        <v>14.62</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.43</v>
+        <v>3.67</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.43</v>
+        <v>8.67</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.43</v>
+        <v>3.67</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="BO13" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.29</v>
+        <v>4.2</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.14</v>
+        <v>4.47</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY13" t="n">
         <v>3.59</v>
@@ -6043,34 +6043,34 @@
         <v>3.84</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.07</v>
+        <v>4.3</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.21</v>
+        <v>4.56</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.95</v>
+        <v>5.96</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.49</v>
+        <v>6.51</v>
       </c>
       <c r="CE13" t="n">
         <v>1.28</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CK13" t="n">
         <v>1.44</v>
@@ -6085,94 +6085,94 @@
         <v>2.01</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="CT13" t="n">
         <v>3.34</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CX13" t="n">
         <v>1.51</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.44</v>
       </c>
       <c r="DA13" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DB13" t="n">
         <v>1.19</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="DH13" t="n">
-        <v>77.14</v>
+        <v>75.53</v>
       </c>
       <c r="DI13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="DK13" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="DM13" t="n">
-        <v>32.93</v>
+        <v>31.34</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.07</v>
+        <v>10.2</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.78</v>
+        <v>13.06</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.86</v>
+        <v>11</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DX13" t="n">
-        <v>8.57</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.72</v>
+        <v>5.53</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="EA13" t="n">
-        <v>16</v>
+        <v>15.87</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0.43</v>
@@ -6305,115 +6305,115 @@
         <v>0.71</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>95</v>
+        <v>96.38</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.14</v>
+        <v>4.88</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>47.57</v>
+        <v>49.62</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.57</v>
+        <v>10.75</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.57</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.140000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AT14" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>56</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BL14" t="n">
         <v>1</v>
       </c>
-      <c r="AU14" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>55.14</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>17</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1.07</v>
-      </c>
       <c r="BM14" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="BO14" t="n">
         <v>2.07</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="BQ14" t="n">
         <v>6.07</v>
@@ -6422,22 +6422,22 @@
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BV14" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BW14" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BX14" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY14" t="n">
         <v>1.22</v>
@@ -6446,16 +6446,16 @@
         <v>1.22</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.57</v>
+        <v>6.42</v>
       </c>
       <c r="CB14" t="n">
-        <v>7.14</v>
+        <v>6.96</v>
       </c>
       <c r="CC14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CD14" t="n">
         <v>1.74</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>1.72</v>
       </c>
       <c r="CE14" t="n">
         <v>1.16</v>
@@ -6470,22 +6470,22 @@
         <v>1.92</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK14" t="n">
         <v>1.35</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CO14" t="n">
         <v>1.06</v>
@@ -6498,17 +6498,17 @@
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="n">
         <v>1.99</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DB14" t="n">
         <v>1.11</v>
@@ -6528,46 +6528,46 @@
         <v>1.8</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="DH14" t="n">
-        <v>108.28</v>
+        <v>108.14</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.21</v>
+        <v>6</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM14" t="n">
-        <v>58.36</v>
+        <v>58.73</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="DP14" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.640000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.22</v>
+        <v>7.4</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6579,28 +6579,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.5</v>
+        <v>59.67</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>18.08</v>
+        <v>17.6</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.86</v>
+        <v>10.4</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7.21</v>
+        <v>7.2</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.57</v>
+        <v>17.73</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="15">
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -6622,82 +6622,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="G15" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="H15" t="n">
-        <v>94.29000000000001</v>
+        <v>92.12</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="K15" t="n">
-        <v>4.57</v>
+        <v>4.12</v>
       </c>
       <c r="L15" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M15" t="n">
-        <v>43.71</v>
+        <v>41.88</v>
       </c>
       <c r="N15" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="P15" t="n">
-        <v>7.71</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="Q15" t="n">
         <v>10</v>
       </c>
       <c r="R15" t="n">
-        <v>9.710000000000001</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="T15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="U15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>44.43</v>
+        <v>44</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.43</v>
+        <v>11.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.57</v>
+        <v>7.38</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.86</v>
+        <v>4.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>14.43</v>
+        <v>14.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6781,70 +6781,70 @@
         <v>2.43</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.07</v>
+        <v>11.33</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.57</v>
+        <v>4.53</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU15" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW15" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BX15" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.16</v>
+        <v>4.11</v>
       </c>
       <c r="CC15" t="n">
         <v>4.56</v>
@@ -6856,16 +6856,16 @@
         <v>1.28</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.59</v>
@@ -6874,13 +6874,13 @@
         <v>1.35</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CO15" t="n">
         <v>1.18</v>
@@ -6889,42 +6889,42 @@
         <v>1.63</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CW15" t="n">
         <v>1.58</v>
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CZ15" t="inlineStr"/>
       <c r="DA15" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DB15" t="n">
         <v>1.19</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
@@ -6933,73 +6933,73 @@
         <v>1.07</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="DH15" t="n">
-        <v>89.72</v>
+        <v>88.86</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.28</v>
+        <v>4.06</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM15" t="n">
-        <v>42.64</v>
+        <v>41.74</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="DP15" t="n">
-        <v>8.640000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9.720000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.640000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.78</v>
+        <v>44.53</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.36</v>
+        <v>12.34</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.359999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4</v>
+        <v>4.13</v>
       </c>
       <c r="EA15" t="n">
-        <v>14.36</v>
+        <v>14.6</v>
       </c>
       <c r="EB15" t="n">
         <v>1.37</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0.25</v>
@@ -7102,49 +7102,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AI16" t="n">
-        <v>77.83</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK16" t="n">
         <v>2</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.67</v>
+        <v>4.86</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AN16" t="n">
-        <v>35.17</v>
+        <v>37.86</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.67</v>
+        <v>10.86</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.5</v>
+        <v>10.29</v>
       </c>
       <c r="AS16" t="n">
-        <v>10</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7156,82 +7156,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.33</v>
+        <v>11.29</v>
       </c>
       <c r="BB16" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.33</v>
+        <v>17.57</v>
       </c>
       <c r="BE16" t="n">
         <v>1.21</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.14</v>
+        <v>11.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.57</v>
+        <v>5.53</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.57</v>
+        <v>5.67</v>
       </c>
       <c r="BR16" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS16" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU16" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV16" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX16" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
         <v>3.04</v>
@@ -7240,16 +7240,16 @@
         <v>2.99</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.85</v>
+        <v>4.77</v>
       </c>
       <c r="CB16" t="n">
-        <v>5.05</v>
+        <v>4.96</v>
       </c>
       <c r="CC16" t="n">
-        <v>11.17</v>
+        <v>9.98</v>
       </c>
       <c r="CD16" t="n">
-        <v>9.710000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="CE16" t="n">
         <v>1.26</v>
@@ -7258,37 +7258,37 @@
         <v>2.27</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CH16" t="n">
         <v>1.61</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CK16" t="n">
         <v>1.38</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
@@ -7303,73 +7303,73 @@
         <v>1.61</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.37</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="DB16" t="n">
         <v>1.19</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DG16" t="n">
         <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>82.84999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="DI16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="DK16" t="n">
-        <v>5</v>
+        <v>5.07</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DM16" t="n">
-        <v>42.72</v>
+        <v>43.47</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO16" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.64</v>
+        <v>10.73</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.57</v>
+        <v>10.87</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
@@ -7381,28 +7381,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.22</v>
+        <v>44.87</v>
       </c>
       <c r="DW16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.71</v>
+        <v>13.54</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.789999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.92</v>
+        <v>4.73</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.5</v>
+        <v>18.54</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="17">
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0.14</v>
@@ -7505,136 +7505,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AI17" t="n">
-        <v>91.14</v>
+        <v>93.62</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AL17" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN17" t="n">
-        <v>51.14</v>
+        <v>50.38</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13.71</v>
+        <v>13</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.859999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.43</v>
+        <v>7.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>51.43</v>
+        <v>52.88</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>16.14</v>
+        <v>16.62</v>
       </c>
       <c r="BB17" t="n">
-        <v>10.29</v>
+        <v>10.75</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.86</v>
+        <v>5.88</v>
       </c>
       <c r="BD17" t="n">
-        <v>21.14</v>
+        <v>21.12</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.140000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL17" t="n">
         <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BN17" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.57</v>
+        <v>4.53</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS17" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU17" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW17" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX17" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY17" t="n">
         <v>2.18</v>
@@ -7643,34 +7643,34 @@
         <v>2.2</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="CD17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CI17" t="n">
         <v>2.26</v>
       </c>
-      <c r="CE17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CF17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="CG17" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="CH17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CI17" t="n">
-        <v>2.27</v>
-      </c>
       <c r="CJ17" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK17" t="n">
         <v>1.47</v>
@@ -7679,7 +7679,7 @@
         <v>1.82</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN17" t="n">
         <v>1.94</v>
@@ -7688,22 +7688,22 @@
         <v>1.19</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="CR17" t="n">
         <v>1.35</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV17" t="n">
         <v>2.35</v>
@@ -7715,97 +7715,97 @@
         <v>1.54</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DB17" t="n">
         <v>1.2</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="DE17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.22</v>
+        <v>2.53</v>
       </c>
       <c r="DH17" t="n">
-        <v>107.14</v>
+        <v>107.4</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ17" t="n">
         <v>2</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.71</v>
+        <v>4.93</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM17" t="n">
-        <v>57.64</v>
+        <v>56.8</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.86</v>
+        <v>12.53</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.14</v>
+        <v>10</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.86</v>
+        <v>6.94</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.5</v>
+        <v>55.07</v>
       </c>
       <c r="DW17" t="n">
         <v>0.14</v>
       </c>
       <c r="DX17" t="n">
-        <v>17.22</v>
+        <v>17.4</v>
       </c>
       <c r="DY17" t="n">
-        <v>11.22</v>
+        <v>11.4</v>
       </c>
       <c r="DZ17" t="n">
         <v>6</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.78</v>
+        <v>20.8</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="18">
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
@@ -7827,49 +7827,49 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="G18" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="H18" t="n">
-        <v>96.70999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J18" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="K18" t="n">
-        <v>5.29</v>
+        <v>5.38</v>
       </c>
       <c r="L18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M18" t="n">
-        <v>35.57</v>
+        <v>35.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="O18" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>11</v>
+        <v>10.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.86</v>
+        <v>13.12</v>
       </c>
       <c r="R18" t="n">
-        <v>6.43</v>
+        <v>6.75</v>
       </c>
       <c r="S18" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="T18" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7881,28 +7881,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>46.29</v>
+        <v>45.12</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.86</v>
+        <v>15.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.86</v>
+        <v>5.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>19.29</v>
+        <v>20.12</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7986,70 +7986,70 @@
         <v>1.57</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.140000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN18" t="n">
         <v>2</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.07</v>
+        <v>4.47</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT18" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU18" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BV18" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="CC18" t="n">
         <v>3.2</v>
@@ -8061,10 +8061,10 @@
         <v>1.31</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CH18" t="n">
         <v>1.52</v>
@@ -8076,31 +8076,31 @@
         <v>1.65</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL18" t="n">
         <v>1.86</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO18" t="n">
         <v>1.2</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CT18" t="n">
         <v>3.26</v>
@@ -8109,73 +8109,73 @@
         <v>1.53</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="DH18" t="n">
-        <v>102.78</v>
+        <v>100.67</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DO18" t="n">
         <v>3</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.78</v>
+        <v>10.6</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.5</v>
+        <v>11.26</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.29</v>
+        <v>7.4</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8187,28 +8187,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.22</v>
+        <v>48.4</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.08</v>
+        <v>14.94</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.720000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.36</v>
+        <v>5.27</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.22</v>
+        <v>20.6</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="19">
@@ -8218,94 +8218,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F19" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="H19" t="n">
-        <v>84.14</v>
+        <v>81.12</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="K19" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="L19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M19" t="n">
-        <v>42.86</v>
+        <v>41.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="O19" t="n">
         <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>9.710000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.86</v>
+        <v>13.25</v>
       </c>
       <c r="R19" t="n">
-        <v>11.14</v>
+        <v>10.62</v>
       </c>
       <c r="S19" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="T19" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>44.43</v>
+        <v>44.25</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>12</v>
+        <v>12.12</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.29</v>
+        <v>7.38</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.71</v>
+        <v>4.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>12</v>
+        <v>12.12</v>
       </c>
       <c r="AD19" t="n">
         <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8389,70 +8389,70 @@
         <v>0.71</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.36</v>
+        <v>5.53</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BU19" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY19" t="n">
         <v>4.14</v>
       </c>
       <c r="BZ19" t="n">
-        <v>4.26</v>
+        <v>4.29</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.23</v>
+        <v>5.15</v>
       </c>
       <c r="CB19" t="n">
-        <v>5.52</v>
+        <v>5.45</v>
       </c>
       <c r="CC19" t="n">
         <v>8.16</v>
@@ -8467,61 +8467,61 @@
         <v>2.15</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK19" t="n">
         <v>1.37</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM19" t="n">
         <v>2.81</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CO19" t="n">
         <v>1.14</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CT19" t="n">
         <v>3.34</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CX19" t="n">
         <v>1.51</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.44</v>
@@ -8530,88 +8530,88 @@
         <v>2.17</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="DG19" t="n">
         <v>1.93</v>
       </c>
       <c r="DH19" t="n">
-        <v>81.56999999999999</v>
+        <v>80.13</v>
       </c>
       <c r="DI19" t="n">
         <v>-0.14</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM19" t="n">
-        <v>38.14</v>
+        <v>37.87</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DP19" t="n">
-        <v>9.640000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.58</v>
+        <v>11.87</v>
       </c>
       <c r="DR19" t="n">
-        <v>10.64</v>
+        <v>10.4</v>
       </c>
       <c r="DS19" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT19" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.07</v>
+        <v>44.93</v>
       </c>
       <c r="DW19" t="n">
         <v>0</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.57</v>
+        <v>10.73</v>
       </c>
       <c r="DY19" t="n">
-        <v>7</v>
+        <v>7.07</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.57</v>
+        <v>3.67</v>
       </c>
       <c r="EA19" t="n">
-        <v>14.36</v>
+        <v>14.26</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="EC19" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>53.43</v>
+        <v>53.29</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -1460,7 +1460,7 @@
         <v>6.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.71</v>
+        <v>17.86</v>
       </c>
       <c r="AD2" t="n">
         <v>1.96</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.67</v>
+        <v>53.6</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
@@ -1766,7 +1766,7 @@
         <v>6</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.33</v>
+        <v>16.4</v>
       </c>
       <c r="EB2" t="n">
         <v>1.83</v>
@@ -3063,10 +3063,10 @@
         <v>0.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>17</v>
+        <v>17.12</v>
       </c>
       <c r="AA6" t="n">
-        <v>12.12</v>
+        <v>12.25</v>
       </c>
       <c r="AB6" t="n">
         <v>4.88</v>
@@ -3075,7 +3075,7 @@
         <v>16.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE6" t="n">
         <v>2.75</v>
@@ -3369,10 +3369,10 @@
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.6</v>
+        <v>13.66</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.93</v>
+        <v>9</v>
       </c>
       <c r="DZ6" t="n">
         <v>4.67</v>
@@ -3541,25 +3541,25 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>51.75</v>
+        <v>51.88</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.25</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.75</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.38</v>
+        <v>5.5</v>
       </c>
       <c r="BC7" t="n">
         <v>4.38</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.88</v>
+        <v>19.75</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BF7" t="n">
         <v>1.38</v>
@@ -3766,25 +3766,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.07</v>
+        <v>52.14</v>
       </c>
       <c r="DW7" t="n">
         <v>0.13</v>
       </c>
       <c r="DX7" t="n">
-        <v>11</v>
+        <v>11.07</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="DZ7" t="n">
         <v>5.07</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.2</v>
+        <v>18.14</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="EC7" t="n">
         <v>1.27</v>
@@ -5168,7 +5168,7 @@
         <v>3.88</v>
       </c>
       <c r="BD11" t="n">
-        <v>22.75</v>
+        <v>22.88</v>
       </c>
       <c r="BE11" t="n">
         <v>1.43</v>
@@ -5393,7 +5393,7 @@
         <v>4.14</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.93</v>
+        <v>21</v>
       </c>
       <c r="EB11" t="n">
         <v>1.46</v>
@@ -7565,10 +7565,10 @@
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>16.62</v>
+        <v>16.75</v>
       </c>
       <c r="BB17" t="n">
-        <v>10.75</v>
+        <v>10.88</v>
       </c>
       <c r="BC17" t="n">
         <v>5.88</v>
@@ -7577,7 +7577,7 @@
         <v>21.12</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BF17" t="n">
         <v>2.25</v>
@@ -7790,10 +7790,10 @@
         <v>0.14</v>
       </c>
       <c r="DX17" t="n">
-        <v>17.4</v>
+        <v>17.47</v>
       </c>
       <c r="DY17" t="n">
-        <v>11.4</v>
+        <v>11.47</v>
       </c>
       <c r="DZ17" t="n">
         <v>6</v>
@@ -7887,10 +7887,10 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.5</v>
+        <v>15.38</v>
       </c>
       <c r="AA18" t="n">
-        <v>9.880000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="AB18" t="n">
         <v>5.62</v>
@@ -7899,7 +7899,7 @@
         <v>20.12</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE18" t="n">
         <v>0.88</v>
@@ -8193,10 +8193,10 @@
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.94</v>
+        <v>14.87</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.67</v>
+        <v>9.6</v>
       </c>
       <c r="DZ18" t="n">
         <v>5.27</v>
@@ -8205,7 +8205,7 @@
         <v>20.6</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="EC18" t="n">
         <v>1.2</v>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F3" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="G3" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>107.88</v>
+        <v>103.22</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J3" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="K3" t="n">
-        <v>6.12</v>
+        <v>5.78</v>
       </c>
       <c r="L3" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="M3" t="n">
-        <v>59.5</v>
+        <v>55</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O3" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="P3" t="n">
-        <v>10.62</v>
+        <v>10.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.5</v>
+        <v>13.33</v>
       </c>
       <c r="R3" t="n">
-        <v>5.5</v>
+        <v>6.22</v>
       </c>
       <c r="S3" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="T3" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>58.5</v>
+        <v>56.78</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1857,19 +1857,19 @@
         <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.75</v>
+        <v>8.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.88</v>
+        <v>16.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF3" t="n">
         <v>0.14</v>
@@ -1953,37 +1953,37 @@
         <v>2.57</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.4</v>
+        <v>10.69</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="BJ3" t="n">
         <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.2</v>
+        <v>5.56</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,31 +1992,31 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU3" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV3" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX3" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.81</v>
+        <v>4.74</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.99</v>
+        <v>4.92</v>
       </c>
       <c r="CC3" t="n">
         <v>2.33</v>
@@ -2031,16 +2031,16 @@
         <v>2.18</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CH3" t="n">
         <v>1.67</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CK3" t="n">
         <v>1.5</v>
@@ -2052,7 +2052,7 @@
         <v>2.45</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO3" t="n">
         <v>1.13</v>
@@ -2076,43 +2076,43 @@
         <v>1.74</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CX3" t="n">
         <v>1.51</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.46</v>
       </c>
       <c r="DA3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB3" t="n">
         <v>1.16</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="DG3" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="DH3" t="n">
-        <v>102.4</v>
+        <v>100.12</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.06</v>
@@ -2121,61 +2121,61 @@
         <v>2</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.53</v>
+        <v>5.38</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DM3" t="n">
-        <v>54.93</v>
+        <v>52.69</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.06</v>
+        <v>11.13</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13</v>
+        <v>12.94</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.53</v>
+        <v>6.87</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.6</v>
+        <v>56.69</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.53</v>
+        <v>14.56</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.6</v>
+        <v>8.56</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.87</v>
+        <v>16.25</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0.12</v>
@@ -2678,139 +2678,139 @@
         <v>0.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.43</v>
+        <v>4.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>104</v>
+        <v>106.75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>7.14</v>
+        <v>7.75</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>56</v>
+        <v>58.75</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.140000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.29</v>
+        <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.14</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.86</v>
+        <v>2.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>55.57</v>
+        <v>55.75</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA5" t="n">
-        <v>17.29</v>
+        <v>17.38</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.859999999999999</v>
+        <v>10.75</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.43</v>
+        <v>6.62</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.14</v>
+        <v>19.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.93</v>
+        <v>3.81</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.67</v>
+        <v>10.94</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.93</v>
+        <v>3.81</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.27</v>
+        <v>5.19</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BU5" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BV5" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY5" t="n">
         <v>1.44</v>
@@ -2819,16 +2819,16 @@
         <v>1.44</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.13</v>
+        <v>5.05</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.51</v>
+        <v>5.41</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="CE5" t="n">
         <v>1.23</v>
@@ -2837,31 +2837,31 @@
         <v>2.14</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CH5" t="n">
         <v>1.68</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK5" t="n">
         <v>1.42</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP5" t="n">
         <v>1.49</v>
@@ -2882,106 +2882,106 @@
         <v>1.77</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX5" t="n">
         <v>1.54</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.42</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="DB5" t="n">
         <v>1.16</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.47</v>
+        <v>3.88</v>
       </c>
       <c r="DH5" t="n">
-        <v>102.13</v>
+        <v>103.62</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.47</v>
+        <v>7.75</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DM5" t="n">
-        <v>55.67</v>
+        <v>57.06</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO5" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="DP5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.67</v>
+        <v>10.75</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.8</v>
+        <v>6.75</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.8</v>
+        <v>54.94</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>18.94</v>
+        <v>18.88</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.74</v>
+        <v>12.07</v>
       </c>
       <c r="DZ5" t="n">
-        <v>7.2</v>
+        <v>6.81</v>
       </c>
       <c r="EA5" t="n">
-        <v>19</v>
+        <v>19.19</v>
       </c>
       <c r="EB5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0.38</v>
@@ -3081,52 +3081,52 @@
         <v>2.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>89.86</v>
+        <v>93.75</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AT6" t="n">
         <v>2</v>
       </c>
-      <c r="AL6" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>13.57</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AU6" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>45.57</v>
+        <v>48</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.710000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.29</v>
+        <v>5.62</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>19</v>
+        <v>19.75</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BF6" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.6</v>
+        <v>10.81</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP6" t="n">
-        <v>5</v>
+        <v>5.19</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.53</v>
+        <v>5.56</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT6" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX6" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY6" t="n">
         <v>2.87</v>
@@ -3222,22 +3222,22 @@
         <v>2.84</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.08</v>
+        <v>4.03</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="CC6" t="n">
-        <v>6.55</v>
+        <v>6.09</v>
       </c>
       <c r="CD6" t="n">
-        <v>7.35</v>
+        <v>6.76</v>
       </c>
       <c r="CE6" t="n">
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CG6" t="n">
         <v>3.29</v>
@@ -3246,7 +3246,7 @@
         <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.66</v>
@@ -3258,10 +3258,10 @@
         <v>1.78</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
@@ -3285,106 +3285,106 @@
         <v>1.59</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="DB6" t="n">
         <v>1.24</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD6" t="n">
         <v>2.78</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG6" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="DH6" t="n">
-        <v>90.2</v>
+        <v>92.12</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.46</v>
+        <v>4.94</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM6" t="n">
-        <v>39.14</v>
+        <v>40.13</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.8</v>
+        <v>13.75</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.74</v>
+        <v>11.13</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.8</v>
+        <v>47.94</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.66</v>
+        <v>13.5</v>
       </c>
       <c r="DY6" t="n">
-        <v>9</v>
+        <v>8.94</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.67</v>
+        <v>4.56</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.6</v>
+        <v>18.06</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0.29</v>
@@ -3484,139 +3484,139 @@
         <v>1.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AI7" t="n">
-        <v>97.62</v>
+        <v>97.44</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AL7" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>42.75</v>
+        <v>42.67</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.619999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.119999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AU7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>51.22</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BN7" t="n">
         <v>1.62</v>
       </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>51.88</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BO7" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.6</v>
+        <v>4.69</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.47</v>
+        <v>6.25</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT7" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BU7" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV7" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY7" t="n">
         <v>2.96</v>
@@ -3625,22 +3625,22 @@
         <v>3.14</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.14</v>
+        <v>4.19</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.01</v>
+        <v>4.29</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.36</v>
+        <v>4.76</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CG7" t="n">
         <v>3.72</v>
@@ -3649,7 +3649,7 @@
         <v>1.64</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.51</v>
@@ -3661,49 +3661,49 @@
         <v>1.62</v>
       </c>
       <c r="CM7" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CO7" t="n">
         <v>1.14</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CR7" t="n">
         <v>1.34</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CT7" t="n">
         <v>3.31</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CX7" t="n">
         <v>1.44</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.63</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DB7" t="n">
         <v>1.17</v>
@@ -3712,82 +3712,82 @@
         <v>1.55</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="DH7" t="n">
-        <v>96.53</v>
+        <v>96.5</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DM7" t="n">
-        <v>47.2</v>
+        <v>46.88</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.33</v>
+        <v>9.32</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.859999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.14</v>
+        <v>51.75</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.07</v>
+        <v>10.75</v>
       </c>
       <c r="DY7" t="n">
-        <v>6</v>
+        <v>5.87</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.07</v>
+        <v>4.88</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.14</v>
+        <v>18.5</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F8" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="G8" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="H8" t="n">
-        <v>115.43</v>
+        <v>113.12</v>
       </c>
       <c r="I8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J8" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="K8" t="n">
-        <v>6.57</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>0.57</v>
+        <v>1.12</v>
       </c>
       <c r="M8" t="n">
-        <v>49.57</v>
+        <v>51.62</v>
       </c>
       <c r="N8" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O8" t="n">
-        <v>3.29</v>
+        <v>4.25</v>
       </c>
       <c r="P8" t="n">
-        <v>10.86</v>
+        <v>10.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="R8" t="n">
-        <v>6.29</v>
+        <v>6.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="T8" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="U8" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>55.43</v>
+        <v>57</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>17.43</v>
+        <v>18.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.57</v>
+        <v>12.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.29</v>
+        <v>21.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -3968,70 +3968,70 @@
         <v>1.62</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.07</v>
+        <v>10.62</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.87</v>
+        <v>5.31</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.2</v>
+        <v>5.31</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX8" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.01</v>
+        <v>4.07</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="CC8" t="n">
         <v>5.19</v>
@@ -4043,13 +4043,13 @@
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI8" t="n">
         <v>2.06</v>
@@ -4058,37 +4058,37 @@
         <v>1.72</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CO8" t="n">
         <v>1.23</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="CT8" t="n">
         <v>3.2</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CV8" t="n">
         <v>2.12</v>
@@ -4100,97 +4100,97 @@
         <v>1.59</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.31</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="DB8" t="n">
         <v>1.25</v>
       </c>
       <c r="DC8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>106.18</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DJ8" t="n">
         <v>1.82</v>
       </c>
-      <c r="DD8" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>106.8</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>1.93</v>
-      </c>
       <c r="DK8" t="n">
-        <v>5.4</v>
+        <v>6.19</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.47</v>
+        <v>0.75</v>
       </c>
       <c r="DM8" t="n">
-        <v>44.07</v>
+        <v>45.44</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.33</v>
+        <v>11.07</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.87</v>
+        <v>10.82</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.14</v>
+        <v>7.19</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.6</v>
+        <v>51.69</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>16</v>
+        <v>16.62</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.6</v>
+        <v>6.62</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.47</v>
+        <v>21</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0.12</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="AI9" t="n">
-        <v>96</v>
+        <v>96.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AL9" t="n">
-        <v>6.14</v>
+        <v>6.62</v>
       </c>
       <c r="AM9" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AN9" t="n">
-        <v>43.86</v>
+        <v>43.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.29</v>
+        <v>10.25</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.57</v>
+        <v>7.62</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>51.57</v>
+        <v>51.12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.14</v>
+        <v>15.75</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.57</v>
+        <v>10.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.57</v>
+        <v>5.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.43</v>
+        <v>20.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.73</v>
+        <v>11</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.13</v>
+        <v>5.31</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.53</v>
+        <v>5.62</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT9" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU9" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BY9" t="n">
         <v>2.38</v>
@@ -4431,16 +4431,16 @@
         <v>2.3</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.05</v>
+        <v>3.83</v>
       </c>
       <c r="CE9" t="n">
         <v>1.27</v>
@@ -4455,31 +4455,31 @@
         <v>1.6</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK9" t="n">
         <v>1.45</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CN9" t="n">
         <v>2.03</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
@@ -4494,22 +4494,22 @@
         <v>1.63</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.48</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="DB9" t="n">
         <v>1.18</v>
@@ -4518,82 +4518,82 @@
         <v>1.6</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="DE9" t="n">
         <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.13</v>
+        <v>3.31</v>
       </c>
       <c r="DH9" t="n">
-        <v>100.4</v>
+        <v>100.25</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.27</v>
+        <v>6.5</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DM9" t="n">
-        <v>51.4</v>
+        <v>50.75</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.07</v>
+        <v>3.12</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.47</v>
+        <v>11.69</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.73</v>
+        <v>10.68</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.87</v>
+        <v>6.94</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.67</v>
+        <v>51.44</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.8</v>
+        <v>16.06</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.4</v>
+        <v>10.68</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.4</v>
+        <v>5.38</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.2</v>
+        <v>17.88</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0.29</v>
@@ -4696,115 +4696,115 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AH10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>84</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>36.44</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>43.11</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BO10" t="n">
         <v>1.88</v>
       </c>
-      <c r="AI10" t="n">
-        <v>84.88</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>38.62</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>14.38</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>44.25</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BP10" t="n">
-        <v>5.47</v>
+        <v>5.56</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4813,19 +4813,19 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BU10" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV10" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BW10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY10" t="n">
         <v>3.56</v>
@@ -4834,55 +4834,55 @@
         <v>3.76</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.16</v>
+        <v>4.51</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.33</v>
+        <v>4.78</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.15</v>
+        <v>6.35</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.28</v>
+        <v>7.29</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.64</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="CR10" t="n">
         <v>1.34</v>
@@ -4897,7 +4897,7 @@
         <v>1.61</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CW10" t="n">
         <v>1.66</v>
@@ -4906,97 +4906,97 @@
         <v>1.46</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.59</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="DB10" t="n">
         <v>1.19</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DH10" t="n">
-        <v>86.47</v>
+        <v>85.88</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM10" t="n">
-        <v>40.73</v>
+        <v>39.37</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.07</v>
+        <v>12.69</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.27</v>
+        <v>11.25</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.6</v>
+        <v>7.75</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.87</v>
+        <v>43.25</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.93</v>
+        <v>11.87</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.53</v>
+        <v>7.37</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.07</v>
+        <v>17.69</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
@@ -5018,82 +5018,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="G11" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="H11" t="n">
-        <v>79.70999999999999</v>
+        <v>84</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>4.71</v>
+        <v>4.88</v>
       </c>
       <c r="L11" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>42.86</v>
+        <v>42.62</v>
       </c>
       <c r="N11" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="P11" t="n">
-        <v>10.14</v>
+        <v>10.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.29</v>
+        <v>13.12</v>
       </c>
       <c r="R11" t="n">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="U11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>48.43</v>
+        <v>49.38</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.71</v>
+        <v>14</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.289999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.86</v>
+        <v>18.12</v>
       </c>
       <c r="AD11" t="n">
         <v>1.49</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
@@ -5177,70 +5177,70 @@
         <v>1.62</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.07</v>
+        <v>9.19</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BP11" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.07</v>
+        <v>5.12</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT11" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU11" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV11" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX11" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.31</v>
+        <v>3.18</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.43</v>
+        <v>3.33</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.11</v>
+        <v>4.07</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="CC11" t="n">
         <v>5.26</v>
@@ -5252,13 +5252,13 @@
         <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI11" t="n">
         <v>2.15</v>
@@ -5273,19 +5273,19 @@
         <v>1.86</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
@@ -5309,97 +5309,97 @@
         <v>1.53</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA11" t="n">
         <v>1.99</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="DE11" t="n">
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>90.38</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>42.44</v>
+      </c>
+      <c r="DN11" t="n">
         <v>1</v>
       </c>
-      <c r="DG11" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="DH11" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="DI11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DJ11" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DK11" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="DL11" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="DM11" t="n">
-        <v>42.53</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>0.93</v>
-      </c>
       <c r="DO11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.34</v>
+        <v>13.25</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.47</v>
+        <v>7.38</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.53</v>
+        <v>49</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.6</v>
+        <v>13.75</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.470000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.14</v>
+        <v>4.06</v>
       </c>
       <c r="EA11" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="EB11" t="n">
         <v>1.46</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0.29</v>
@@ -5499,52 +5499,52 @@
         <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AI12" t="n">
-        <v>103</v>
+        <v>106.89</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AL12" t="n">
-        <v>5.12</v>
+        <v>5.33</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.62</v>
+        <v>60.44</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.5</v>
+        <v>13.22</v>
       </c>
       <c r="AR12" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="AS12" t="n">
-        <v>6</v>
+        <v>5.78</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>59.75</v>
+        <v>60.56</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA12" t="n">
-        <v>16.38</v>
+        <v>16.33</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.380000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>7</v>
+        <v>7.11</v>
       </c>
       <c r="BD12" t="n">
-        <v>22.38</v>
+        <v>22.11</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.67</v>
+        <v>9.81</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="BJ12" t="n">
         <v>1</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.67</v>
+        <v>4.94</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT12" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BU12" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BV12" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BW12" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BX12" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BY12" t="n">
         <v>2.35</v>
@@ -5643,22 +5643,22 @@
         <v>3.96</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="CE12" t="n">
         <v>1.25</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="CH12" t="n">
         <v>1.62</v>
@@ -5670,25 +5670,25 @@
         <v>1.51</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CR12" t="n">
         <v>1.34</v>
@@ -5703,22 +5703,22 @@
         <v>1.72</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CX12" t="n">
         <v>1.49</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.5</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DB12" t="n">
         <v>1.16</v>
@@ -5727,82 +5727,82 @@
         <v>1.52</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="DH12" t="n">
-        <v>105.07</v>
+        <v>107.13</v>
       </c>
       <c r="DI12" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.53</v>
+        <v>5.62</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="DM12" t="n">
-        <v>52.4</v>
+        <v>53.81</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.66</v>
+        <v>12.56</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.87</v>
+        <v>12.56</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.47</v>
+        <v>5.38</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.27</v>
+        <v>57.88</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX12" t="n">
         <v>15.94</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.07</v>
+        <v>9</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.86</v>
+        <v>6.94</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.33</v>
+        <v>21.25</v>
       </c>
       <c r="EB12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="EC12" t="n">
         <v>1.87</v>
-      </c>
-      <c r="EC12" t="n">
-        <v>1.86</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="F13" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="G13" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="H13" t="n">
-        <v>79.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J13" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="L13" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="M13" t="n">
-        <v>34.29</v>
+        <v>34.75</v>
       </c>
       <c r="N13" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>10.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.43</v>
+        <v>12.5</v>
       </c>
       <c r="R13" t="n">
-        <v>11.14</v>
+        <v>11.25</v>
       </c>
       <c r="S13" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>37.43</v>
+        <v>37.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.57</v>
+        <v>5.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.29</v>
+        <v>17.62</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AF13" t="n">
         <v>0.25</v>
@@ -5983,70 +5983,70 @@
         <v>2.12</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.67</v>
+        <v>9</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="BO13" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.2</v>
+        <v>4.44</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BV13" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.84</v>
+        <v>3.68</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="CC13" t="n">
         <v>5.96</v>
@@ -6061,13 +6061,13 @@
         <v>2.31</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CH13" t="n">
         <v>1.58</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.61</v>
@@ -6076,22 +6076,22 @@
         <v>1.44</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP13" t="n">
         <v>1.6</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6109,70 +6109,70 @@
         <v>2.37</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="DB13" t="n">
         <v>1.19</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DH13" t="n">
-        <v>75.53</v>
+        <v>76.69</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="DK13" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DM13" t="n">
-        <v>31.34</v>
+        <v>31.75</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.2</v>
+        <v>10.63</v>
       </c>
       <c r="DQ13" t="n">
         <v>13.06</v>
       </c>
       <c r="DR13" t="n">
-        <v>11</v>
+        <v>11.07</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>41.6</v>
+        <v>41.18</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX13" t="n">
-        <v>8.470000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.53</v>
+        <v>5.5</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="EA13" t="n">
-        <v>15.87</v>
+        <v>16.12</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F14" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="G14" t="n">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="H14" t="n">
-        <v>121.57</v>
+        <v>119.5</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J14" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="K14" t="n">
-        <v>7.29</v>
+        <v>7.62</v>
       </c>
       <c r="L14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M14" t="n">
-        <v>69.14</v>
+        <v>68.38</v>
       </c>
       <c r="N14" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="O14" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="P14" t="n">
-        <v>10.43</v>
+        <v>10.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.710000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="R14" t="n">
-        <v>6.29</v>
+        <v>6.25</v>
       </c>
       <c r="S14" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="T14" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>63.86</v>
+        <v>64.12</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.29</v>
+        <v>21.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.57</v>
+        <v>13.62</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.71</v>
+        <v>7.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.14</v>
+        <v>18.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="AF14" t="n">
         <v>0.25</v>
@@ -6386,70 +6386,70 @@
         <v>1.62</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.47</v>
+        <v>10.69</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BL14" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.4</v>
+        <v>4.56</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.07</v>
+        <v>6.12</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT14" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BU14" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BV14" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BW14" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BX14" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.42</v>
+        <v>6.63</v>
       </c>
       <c r="CB14" t="n">
-        <v>6.96</v>
+        <v>7.24</v>
       </c>
       <c r="CC14" t="n">
         <v>1.75</v>
@@ -6461,40 +6461,40 @@
         <v>1.16</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.55</v>
+        <v>4.62</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CO14" t="n">
         <v>1.06</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CQ14" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
@@ -6505,102 +6505,102 @@
         <v>1.99</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CW14" t="n">
         <v>1.6</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="DB14" t="n">
         <v>1.11</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="DH14" t="n">
-        <v>108.14</v>
+        <v>107.94</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DK14" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM14" t="n">
-        <v>58.73</v>
+        <v>59</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.6</v>
+        <v>10.68</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.93</v>
+        <v>8.68</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.4</v>
+        <v>7.32</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.67</v>
+        <v>60.06</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>17.6</v>
+        <v>17.82</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.4</v>
+        <v>10.62</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7.2</v>
+        <v>7.18</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.73</v>
+        <v>17.81</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="15">
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -6622,82 +6622,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="G15" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="H15" t="n">
-        <v>92.12</v>
+        <v>93.33</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="K15" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="L15" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="M15" t="n">
-        <v>41.88</v>
+        <v>41.78</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="P15" t="n">
-        <v>8.119999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>10.56</v>
       </c>
       <c r="R15" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="S15" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>44</v>
+        <v>44.89</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.5</v>
+        <v>11.44</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.38</v>
+        <v>7.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="AC15" t="n">
-        <v>14.88</v>
+        <v>15.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6784,67 +6784,67 @@
         <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.33</v>
+        <v>11.56</v>
       </c>
       <c r="BI15" t="n">
         <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.53</v>
+        <v>4.75</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.8</v>
+        <v>6.81</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT15" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV15" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW15" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BX15" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="CC15" t="n">
         <v>4.56</v>
@@ -6853,7 +6853,7 @@
         <v>4.97</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF15" t="n">
         <v>2.3</v>
@@ -6865,10 +6865,10 @@
         <v>1.56</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CK15" t="n">
         <v>1.35</v>
@@ -6877,7 +6877,7 @@
         <v>1.74</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CN15" t="n">
         <v>2.14</v>
@@ -6886,10 +6886,10 @@
         <v>1.18</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
@@ -6904,18 +6904,18 @@
         <v>1.62</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CW15" t="n">
         <v>1.58</v>
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ15" t="inlineStr"/>
       <c r="DA15" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DB15" t="n">
         <v>1.19</v>
@@ -6924,82 +6924,82 @@
         <v>1.63</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DH15" t="n">
-        <v>88.86</v>
+        <v>89.75</v>
       </c>
       <c r="DI15" t="n">
         <v>0</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="DK15" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>45</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="DZ15" t="n">
         <v>4.06</v>
       </c>
-      <c r="DL15" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="DM15" t="n">
-        <v>41.74</v>
-      </c>
-      <c r="DN15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DO15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="DP15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="DQ15" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="DR15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="DS15" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DT15" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV15" t="n">
-        <v>44.53</v>
-      </c>
-      <c r="DW15" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DX15" t="n">
-        <v>12.34</v>
-      </c>
-      <c r="DY15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="DZ15" t="n">
-        <v>4.13</v>
-      </c>
       <c r="EA15" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="16">
@@ -7009,61 +7009,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F16" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="G16" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="H16" t="n">
-        <v>86.62</v>
+        <v>83.11</v>
       </c>
       <c r="I16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="K16" t="n">
-        <v>5.25</v>
+        <v>5.22</v>
       </c>
       <c r="L16" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="M16" t="n">
-        <v>48.38</v>
+        <v>45.11</v>
       </c>
       <c r="N16" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>10.62</v>
+        <v>10.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.38</v>
+        <v>11.22</v>
       </c>
       <c r="R16" t="n">
-        <v>7</v>
+        <v>7.11</v>
       </c>
       <c r="S16" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="T16" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7075,28 +7075,28 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>47.38</v>
+        <v>45.78</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.5</v>
+        <v>14.89</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.380000000000001</v>
+        <v>9</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.12</v>
+        <v>5.89</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.38</v>
+        <v>19.22</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7180,70 +7180,70 @@
         <v>1.71</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.2</v>
+        <v>11.25</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.53</v>
+        <v>5.75</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS16" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT16" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV16" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY16" t="n">
         <v>3.04</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.77</v>
+        <v>4.71</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.96</v>
+        <v>4.9</v>
       </c>
       <c r="CC16" t="n">
         <v>9.98</v>
@@ -7255,37 +7255,37 @@
         <v>1.26</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="CH16" t="n">
         <v>1.61</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ16" t="n">
         <v>2.34</v>
@@ -7294,19 +7294,19 @@
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CT16" t="n">
         <v>3.3</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
@@ -7318,55 +7318,55 @@
         <v>2.37</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DB16" t="n">
         <v>1.19</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="DG16" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DH16" t="n">
-        <v>83.2</v>
+        <v>81.44</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.07</v>
+        <v>5.06</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DM16" t="n">
-        <v>43.47</v>
+        <v>41.94</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.73</v>
+        <v>10.56</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.87</v>
+        <v>10.81</v>
       </c>
       <c r="DR16" t="n">
         <v>8</v>
@@ -7381,28 +7381,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.87</v>
+        <v>44.13</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.54</v>
+        <v>13.32</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.73</v>
+        <v>4.69</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.54</v>
+        <v>18.5</v>
       </c>
       <c r="EB16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="EC16" t="n">
         <v>1.5</v>
-      </c>
-      <c r="EC16" t="n">
-        <v>1.6</v>
       </c>
     </row>
     <row r="17">
@@ -7412,94 +7412,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="H17" t="n">
-        <v>123.14</v>
+        <v>121</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.43</v>
+        <v>5.12</v>
       </c>
       <c r="L17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M17" t="n">
-        <v>64.14</v>
+        <v>62.88</v>
       </c>
       <c r="N17" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>11.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.43</v>
+        <v>10.12</v>
       </c>
       <c r="R17" t="n">
-        <v>6.29</v>
+        <v>6</v>
       </c>
       <c r="S17" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>57.57</v>
+        <v>57.12</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.29</v>
+        <v>18.88</v>
       </c>
       <c r="AA17" t="n">
-        <v>12.14</v>
+        <v>12.62</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.14</v>
+        <v>6.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.43</v>
+        <v>20.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7583,70 +7583,70 @@
         <v>2.25</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.529999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL17" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BN17" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.53</v>
+        <v>4.62</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="BR17" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS17" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT17" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV17" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW17" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="CC17" t="n">
         <v>2.25</v>
@@ -7655,73 +7655,73 @@
         <v>2.33</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CK17" t="n">
         <v>1.47</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CN17" t="n">
         <v>1.94</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CR17" t="n">
         <v>1.35</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CT17" t="n">
         <v>3.31</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX17" t="n">
         <v>1.54</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.41</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DB17" t="n">
         <v>1.2</v>
@@ -7730,82 +7730,82 @@
         <v>1.66</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DH17" t="n">
-        <v>107.4</v>
+        <v>107.31</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.93</v>
+        <v>4.81</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM17" t="n">
-        <v>56.8</v>
+        <v>56.63</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.53</v>
+        <v>12.19</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.94</v>
+        <v>6.75</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>55.07</v>
+        <v>55</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>17.47</v>
+        <v>17.81</v>
       </c>
       <c r="DY17" t="n">
-        <v>11.47</v>
+        <v>11.75</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6</v>
+        <v>6.06</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.8</v>
+        <v>20.81</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="18">
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7908,49 +7908,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AI18" t="n">
-        <v>108.86</v>
+        <v>107.12</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
         <v>5</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN18" t="n">
-        <v>43.43</v>
+        <v>40.38</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.57</v>
+        <v>10.75</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.140000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7962,82 +7962,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>52.14</v>
+        <v>51.12</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>14.29</v>
+        <v>13.88</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.43</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="BD18" t="n">
-        <v>21.14</v>
+        <v>20.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.470000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN18" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BP18" t="n">
         <v>5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT18" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU18" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV18" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY18" t="n">
         <v>1.91</v>
@@ -8046,28 +8046,28 @@
         <v>1.94</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI18" t="n">
         <v>2.17</v>
@@ -8082,19 +8082,19 @@
         <v>1.86</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CO18" t="n">
         <v>1.2</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8109,73 +8109,73 @@
         <v>1.53</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX18" t="n">
         <v>1.5</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DB18" t="n">
         <v>1.23</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="DH18" t="n">
-        <v>100.67</v>
+        <v>100.31</v>
       </c>
       <c r="DI18" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.2</v>
+        <v>37.94</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="DO18" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.6</v>
+        <v>10.68</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.26</v>
+        <v>11.18</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.4</v>
+        <v>7.44</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8187,28 +8187,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.4</v>
+        <v>48.12</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.87</v>
+        <v>14.63</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.6</v>
+        <v>9.32</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.27</v>
+        <v>5.31</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.6</v>
+        <v>20.31</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="19">
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0.12</v>
@@ -8311,49 +8311,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AI19" t="n">
-        <v>79</v>
+        <v>75.75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0.29</v>
+        <v>-0.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>33.43</v>
+        <v>31.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.57</v>
+        <v>9.75</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.29</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.14</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8365,82 +8365,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>45.71</v>
+        <v>44</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.140000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.71</v>
+        <v>6.25</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="BD19" t="n">
-        <v>16.71</v>
+        <v>16.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="BH19" t="n">
-        <v>10</v>
+        <v>10.56</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.53</v>
+        <v>5.94</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.47</v>
+        <v>4.62</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT19" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BU19" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV19" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BY19" t="n">
         <v>4.14</v>
@@ -8449,16 +8449,16 @@
         <v>4.29</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="CB19" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="CC19" t="n">
-        <v>8.16</v>
+        <v>8.07</v>
       </c>
       <c r="CD19" t="n">
-        <v>9.18</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="CE19" t="n">
         <v>1.23</v>
@@ -8467,13 +8467,13 @@
         <v>2.15</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.61</v>
@@ -8497,25 +8497,25 @@
         <v>1.52</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CT19" t="n">
         <v>3.34</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX19" t="n">
         <v>1.51</v>
@@ -8533,52 +8533,52 @@
         <v>1.16</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DE19" t="n">
         <v>0.06</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="DH19" t="n">
-        <v>80.13</v>
+        <v>78.44</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.73</v>
+        <v>3.56</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM19" t="n">
-        <v>37.87</v>
+        <v>36.62</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="DP19" t="n">
-        <v>9.470000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.87</v>
+        <v>11.57</v>
       </c>
       <c r="DR19" t="n">
-        <v>10.4</v>
+        <v>10.25</v>
       </c>
       <c r="DS19" t="n">
         <v>0.06</v>
@@ -8590,25 +8590,25 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>44.93</v>
+        <v>44.12</v>
       </c>
       <c r="DW19" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.73</v>
+        <v>10.31</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.07</v>
+        <v>6.82</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="EA19" t="n">
-        <v>14.26</v>
+        <v>14.31</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="EC19" t="n">
         <v>1</v>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -3523,7 +3523,7 @@
         <v>8.33</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.220000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="AT7" t="n">
         <v>2.11</v>
@@ -3556,7 +3556,7 @@
         <v>4.11</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.22</v>
+        <v>20.33</v>
       </c>
       <c r="BE7" t="n">
         <v>1.2</v>
@@ -3754,7 +3754,7 @@
         <v>9.619999999999999</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.94</v>
+        <v>9</v>
       </c>
       <c r="DS7" t="n">
         <v>0.06</v>
@@ -3781,7 +3781,7 @@
         <v>4.88</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.5</v>
+        <v>18.56</v>
       </c>
       <c r="EB7" t="n">
         <v>1.36</v>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>51.12</v>
+        <v>51</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.12</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.44</v>
+        <v>51.38</v>
       </c>
       <c r="DW9" t="n">
         <v>0.12</v>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>60.56</v>
+        <v>60.67</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.22</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.88</v>
+        <v>57.94</v>
       </c>
       <c r="DW12" t="n">
         <v>0.12</v>
@@ -6290,16 +6290,16 @@
         <v>21.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.62</v>
+        <v>13.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.62</v>
+        <v>7.5</v>
       </c>
       <c r="AC14" t="n">
         <v>18.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AE14" t="n">
         <v>0.88</v>
@@ -6588,16 +6588,16 @@
         <v>17.82</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.62</v>
+        <v>10.68</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7.18</v>
+        <v>7.12</v>
       </c>
       <c r="EA14" t="n">
         <v>17.81</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="EC14" t="n">
         <v>1.25</v>
@@ -6676,7 +6676,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>44.89</v>
+        <v>45</v>
       </c>
       <c r="Y15" t="n">
         <v>0.11</v>
@@ -6978,7 +6978,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45</v>
+        <v>45.06</v>
       </c>
       <c r="DW15" t="n">
         <v>0.12</v>
@@ -7075,7 +7075,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>45.78</v>
+        <v>45.67</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -7381,7 +7381,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.13</v>
+        <v>44.06</v>
       </c>
       <c r="DW16" t="n">
         <v>0.06</v>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0.29</v>
@@ -1469,139 +1469,139 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.88</v>
+        <v>3.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>100</v>
+        <v>99.56</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.62</v>
+        <v>5.89</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AN2" t="n">
-        <v>45.88</v>
+        <v>47.33</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.75</v>
+        <v>11.67</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.25</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>7.44</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AU2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>1.25</v>
       </c>
-      <c r="AV2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>53.88</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BK2" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.87</v>
+        <v>4.75</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.67</v>
+        <v>5.94</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT2" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BU2" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BV2" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BX2" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BY2" t="n">
         <v>1.78</v>
@@ -1610,40 +1610,40 @@
         <v>1.85</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.43</v>
+        <v>4.42</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="CE2" t="n">
         <v>1.24</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CH2" t="n">
         <v>1.64</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.56</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM2" t="n">
         <v>2.54</v>
@@ -1658,13 +1658,13 @@
         <v>1.5</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CR2" t="n">
         <v>1.33</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CT2" t="n">
         <v>3.32</v>
@@ -1673,7 +1673,7 @@
         <v>1.7</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CW2" t="n">
         <v>1.6</v>
@@ -1685,7 +1685,7 @@
         <v>1.79</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DA2" t="n">
         <v>2.02</v>
@@ -1697,82 +1697,82 @@
         <v>1.52</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.34</v>
+        <v>3.56</v>
       </c>
       <c r="DH2" t="n">
-        <v>102.47</v>
+        <v>102.07</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.2</v>
+        <v>6.31</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.27</v>
+        <v>49.87</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.27</v>
+        <v>10.31</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.33</v>
+        <v>10.75</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.6</v>
+        <v>7.31</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.6</v>
+        <v>54.38</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.6</v>
+        <v>16.87</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.6</v>
+        <v>10.68</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6</v>
+        <v>6.19</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.4</v>
+        <v>16.38</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0.11</v>
@@ -1872,118 +1872,118 @@
         <v>1.44</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>95.12</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP3" t="n">
         <v>2</v>
       </c>
-      <c r="AH3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>96.14</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>49.71</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>11.57</v>
+        <v>11.12</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.43</v>
+        <v>11.88</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.71</v>
+        <v>7.62</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>56.57</v>
+        <v>57.12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA3" t="n">
-        <v>14</v>
+        <v>14.62</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.43</v>
+        <v>8.75</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.57</v>
+        <v>5.88</v>
       </c>
       <c r="BD3" t="n">
-        <v>15.71</v>
+        <v>16.12</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.69</v>
+        <v>10.53</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="BJ3" t="n">
         <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.12</v>
+        <v>4.88</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.56</v>
+        <v>5.65</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,19 +1992,19 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU3" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BV3" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX3" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BY3" t="n">
         <v>1.67</v>
@@ -2013,16 +2013,16 @@
         <v>1.69</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.74</v>
+        <v>4.69</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.92</v>
+        <v>4.87</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="CE3" t="n">
         <v>1.24</v>
@@ -2034,19 +2034,19 @@
         <v>3.76</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK3" t="n">
         <v>1.5</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM3" t="n">
         <v>2.45</v>
@@ -2061,7 +2061,7 @@
         <v>1.49</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
@@ -2076,22 +2076,22 @@
         <v>1.74</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CX3" t="n">
         <v>1.51</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.46</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB3" t="n">
         <v>1.16</v>
@@ -2100,49 +2100,49 @@
         <v>1.51</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.87</v>
+        <v>3.06</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.12</v>
+        <v>99.41</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.38</v>
+        <v>5.47</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DM3" t="n">
-        <v>52.69</v>
+        <v>53.24</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.13</v>
+        <v>10.94</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.94</v>
+        <v>12.65</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.87</v>
+        <v>6.88</v>
       </c>
       <c r="DS3" t="n">
         <v>0.06</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>56.69</v>
+        <v>56.94</v>
       </c>
       <c r="DW3" t="n">
         <v>0.06</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.56</v>
+        <v>14.82</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.56</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6</v>
+        <v>6.12</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.25</v>
+        <v>16.41</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G4" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
-        <v>92.12</v>
+        <v>92.22</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="L4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>33.12</v>
+        <v>33.89</v>
       </c>
       <c r="N4" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="P4" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.25</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>10.25</v>
+        <v>10.22</v>
       </c>
       <c r="S4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T4" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="U4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>43.88</v>
+        <v>44.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>12</v>
+        <v>12.11</v>
       </c>
       <c r="AA4" t="n">
-        <v>8</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AB4" t="n">
         <v>4</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.12</v>
+        <v>17</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF4" t="n">
         <v>0.14</v>
@@ -2356,70 +2356,70 @@
         <v>1.57</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.6</v>
+        <v>9.25</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.53</v>
+        <v>4.25</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT4" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV4" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>3.56</v>
       </c>
-      <c r="BZ4" t="n">
-        <v>3.74</v>
-      </c>
       <c r="CA4" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
       <c r="CC4" t="n">
         <v>4.69</v>
@@ -2431,13 +2431,13 @@
         <v>1.27</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI4" t="n">
         <v>2.33</v>
@@ -2446,31 +2446,31 @@
         <v>1.57</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CN4" t="n">
         <v>2.05</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CT4" t="n">
         <v>3.3</v>
@@ -2485,13 +2485,13 @@
         <v>1.58</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CY4" t="n">
         <v>1.78</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DA4" t="n">
         <v>2.03</v>
@@ -2500,85 +2500,85 @@
         <v>1.18</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DD4" t="n">
         <v>2.48</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="DH4" t="n">
-        <v>90.66</v>
+        <v>90.81</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.14</v>
+        <v>4.06</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM4" t="n">
-        <v>38.13</v>
+        <v>38.25</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="DO4" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="DP4" t="n">
-        <v>14</v>
+        <v>13.94</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.06</v>
+        <v>8.94</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.34</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.07</v>
+        <v>44.31</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.07</v>
+        <v>12.12</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.8</v>
+        <v>7.87</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.26</v>
+        <v>17.19</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F5" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="H5" t="n">
-        <v>100.5</v>
+        <v>99.11</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="K5" t="n">
-        <v>7.75</v>
+        <v>7.67</v>
       </c>
       <c r="L5" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="M5" t="n">
-        <v>55.38</v>
+        <v>53.22</v>
       </c>
       <c r="N5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="O5" t="n">
-        <v>4.25</v>
+        <v>3.89</v>
       </c>
       <c r="P5" t="n">
-        <v>9.25</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="Q5" t="n">
         <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="S5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="U5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>54.12</v>
+        <v>53.22</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>20.38</v>
+        <v>19.22</v>
       </c>
       <c r="AA5" t="n">
-        <v>13.38</v>
+        <v>12.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.88</v>
+        <v>18.56</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AF5" t="n">
         <v>0.12</v>
@@ -2759,70 +2759,70 @@
         <v>2.12</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.81</v>
+        <v>3.71</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.94</v>
+        <v>11.41</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.81</v>
+        <v>3.71</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BL5" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.19</v>
+        <v>5.29</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.75</v>
+        <v>6.12</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BV5" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BW5" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BX5" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.05</v>
+        <v>4.99</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.41</v>
+        <v>5.34</v>
       </c>
       <c r="CC5" t="n">
         <v>1.81</v>
@@ -2837,7 +2837,7 @@
         <v>2.14</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="CH5" t="n">
         <v>1.68</v>
@@ -2846,19 +2846,19 @@
         <v>2.22</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL5" t="n">
         <v>1.8</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO5" t="n">
         <v>1.14</v>
@@ -2873,31 +2873,31 @@
         <v>1.33</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CT5" t="n">
         <v>3.32</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CV5" t="n">
         <v>2.32</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.42</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DB5" t="n">
         <v>1.16</v>
@@ -2906,82 +2906,82 @@
         <v>1.5</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="DH5" t="n">
-        <v>103.62</v>
+        <v>102.71</v>
       </c>
       <c r="DI5" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.75</v>
+        <v>7.71</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DM5" t="n">
-        <v>57.06</v>
+        <v>55.82</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.88</v>
+        <v>3.71</v>
       </c>
       <c r="DP5" t="n">
-        <v>9.380000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.75</v>
+        <v>10.76</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.75</v>
+        <v>6.83</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.94</v>
+        <v>54.41</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DX5" t="n">
-        <v>18.88</v>
+        <v>18.35</v>
       </c>
       <c r="DY5" t="n">
-        <v>12.07</v>
+        <v>11.71</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.81</v>
+        <v>6.65</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.19</v>
+        <v>19</v>
       </c>
       <c r="EB5" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="6">
@@ -2991,25 +2991,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="F6" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="G6" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="H6" t="n">
-        <v>90.5</v>
+        <v>89</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3018,67 +3018,67 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>5.62</v>
+        <v>5.56</v>
       </c>
       <c r="L6" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="M6" t="n">
-        <v>45.38</v>
+        <v>43.11</v>
       </c>
       <c r="N6" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>14</v>
+        <v>14.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.88</v>
+        <v>10.89</v>
       </c>
       <c r="R6" t="n">
-        <v>6.25</v>
+        <v>6.78</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>47.88</v>
+        <v>46.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z6" t="n">
-        <v>17.12</v>
+        <v>16.89</v>
       </c>
       <c r="AA6" t="n">
-        <v>12.25</v>
+        <v>11.89</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="AC6" t="n">
-        <v>16.38</v>
+        <v>15.89</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AF6" t="n">
         <v>0.12</v>
@@ -3162,67 +3162,67 @@
         <v>2.12</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.81</v>
+        <v>10.94</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BM6" t="n">
         <v>0.88</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.19</v>
+        <v>5.06</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.56</v>
+        <v>5.82</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU6" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BV6" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BX6" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.87</v>
+        <v>3.09</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.84</v>
+        <v>3.04</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="CB6" t="n">
         <v>4.26</v>
@@ -3234,28 +3234,28 @@
         <v>6.76</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF6" t="n">
         <v>2.45</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CI6" t="n">
         <v>2.17</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CM6" t="n">
         <v>2.66</v>
@@ -3264,19 +3264,19 @@
         <v>2.02</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CT6" t="n">
         <v>3.15</v>
@@ -3291,67 +3291,67 @@
         <v>1.68</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY6" t="n">
         <v>1.78</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DA6" t="n">
         <v>2.04</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="DH6" t="n">
-        <v>92.12</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="DK6" t="n">
         <v>4.94</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.13</v>
+        <v>39.24</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.13</v>
+        <v>11.12</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.5</v>
+        <v>7.71</v>
       </c>
       <c r="DS6" t="n">
         <v>0.12</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.94</v>
+        <v>47.12</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.5</v>
+        <v>13.59</v>
       </c>
       <c r="DY6" t="n">
         <v>8.94</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.56</v>
+        <v>4.65</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.06</v>
+        <v>17.71</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F7" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="G7" t="n">
-        <v>3.86</v>
+        <v>3.38</v>
       </c>
       <c r="H7" t="n">
-        <v>95.29000000000001</v>
+        <v>94.25</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="K7" t="n">
-        <v>6.86</v>
+        <v>6.12</v>
       </c>
       <c r="L7" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>52.29</v>
+        <v>50.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.29</v>
+        <v>11.5</v>
       </c>
       <c r="R7" t="n">
-        <v>8.57</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="U7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52.43</v>
+        <v>51.75</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.43</v>
+        <v>11.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.57</v>
+        <v>6.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.86</v>
+        <v>5.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.29</v>
+        <v>16.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF7" t="n">
         <v>0.22</v>
@@ -3565,70 +3565,70 @@
         <v>1.56</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.31</v>
+        <v>3.24</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.06</v>
+        <v>10.94</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.31</v>
+        <v>3.24</v>
       </c>
       <c r="BJ7" t="n">
         <v>1</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.69</v>
+        <v>4.76</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.25</v>
+        <v>6.06</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT7" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV7" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW7" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX7" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.19</v>
+        <v>4.13</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.35</v>
+        <v>4.31</v>
       </c>
       <c r="CC7" t="n">
         <v>4.29</v>
@@ -3637,22 +3637,22 @@
         <v>4.76</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CK7" t="n">
         <v>1.34</v>
@@ -3661,7 +3661,7 @@
         <v>1.62</v>
       </c>
       <c r="CM7" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CN7" t="n">
         <v>2.21</v>
@@ -3670,10 +3670,10 @@
         <v>1.14</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CR7" t="n">
         <v>1.34</v>
@@ -3688,7 +3688,7 @@
         <v>1.72</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CW7" t="n">
         <v>1.55</v>
@@ -3706,55 +3706,55 @@
         <v>2.21</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="DH7" t="n">
-        <v>96.5</v>
+        <v>95.94</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.38</v>
+        <v>5.11</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.88</v>
+        <v>46.35</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.32</v>
+        <v>9.35</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.619999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="DR7" t="n">
-        <v>9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0.06</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.75</v>
+        <v>51.47</v>
       </c>
       <c r="DW7" t="n">
         <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.75</v>
+        <v>10.59</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.87</v>
+        <v>5.82</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.88</v>
+        <v>4.76</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.56</v>
+        <v>18.71</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0.12</v>
@@ -3887,139 +3887,139 @@
         <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AI8" t="n">
-        <v>99.25</v>
+        <v>100.67</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.38</v>
+        <v>4.78</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>39.25</v>
+        <v>39.33</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.75</v>
+        <v>11.89</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.25</v>
+        <v>11.11</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.88</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>46.38</v>
+        <v>47.11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA8" t="n">
-        <v>14.75</v>
+        <v>14.67</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.5</v>
+        <v>7.89</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.25</v>
+        <v>6.78</v>
       </c>
       <c r="BD8" t="n">
-        <v>20.75</v>
+        <v>20.67</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.62</v>
+        <v>10.53</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.31</v>
+        <v>5.18</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU8" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV8" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX8" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY8" t="n">
         <v>2.08</v>
@@ -4028,22 +4028,22 @@
         <v>2.17</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.07</v>
+        <v>4.03</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="CC8" t="n">
-        <v>5.19</v>
+        <v>4.87</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.22</v>
+        <v>4.88</v>
       </c>
       <c r="CE8" t="n">
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CG8" t="n">
         <v>3.22</v>
@@ -4052,31 +4052,31 @@
         <v>1.5</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP8" t="n">
         <v>1.74</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4091,25 +4091,25 @@
         <v>1.52</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX8" t="n">
         <v>1.59</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.31</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DC8" t="n">
         <v>1.8</v>
@@ -4118,46 +4118,46 @@
         <v>2.94</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DG8" t="n">
         <v>2.94</v>
       </c>
       <c r="DH8" t="n">
-        <v>106.18</v>
+        <v>106.53</v>
       </c>
       <c r="DI8" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.19</v>
+        <v>6.3</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="DM8" t="n">
-        <v>45.44</v>
+        <v>45.11</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.07</v>
+        <v>11.18</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.82</v>
+        <v>10.77</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.19</v>
+        <v>7.29</v>
       </c>
       <c r="DS8" t="n">
         <v>0.18</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.69</v>
+        <v>51.76</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.62</v>
+        <v>16.47</v>
       </c>
       <c r="DY8" t="n">
-        <v>10</v>
+        <v>10.06</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.62</v>
+        <v>6.41</v>
       </c>
       <c r="EA8" t="n">
-        <v>21</v>
+        <v>20.94</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0.12</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="AI9" t="n">
-        <v>96.25</v>
+        <v>97</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AL9" t="n">
-        <v>6.62</v>
+        <v>6.33</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AN9" t="n">
-        <v>43.5</v>
+        <v>43.44</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14</v>
+        <v>13.44</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.25</v>
+        <v>10.33</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.62</v>
+        <v>7.33</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>51</v>
+        <v>51.78</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.75</v>
+        <v>15.67</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.25</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.5</v>
+        <v>5.78</v>
       </c>
       <c r="BD9" t="n">
-        <v>20.5</v>
+        <v>20.11</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BH9" t="n">
-        <v>11</v>
+        <v>10.82</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.31</v>
+        <v>5.29</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.62</v>
+        <v>5.47</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT9" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BU9" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV9" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX9" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BY9" t="n">
         <v>2.38</v>
@@ -4431,16 +4431,16 @@
         <v>2.3</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.83</v>
+        <v>3.63</v>
       </c>
       <c r="CE9" t="n">
         <v>1.27</v>
@@ -4449,7 +4449,7 @@
         <v>2.28</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CH9" t="n">
         <v>1.6</v>
@@ -4461,25 +4461,25 @@
         <v>1.56</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CO9" t="n">
         <v>1.16</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
@@ -4494,7 +4494,7 @@
         <v>1.63</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CW9" t="n">
         <v>1.56</v>
@@ -4503,7 +4503,7 @@
         <v>1.5</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.48</v>
@@ -4524,76 +4524,76 @@
         <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.31</v>
+        <v>3.18</v>
       </c>
       <c r="DH9" t="n">
-        <v>100.25</v>
+        <v>100.41</v>
       </c>
       <c r="DI9" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="DL9" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DM9" t="n">
-        <v>50.75</v>
+        <v>50.29</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO9" t="n">
         <v>3.12</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.69</v>
+        <v>11.53</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.68</v>
+        <v>10.7</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.94</v>
+        <v>6.82</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.38</v>
+        <v>51.77</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX9" t="n">
-        <v>16.06</v>
+        <v>16</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.68</v>
+        <v>10.47</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.38</v>
+        <v>5.53</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.88</v>
+        <v>17.82</v>
       </c>
       <c r="EB9" t="n">
         <v>1.76</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F10" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="G10" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="H10" t="n">
-        <v>88.29000000000001</v>
+        <v>87.12</v>
       </c>
       <c r="I10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J10" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="K10" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M10" t="n">
-        <v>43.14</v>
+        <v>42.25</v>
       </c>
       <c r="N10" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="P10" t="n">
-        <v>11.57</v>
+        <v>11.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.86</v>
+        <v>11.5</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>7.12</v>
       </c>
       <c r="S10" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>43.43</v>
+        <v>43.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.57</v>
+        <v>14.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.57</v>
+        <v>6</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.86</v>
+        <v>15.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,37 +4774,37 @@
         <v>2.44</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="BH10" t="n">
-        <v>11.06</v>
+        <v>10.88</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.56</v>
+        <v>5.53</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4813,31 +4813,31 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BU10" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV10" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW10" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BX10" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.51</v>
+        <v>4.47</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.78</v>
+        <v>4.72</v>
       </c>
       <c r="CC10" t="n">
         <v>6.35</v>
@@ -4849,28 +4849,28 @@
         <v>1.27</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CH10" t="n">
         <v>1.6</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL10" t="n">
         <v>1.67</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CN10" t="n">
         <v>2.18</v>
@@ -4897,10 +4897,10 @@
         <v>1.61</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX10" t="n">
         <v>1.46</v>
@@ -4912,7 +4912,7 @@
         <v>2.59</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DB10" t="n">
         <v>1.19</v>
@@ -4924,79 +4924,79 @@
         <v>2.49</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DH10" t="n">
-        <v>85.88</v>
+        <v>85.47</v>
       </c>
       <c r="DI10" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.37</v>
+        <v>39.17</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.69</v>
+        <v>12.65</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.25</v>
+        <v>11.12</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.75</v>
+        <v>7.76</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.25</v>
+        <v>43.18</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.87</v>
+        <v>11.64</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.37</v>
+        <v>7.29</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.69</v>
+        <v>17.29</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="EC10" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="11">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
@@ -5018,82 +5018,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="H11" t="n">
-        <v>84</v>
+        <v>87.11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>4.88</v>
+        <v>5.22</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="M11" t="n">
-        <v>42.62</v>
+        <v>43.67</v>
       </c>
       <c r="N11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>13.12</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.12</v>
-      </c>
       <c r="U11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49.38</v>
+        <v>50.78</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>14</v>
+        <v>13.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.75</v>
+        <v>9.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.12</v>
+        <v>17.56</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
@@ -5177,70 +5177,70 @@
         <v>1.62</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.19</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.12</v>
+        <v>5.06</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU11" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX11" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.18</v>
+        <v>3.03</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.33</v>
+        <v>3.16</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="CC11" t="n">
         <v>5.26</v>
@@ -5249,13 +5249,13 @@
         <v>5.53</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CH11" t="n">
         <v>1.52</v>
@@ -5267,40 +5267,40 @@
         <v>1.67</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL11" t="n">
         <v>1.86</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CO11" t="n">
         <v>1.2</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CQ11" t="n">
         <v>2.69</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CU11" t="n">
         <v>1.54</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW11" t="n">
         <v>1.7</v>
@@ -5309,13 +5309,13 @@
         <v>1.53</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.43</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB11" t="n">
         <v>1.22</v>
@@ -5324,82 +5324,82 @@
         <v>1.71</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DE11" t="n">
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DH11" t="n">
-        <v>90.38</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ11" t="n">
         <v>2.12</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.32</v>
+        <v>5.47</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.44</v>
+        <v>43</v>
       </c>
       <c r="DN11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.5</v>
+        <v>11.47</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.25</v>
+        <v>13.41</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.38</v>
+        <v>7.47</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49</v>
+        <v>49.76</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.75</v>
+        <v>13.59</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.68</v>
+        <v>9.65</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.5</v>
+        <v>20.06</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="F12" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="G12" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="H12" t="n">
-        <v>107.43</v>
+        <v>105.62</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>5.38</v>
       </c>
       <c r="L12" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M12" t="n">
-        <v>45.29</v>
+        <v>46.38</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="P12" t="n">
-        <v>11.71</v>
+        <v>11.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.57</v>
+        <v>14.62</v>
       </c>
       <c r="R12" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>54.43</v>
+        <v>52.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.43</v>
+        <v>15.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.710000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.71</v>
+        <v>6.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.14</v>
+        <v>19.75</v>
       </c>
       <c r="AD12" t="n">
         <v>1.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
         <v>0.11</v>
@@ -5580,67 +5580,67 @@
         <v>2.11</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.81</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="BJ12" t="n">
         <v>1</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.94</v>
+        <v>4.71</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT12" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BU12" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BV12" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BW12" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX12" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CB12" t="n">
         <v>4.1</v>
@@ -5655,40 +5655,40 @@
         <v>1.25</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CG12" t="n">
         <v>3.7</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL12" t="n">
         <v>1.7</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CR12" t="n">
         <v>1.34</v>
@@ -5703,7 +5703,7 @@
         <v>1.72</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CW12" t="n">
         <v>1.49</v>
@@ -5730,79 +5730,79 @@
         <v>2.28</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="DF12" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="DH12" t="n">
-        <v>107.13</v>
+        <v>106.29</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.62</v>
+        <v>5.35</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DM12" t="n">
-        <v>53.81</v>
+        <v>53.82</v>
       </c>
       <c r="DN12" t="n">
         <v>1</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.56</v>
+        <v>12.29</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.56</v>
+        <v>12.29</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.38</v>
+        <v>5.41</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.94</v>
+        <v>56.83</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.94</v>
+        <v>15.88</v>
       </c>
       <c r="DY12" t="n">
         <v>9</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.94</v>
+        <v>6.88</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.25</v>
+        <v>21</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0.25</v>
@@ -5902,52 +5902,52 @@
         <v>1.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" t="n">
-        <v>71.88</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN13" t="n">
-        <v>28.75</v>
+        <v>30.56</v>
       </c>
       <c r="AO13" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.38</v>
+        <v>10</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.62</v>
+        <v>13.56</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.88</v>
+        <v>10.78</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>45.25</v>
+        <v>46</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.75</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.5</v>
+        <v>5.56</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="BD13" t="n">
-        <v>14.62</v>
+        <v>14.78</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="BH13" t="n">
-        <v>9</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO13" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.44</v>
+        <v>4.18</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU13" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW13" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX13" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY13" t="n">
         <v>3.44</v>
@@ -6043,28 +6043,28 @@
         <v>3.68</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.96</v>
+        <v>5.65</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.51</v>
+        <v>6.15</v>
       </c>
       <c r="CE13" t="n">
         <v>1.28</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CI13" t="n">
         <v>2.24</v>
@@ -6076,7 +6076,7 @@
         <v>1.44</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM13" t="n">
         <v>2.58</v>
@@ -6106,19 +6106,19 @@
         <v>1.65</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CW13" t="n">
         <v>1.63</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY13" t="n">
         <v>1.82</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DA13" t="n">
         <v>1.99</v>
@@ -6133,46 +6133,46 @@
         <v>2.5</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DH13" t="n">
-        <v>76.69</v>
+        <v>78.06</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="DK13" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DM13" t="n">
-        <v>31.75</v>
+        <v>32.53</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.63</v>
+        <v>10.41</v>
       </c>
       <c r="DQ13" t="n">
         <v>13.06</v>
       </c>
       <c r="DR13" t="n">
-        <v>11.07</v>
+        <v>11</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,16 +6184,16 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>41.18</v>
+        <v>41.82</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX13" t="n">
-        <v>8.43</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="DZ13" t="n">
         <v>2.94</v>
@@ -6202,10 +6202,10 @@
         <v>16.12</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0.38</v>
@@ -6305,52 +6305,52 @@
         <v>0.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>1.56</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="AI14" t="n">
-        <v>96.38</v>
+        <v>96</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.88</v>
+        <v>5.67</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AN14" t="n">
-        <v>49.62</v>
+        <v>50.78</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10.75</v>
+        <v>11.11</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.119999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.380000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>56</v>
+        <v>56.11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.38</v>
+        <v>14.33</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.62</v>
+        <v>7.44</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.75</v>
+        <v>6.89</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.38</v>
+        <v>17.22</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.69</v>
+        <v>10.88</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="BJ14" t="n">
         <v>1</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.12</v>
+        <v>6.29</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT14" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BU14" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BV14" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BW14" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BX14" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY14" t="n">
         <v>1.2</v>
@@ -6446,13 +6446,13 @@
         <v>1.2</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.63</v>
+        <v>6.49</v>
       </c>
       <c r="CB14" t="n">
-        <v>7.24</v>
+        <v>7.06</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CD14" t="n">
         <v>1.74</v>
@@ -6461,51 +6461,51 @@
         <v>1.16</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CI14" t="n">
         <v>2.41</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL14" t="n">
         <v>1.68</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CO14" t="n">
         <v>1.06</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CQ14" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CW14" t="n">
         <v>1.6</v>
@@ -6528,46 +6528,46 @@
         <v>1.78</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="DH14" t="n">
-        <v>107.94</v>
+        <v>107.06</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.25</v>
+        <v>6.59</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="DM14" t="n">
-        <v>59</v>
+        <v>59.06</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.68</v>
+        <v>10.88</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.68</v>
+        <v>8.59</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.32</v>
+        <v>7.47</v>
       </c>
       <c r="DS14" t="n">
         <v>0.12</v>
@@ -6579,28 +6579,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>60.06</v>
+        <v>59.88</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX14" t="n">
-        <v>17.82</v>
+        <v>17.59</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.68</v>
+        <v>10.41</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7.12</v>
+        <v>7.18</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.81</v>
+        <v>17.7</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="15">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6703,136 +6703,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>85.14</v>
+        <v>86</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.57</v>
+        <v>45.25</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.57</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.43</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.57</v>
+        <v>9.25</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>45.14</v>
+        <v>47.12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.29</v>
+        <v>14.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.140000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.14</v>
+        <v>4.88</v>
       </c>
       <c r="BD15" t="n">
-        <v>14.29</v>
+        <v>14.62</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.56</v>
+        <v>11.71</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.75</v>
+        <v>4.82</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.81</v>
+        <v>6.88</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU15" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV15" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW15" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX15" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY15" t="n">
         <v>2.94</v>
@@ -6841,16 +6841,16 @@
         <v>3.04</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.56</v>
+        <v>4.26</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.97</v>
+        <v>4.65</v>
       </c>
       <c r="CE15" t="n">
         <v>1.27</v>
@@ -6859,22 +6859,22 @@
         <v>2.3</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CH15" t="n">
         <v>1.56</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CK15" t="n">
         <v>1.35</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CM15" t="n">
         <v>2.88</v>
@@ -6886,7 +6886,7 @@
         <v>1.18</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CQ15" t="n">
         <v>2.49</v>
@@ -6895,7 +6895,7 @@
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CT15" t="n">
         <v>3.26</v>
@@ -6904,10 +6904,10 @@
         <v>1.62</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="CZ15" t="inlineStr"/>
       <c r="DA15" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DB15" t="n">
         <v>1.19</v>
@@ -6924,7 +6924,7 @@
         <v>1.63</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
@@ -6933,73 +6933,73 @@
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="DH15" t="n">
-        <v>89.75</v>
+        <v>89.88</v>
       </c>
       <c r="DI15" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.12</v>
+        <v>4.35</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM15" t="n">
-        <v>41.69</v>
+        <v>43.41</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="DP15" t="n">
-        <v>8.869999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.07</v>
+        <v>10.24</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.630000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.06</v>
+        <v>46</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.25</v>
+        <v>12.88</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.18</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.06</v>
+        <v>4.41</v>
       </c>
       <c r="EA15" t="n">
-        <v>15</v>
+        <v>15.12</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0.22</v>
@@ -7102,49 +7102,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AI16" t="n">
-        <v>79.29000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.86</v>
+        <v>4.62</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>37.86</v>
+        <v>37.38</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.86</v>
+        <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.29</v>
+        <v>10.38</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.140000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7156,82 +7156,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>42</v>
+        <v>41.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.29</v>
+        <v>11.25</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.57</v>
+        <v>17.38</v>
       </c>
       <c r="BE16" t="n">
         <v>1.21</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.25</v>
+        <v>11.24</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM16" t="n">
         <v>0.88</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.75</v>
+        <v>5.82</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.5</v>
+        <v>5.41</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS16" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU16" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV16" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX16" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY16" t="n">
         <v>3.04</v>
@@ -7240,31 +7240,31 @@
         <v>3.02</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.71</v>
+        <v>4.66</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.9</v>
+        <v>4.84</v>
       </c>
       <c r="CC16" t="n">
-        <v>9.98</v>
+        <v>9.26</v>
       </c>
       <c r="CD16" t="n">
-        <v>8.74</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CE16" t="n">
         <v>1.26</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.64</v>
@@ -7279,40 +7279,40 @@
         <v>2.85</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CT16" t="n">
         <v>3.3</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.37</v>
@@ -7324,52 +7324,52 @@
         <v>1.19</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="DE16" t="n">
         <v>0.12</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="DH16" t="n">
-        <v>81.44</v>
+        <v>81.53</v>
       </c>
       <c r="DI16" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.06</v>
+        <v>4.94</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.94</v>
+        <v>41.47</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.56</v>
+        <v>10.88</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
       <c r="DR16" t="n">
-        <v>8</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
@@ -7381,28 +7381,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.06</v>
+        <v>43.71</v>
       </c>
       <c r="DW16" t="n">
         <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.32</v>
+        <v>13.18</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.619999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.5</v>
+        <v>18.35</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="17">
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0.12</v>
@@ -7505,136 +7505,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AI17" t="n">
-        <v>93.62</v>
+        <v>95.33</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.5</v>
+        <v>5.33</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN17" t="n">
-        <v>50.38</v>
+        <v>53.78</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.88</v>
+        <v>2.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13</v>
+        <v>12.78</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.619999999999999</v>
+        <v>10.22</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.5</v>
+        <v>7.33</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>52.88</v>
+        <v>53</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>16.75</v>
+        <v>18.11</v>
       </c>
       <c r="BB17" t="n">
-        <v>10.88</v>
+        <v>11.67</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.88</v>
+        <v>6.44</v>
       </c>
       <c r="BD17" t="n">
-        <v>21.12</v>
+        <v>20</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="BH17" t="n">
-        <v>8.56</v>
+        <v>9.18</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL17" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BN17" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.62</v>
+        <v>4.76</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.94</v>
+        <v>4.41</v>
       </c>
       <c r="BR17" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT17" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU17" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV17" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW17" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX17" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY17" t="n">
         <v>2.08</v>
@@ -7649,16 +7649,16 @@
         <v>4.21</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="CE17" t="n">
         <v>1.26</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CG17" t="n">
         <v>3.42</v>
@@ -7679,7 +7679,7 @@
         <v>1.81</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN17" t="n">
         <v>1.94</v>
@@ -7691,13 +7691,13 @@
         <v>1.6</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CR17" t="n">
         <v>1.35</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CT17" t="n">
         <v>3.31</v>
@@ -7706,10 +7706,10 @@
         <v>1.58</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX17" t="n">
         <v>1.54</v>
@@ -7727,85 +7727,85 @@
         <v>1.2</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="DH17" t="n">
-        <v>107.31</v>
+        <v>107.41</v>
       </c>
       <c r="DI17" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.81</v>
+        <v>5.23</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM17" t="n">
-        <v>56.63</v>
+        <v>58.06</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.19</v>
+        <v>12.12</v>
       </c>
       <c r="DQ17" t="n">
-        <v>9.869999999999999</v>
+        <v>10.17</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>55</v>
+        <v>54.94</v>
       </c>
       <c r="DW17" t="n">
         <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>17.81</v>
+        <v>18.47</v>
       </c>
       <c r="DY17" t="n">
-        <v>11.75</v>
+        <v>12.12</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.06</v>
+        <v>6.35</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.81</v>
+        <v>20.24</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="18">
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -7827,49 +7827,49 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="G18" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="H18" t="n">
-        <v>93.5</v>
+        <v>94.11</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J18" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="K18" t="n">
-        <v>5.38</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>35.5</v>
+        <v>37.78</v>
       </c>
       <c r="N18" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="P18" t="n">
-        <v>10.62</v>
+        <v>10.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.12</v>
+        <v>13.22</v>
       </c>
       <c r="R18" t="n">
-        <v>6.75</v>
+        <v>6.89</v>
       </c>
       <c r="S18" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7881,28 +7881,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>45.12</v>
+        <v>44.89</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.38</v>
+        <v>15.44</v>
       </c>
       <c r="AA18" t="n">
-        <v>9.75</v>
+        <v>10.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.62</v>
+        <v>5.22</v>
       </c>
       <c r="AC18" t="n">
-        <v>20.12</v>
+        <v>20.33</v>
       </c>
       <c r="AD18" t="n">
         <v>1.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7989,22 +7989,22 @@
         <v>3</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.56</v>
+        <v>9.82</v>
       </c>
       <c r="BI18" t="n">
         <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BN18" t="n">
         <v>1.88</v>
@@ -8016,40 +8016,40 @@
         <v>5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.56</v>
+        <v>4.82</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU18" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV18" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="CC18" t="n">
         <v>3.15</v>
@@ -8058,28 +8058,28 @@
         <v>3.4</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK18" t="n">
         <v>1.43</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM18" t="n">
         <v>2.64</v>
@@ -8091,28 +8091,28 @@
         <v>1.2</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="CT18" t="n">
         <v>3.26</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CX18" t="n">
         <v>1.5</v>
@@ -8139,43 +8139,43 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="DH18" t="n">
-        <v>100.31</v>
+        <v>100.23</v>
       </c>
       <c r="DI18" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.19</v>
+        <v>5</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM18" t="n">
-        <v>37.94</v>
+        <v>39</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.68</v>
+        <v>10.47</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.18</v>
+        <v>11.35</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.44</v>
+        <v>7.47</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8187,28 +8187,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.12</v>
+        <v>47.82</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.63</v>
+        <v>14.71</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.32</v>
+        <v>9.59</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.31</v>
+        <v>5.12</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.31</v>
+        <v>20.41</v>
       </c>
       <c r="EB18" t="n">
         <v>1.57</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="19">
@@ -8218,94 +8218,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="H19" t="n">
-        <v>81.12</v>
+        <v>79.33</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="K19" t="n">
-        <v>4.25</v>
+        <v>4.44</v>
       </c>
       <c r="L19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M19" t="n">
-        <v>41.75</v>
+        <v>41.22</v>
       </c>
       <c r="N19" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="P19" t="n">
-        <v>9.380000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>13.25</v>
+        <v>12.44</v>
       </c>
       <c r="R19" t="n">
-        <v>10.62</v>
+        <v>10.67</v>
       </c>
       <c r="S19" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="U19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>44.25</v>
+        <v>43.67</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.38</v>
+        <v>7.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.12</v>
+        <v>12.89</v>
       </c>
       <c r="AD19" t="n">
         <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8389,70 +8389,70 @@
         <v>0.75</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.56</v>
+        <v>10.76</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BP19" t="n">
         <v>5.94</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.62</v>
+        <v>4.82</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>93.75</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BU19" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV19" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY19" t="n">
-        <v>4.14</v>
+        <v>4.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>4.29</v>
+        <v>4.12</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.14</v>
+        <v>5.06</v>
       </c>
       <c r="CB19" t="n">
-        <v>5.43</v>
+        <v>5.32</v>
       </c>
       <c r="CC19" t="n">
         <v>8.07</v>
@@ -8464,16 +8464,16 @@
         <v>1.23</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CH19" t="n">
         <v>1.67</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.61</v>
@@ -8482,7 +8482,7 @@
         <v>1.37</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM19" t="n">
         <v>2.81</v>
@@ -8494,28 +8494,28 @@
         <v>1.14</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CT19" t="n">
         <v>3.34</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CX19" t="n">
         <v>1.51</v>
@@ -8530,55 +8530,55 @@
         <v>2.17</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="DC19" t="n">
         <v>1.51</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DE19" t="n">
         <v>0.06</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="DH19" t="n">
-        <v>78.44</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>-0.12</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="DL19" t="n">
         <v>0.18</v>
       </c>
       <c r="DM19" t="n">
-        <v>36.62</v>
+        <v>36.65</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DP19" t="n">
-        <v>9.57</v>
+        <v>9.82</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.57</v>
+        <v>11.24</v>
       </c>
       <c r="DR19" t="n">
-        <v>10.25</v>
+        <v>10.3</v>
       </c>
       <c r="DS19" t="n">
         <v>0.06</v>
@@ -8590,28 +8590,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>44.12</v>
+        <v>43.83</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.31</v>
+        <v>10.41</v>
       </c>
       <c r="DY19" t="n">
         <v>6.82</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="EA19" t="n">
-        <v>14.31</v>
+        <v>14.59</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="EC19" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1685,7 +1685,7 @@
         <v>1.79</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DA2" t="n">
         <v>2.02</v>
@@ -2816,13 +2816,13 @@
         <v>1.45</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="CA5" t="n">
         <v>4.99</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.34</v>
+        <v>5.32</v>
       </c>
       <c r="CC5" t="n">
         <v>1.81</v>
@@ -2882,22 +2882,22 @@
         <v>1.76</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CW5" t="n">
         <v>1.67</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DB5" t="n">
         <v>1.16</v>
@@ -2906,7 +2906,7 @@
         <v>1.5</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DE5" t="n">
         <v>0.11</v>
@@ -3219,7 +3219,7 @@
         <v>3.09</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CA6" t="n">
         <v>4.04</v>
@@ -3291,13 +3291,13 @@
         <v>1.68</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY6" t="n">
         <v>1.78</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DA6" t="n">
         <v>2.04</v>
@@ -3622,7 +3622,7 @@
         <v>2.97</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="CA7" t="n">
         <v>4.13</v>
@@ -3679,13 +3679,13 @@
         <v>1.34</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="CT7" t="n">
         <v>3.31</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CV7" t="n">
         <v>2.57</v>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AL8" t="n">
         <v>4.78</v>
@@ -3914,7 +3914,7 @@
         <v>39.33</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP8" t="n">
         <v>2.56</v>
@@ -3965,7 +3965,7 @@
         <v>1.69</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="BG8" t="n">
         <v>2.76</v>
@@ -4031,7 +4031,7 @@
         <v>4.03</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="CC8" t="n">
         <v>4.87</v>
@@ -4082,7 +4082,7 @@
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CT8" t="n">
         <v>3.2</v>
@@ -4100,13 +4100,13 @@
         <v>1.59</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.31</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="DB8" t="n">
         <v>1.24</v>
@@ -4133,7 +4133,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="DK8" t="n">
         <v>6.3</v>
@@ -4145,7 +4145,7 @@
         <v>45.11</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="DO8" t="n">
         <v>3.36</v>
@@ -4190,7 +4190,7 @@
         <v>1.82</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="9">
@@ -5072,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>50.78</v>
+        <v>50.89</v>
       </c>
       <c r="Y11" t="n">
         <v>0.11</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.76</v>
+        <v>49.82</v>
       </c>
       <c r="DW11" t="n">
         <v>0.24</v>
@@ -5481,19 +5481,19 @@
         <v>0.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.38</v>
+        <v>15.25</v>
       </c>
       <c r="AA12" t="n">
         <v>8.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.62</v>
+        <v>6.5</v>
       </c>
       <c r="AC12" t="n">
         <v>19.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AE12" t="n">
         <v>1.75</v>
@@ -5787,19 +5787,19 @@
         <v>0.17</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.88</v>
+        <v>15.82</v>
       </c>
       <c r="DY12" t="n">
         <v>9</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.88</v>
+        <v>6.82</v>
       </c>
       <c r="EA12" t="n">
         <v>21</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="EC12" t="n">
         <v>1.94</v>
@@ -6449,13 +6449,13 @@
         <v>6.49</v>
       </c>
       <c r="CB14" t="n">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
       <c r="CC14" t="n">
         <v>1.73</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CE14" t="n">
         <v>1.16</v>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="n">
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>47.12</v>
+        <v>47</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.12</v>
@@ -6850,7 +6850,7 @@
         <v>4.26</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.65</v>
+        <v>4.64</v>
       </c>
       <c r="CE15" t="n">
         <v>1.27</v>
@@ -6895,7 +6895,7 @@
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CT15" t="n">
         <v>3.26</v>
@@ -6907,7 +6907,7 @@
         <v>2.49</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="CZ15" t="inlineStr"/>
       <c r="DA15" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DB15" t="n">
         <v>1.19</v>
@@ -6924,7 +6924,7 @@
         <v>1.63</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
@@ -6978,7 +6978,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46</v>
+        <v>45.94</v>
       </c>
       <c r="DW15" t="n">
         <v>0.11</v>
@@ -7156,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>41.5</v>
+        <v>41.38</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.12</v>
@@ -7381,7 +7381,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.71</v>
+        <v>43.65</v>
       </c>
       <c r="DW16" t="n">
         <v>0.06</v>
@@ -7646,13 +7646,13 @@
         <v>4.08</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="CC17" t="n">
         <v>2.54</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="CE17" t="n">
         <v>1.26</v>
@@ -7697,7 +7697,7 @@
         <v>1.35</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CT17" t="n">
         <v>3.31</v>
@@ -7715,13 +7715,13 @@
         <v>1.54</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DB17" t="n">
         <v>1.2</v>
@@ -7730,7 +7730,7 @@
         <v>1.65</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
@@ -7887,19 +7887,19 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.44</v>
+        <v>15.56</v>
       </c>
       <c r="AA18" t="n">
         <v>10.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.22</v>
+        <v>5.33</v>
       </c>
       <c r="AC18" t="n">
         <v>20.33</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE18" t="n">
         <v>1.11</v>
@@ -8043,13 +8043,13 @@
         <v>2.21</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="CA18" t="n">
         <v>3.87</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="CC18" t="n">
         <v>3.15</v>
@@ -8100,7 +8100,7 @@
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CT18" t="n">
         <v>3.26</v>
@@ -8109,7 +8109,7 @@
         <v>1.54</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CW18" t="n">
         <v>1.69</v>
@@ -8193,19 +8193,19 @@
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.71</v>
+        <v>14.77</v>
       </c>
       <c r="DY18" t="n">
         <v>9.59</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.12</v>
+        <v>5.17</v>
       </c>
       <c r="EA18" t="n">
         <v>20.41</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="EC18" t="n">
         <v>1.35</v>
@@ -8284,7 +8284,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>43.67</v>
+        <v>43.78</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
         <v>4.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>4.12</v>
+        <v>4.14</v>
       </c>
       <c r="CA19" t="n">
         <v>5.06</v>
@@ -8521,13 +8521,13 @@
         <v>1.51</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.44</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DB19" t="n">
         <v>1.17</v>
@@ -8590,7 +8590,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>43.83</v>
+        <v>43.88</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -3003,7 +3003,7 @@
         <v>0.44</v>
       </c>
       <c r="F6" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="G6" t="n">
         <v>2.44</v>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="K6" t="n">
         <v>5.56</v>
@@ -3078,7 +3078,7 @@
         <v>1.72</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="AF6" t="n">
         <v>0.12</v>
@@ -3315,7 +3315,7 @@
         <v>0.29</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="DG6" t="n">
         <v>2.23</v>
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="DK6" t="n">
         <v>4.94</v>
@@ -3384,7 +3384,7 @@
         <v>1.47</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="7">
@@ -3547,19 +3547,19 @@
         <v>0.22</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.44</v>
+        <v>9.56</v>
       </c>
       <c r="BB7" t="n">
         <v>5.33</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.11</v>
+        <v>4.22</v>
       </c>
       <c r="BD7" t="n">
         <v>20.33</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BF7" t="n">
         <v>1.56</v>
@@ -3772,19 +3772,19 @@
         <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.59</v>
+        <v>10.65</v>
       </c>
       <c r="DY7" t="n">
         <v>5.82</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.76</v>
+        <v>4.82</v>
       </c>
       <c r="EA7" t="n">
         <v>18.71</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="EC7" t="n">
         <v>1.41</v>
@@ -3890,7 +3890,7 @@
         <v>0.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
         <v>2.22</v>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AL8" t="n">
         <v>4.78</v>
@@ -3965,7 +3965,7 @@
         <v>1.69</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="BG8" t="n">
         <v>2.76</v>
@@ -4121,7 +4121,7 @@
         <v>0.11</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="DG8" t="n">
         <v>2.94</v>
@@ -4133,7 +4133,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DK8" t="n">
         <v>6.3</v>
@@ -4190,7 +4190,7 @@
         <v>1.82</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="9">
@@ -7424,7 +7424,7 @@
         <v>0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="G17" t="n">
         <v>2.25</v>
@@ -7436,7 +7436,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="K17" t="n">
         <v>5.12</v>
@@ -7499,7 +7499,7 @@
         <v>2.08</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7736,7 +7736,7 @@
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="DG17" t="n">
         <v>2.65</v>
@@ -7748,7 +7748,7 @@
         <v>0.12</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="DK17" t="n">
         <v>5.23</v>
@@ -7805,7 +7805,7 @@
         <v>2.03</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="18">
@@ -8230,7 +8230,7 @@
         <v>0.11</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="G19" t="n">
         <v>2.56</v>
@@ -8242,7 +8242,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="K19" t="n">
         <v>4.44</v>
@@ -8305,7 +8305,7 @@
         <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8542,7 +8542,7 @@
         <v>0.06</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="DG19" t="n">
         <v>2</v>
@@ -8554,7 +8554,7 @@
         <v>-0.12</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="DK19" t="n">
         <v>3.71</v>
@@ -8611,7 +8611,7 @@
         <v>1.18</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="F2" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="G2" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="H2" t="n">
-        <v>105.29</v>
+        <v>104.75</v>
       </c>
       <c r="I2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="K2" t="n">
-        <v>6.86</v>
+        <v>6.88</v>
       </c>
       <c r="L2" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="M2" t="n">
-        <v>53.14</v>
+        <v>54.12</v>
       </c>
       <c r="N2" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>8.57</v>
+        <v>8.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.43</v>
+        <v>10.25</v>
       </c>
       <c r="R2" t="n">
-        <v>7.14</v>
+        <v>6.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="T2" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>53.29</v>
+        <v>52.75</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.71</v>
+        <v>17.62</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.57</v>
+        <v>6.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.86</v>
+        <v>17.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
         <v>0.11</v>
@@ -1550,70 +1550,70 @@
         <v>2.78</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.69</v>
+        <v>3.53</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.69</v>
+        <v>10.59</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.69</v>
+        <v>3.53</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.94</v>
+        <v>5.82</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BT2" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BU2" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BV2" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW2" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX2" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.42</v>
+        <v>4.64</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.55</v>
+        <v>4.79</v>
       </c>
       <c r="CC2" t="n">
         <v>2.09</v>
@@ -1622,157 +1622,157 @@
         <v>2.16</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CO2" t="n">
         <v>1.14</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="CR2" t="n">
         <v>1.33</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CT2" t="n">
         <v>3.32</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="CX2" t="n">
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.44</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="DB2" t="n">
         <v>1.16</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="DH2" t="n">
-        <v>102.07</v>
+        <v>102</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.31</v>
+        <v>6.36</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.87</v>
+        <v>50.53</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.31</v>
+        <v>10.3</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.75</v>
+        <v>10.65</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.31</v>
+        <v>7.05</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.38</v>
+        <v>54.06</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.87</v>
+        <v>16.88</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.68</v>
+        <v>10.59</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6.19</v>
+        <v>6.29</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.38</v>
+        <v>16.41</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0.25</v>
@@ -5902,139 +5902,139 @@
         <v>1.88</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>45</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BN13" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>30.56</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>13.56</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>14.78</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.41</v>
-      </c>
       <c r="BO13" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.18</v>
+        <v>4.06</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.53</v>
+        <v>4.67</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT13" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU13" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW13" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX13" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY13" t="n">
         <v>3.44</v>
@@ -6043,34 +6043,34 @@
         <v>3.68</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.21</v>
+        <v>4.28</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.46</v>
+        <v>4.53</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.65</v>
+        <v>6.04</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.15</v>
+        <v>6.44</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK13" t="n">
         <v>1.44</v>
@@ -6085,19 +6085,19 @@
         <v>2</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CT13" t="n">
         <v>3.34</v>
@@ -6106,22 +6106,22 @@
         <v>1.65</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX13" t="n">
         <v>1.51</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB13" t="n">
         <v>1.19</v>
@@ -6130,49 +6130,49 @@
         <v>1.61</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="DH13" t="n">
-        <v>78.06</v>
+        <v>77.56</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="DK13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="DM13" t="n">
-        <v>32.53</v>
+        <v>31.83</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.41</v>
+        <v>10.45</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.06</v>
+        <v>12.67</v>
       </c>
       <c r="DR13" t="n">
-        <v>11</v>
+        <v>10.89</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>41.82</v>
+        <v>41.5</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX13" t="n">
-        <v>8.470000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.53</v>
+        <v>5.33</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.12</v>
+        <v>16.16</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -7412,94 +7412,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="G17" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="H17" t="n">
-        <v>121</v>
+        <v>124.22</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="K17" t="n">
-        <v>5.12</v>
+        <v>5.33</v>
       </c>
       <c r="L17" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="M17" t="n">
-        <v>62.88</v>
+        <v>66.44</v>
       </c>
       <c r="N17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="P17" t="n">
-        <v>11.38</v>
+        <v>10.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.12</v>
+        <v>10.22</v>
       </c>
       <c r="R17" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>57.12</v>
+        <v>57.89</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.88</v>
+        <v>19.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>12.62</v>
+        <v>13.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7583,19 +7583,19 @@
         <v>2</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.18</v>
+        <v>9.17</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL17" t="n">
         <v>0.9399999999999999</v>
@@ -7607,46 +7607,46 @@
         <v>1.94</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.76</v>
+        <v>4.61</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.41</v>
+        <v>4.56</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT17" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU17" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV17" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX17" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.08</v>
+        <v>4.16</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.19</v>
+        <v>4.28</v>
       </c>
       <c r="CC17" t="n">
         <v>2.54</v>
@@ -7658,22 +7658,22 @@
         <v>1.26</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="CH17" t="n">
         <v>1.58</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL17" t="n">
         <v>1.81</v>
@@ -7688,124 +7688,124 @@
         <v>1.18</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CR17" t="n">
         <v>1.35</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CT17" t="n">
         <v>3.31</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB17" t="n">
         <v>1.2</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="DH17" t="n">
-        <v>107.41</v>
+        <v>109.78</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.23</v>
+        <v>5.33</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM17" t="n">
-        <v>58.06</v>
+        <v>60.11</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.12</v>
+        <v>11.78</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.17</v>
+        <v>10.22</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.94</v>
+        <v>55.44</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>18.47</v>
+        <v>18.89</v>
       </c>
       <c r="DY17" t="n">
-        <v>12.12</v>
+        <v>12.5</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.35</v>
+        <v>6.39</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.24</v>
+        <v>20.5</v>
       </c>
       <c r="EB17" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="18">
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
         <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0.11</v>
@@ -8311,49 +8311,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" t="n">
-        <v>75.75</v>
+        <v>79.11</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="AK19" t="n">
         <v>1</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN19" t="n">
-        <v>31.5</v>
+        <v>33</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.75</v>
+        <v>9.67</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.880000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.880000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8365,82 +8365,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>44</v>
+        <v>44.78</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.25</v>
+        <v>6.11</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="BD19" t="n">
-        <v>16.5</v>
+        <v>17.11</v>
       </c>
       <c r="BE19" t="n">
         <v>0.93</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.76</v>
+        <v>10.67</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="BJ19" t="n">
         <v>1.06</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.94</v>
+        <v>5.89</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV19" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY19" t="n">
         <v>4.01</v>
@@ -8449,136 +8449,136 @@
         <v>4.14</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.06</v>
+        <v>5.22</v>
       </c>
       <c r="CB19" t="n">
-        <v>5.32</v>
+        <v>5.5</v>
       </c>
       <c r="CC19" t="n">
-        <v>8.07</v>
+        <v>8.84</v>
       </c>
       <c r="CD19" t="n">
-        <v>9.029999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="CE19" t="n">
         <v>1.23</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK19" t="n">
         <v>1.37</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CO19" t="n">
         <v>1.14</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CT19" t="n">
         <v>3.34</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="CX19" t="n">
         <v>1.51</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.44</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DE19" t="n">
         <v>0.06</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="DG19" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DH19" t="n">
-        <v>77.65000000000001</v>
+        <v>79.22</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM19" t="n">
-        <v>36.65</v>
+        <v>37.11</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DP19" t="n">
-        <v>9.82</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.24</v>
+        <v>11.16</v>
       </c>
       <c r="DR19" t="n">
-        <v>10.3</v>
+        <v>10.23</v>
       </c>
       <c r="DS19" t="n">
         <v>0.06</v>
@@ -8590,28 +8590,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>43.88</v>
+        <v>44.28</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.41</v>
+        <v>10.22</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.82</v>
+        <v>6.72</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="EA19" t="n">
-        <v>14.59</v>
+        <v>15</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0.11</v>
@@ -1872,118 +1872,118 @@
         <v>1.44</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AI3" t="n">
-        <v>95.12</v>
+        <v>97.78</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.12</v>
+        <v>4.89</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>51.25</v>
+        <v>50.56</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP3" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.12</v>
+        <v>10.56</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.88</v>
+        <v>11.22</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.62</v>
+        <v>7.11</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>57.12</v>
+        <v>58</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA3" t="n">
-        <v>14.62</v>
+        <v>14.78</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.75</v>
+        <v>8.44</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.88</v>
+        <v>6.33</v>
       </c>
       <c r="BD3" t="n">
-        <v>16.12</v>
+        <v>16.22</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.53</v>
+        <v>10.56</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.88</v>
+        <v>4.72</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.65</v>
+        <v>5.83</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,19 +1992,19 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU3" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX3" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY3" t="n">
         <v>1.67</v>
@@ -2013,70 +2013,70 @@
         <v>1.69</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.87</v>
+        <v>4.82</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="CE3" t="n">
         <v>1.24</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.61</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO3" t="n">
         <v>1.13</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CT3" t="n">
         <v>3.32</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CW3" t="n">
         <v>1.63</v>
@@ -2091,7 +2091,7 @@
         <v>2.46</v>
       </c>
       <c r="DA3" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DB3" t="n">
         <v>1.16</v>
@@ -2100,49 +2100,49 @@
         <v>1.51</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="DE3" t="n">
         <v>0.11</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DG3" t="n">
         <v>3.06</v>
       </c>
       <c r="DH3" t="n">
-        <v>99.41</v>
+        <v>100.5</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.47</v>
+        <v>5.34</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM3" t="n">
-        <v>53.24</v>
+        <v>52.78</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.94</v>
+        <v>10.67</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.65</v>
+        <v>12.27</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.88</v>
+        <v>6.66</v>
       </c>
       <c r="DS3" t="n">
         <v>0.06</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>56.94</v>
+        <v>57.39</v>
       </c>
       <c r="DW3" t="n">
         <v>0.06</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.82</v>
+        <v>14.89</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.710000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.12</v>
+        <v>6.33</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.41</v>
+        <v>16.44</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="EC3" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0.33</v>
@@ -2275,139 +2275,139 @@
         <v>1.44</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>89</v>
+        <v>90.38</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>43.86</v>
+        <v>42</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.71</v>
+        <v>8</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.289999999999999</v>
+        <v>7.62</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>44.29</v>
+        <v>45</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.14</v>
+        <v>11.62</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.57</v>
+        <v>7.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.43</v>
+        <v>17.38</v>
       </c>
       <c r="BE4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO4" t="n">
         <v>1.41</v>
       </c>
-      <c r="BF4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BP4" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT4" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BX4" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY4" t="n">
         <v>3.4</v>
@@ -2416,55 +2416,55 @@
         <v>3.56</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.07</v>
+        <v>4.31</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.19</v>
+        <v>4.53</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.69</v>
+        <v>5.73</v>
       </c>
       <c r="CD4" t="n">
-        <v>5</v>
+        <v>6.12</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="CH4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CJ4" t="n">
         <v>1.58</v>
       </c>
-      <c r="CI4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>1.57</v>
-      </c>
       <c r="CK4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CO4" t="n">
         <v>1.16</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
@@ -2479,106 +2479,106 @@
         <v>1.64</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX4" t="n">
         <v>1.49</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.49</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="DB4" t="n">
         <v>1.18</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF4" t="n">
         <v>1.06</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="DH4" t="n">
-        <v>90.81</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="DK4" t="n">
         <v>4.06</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM4" t="n">
-        <v>38.25</v>
+        <v>37.71</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.94</v>
+        <v>13.53</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.94</v>
+        <v>9</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.380000000000001</v>
+        <v>9</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.31</v>
+        <v>44.65</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.12</v>
+        <v>11.88</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.87</v>
+        <v>7.71</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.19</v>
+        <v>17.18</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.11</v>
@@ -2678,139 +2678,139 @@
         <v>0.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
-        <v>106.75</v>
+        <v>104</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AL5" t="n">
-        <v>7.75</v>
+        <v>7.22</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>58.75</v>
+        <v>57.33</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.5</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.5</v>
+        <v>10.56</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>7.22</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>55.75</v>
+        <v>54.33</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA5" t="n">
-        <v>17.38</v>
+        <v>16.22</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.75</v>
+        <v>10</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.62</v>
+        <v>6.22</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.5</v>
+        <v>19.44</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.41</v>
+        <v>11.22</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BL5" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.29</v>
+        <v>5.11</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT5" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU5" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BV5" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BW5" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BX5" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY5" t="n">
         <v>1.45</v>
@@ -2819,46 +2819,46 @@
         <v>1.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.99</v>
+        <v>4.92</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.32</v>
+        <v>5.24</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="CE5" t="n">
         <v>1.23</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CK5" t="n">
         <v>1.43</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM5" t="n">
         <v>2.6</v>
       </c>
       <c r="CN5" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CO5" t="n">
         <v>1.14</v>
@@ -2867,88 +2867,88 @@
         <v>1.49</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CR5" t="n">
         <v>1.33</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CT5" t="n">
         <v>3.32</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX5" t="n">
         <v>1.52</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.45</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB5" t="n">
         <v>1.16</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DE5" t="n">
         <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DG5" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="DH5" t="n">
-        <v>102.71</v>
+        <v>101.56</v>
       </c>
       <c r="DI5" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.71</v>
+        <v>7.44</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM5" t="n">
-        <v>55.82</v>
+        <v>55.28</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.71</v>
+        <v>3.56</v>
       </c>
       <c r="DP5" t="n">
-        <v>9.710000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.76</v>
+        <v>10.78</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.83</v>
+        <v>6.94</v>
       </c>
       <c r="DS5" t="n">
         <v>0.11</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.41</v>
+        <v>53.78</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX5" t="n">
-        <v>18.35</v>
+        <v>17.72</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.71</v>
+        <v>11.28</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.65</v>
+        <v>6.44</v>
       </c>
       <c r="EA5" t="n">
         <v>19</v>
       </c>
       <c r="EB5" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0.44</v>
@@ -3081,52 +3081,52 @@
         <v>2.67</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>92.44</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
         <v>2</v>
       </c>
-      <c r="AI6" t="n">
-        <v>93.75</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AL6" t="n">
-        <v>4.25</v>
+        <v>3.89</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>34.88</v>
+        <v>34.89</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.38</v>
+        <v>11.22</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.75</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AT6" t="n">
         <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48</v>
+        <v>46.89</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.880000000000001</v>
+        <v>10.11</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.75</v>
+        <v>18.89</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.94</v>
+        <v>10.89</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.82</v>
+        <v>5.83</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT6" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU6" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV6" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW6" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX6" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY6" t="n">
         <v>3.09</v>
@@ -3222,16 +3222,16 @@
         <v>3.05</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="CC6" t="n">
-        <v>6.09</v>
+        <v>5.79</v>
       </c>
       <c r="CD6" t="n">
-        <v>6.76</v>
+        <v>6.47</v>
       </c>
       <c r="CE6" t="n">
         <v>1.3</v>
@@ -3246,7 +3246,7 @@
         <v>1.54</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.65</v>
@@ -3255,10 +3255,10 @@
         <v>1.43</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CN6" t="n">
         <v>2.02</v>
@@ -3270,37 +3270,37 @@
         <v>1.68</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS6" t="n">
         <v>2.55</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="CU6" t="n">
         <v>1.59</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="DB6" t="n">
         <v>1.23</v>
@@ -3309,82 +3309,82 @@
         <v>1.73</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="DH6" t="n">
-        <v>91.23999999999999</v>
+        <v>90.72</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.94</v>
+        <v>4.72</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM6" t="n">
-        <v>39.24</v>
+        <v>39</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="DP6" t="n">
-        <v>14</v>
+        <v>13.72</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.12</v>
+        <v>11.06</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.71</v>
+        <v>8</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.12</v>
+        <v>46.61</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.59</v>
+        <v>13.5</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.94</v>
+        <v>8.84</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.71</v>
+        <v>17.39</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F7" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>3.38</v>
+        <v>3.67</v>
       </c>
       <c r="H7" t="n">
-        <v>94.25</v>
+        <v>97.22</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="K7" t="n">
-        <v>6.12</v>
+        <v>6.44</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>50.5</v>
+        <v>51.33</v>
       </c>
       <c r="N7" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="P7" t="n">
-        <v>9.119999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.5</v>
+        <v>11.22</v>
       </c>
       <c r="R7" t="n">
-        <v>8.880000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.75</v>
+        <v>52.89</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.88</v>
+        <v>13.11</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.38</v>
+        <v>7.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.5</v>
+        <v>5.78</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.88</v>
+        <v>17.22</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AF7" t="n">
         <v>0.22</v>
@@ -3565,34 +3565,34 @@
         <v>1.56</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.94</v>
+        <v>10.89</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="BJ7" t="n">
         <v>1</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.76</v>
+        <v>4.72</v>
       </c>
       <c r="BQ7" t="n">
         <v>6.06</v>
@@ -3601,34 +3601,34 @@
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT7" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV7" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX7" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.31</v>
+        <v>4.28</v>
       </c>
       <c r="CC7" t="n">
         <v>4.29</v>
@@ -3640,31 +3640,31 @@
         <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.52</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL7" t="n">
         <v>1.62</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CO7" t="n">
         <v>1.14</v>
@@ -3673,25 +3673,25 @@
         <v>1.56</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CR7" t="n">
         <v>1.34</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CX7" t="n">
         <v>1.44</v>
@@ -3700,7 +3700,7 @@
         <v>1.64</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="DA7" t="n">
         <v>2.21</v>
@@ -3709,52 +3709,52 @@
         <v>1.18</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="DH7" t="n">
-        <v>95.94</v>
+        <v>97.33</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.11</v>
+        <v>5.33</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.35</v>
+        <v>47</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.35</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.82</v>
+        <v>9.77</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="DS7" t="n">
         <v>0.06</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.47</v>
+        <v>52.06</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.65</v>
+        <v>11.34</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.82</v>
+        <v>6.33</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.71</v>
+        <v>18.77</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F8" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="G8" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="H8" t="n">
-        <v>113.12</v>
+        <v>117.89</v>
       </c>
       <c r="I8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J8" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>7.44</v>
       </c>
       <c r="L8" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>51.62</v>
+        <v>51.44</v>
       </c>
       <c r="N8" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>4.25</v>
+        <v>3.78</v>
       </c>
       <c r="P8" t="n">
-        <v>10.38</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.38</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="S8" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="T8" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="U8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>57</v>
+        <v>56.78</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.5</v>
+        <v>18.22</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.5</v>
+        <v>12.33</v>
       </c>
       <c r="AB8" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.25</v>
+        <v>21.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3968,70 +3968,70 @@
         <v>1.44</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.53</v>
+        <v>10.33</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.35</v>
+        <v>5.17</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="BR8" t="n">
-        <v>100</v>
+        <v>94.44</v>
       </c>
       <c r="BS8" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU8" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="CC8" t="n">
         <v>4.87</v>
@@ -4043,40 +4043,40 @@
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK8" t="n">
         <v>1.53</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN8" t="n">
         <v>1.86</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4097,100 +4097,100 @@
         <v>1.77</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY8" t="n">
         <v>1.94</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="DE8" t="n">
         <v>0.11</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="DG8" t="n">
         <v>2.94</v>
       </c>
       <c r="DH8" t="n">
-        <v>106.53</v>
+        <v>109.28</v>
       </c>
       <c r="DI8" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.3</v>
+        <v>6.11</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DM8" t="n">
-        <v>45.11</v>
+        <v>45.38</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.18</v>
+        <v>10.94</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.77</v>
+        <v>10.5</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.29</v>
+        <v>7.22</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.76</v>
+        <v>51.94</v>
       </c>
       <c r="DW8" t="n">
         <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.47</v>
+        <v>16.44</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.06</v>
+        <v>10.11</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.41</v>
+        <v>6.34</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.94</v>
+        <v>21.17</v>
       </c>
       <c r="EB8" t="n">
         <v>1.82</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="H9" t="n">
-        <v>104.25</v>
+        <v>105.89</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="K9" t="n">
-        <v>6.38</v>
+        <v>6.22</v>
       </c>
       <c r="L9" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="M9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="P9" t="n">
-        <v>9.380000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.12</v>
+        <v>10.56</v>
       </c>
       <c r="R9" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="S9" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="T9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.75</v>
+        <v>52.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.38</v>
+        <v>16.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.12</v>
+        <v>10.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.25</v>
+        <v>5.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.25</v>
+        <v>15.56</v>
       </c>
       <c r="AD9" t="n">
         <v>1.82</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>1.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.82</v>
+        <v>10.67</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM9" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.29</v>
+        <v>5.11</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT9" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BU9" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV9" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX9" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="CC9" t="n">
         <v>3.33</v>
@@ -4455,7 +4455,7 @@
         <v>1.6</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.56</v>
@@ -4464,10 +4464,10 @@
         <v>1.44</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CN9" t="n">
         <v>2.04</v>
@@ -4476,10 +4476,10 @@
         <v>1.16</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
@@ -4494,7 +4494,7 @@
         <v>1.63</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CW9" t="n">
         <v>1.56</v>
@@ -4509,7 +4509,7 @@
         <v>2.48</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB9" t="n">
         <v>1.18</v>
@@ -4524,55 +4524,55 @@
         <v>0.06</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="DH9" t="n">
-        <v>100.41</v>
+        <v>101.44</v>
       </c>
       <c r="DI9" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.35</v>
+        <v>6.28</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DM9" t="n">
-        <v>50.29</v>
+        <v>50.22</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.53</v>
+        <v>11.5</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.7</v>
+        <v>10.44</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.77</v>
+        <v>52.06</v>
       </c>
       <c r="DW9" t="n">
         <v>0.11</v>
@@ -4581,19 +4581,19 @@
         <v>16</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.47</v>
+        <v>10.39</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.53</v>
+        <v>5.61</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.82</v>
+        <v>17.83</v>
       </c>
       <c r="EB9" t="n">
         <v>1.76</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0.25</v>
@@ -4696,115 +4696,115 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>84</v>
+        <v>83.2</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.44</v>
+        <v>36.6</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.56</v>
+        <v>13.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.78</v>
+        <v>10.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.33</v>
+        <v>8.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>43.11</v>
+        <v>43.7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.11</v>
+        <v>5.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.11</v>
+        <v>19.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.88</v>
+        <v>11.06</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="BJ10" t="n">
         <v>1.06</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.53</v>
+        <v>5.56</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4813,19 +4813,19 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BU10" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV10" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW10" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BX10" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY10" t="n">
         <v>3.53</v>
@@ -4834,16 +4834,16 @@
         <v>3.74</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.47</v>
+        <v>4.43</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.72</v>
+        <v>4.66</v>
       </c>
       <c r="CC10" t="n">
-        <v>6.35</v>
+        <v>6.15</v>
       </c>
       <c r="CD10" t="n">
-        <v>7.29</v>
+        <v>6.99</v>
       </c>
       <c r="CE10" t="n">
         <v>1.27</v>
@@ -4852,10 +4852,10 @@
         <v>2.29</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI10" t="n">
         <v>2.22</v>
@@ -4867,22 +4867,22 @@
         <v>1.36</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CO10" t="n">
         <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CR10" t="n">
         <v>1.34</v>
@@ -4906,64 +4906,64 @@
         <v>1.46</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.59</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC10" t="n">
         <v>1.61</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="DH10" t="n">
-        <v>85.47</v>
+        <v>84.94</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.17</v>
+        <v>39.11</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.65</v>
+        <v>12.83</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.12</v>
+        <v>10.83</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.76</v>
+        <v>7.83</v>
       </c>
       <c r="DS10" t="n">
         <v>0.11</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.18</v>
+        <v>43.5</v>
       </c>
       <c r="DW10" t="n">
         <v>0.11</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.64</v>
+        <v>11.33</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.29</v>
+        <v>7.11</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.35</v>
+        <v>4.22</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.29</v>
+        <v>17.61</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5096,139 +5096,139 @@
         <v>1.78</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>96.33</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>13.11</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO11" t="n">
         <v>1</v>
       </c>
-      <c r="AH11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>96.75</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>42.25</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12.88</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>48.62</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>22.88</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BP11" t="n">
-        <v>4.24</v>
+        <v>4.11</v>
       </c>
       <c r="BQ11" t="n">
         <v>5.06</v>
       </c>
       <c r="BR11" t="n">
-        <v>100</v>
+        <v>94.44</v>
       </c>
       <c r="BS11" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX11" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
         <v>3.03</v>
@@ -5237,31 +5237,31 @@
         <v>3.16</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.26</v>
+        <v>5.2</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.53</v>
+        <v>5.51</v>
       </c>
       <c r="CE11" t="n">
         <v>1.3</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.67</v>
@@ -5270,10 +5270,10 @@
         <v>1.46</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN11" t="n">
         <v>1.94</v>
@@ -5282,10 +5282,10 @@
         <v>1.2</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CR11" t="n">
         <v>1.36</v>
@@ -5306,67 +5306,67 @@
         <v>1.7</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY11" t="n">
         <v>1.81</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DA11" t="n">
         <v>2</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE11" t="n">
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="DH11" t="n">
-        <v>91.65000000000001</v>
+        <v>91.72</v>
       </c>
       <c r="DI11" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.47</v>
+        <v>5.39</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="DM11" t="n">
         <v>43</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.47</v>
+        <v>11.16</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.41</v>
+        <v>13.06</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.47</v>
+        <v>7.78</v>
       </c>
       <c r="DS11" t="n">
         <v>0.11</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.82</v>
+        <v>49.56</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.59</v>
+        <v>13.39</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.65</v>
+        <v>9.56</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.06</v>
+        <v>20.28</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="12">
@@ -6097,7 +6097,7 @@
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CT13" t="n">
         <v>3.34</v>
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="H14" t="n">
-        <v>119.5</v>
+        <v>119.11</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="K14" t="n">
-        <v>7.62</v>
+        <v>7.44</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M14" t="n">
-        <v>68.38</v>
+        <v>67.56</v>
       </c>
       <c r="N14" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="O14" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="P14" t="n">
-        <v>10.62</v>
+        <v>10.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.25</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="S14" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="U14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>64.12</v>
+        <v>62.56</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.25</v>
+        <v>20.67</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.75</v>
+        <v>13.11</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.5</v>
+        <v>7.56</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.25</v>
+        <v>18.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AF14" t="n">
         <v>0.22</v>
@@ -6386,16 +6386,16 @@
         <v>1.89</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.29</v>
+        <v>4.39</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.88</v>
+        <v>10.83</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.29</v>
+        <v>4.39</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="BK14" t="n">
         <v>1.06</v>
@@ -6404,40 +6404,40 @@
         <v>1</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.29</v>
+        <v>6.33</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT14" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BU14" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BV14" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BW14" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BX14" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY14" t="n">
         <v>1.2</v>
@@ -6446,10 +6446,10 @@
         <v>1.2</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.49</v>
+        <v>6.57</v>
       </c>
       <c r="CB14" t="n">
-        <v>7.05</v>
+        <v>7.21</v>
       </c>
       <c r="CC14" t="n">
         <v>1.73</v>
@@ -6461,28 +6461,28 @@
         <v>1.16</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.56</v>
+        <v>4.58</v>
       </c>
       <c r="CH14" t="n">
         <v>1.93</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CN14" t="n">
         <v>2.21</v>
@@ -6494,7 +6494,7 @@
         <v>1.31</v>
       </c>
       <c r="CQ14" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
@@ -6505,18 +6505,18 @@
         <v>1.96</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DB14" t="n">
         <v>1.11</v>
@@ -6525,82 +6525,82 @@
         <v>1.3</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="DH14" t="n">
-        <v>107.06</v>
+        <v>107.56</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.11</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.59</v>
+        <v>6.56</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM14" t="n">
-        <v>59.06</v>
+        <v>59.17</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.88</v>
+        <v>10.84</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.59</v>
+        <v>8.5</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.47</v>
+        <v>7.44</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.88</v>
+        <v>59.34</v>
       </c>
       <c r="DW14" t="n">
         <v>0.06</v>
       </c>
       <c r="DX14" t="n">
-        <v>17.59</v>
+        <v>17.5</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.41</v>
+        <v>10.27</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7.18</v>
+        <v>7.22</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.7</v>
+        <v>17.72</v>
       </c>
       <c r="EB14" t="n">
         <v>2.04</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="15">
@@ -6610,94 +6610,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="G15" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="H15" t="n">
-        <v>93.33</v>
+        <v>93.5</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="K15" t="n">
-        <v>4.22</v>
+        <v>4.7</v>
       </c>
       <c r="L15" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="M15" t="n">
-        <v>41.78</v>
+        <v>42.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>8.33</v>
+        <v>8.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>10.56</v>
+        <v>11.1</v>
       </c>
       <c r="R15" t="n">
-        <v>9.67</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.44</v>
+        <v>12.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.44</v>
+        <v>8</v>
       </c>
       <c r="AB15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>15.56</v>
+        <v>15.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6781,70 +6781,70 @@
         <v>2.38</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.71</v>
+        <v>11.83</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.82</v>
+        <v>4.89</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.88</v>
+        <v>6.94</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV15" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW15" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX15" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="CC15" t="n">
         <v>4.26</v>
@@ -6865,22 +6865,22 @@
         <v>1.56</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CK15" t="n">
         <v>1.35</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM15" t="n">
         <v>2.88</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CO15" t="n">
         <v>1.18</v>
@@ -6889,7 +6889,7 @@
         <v>1.63</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
@@ -6911,11 +6911,11 @@
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CZ15" t="inlineStr"/>
       <c r="DA15" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DB15" t="n">
         <v>1.19</v>
@@ -6927,79 +6927,79 @@
         <v>2.54</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF15" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="DH15" t="n">
-        <v>89.88</v>
+        <v>90.17</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.35</v>
+        <v>4.61</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.41</v>
+        <v>43.89</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DP15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.24</v>
+        <v>10.56</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.470000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.94</v>
+        <v>46.22</v>
       </c>
       <c r="DW15" t="n">
         <v>0.11</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.88</v>
+        <v>13.39</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.470000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.41</v>
+        <v>4.67</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.12</v>
+        <v>15.22</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="16">
@@ -7009,61 +7009,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F16" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="H16" t="n">
-        <v>83.11</v>
+        <v>82.3</v>
       </c>
       <c r="I16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="K16" t="n">
-        <v>5.22</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M16" t="n">
-        <v>45.11</v>
+        <v>44.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>10.33</v>
+        <v>9.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.22</v>
+        <v>10.7</v>
       </c>
       <c r="R16" t="n">
-        <v>7.11</v>
+        <v>6.7</v>
       </c>
       <c r="S16" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7075,28 +7075,28 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>45.67</v>
+        <v>44.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.89</v>
+        <v>14.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.89</v>
+        <v>5.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.22</v>
+        <v>19</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7180,70 +7180,70 @@
         <v>1.88</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.24</v>
+        <v>11.22</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.82</v>
+        <v>5.61</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.41</v>
+        <v>5.61</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS16" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX16" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.84</v>
+        <v>4.78</v>
       </c>
       <c r="CC16" t="n">
         <v>9.26</v>
@@ -7258,7 +7258,7 @@
         <v>2.29</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CH16" t="n">
         <v>1.6</v>
@@ -7276,10 +7276,10 @@
         <v>1.71</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
@@ -7288,7 +7288,7 @@
         <v>1.57</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
@@ -7306,13 +7306,13 @@
         <v>2.36</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.37</v>
@@ -7327,49 +7327,49 @@
         <v>1.6</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>81.53</v>
+        <v>81.17</v>
       </c>
       <c r="DI16" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.94</v>
+        <v>5.11</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.47</v>
+        <v>41.34</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.88</v>
+        <v>10.61</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.82</v>
+        <v>10.56</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
@@ -7381,28 +7381,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.65</v>
+        <v>43.17</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.18</v>
+        <v>12.83</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.529999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.65</v>
+        <v>4.56</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.35</v>
+        <v>18.28</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="17">
@@ -7697,13 +7697,13 @@
         <v>1.35</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CT17" t="n">
         <v>3.31</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV17" t="n">
         <v>2.33</v>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.38</v>
@@ -1469,139 +1469,139 @@
         <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>99.56</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="AM2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BM2" t="n">
         <v>0.89</v>
       </c>
-      <c r="AN2" t="n">
-        <v>47.33</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7.44</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>55.22</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>15.22</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.88</v>
-      </c>
       <c r="BN2" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO2" t="n">
         <v>2</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.76</v>
+        <v>4.67</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.82</v>
+        <v>5.89</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT2" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BU2" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BV2" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW2" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX2" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY2" t="n">
         <v>1.7</v>
@@ -1616,10 +1616,10 @@
         <v>4.79</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="CE2" t="n">
         <v>1.23</v>
@@ -1628,7 +1628,7 @@
         <v>2.16</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CH2" t="n">
         <v>1.65</v>
@@ -1652,7 +1652,7 @@
         <v>2.03</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="CP2" t="n">
         <v>1.49</v>
@@ -1673,7 +1673,7 @@
         <v>1.71</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CW2" t="n">
         <v>1.63</v>
@@ -1685,10 +1685,10 @@
         <v>1.77</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB2" t="n">
         <v>1.16</v>
@@ -1700,79 +1700,79 @@
         <v>2.28</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.59</v>
+        <v>3.67</v>
       </c>
       <c r="DH2" t="n">
-        <v>102</v>
+        <v>101.5</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.36</v>
+        <v>6.39</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.53</v>
+        <v>49.78</v>
       </c>
       <c r="DN2" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.65</v>
+        <v>10.72</v>
       </c>
       <c r="DR2" t="n">
         <v>7.05</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.06</v>
+        <v>54</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.88</v>
+        <v>16.61</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.59</v>
+        <v>10.45</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6.29</v>
+        <v>6.17</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.41</v>
+        <v>16.5</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="H3" t="n">
-        <v>103.22</v>
+        <v>101.5</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="K3" t="n">
-        <v>5.78</v>
+        <v>5.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O3" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="P3" t="n">
-        <v>10.78</v>
+        <v>10.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.33</v>
+        <v>13.6</v>
       </c>
       <c r="R3" t="n">
-        <v>6.22</v>
+        <v>6.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>56.78</v>
+        <v>56.2</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.67</v>
+        <v>9</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.33</v>
+        <v>6.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="AD3" t="n">
         <v>1.79</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF3" t="n">
         <v>0.11</v>
@@ -1953,37 +1953,37 @@
         <v>2.44</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.56</v>
+        <v>10.32</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.72</v>
+        <v>4.68</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.83</v>
+        <v>5.63</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,31 +1992,31 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU3" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BV3" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX3" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="BZ3" t="n">
         <v>1.69</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.65</v>
+        <v>4.61</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="CC3" t="n">
         <v>2.35</v>
@@ -2031,7 +2031,7 @@
         <v>2.19</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CH3" t="n">
         <v>1.67</v>
@@ -2040,40 +2040,40 @@
         <v>2.31</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL3" t="n">
         <v>1.83</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO3" t="n">
         <v>1.13</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CT3" t="n">
         <v>3.32</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CV3" t="n">
         <v>2.41</v>
@@ -2085,97 +2085,97 @@
         <v>1.51</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.46</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB3" t="n">
         <v>1.16</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DD3" t="n">
         <v>2.28</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.5</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ3" t="n">
         <v>2</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.34</v>
+        <v>5.11</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="DM3" t="n">
-        <v>52.78</v>
+        <v>51.84</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.67</v>
+        <v>10.69</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.27</v>
+        <v>12.47</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.66</v>
+        <v>6.74</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.39</v>
+        <v>57.05</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.89</v>
+        <v>15.05</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.56</v>
+        <v>8.73</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.33</v>
+        <v>6.31</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.44</v>
+        <v>16.1</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="H4" t="n">
-        <v>92.22</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>33.89</v>
+        <v>35.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="P4" t="n">
-        <v>13.11</v>
+        <v>12.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>10.22</v>
+        <v>9.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>44.33</v>
+        <v>46.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.11</v>
+        <v>12.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.109999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AC4" t="n">
-        <v>17</v>
+        <v>17.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
         <v>0.12</v>
@@ -2356,70 +2356,70 @@
         <v>1.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.289999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.18</v>
+        <v>4.39</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.12</v>
+        <v>4.94</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT4" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV4" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX4" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.56</v>
+        <v>3.44</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
       <c r="CC4" t="n">
         <v>5.73</v>
@@ -2431,13 +2431,13 @@
         <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CI4" t="n">
         <v>2.31</v>
@@ -2449,103 +2449,103 @@
         <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO4" t="n">
         <v>1.16</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX4" t="n">
         <v>1.49</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.49</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="DH4" t="n">
-        <v>91.34999999999999</v>
+        <v>92.45</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DM4" t="n">
-        <v>37.71</v>
+        <v>38.44</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.59</v>
+        <v>0.55</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.53</v>
+        <v>13.39</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9</v>
+        <v>8.94</v>
       </c>
       <c r="DR4" t="n">
-        <v>9</v>
+        <v>8.66</v>
       </c>
       <c r="DS4" t="n">
         <v>0.11</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.65</v>
+        <v>45.61</v>
       </c>
       <c r="DW4" t="n">
         <v>0.17</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.88</v>
+        <v>11.94</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.71</v>
+        <v>7.83</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.18</v>
+        <v>17.61</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="G5" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="H5" t="n">
-        <v>99.11</v>
+        <v>101.1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="n">
-        <v>7.67</v>
+        <v>7.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="M5" t="n">
-        <v>53.22</v>
+        <v>56</v>
       </c>
       <c r="N5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
-        <v>9.890000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="Q5" t="n">
         <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>53.22</v>
+        <v>53.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.22</v>
+        <v>19.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.56</v>
+        <v>12.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.67</v>
+        <v>7.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.56</v>
+        <v>18.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AF5" t="n">
         <v>0.11</v>
@@ -2759,58 +2759,58 @@
         <v>1.89</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.72</v>
+        <v>3.89</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.22</v>
+        <v>11.11</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.72</v>
+        <v>3.89</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.11</v>
+        <v>5.05</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.11</v>
+        <v>6.05</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT5" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BU5" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BV5" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BW5" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BX5" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY5" t="n">
         <v>1.45</v>
@@ -2822,7 +2822,7 @@
         <v>4.92</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.24</v>
+        <v>5.2</v>
       </c>
       <c r="CC5" t="n">
         <v>1.86</v>
@@ -2834,13 +2834,13 @@
         <v>1.23</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CG5" t="n">
         <v>3.81</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CI5" t="n">
         <v>2.24</v>
@@ -2849,16 +2849,16 @@
         <v>1.65</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CO5" t="n">
         <v>1.14</v>
@@ -2867,7 +2867,7 @@
         <v>1.49</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CR5" t="n">
         <v>1.33</v>
@@ -2891,13 +2891,13 @@
         <v>1.52</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.45</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="DB5" t="n">
         <v>1.16</v>
@@ -2906,82 +2906,82 @@
         <v>1.51</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.56</v>
+        <v>102.47</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.44</v>
+        <v>7.53</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DM5" t="n">
-        <v>55.28</v>
+        <v>56.63</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="DP5" t="n">
-        <v>9.5</v>
+        <v>9.32</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.78</v>
+        <v>10.79</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.94</v>
+        <v>6.89</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53.78</v>
+        <v>53.89</v>
       </c>
       <c r="DW5" t="n">
         <v>0.16</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.72</v>
+        <v>17.95</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.28</v>
+        <v>11.21</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.44</v>
+        <v>6.74</v>
       </c>
       <c r="EA5" t="n">
-        <v>19</v>
+        <v>18.84</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="F6" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
-        <v>89</v>
+        <v>87.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="K6" t="n">
-        <v>5.56</v>
+        <v>5.4</v>
       </c>
       <c r="L6" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>43.11</v>
+        <v>41</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>14.44</v>
+        <v>14</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.89</v>
+        <v>10.9</v>
       </c>
       <c r="R6" t="n">
-        <v>6.78</v>
+        <v>7.3</v>
       </c>
       <c r="S6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>46.33</v>
+        <v>44.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.89</v>
+        <v>15.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.89</v>
+        <v>11.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.89</v>
+        <v>15.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0.11</v>
@@ -3162,70 +3162,70 @@
         <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.89</v>
+        <v>11.26</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="BJ6" t="n">
         <v>1.11</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BM6" t="n">
         <v>0.89</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BP6" t="n">
-        <v>5</v>
+        <v>5.26</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.83</v>
+        <v>5.95</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT6" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU6" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV6" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW6" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX6" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.09</v>
+        <v>3.43</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.05</v>
+        <v>3.27</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.02</v>
+        <v>4.1</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="CC6" t="n">
         <v>5.79</v>
@@ -3237,10 +3237,10 @@
         <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="CH6" t="n">
         <v>1.54</v>
@@ -3252,31 +3252,31 @@
         <v>1.65</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CO6" t="n">
         <v>1.19</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CT6" t="n">
         <v>3.19</v>
@@ -3294,64 +3294,64 @@
         <v>1.5</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.49</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="DB6" t="n">
         <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="DH6" t="n">
-        <v>90.72</v>
+        <v>90</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.72</v>
+        <v>4.68</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM6" t="n">
-        <v>39</v>
+        <v>38.11</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.72</v>
+        <v>13.53</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.06</v>
+        <v>11.05</v>
       </c>
       <c r="DR6" t="n">
-        <v>8</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DS6" t="n">
         <v>0.11</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.61</v>
+        <v>45.74</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.5</v>
+        <v>13.1</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.84</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.66</v>
+        <v>4.47</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.39</v>
+        <v>16.95</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0.22</v>
@@ -3484,52 +3484,52 @@
         <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>97.44</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>42.67</v>
+        <v>42.3</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.56</v>
+        <v>10.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.33</v>
+        <v>8.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.33</v>
+        <v>9.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>51.22</v>
+        <v>51</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.56</v>
+        <v>9.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.33</v>
+        <v>19.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.89</v>
+        <v>10.63</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.72</v>
+        <v>4.68</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.06</v>
+        <v>5.84</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BU7" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BV7" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY7" t="n">
         <v>2.85</v>
@@ -3625,28 +3625,28 @@
         <v>3.05</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="CB7" t="n">
         <v>4.28</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.29</v>
+        <v>4.32</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="CE7" t="n">
         <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CI7" t="n">
         <v>2.43</v>
@@ -3688,7 +3688,7 @@
         <v>1.69</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CW7" t="n">
         <v>1.56</v>
@@ -3715,79 +3715,79 @@
         <v>2.41</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="DH7" t="n">
-        <v>97.33</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.33</v>
+        <v>5.31</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM7" t="n">
-        <v>47</v>
+        <v>46.58</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.390000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.77</v>
+        <v>9.84</v>
       </c>
       <c r="DR7" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.06</v>
+        <v>51.9</v>
       </c>
       <c r="DW7" t="n">
         <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.34</v>
+        <v>11.26</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.33</v>
+        <v>6.21</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.77</v>
+        <v>18.53</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0.11</v>
@@ -3887,139 +3887,139 @@
         <v>1.67</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AI8" t="n">
-        <v>100.67</v>
+        <v>99.7</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.78</v>
+        <v>4.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>39.33</v>
+        <v>39.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.89</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AT8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="BE8" t="n">
         <v>1.67</v>
       </c>
-      <c r="AU8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>47.11</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>20.67</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.69</v>
-      </c>
       <c r="BF8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.33</v>
+        <v>10.26</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.17</v>
+        <v>5.11</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU8" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX8" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY8" t="n">
         <v>2.04</v>
@@ -4028,25 +4028,25 @@
         <v>2.12</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.12</v>
+        <v>4.09</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.87</v>
+        <v>4.72</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="CE8" t="n">
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CH8" t="n">
         <v>1.49</v>
@@ -4055,25 +4055,25 @@
         <v>2.06</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK8" t="n">
         <v>1.53</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO8" t="n">
         <v>1.23</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CQ8" t="n">
         <v>2.8</v>
@@ -4082,82 +4082,82 @@
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CT8" t="n">
         <v>3.2</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV8" t="n">
         <v>2.14</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX8" t="n">
         <v>1.58</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.32</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB8" t="n">
         <v>1.25</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="DH8" t="n">
-        <v>109.28</v>
+        <v>108.32</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.11</v>
+        <v>6.1</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DM8" t="n">
-        <v>45.38</v>
+        <v>45.16</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.94</v>
+        <v>11.05</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.5</v>
+        <v>10.53</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.22</v>
+        <v>7</v>
       </c>
       <c r="DS8" t="n">
         <v>0.16</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.94</v>
+        <v>51.53</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.44</v>
+        <v>16.21</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.11</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.34</v>
+        <v>6.32</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.17</v>
+        <v>21.26</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="G9" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>105.89</v>
+        <v>106.2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="K9" t="n">
-        <v>6.22</v>
+        <v>5.9</v>
       </c>
       <c r="L9" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="M9" t="n">
-        <v>57</v>
+        <v>55.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="O9" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="P9" t="n">
-        <v>9.56</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.56</v>
+        <v>10.8</v>
       </c>
       <c r="R9" t="n">
-        <v>6.33</v>
+        <v>6.3</v>
       </c>
       <c r="S9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="U9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>52.33</v>
+        <v>52.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.33</v>
+        <v>16.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.89</v>
+        <v>11</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.56</v>
+        <v>17</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>1.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.67</v>
+        <v>10.58</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BP9" t="n">
         <v>5.11</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.5</v>
+        <v>5.42</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BU9" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV9" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX9" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="CC9" t="n">
         <v>3.33</v>
@@ -4446,58 +4446,58 @@
         <v>1.27</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK9" t="n">
         <v>1.44</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CN9" t="n">
         <v>2.04</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
@@ -4512,55 +4512,55 @@
         <v>2.08</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF9" t="n">
         <v>1.11</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="DH9" t="n">
-        <v>101.44</v>
+        <v>101.84</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.28</v>
+        <v>6.1</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DM9" t="n">
-        <v>50.22</v>
+        <v>49.95</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO9" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.5</v>
+        <v>11.47</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.44</v>
+        <v>10.58</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.83</v>
+        <v>6.79</v>
       </c>
       <c r="DS9" t="n">
         <v>0.16</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.06</v>
+        <v>52.26</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX9" t="n">
         <v>16</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.39</v>
+        <v>10.47</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.61</v>
+        <v>5.53</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.83</v>
+        <v>18.47</v>
       </c>
       <c r="EB9" t="n">
         <v>1.76</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F10" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="G10" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="H10" t="n">
-        <v>87.12</v>
+        <v>90.22</v>
       </c>
       <c r="I10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="L10" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="M10" t="n">
-        <v>42.25</v>
+        <v>42.11</v>
       </c>
       <c r="N10" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O10" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="P10" t="n">
-        <v>11.62</v>
+        <v>11.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.5</v>
+        <v>11.78</v>
       </c>
       <c r="R10" t="n">
-        <v>7.12</v>
+        <v>7.33</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>43.25</v>
+        <v>43.89</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.62</v>
+        <v>14.22</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.619999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="AB10" t="n">
-        <v>6</v>
+        <v>5.56</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.25</v>
+        <v>15.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,37 +4774,37 @@
         <v>2.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BH10" t="n">
-        <v>11.06</v>
+        <v>10.79</v>
       </c>
       <c r="BI10" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.56</v>
+        <v>5.47</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.5</v>
+        <v>5.32</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4813,25 +4813,25 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV10" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW10" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BX10" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.53</v>
+        <v>3.84</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.74</v>
+        <v>4.05</v>
       </c>
       <c r="CA10" t="n">
         <v>4.43</v>
@@ -4849,28 +4849,28 @@
         <v>1.27</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CH10" t="n">
         <v>1.59</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK10" t="n">
         <v>1.36</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CN10" t="n">
         <v>2.19</v>
@@ -4882,7 +4882,7 @@
         <v>1.6</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CR10" t="n">
         <v>1.34</v>
@@ -4897,10 +4897,10 @@
         <v>1.61</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX10" t="n">
         <v>1.46</v>
@@ -4912,28 +4912,28 @@
         <v>2.59</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC10" t="n">
         <v>1.61</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DH10" t="n">
-        <v>84.94</v>
+        <v>86.53</v>
       </c>
       <c r="DI10" t="n">
         <v>0.05</v>
@@ -4942,58 +4942,58 @@
         <v>2.16</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.11</v>
+        <v>39.21</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.83</v>
+        <v>12.79</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.83</v>
+        <v>11</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.83</v>
+        <v>7.89</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.5</v>
+        <v>43.79</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.33</v>
+        <v>11.31</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.11</v>
+        <v>7.21</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.22</v>
+        <v>4.11</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.61</v>
+        <v>17.74</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="EC10" t="n">
         <v>2</v>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
@@ -5021,79 +5021,79 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="H11" t="n">
-        <v>87.11</v>
+        <v>88</v>
       </c>
       <c r="I11" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>5.22</v>
+        <v>4.9</v>
       </c>
       <c r="L11" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="M11" t="n">
-        <v>43.67</v>
+        <v>43</v>
       </c>
       <c r="N11" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="O11" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>10.22</v>
+        <v>10.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.44</v>
+        <v>13.6</v>
       </c>
       <c r="R11" t="n">
-        <v>6.78</v>
+        <v>6.6</v>
       </c>
       <c r="S11" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>50.89</v>
+        <v>50.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.67</v>
+        <v>13.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.67</v>
+        <v>9.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>17.56</v>
+        <v>18.5</v>
       </c>
       <c r="AD11" t="n">
         <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
         <v>0.11</v>
@@ -5177,70 +5177,70 @@
         <v>1.67</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.33</v>
+        <v>2.58</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.17</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.33</v>
+        <v>2.58</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BP11" t="n">
         <v>4.11</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.06</v>
+        <v>4.84</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU11" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BV11" t="n">
-        <v>5.56</v>
+        <v>10.53</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.56</v>
+        <v>10.53</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.19</v>
+        <v>4.16</v>
       </c>
       <c r="CC11" t="n">
         <v>5.2</v>
@@ -5255,16 +5255,16 @@
         <v>2.49</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH11" t="n">
         <v>1.51</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK11" t="n">
         <v>1.46</v>
@@ -5285,13 +5285,13 @@
         <v>1.71</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CR11" t="n">
         <v>1.36</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CT11" t="n">
         <v>3.25</v>
@@ -5300,7 +5300,7 @@
         <v>1.54</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CW11" t="n">
         <v>1.7</v>
@@ -5324,82 +5324,82 @@
         <v>1.73</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="DH11" t="n">
-        <v>91.72</v>
+        <v>91.95</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.39</v>
+        <v>5.21</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="DM11" t="n">
-        <v>43</v>
+        <v>42.68</v>
       </c>
       <c r="DN11" t="n">
         <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.16</v>
+        <v>11.26</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.06</v>
+        <v>13.16</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.78</v>
+        <v>7.63</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.56</v>
+        <v>49.37</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.39</v>
+        <v>13.42</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.56</v>
+        <v>9.52</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.28</v>
+        <v>20.63</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0.38</v>
@@ -5499,52 +5499,52 @@
         <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>106.89</v>
+        <v>107.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AL12" t="n">
-        <v>5.33</v>
+        <v>5.1</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.44</v>
+        <v>56.7</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.22</v>
+        <v>13.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>10.22</v>
+        <v>10.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.78</v>
+        <v>5.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>60.67</v>
+        <v>60</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>16.33</v>
+        <v>15.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.220000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.11</v>
+        <v>7.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>22.11</v>
+        <v>22.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.24</v>
+        <v>4.39</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.710000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.24</v>
+        <v>4.39</v>
       </c>
       <c r="BJ12" t="n">
         <v>1</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5</v>
+        <v>4.78</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT12" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BV12" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BW12" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BX12" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BY12" t="n">
         <v>2.34</v>
@@ -5640,31 +5640,31 @@
         <v>2.53</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CE12" t="n">
         <v>1.25</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.5</v>
@@ -5673,10 +5673,10 @@
         <v>1.4</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CN12" t="n">
         <v>2.07</v>
@@ -5685,28 +5685,28 @@
         <v>1.15</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CR12" t="n">
         <v>1.34</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CT12" t="n">
         <v>3.34</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CX12" t="n">
         <v>1.49</v>
@@ -5718,91 +5718,91 @@
         <v>2.5</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DB12" t="n">
         <v>1.16</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="DH12" t="n">
-        <v>106.29</v>
+        <v>106.55</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.35</v>
+        <v>5.22</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DM12" t="n">
-        <v>53.82</v>
+        <v>52.11</v>
       </c>
       <c r="DN12" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.29</v>
+        <v>12.44</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.29</v>
+        <v>12.33</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.41</v>
+        <v>5.5</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>56.83</v>
+        <v>56.67</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.82</v>
+        <v>15.56</v>
       </c>
       <c r="DY12" t="n">
-        <v>9</v>
+        <v>8.67</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.82</v>
+        <v>6.89</v>
       </c>
       <c r="EA12" t="n">
-        <v>21</v>
+        <v>21.22</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="F13" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="G13" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>81.5</v>
+        <v>85.22</v>
       </c>
       <c r="I13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J13" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="K13" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="L13" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>34.75</v>
+        <v>34.67</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="P13" t="n">
-        <v>10.88</v>
+        <v>11</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.5</v>
+        <v>12.67</v>
       </c>
       <c r="R13" t="n">
-        <v>11.25</v>
+        <v>10.67</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>37.12</v>
+        <v>38.22</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.119999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.62</v>
+        <v>17.11</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AF13" t="n">
         <v>0.2</v>
@@ -5983,70 +5983,70 @@
         <v>2.1</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.720000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.67</v>
+        <v>4.79</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU13" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW13" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX13" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.44</v>
+        <v>3.72</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.68</v>
+        <v>3.91</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.28</v>
+        <v>4.31</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.53</v>
+        <v>4.54</v>
       </c>
       <c r="CC13" t="n">
         <v>6.04</v>
@@ -6058,28 +6058,28 @@
         <v>1.27</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="CH13" t="n">
         <v>1.58</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK13" t="n">
         <v>1.44</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CN13" t="n">
         <v>2</v>
@@ -6091,7 +6091,7 @@
         <v>1.59</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6112,13 +6112,13 @@
         <v>1.64</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY13" t="n">
         <v>1.81</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DA13" t="n">
         <v>2</v>
@@ -6127,52 +6127,52 @@
         <v>1.19</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="DH13" t="n">
-        <v>77.56</v>
+        <v>79.53</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="DK13" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DM13" t="n">
-        <v>31.83</v>
+        <v>31.95</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.45</v>
+        <v>10.53</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.67</v>
+        <v>12.74</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.89</v>
+        <v>10.63</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>41.5</v>
+        <v>41.79</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX13" t="n">
-        <v>8.16</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.33</v>
+        <v>5.42</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.16</v>
+        <v>16</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0.44</v>
@@ -6305,52 +6305,52 @@
         <v>0.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AI14" t="n">
-        <v>96</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.67</v>
+        <v>6.5</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AN14" t="n">
-        <v>50.78</v>
+        <v>55.3</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.89</v>
+        <v>2.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.890000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.56</v>
+        <v>8.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>56.11</v>
+        <v>57.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.33</v>
+        <v>14.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.44</v>
+        <v>7.7</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.89</v>
+        <v>7</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.22</v>
+        <v>18</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.83</v>
+        <v>11.21</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BL14" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.5</v>
+        <v>4.79</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.33</v>
+        <v>6.42</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BU14" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BV14" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BW14" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BX14" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY14" t="n">
         <v>1.2</v>
@@ -6446,31 +6446,31 @@
         <v>1.2</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.57</v>
+        <v>6.51</v>
       </c>
       <c r="CB14" t="n">
-        <v>7.21</v>
+        <v>7.08</v>
       </c>
       <c r="CC14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CD14" t="n">
         <v>1.73</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>1.75</v>
       </c>
       <c r="CE14" t="n">
         <v>1.16</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.57</v>
@@ -6479,13 +6479,13 @@
         <v>1.34</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CO14" t="n">
         <v>1.06</v>
@@ -6494,21 +6494,21 @@
         <v>1.31</v>
       </c>
       <c r="CQ14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CV14" t="n">
         <v>2.5</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
@@ -6516,91 +6516,91 @@
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DB14" t="n">
         <v>1.11</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="DH14" t="n">
-        <v>107.56</v>
+        <v>109</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.56</v>
+        <v>6.95</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="DM14" t="n">
-        <v>59.17</v>
+        <v>61.11</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.78</v>
+        <v>3.11</v>
       </c>
       <c r="DP14" t="n">
         <v>10.84</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.5</v>
+        <v>8.58</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.44</v>
+        <v>7.52</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.34</v>
+        <v>59.9</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX14" t="n">
-        <v>17.5</v>
+        <v>17.53</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.27</v>
+        <v>10.26</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7.22</v>
+        <v>7.27</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.72</v>
+        <v>18.1</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="15">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0.1</v>
@@ -6703,136 +6703,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AI15" t="n">
-        <v>86</v>
+        <v>87.22</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN15" t="n">
-        <v>45.25</v>
+        <v>42.67</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.119999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.880000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.25</v>
+        <v>9.44</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>47</v>
+        <v>46.67</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA15" t="n">
-        <v>14.5</v>
+        <v>14.33</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.619999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="BD15" t="n">
-        <v>14.62</v>
+        <v>14.67</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.83</v>
+        <v>11.68</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="BO15" t="n">
         <v>1.11</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.89</v>
+        <v>4.84</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.94</v>
+        <v>6.84</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU15" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV15" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BW15" t="n">
-        <v>16.67</v>
+        <v>21.05</v>
       </c>
       <c r="BX15" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BY15" t="n">
         <v>2.82</v>
@@ -6841,28 +6841,28 @@
         <v>2.93</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.26</v>
+        <v>4.57</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.64</v>
+        <v>4.82</v>
       </c>
       <c r="CE15" t="n">
         <v>1.27</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CI15" t="n">
         <v>2.33</v>
@@ -6871,102 +6871,102 @@
         <v>1.58</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CO15" t="n">
         <v>1.18</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CT15" t="n">
         <v>3.26</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CW15" t="n">
         <v>1.58</v>
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CZ15" t="inlineStr"/>
       <c r="DA15" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DB15" t="n">
         <v>1.19</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="DH15" t="n">
-        <v>90.17</v>
+        <v>90.53</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.61</v>
+        <v>4.37</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.89</v>
+        <v>42.74</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.83</v>
+        <v>0.95</v>
       </c>
       <c r="DO15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DP15" t="n">
-        <v>8.550000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.56</v>
+        <v>10.31</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.220000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="DS15" t="n">
         <v>0.16</v>
@@ -6978,28 +6978,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.22</v>
+        <v>46.11</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.39</v>
+        <v>13.37</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.720000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.22</v>
+        <v>15.21</v>
       </c>
       <c r="EB15" t="n">
         <v>1.49</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0.2</v>
@@ -7102,49 +7102,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>79.75</v>
+        <v>80.56</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.62</v>
+        <v>4.89</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN16" t="n">
-        <v>37.38</v>
+        <v>37.44</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.5</v>
+        <v>11.11</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.38</v>
+        <v>10.44</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.619999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7156,82 +7156,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>41.38</v>
+        <v>41</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.25</v>
+        <v>11.89</v>
       </c>
       <c r="BB16" t="n">
-        <v>8</v>
+        <v>8.67</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.38</v>
+        <v>17.44</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.22</v>
+        <v>11.16</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.61</v>
+        <v>5.74</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.61</v>
+        <v>5.42</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU16" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BV16" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY16" t="n">
         <v>3.15</v>
@@ -7240,40 +7240,40 @@
         <v>3.11</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.78</v>
+        <v>4.71</v>
       </c>
       <c r="CC16" t="n">
-        <v>9.26</v>
+        <v>8.56</v>
       </c>
       <c r="CD16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK16" t="n">
         <v>1.37</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM16" t="n">
         <v>2.84</v>
@@ -7285,34 +7285,34 @@
         <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CV16" t="n">
         <v>2.36</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.37</v>
@@ -7321,55 +7321,55 @@
         <v>2.17</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DE16" t="n">
         <v>0.11</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="DG16" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DH16" t="n">
-        <v>81.17</v>
+        <v>81.48</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.11</v>
+        <v>5.21</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.34</v>
+        <v>41.16</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.61</v>
+        <v>10.47</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.56</v>
+        <v>10.58</v>
       </c>
       <c r="DR16" t="n">
-        <v>8</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
@@ -7381,28 +7381,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.17</v>
+        <v>42.89</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.83</v>
+        <v>13.05</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.279999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.28</v>
+        <v>18.26</v>
       </c>
       <c r="EB16" t="n">
         <v>1.43</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="17">
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0.11</v>
@@ -7505,136 +7505,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AH17" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AI17" t="n">
-        <v>95.33</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN17" t="n">
-        <v>53.78</v>
+        <v>51.7</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.78</v>
+        <v>12.9</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.22</v>
+        <v>10.3</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.33</v>
+        <v>7.7</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>53</v>
+        <v>52.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BA17" t="n">
-        <v>18.11</v>
+        <v>18.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>11.67</v>
+        <v>11.7</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.44</v>
+        <v>6.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="BF17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.17</v>
+        <v>9</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM17" t="n">
         <v>1</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.56</v>
+        <v>4.42</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT17" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU17" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV17" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY17" t="n">
         <v>2</v>
@@ -7643,16 +7643,16 @@
         <v>2.01</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.28</v>
+        <v>4.3</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="CE17" t="n">
         <v>1.26</v>
@@ -7661,7 +7661,7 @@
         <v>2.3</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CH17" t="n">
         <v>1.58</v>
@@ -7676,13 +7676,13 @@
         <v>1.46</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CO17" t="n">
         <v>1.18</v>
@@ -7691,7 +7691,7 @@
         <v>1.59</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CR17" t="n">
         <v>1.35</v>
@@ -7706,22 +7706,22 @@
         <v>1.58</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX17" t="n">
         <v>1.52</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.45</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DB17" t="n">
         <v>1.2</v>
@@ -7730,82 +7730,82 @@
         <v>1.64</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="DH17" t="n">
-        <v>109.78</v>
+        <v>109.16</v>
       </c>
       <c r="DI17" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.33</v>
+        <v>5.16</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DM17" t="n">
-        <v>60.11</v>
+        <v>58.68</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.78</v>
+        <v>11.9</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.22</v>
+        <v>10.26</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.5</v>
+        <v>6.74</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>55.44</v>
+        <v>55.21</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DX17" t="n">
-        <v>18.89</v>
+        <v>18.84</v>
       </c>
       <c r="DY17" t="n">
-        <v>12.5</v>
+        <v>12.47</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.39</v>
+        <v>6.37</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.5</v>
+        <v>20.74</v>
       </c>
       <c r="EB17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="18">
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7908,49 +7908,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AI18" t="n">
-        <v>107.12</v>
+        <v>105.44</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AL18" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN18" t="n">
-        <v>40.38</v>
+        <v>39.33</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.75</v>
+        <v>11.11</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.25</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.119999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7962,82 +7962,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>51.12</v>
+        <v>51.56</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.88</v>
+        <v>14.11</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.880000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BC18" t="n">
         <v>5</v>
       </c>
       <c r="BD18" t="n">
-        <v>20.5</v>
+        <v>20.33</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="BG18" t="n">
         <v>3</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.82</v>
+        <v>9.67</v>
       </c>
       <c r="BI18" t="n">
         <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BP18" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU18" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV18" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY18" t="n">
         <v>2.21</v>
@@ -8046,25 +8046,25 @@
         <v>2.18</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="CE18" t="n">
         <v>1.31</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CH18" t="n">
         <v>1.52</v>
@@ -8079,13 +8079,13 @@
         <v>1.43</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CO18" t="n">
         <v>1.2</v>
@@ -8094,7 +8094,7 @@
         <v>1.69</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8109,7 +8109,7 @@
         <v>1.54</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW18" t="n">
         <v>1.69</v>
@@ -8118,13 +8118,13 @@
         <v>1.5</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.48</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DB18" t="n">
         <v>1.23</v>
@@ -8133,49 +8133,49 @@
         <v>1.76</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="DH18" t="n">
-        <v>100.23</v>
+        <v>99.78</v>
       </c>
       <c r="DI18" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="DK18" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM18" t="n">
-        <v>39</v>
+        <v>38.56</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.47</v>
+        <v>10.66</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.35</v>
+        <v>11.5</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.47</v>
+        <v>7.34</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8187,28 +8187,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.82</v>
+        <v>48.22</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.77</v>
+        <v>14.84</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.59</v>
+        <v>9.66</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.41</v>
+        <v>20.33</v>
       </c>
       <c r="EB18" t="n">
         <v>1.58</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="19">
@@ -8218,94 +8218,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F19" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="H19" t="n">
-        <v>79.33</v>
+        <v>80.5</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4.44</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="M19" t="n">
-        <v>41.22</v>
+        <v>41.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="P19" t="n">
-        <v>9.890000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.44</v>
+        <v>12.6</v>
       </c>
       <c r="R19" t="n">
-        <v>10.67</v>
+        <v>10.7</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>43.78</v>
+        <v>43.9</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.11</v>
+        <v>11.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.89</v>
+        <v>12.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8389,70 +8389,70 @@
         <v>0.78</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.67</v>
+        <v>10.47</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.89</v>
+        <v>5.74</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BU19" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV19" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY19" t="n">
         <v>4.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.22</v>
+        <v>5.14</v>
       </c>
       <c r="CB19" t="n">
-        <v>5.5</v>
+        <v>5.42</v>
       </c>
       <c r="CC19" t="n">
         <v>8.84</v>
@@ -8464,16 +8464,16 @@
         <v>1.23</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.62</v>
@@ -8491,13 +8491,13 @@
         <v>2.16</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
@@ -8512,7 +8512,7 @@
         <v>1.78</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CW19" t="n">
         <v>1.65</v>
@@ -8530,88 +8530,88 @@
         <v>2.2</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="DH19" t="n">
-        <v>79.22</v>
+        <v>79.84</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.61</v>
+        <v>3.47</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DM19" t="n">
-        <v>37.11</v>
+        <v>37.68</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="DP19" t="n">
-        <v>9.779999999999999</v>
+        <v>10</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.16</v>
+        <v>11.32</v>
       </c>
       <c r="DR19" t="n">
-        <v>10.23</v>
+        <v>10.26</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>44.28</v>
+        <v>44.32</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.22</v>
+        <v>10.05</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.72</v>
+        <v>6.58</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="EA19" t="n">
-        <v>15</v>
+        <v>14.84</v>
       </c>
       <c r="EB19" t="n">
         <v>1.16</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F2" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="G2" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="H2" t="n">
-        <v>104.75</v>
+        <v>105.78</v>
       </c>
       <c r="I2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J2" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="K2" t="n">
-        <v>6.88</v>
+        <v>6.56</v>
       </c>
       <c r="L2" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M2" t="n">
-        <v>54.12</v>
+        <v>54.56</v>
       </c>
       <c r="N2" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="P2" t="n">
-        <v>8.75</v>
+        <v>8.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.25</v>
+        <v>10.22</v>
       </c>
       <c r="R2" t="n">
-        <v>6.62</v>
+        <v>6.33</v>
       </c>
       <c r="S2" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="T2" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="U2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>52.75</v>
+        <v>53.56</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.62</v>
+        <v>17.11</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.88</v>
+        <v>10.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.75</v>
+        <v>6.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.75</v>
+        <v>18.22</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AF2" t="n">
         <v>0.1</v>
@@ -1550,70 +1550,70 @@
         <v>2.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.56</v>
+        <v>10.47</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM2" t="n">
         <v>0.89</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BO2" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.67</v>
+        <v>4.47</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT2" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BU2" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BV2" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW2" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX2" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.64</v>
+        <v>4.69</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.79</v>
+        <v>4.83</v>
       </c>
       <c r="CC2" t="n">
         <v>2.03</v>
@@ -1628,13 +1628,13 @@
         <v>2.16</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="CH2" t="n">
         <v>1.65</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.58</v>
@@ -1646,10 +1646,10 @@
         <v>1.84</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CO2" t="n">
         <v>1.13</v>
@@ -1673,22 +1673,22 @@
         <v>1.71</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX2" t="n">
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.45</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="DB2" t="n">
         <v>1.16</v>
@@ -1700,79 +1700,79 @@
         <v>2.28</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.5</v>
+        <v>102.16</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.39</v>
+        <v>6.27</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.78</v>
+        <v>50.21</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.5</v>
+        <v>10.37</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.72</v>
+        <v>10.68</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.05</v>
+        <v>6.89</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54</v>
+        <v>54.32</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.61</v>
+        <v>16.42</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.45</v>
+        <v>10.37</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6.17</v>
+        <v>6.05</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.5</v>
+        <v>16.79</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0.3</v>
@@ -2275,139 +2275,139 @@
         <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AH4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>89.78</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP4" t="n">
         <v>2</v>
       </c>
-      <c r="AI4" t="n">
-        <v>90.38</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>13.56</v>
       </c>
       <c r="AR4" t="n">
         <v>8</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.62</v>
+        <v>7.67</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>45</v>
+        <v>44.44</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.62</v>
+        <v>11.22</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.25</v>
+        <v>7.11</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.38</v>
+        <v>17.44</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.33</v>
+        <v>9.32</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL4" t="n">
         <v>0.89</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.39</v>
+        <v>4.21</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.94</v>
+        <v>5.11</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT4" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BU4" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV4" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX4" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY4" t="n">
         <v>3.29</v>
@@ -2416,34 +2416,34 @@
         <v>3.44</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.47</v>
+        <v>4.53</v>
       </c>
       <c r="CC4" t="n">
-        <v>5.73</v>
+        <v>6.01</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.12</v>
+        <v>6.4</v>
       </c>
       <c r="CE4" t="n">
         <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CK4" t="n">
         <v>1.4</v>
@@ -2461,10 +2461,10 @@
         <v>1.16</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
@@ -2479,106 +2479,106 @@
         <v>1.63</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX4" t="n">
         <v>1.49</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.49</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB4" t="n">
         <v>1.19</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="DH4" t="n">
-        <v>92.45</v>
+        <v>92.05</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="DK4" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>38.31</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>45.31</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="DZ4" t="n">
         <v>4</v>
       </c>
-      <c r="DL4" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>38.44</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="DQ4" t="n">
-        <v>8.94</v>
-      </c>
-      <c r="DR4" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="DS4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DT4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV4" t="n">
-        <v>45.61</v>
-      </c>
-      <c r="DW4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DX4" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="DY4" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="DZ4" t="n">
-        <v>4.11</v>
-      </c>
       <c r="EA4" t="n">
-        <v>17.61</v>
+        <v>17.63</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="5">
@@ -4272,19 +4272,19 @@
         <v>0.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="AA9" t="n">
         <v>11</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AC9" t="n">
         <v>17</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AE9" t="n">
         <v>1.4</v>
@@ -4578,19 +4578,19 @@
         <v>0.1</v>
       </c>
       <c r="DX9" t="n">
-        <v>16</v>
+        <v>16.05</v>
       </c>
       <c r="DY9" t="n">
         <v>10.47</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.53</v>
+        <v>5.58</v>
       </c>
       <c r="EA9" t="n">
         <v>18.47</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="EC9" t="n">
         <v>1.53</v>
@@ -7962,7 +7962,7 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>51.56</v>
+        <v>51.44</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.22</v>
+        <v>48.16</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
@@ -8284,7 +8284,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -8590,7 +8590,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>44.32</v>
+        <v>44.37</v>
       </c>
       <c r="DW19" t="n">
         <v>0.05</v>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1613,7 +1613,7 @@
         <v>4.69</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.83</v>
+        <v>4.82</v>
       </c>
       <c r="CC2" t="n">
         <v>2.03</v>
@@ -1673,7 +1673,7 @@
         <v>1.71</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CW2" t="n">
         <v>1.64</v>
@@ -1682,13 +1682,13 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.45</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DB2" t="n">
         <v>1.16</v>
@@ -2419,13 +2419,13 @@
         <v>4.33</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="CC4" t="n">
         <v>6.01</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.4</v>
+        <v>6.39</v>
       </c>
       <c r="CE4" t="n">
         <v>1.26</v>
@@ -2482,7 +2482,7 @@
         <v>2.42</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CX4" t="n">
         <v>1.49</v>
@@ -2494,7 +2494,7 @@
         <v>2.49</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DB4" t="n">
         <v>1.19</v>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0.33</v>
@@ -1469,139 +1469,139 @@
         <v>1.89</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.5</v>
+        <v>3.09</v>
       </c>
       <c r="AI2" t="n">
-        <v>98.90000000000001</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AL2" t="n">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.3</v>
+        <v>46.18</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.9</v>
+        <v>12.27</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.1</v>
+        <v>11.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>7.82</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>55</v>
+        <v>54.64</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA2" t="n">
-        <v>15.8</v>
+        <v>15.45</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.1</v>
+        <v>9.91</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="BD2" t="n">
-        <v>15.5</v>
+        <v>15.91</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.47</v>
+        <v>3.35</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.47</v>
+        <v>10.25</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.47</v>
+        <v>3.35</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.47</v>
+        <v>4.2</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6</v>
+        <v>5.65</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT2" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BU2" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BV2" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW2" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX2" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BY2" t="n">
         <v>1.66</v>
@@ -1610,10 +1610,10 @@
         <v>1.72</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.69</v>
+        <v>4.64</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.82</v>
+        <v>4.76</v>
       </c>
       <c r="CC2" t="n">
         <v>2.03</v>
@@ -1625,10 +1625,10 @@
         <v>1.23</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CH2" t="n">
         <v>1.65</v>
@@ -1643,22 +1643,22 @@
         <v>1.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CN2" t="n">
         <v>2.04</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CR2" t="n">
         <v>1.33</v>
@@ -1682,97 +1682,97 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.45</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DB2" t="n">
         <v>1.16</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="DH2" t="n">
-        <v>102.16</v>
+        <v>101.6</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.27</v>
+        <v>6</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.21</v>
+        <v>49.95</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.37</v>
+        <v>10.65</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.68</v>
+        <v>10.8</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.89</v>
+        <v>7.15</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.32</v>
+        <v>54.15</v>
       </c>
       <c r="DW2" t="n">
         <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.42</v>
+        <v>16.2</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.37</v>
+        <v>10.25</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.79</v>
+        <v>16.95</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="H3" t="n">
-        <v>101.5</v>
+        <v>102.09</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3</v>
+        <v>5.73</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="M3" t="n">
-        <v>53</v>
+        <v>58.91</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O3" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>10.8</v>
+        <v>10.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.6</v>
+        <v>13.55</v>
       </c>
       <c r="R3" t="n">
-        <v>6.4</v>
+        <v>6.27</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>56.2</v>
+        <v>57</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.3</v>
+        <v>16.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>9</v>
+        <v>9.73</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="AC3" t="n">
-        <v>16</v>
+        <v>16.09</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AF3" t="n">
         <v>0.11</v>
@@ -1953,37 +1953,37 @@
         <v>2.44</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.32</v>
+        <v>10.3</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.68</v>
+        <v>4.8</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.63</v>
+        <v>5.5</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,31 +1992,31 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU3" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BV3" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX3" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.61</v>
+        <v>4.67</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.78</v>
+        <v>4.85</v>
       </c>
       <c r="CC3" t="n">
         <v>2.35</v>
@@ -2028,16 +2028,16 @@
         <v>1.24</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.6</v>
@@ -2046,22 +2046,22 @@
         <v>1.48</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM3" t="n">
         <v>2.48</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO3" t="n">
         <v>1.13</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
@@ -2076,28 +2076,28 @@
         <v>1.72</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX3" t="n">
         <v>1.51</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.46</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DB3" t="n">
         <v>1.16</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="DD3" t="n">
         <v>2.28</v>
@@ -2106,43 +2106,43 @@
         <v>0.1</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DH3" t="n">
-        <v>99.73999999999999</v>
+        <v>100.15</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.11</v>
+        <v>5.35</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="DM3" t="n">
-        <v>51.84</v>
+        <v>55.15</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.69</v>
+        <v>10.65</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.74</v>
+        <v>6.65</v>
       </c>
       <c r="DS3" t="n">
         <v>0.05</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.05</v>
+        <v>57.45</v>
       </c>
       <c r="DW3" t="n">
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.05</v>
+        <v>15.85</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.73</v>
+        <v>9.15</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.31</v>
+        <v>6.7</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.1</v>
+        <v>16.15</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0.3</v>
@@ -2275,139 +2275,139 @@
         <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>89.78</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>41.33</v>
+        <v>39.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.56</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS4" t="n">
         <v>8</v>
       </c>
-      <c r="AS4" t="n">
-        <v>7.67</v>
-      </c>
       <c r="AT4" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>44.44</v>
+        <v>43.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.22</v>
+        <v>10.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.11</v>
+        <v>3.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.44</v>
+        <v>16.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.32</v>
+        <v>9.65</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.21</v>
+        <v>4.35</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.11</v>
+        <v>5.3</v>
       </c>
       <c r="BR4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BS4" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT4" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU4" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX4" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
         <v>3.29</v>
@@ -2416,16 +2416,16 @@
         <v>3.44</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.52</v>
+        <v>4.6</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.01</v>
+        <v>6.39</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.39</v>
+        <v>6.86</v>
       </c>
       <c r="CE4" t="n">
         <v>1.26</v>
@@ -2434,28 +2434,28 @@
         <v>2.27</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CK4" t="n">
         <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO4" t="n">
         <v>1.16</v>
@@ -2464,7 +2464,7 @@
         <v>1.59</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
@@ -2479,10 +2479,10 @@
         <v>1.63</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CX4" t="n">
         <v>1.49</v>
@@ -2497,55 +2497,55 @@
         <v>2.08</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DC4" t="n">
         <v>1.59</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="DH4" t="n">
-        <v>92.05</v>
+        <v>92.75</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DM4" t="n">
-        <v>38.31</v>
+        <v>37.55</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.21</v>
+        <v>12.95</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.890000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.630000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="DS4" t="n">
         <v>0.1</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.31</v>
+        <v>44.8</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.74</v>
+        <v>11.55</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.74</v>
+        <v>7.7</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.63</v>
+        <v>17.35</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="H5" t="n">
-        <v>101.1</v>
+        <v>102.73</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="K5" t="n">
-        <v>7.8</v>
+        <v>7.82</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="M5" t="n">
-        <v>56</v>
+        <v>57.91</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="O5" t="n">
-        <v>3.9</v>
+        <v>4.18</v>
       </c>
       <c r="P5" t="n">
-        <v>9.5</v>
+        <v>9.73</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>11.55</v>
       </c>
       <c r="R5" t="n">
-        <v>6.6</v>
+        <v>6.27</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>53.5</v>
+        <v>54.64</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.5</v>
+        <v>19.18</v>
       </c>
       <c r="AA5" t="n">
-        <v>12.3</v>
+        <v>11.91</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.2</v>
+        <v>7.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.3</v>
+        <v>17.82</v>
       </c>
       <c r="AD5" t="n">
         <v>2.14</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AF5" t="n">
         <v>0.11</v>
@@ -2759,70 +2759,70 @@
         <v>1.89</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.05</v>
+        <v>5.85</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT5" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BU5" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BV5" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BW5" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BX5" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.2</v>
+        <v>5.33</v>
       </c>
       <c r="CC5" t="n">
         <v>1.86</v>
@@ -2834,58 +2834,58 @@
         <v>1.23</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.81</v>
+        <v>3.85</v>
       </c>
       <c r="CH5" t="n">
         <v>1.68</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.65</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CO5" t="n">
         <v>1.14</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CR5" t="n">
         <v>1.33</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CT5" t="n">
         <v>3.32</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX5" t="n">
         <v>1.52</v>
@@ -2903,10 +2903,10 @@
         <v>1.16</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DE5" t="n">
         <v>0.1</v>
@@ -2915,40 +2915,40 @@
         <v>0.95</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="DH5" t="n">
-        <v>102.47</v>
+        <v>103.3</v>
       </c>
       <c r="DI5" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.53</v>
+        <v>7.55</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DM5" t="n">
-        <v>56.63</v>
+        <v>57.65</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="DP5" t="n">
-        <v>9.32</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.79</v>
+        <v>11.1</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.89</v>
+        <v>6.7</v>
       </c>
       <c r="DS5" t="n">
         <v>0.1</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53.89</v>
+        <v>54.5</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.95</v>
+        <v>17.85</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.21</v>
+        <v>11.05</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.74</v>
+        <v>6.8</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.84</v>
+        <v>18.55</v>
       </c>
       <c r="EB5" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0.4</v>
@@ -3081,16 +3081,16 @@
         <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" t="n">
-        <v>92.44</v>
+        <v>91</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -3099,34 +3099,34 @@
         <v>2</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>34.89</v>
+        <v>33.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.22</v>
+        <v>11.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.220000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,22 +3138,22 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.89</v>
+        <v>46.2</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.78</v>
+        <v>5.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.89</v>
+        <v>18.2</v>
       </c>
       <c r="BE6" t="n">
         <v>1.2</v>
@@ -3162,58 +3162,58 @@
         <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>11.26</v>
+        <v>11.65</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.26</v>
+        <v>5.55</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.95</v>
+        <v>6.05</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV6" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY6" t="n">
         <v>3.43</v>
@@ -3222,46 +3222,46 @@
         <v>3.27</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="CB6" t="n">
         <v>4.27</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.79</v>
+        <v>5.76</v>
       </c>
       <c r="CD6" t="n">
-        <v>6.47</v>
+        <v>6.51</v>
       </c>
       <c r="CE6" t="n">
         <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CH6" t="n">
         <v>1.54</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO6" t="n">
         <v>1.19</v>
@@ -3270,13 +3270,13 @@
         <v>1.67</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CT6" t="n">
         <v>3.19</v>
@@ -3285,22 +3285,22 @@
         <v>1.59</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CY6" t="n">
         <v>1.76</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB6" t="n">
         <v>1.23</v>
@@ -3309,82 +3309,82 @@
         <v>1.72</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="DH6" t="n">
-        <v>90</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.68</v>
+        <v>4.6</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.11</v>
+        <v>37.4</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.53</v>
+        <v>13.6</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.05</v>
+        <v>11.1</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.210000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.74</v>
+        <v>45.45</v>
       </c>
       <c r="DW6" t="n">
         <v>0.05</v>
       </c>
       <c r="DX6" t="n">
-        <v>13.1</v>
+        <v>12.95</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.630000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.47</v>
+        <v>4.55</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.95</v>
+        <v>16.7</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="7">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="G8" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>117.89</v>
+        <v>119.1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J8" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="K8" t="n">
-        <v>7.44</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>51.44</v>
+        <v>53.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3.78</v>
+        <v>4.3</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.890000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="R8" t="n">
-        <v>6.44</v>
+        <v>6.2</v>
       </c>
       <c r="S8" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="T8" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>56.78</v>
+        <v>57.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.22</v>
+        <v>18.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.33</v>
+        <v>13.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.67</v>
+        <v>21.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AF8" t="n">
         <v>0.1</v>
@@ -3968,70 +3968,70 @@
         <v>1.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.26</v>
+        <v>10.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.16</v>
+        <v>5.45</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.11</v>
+        <v>5.25</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS8" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT8" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU8" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV8" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX8" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="CC8" t="n">
         <v>4.72</v>
@@ -4043,7 +4043,7 @@
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG8" t="n">
         <v>3.17</v>
@@ -4052,19 +4052,19 @@
         <v>1.49</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK8" t="n">
         <v>1.53</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN8" t="n">
         <v>1.87</v>
@@ -4076,13 +4076,13 @@
         <v>1.77</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CT8" t="n">
         <v>3.2</v>
@@ -4091,22 +4091,22 @@
         <v>1.51</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY8" t="n">
         <v>1.92</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB8" t="n">
         <v>1.25</v>
@@ -4115,82 +4115,82 @@
         <v>1.82</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="DH8" t="n">
-        <v>108.32</v>
+        <v>109.4</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.74</v>
+        <v>0.9</v>
       </c>
       <c r="DM8" t="n">
-        <v>45.16</v>
+        <v>46.5</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.05</v>
+        <v>11.1</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.53</v>
+        <v>10.75</v>
       </c>
       <c r="DR8" t="n">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.53</v>
+        <v>51.95</v>
       </c>
       <c r="DW8" t="n">
         <v>0.1</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.21</v>
+        <v>16.65</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.890000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.32</v>
+        <v>6.25</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.26</v>
+        <v>21.3</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="9">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0.22</v>
@@ -4696,115 +4696,115 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AI10" t="n">
-        <v>83.2</v>
+        <v>81.55</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.5</v>
+        <v>4.18</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.6</v>
+        <v>34.27</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.8</v>
+        <v>14.09</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.3</v>
+        <v>10.36</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.4</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>43.7</v>
+        <v>42.82</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.9</v>
+        <v>5.73</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.5</v>
+        <v>19.18</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.79</v>
+        <v>10.7</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BM10" t="n">
         <v>0.95</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.47</v>
+        <v>5.55</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.32</v>
+        <v>5.15</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4813,19 +4813,19 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BU10" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BV10" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BW10" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BX10" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY10" t="n">
         <v>3.84</v>
@@ -4834,73 +4834,73 @@
         <v>4.05</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.43</v>
+        <v>4.54</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.66</v>
+        <v>4.81</v>
       </c>
       <c r="CC10" t="n">
-        <v>6.15</v>
+        <v>6.55</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.99</v>
+        <v>7.49</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.51</v>
+        <v>3.57</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.64</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="CR10" t="n">
         <v>1.34</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="CT10" t="n">
         <v>3.36</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX10" t="n">
         <v>1.46</v>
@@ -4918,82 +4918,82 @@
         <v>1.19</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="DE10" t="n">
         <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="DH10" t="n">
-        <v>86.53</v>
+        <v>85.45</v>
       </c>
       <c r="DI10" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.47</v>
+        <v>4.3</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DM10" t="n">
-        <v>39.21</v>
+        <v>37.8</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.79</v>
+        <v>13</v>
       </c>
       <c r="DQ10" t="n">
         <v>11</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.89</v>
+        <v>7.9</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.79</v>
+        <v>43.3</v>
       </c>
       <c r="DW10" t="n">
         <v>0.1</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.31</v>
+        <v>11.1</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.21</v>
+        <v>7.05</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.74</v>
+        <v>17.65</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="EC10" t="n">
         <v>2</v>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5096,139 +5096,139 @@
         <v>1.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>96.33</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AL11" t="n">
-        <v>5.56</v>
+        <v>5.4</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AN11" t="n">
-        <v>42.33</v>
+        <v>40.1</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.11</v>
+        <v>12.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.67</v>
+        <v>12.7</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.779999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>48.22</v>
+        <v>46.1</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.11</v>
+        <v>12.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.44</v>
+        <v>8.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.949999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.11</v>
+        <v>4.15</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.84</v>
+        <v>5.05</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS11" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU11" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW11" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY11" t="n">
         <v>2.98</v>
@@ -5237,55 +5237,55 @@
         <v>3.1</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.01</v>
+        <v>4.07</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.16</v>
+        <v>4.23</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.2</v>
+        <v>5.43</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.51</v>
+        <v>5.74</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.29</v>
+        <v>3.34</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CI11" t="n">
         <v>2.15</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CK11" t="n">
         <v>1.46</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CR11" t="n">
         <v>1.36</v>
@@ -5300,7 +5300,7 @@
         <v>1.54</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW11" t="n">
         <v>1.7</v>
@@ -5309,64 +5309,64 @@
         <v>1.52</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.44</v>
       </c>
       <c r="DA11" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="DE11" t="n">
         <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="DH11" t="n">
-        <v>91.95</v>
+        <v>91.8</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.21</v>
+        <v>5.15</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.68</v>
+        <v>41.55</v>
       </c>
       <c r="DN11" t="n">
         <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.26</v>
+        <v>11.35</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.16</v>
+        <v>13.15</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.63</v>
+        <v>7.8</v>
       </c>
       <c r="DS11" t="n">
         <v>0.1</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.37</v>
+        <v>48.25</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.42</v>
+        <v>13.05</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.52</v>
+        <v>9.25</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.63</v>
+        <v>20.25</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="H12" t="n">
-        <v>105.62</v>
+        <v>107.56</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="K12" t="n">
-        <v>5.38</v>
+        <v>5.89</v>
       </c>
       <c r="L12" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="M12" t="n">
-        <v>46.38</v>
+        <v>46.22</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O12" t="n">
-        <v>1.88</v>
+        <v>2.56</v>
       </c>
       <c r="P12" t="n">
-        <v>11.25</v>
+        <v>10.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.62</v>
+        <v>14.33</v>
       </c>
       <c r="R12" t="n">
         <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.5</v>
+        <v>51.67</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.25</v>
+        <v>15</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.75</v>
+        <v>20.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
         <v>0.2</v>
@@ -5580,70 +5580,70 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.44</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
       <c r="BJ12" t="n">
         <v>1</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.67</v>
+        <v>4.95</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.78</v>
+        <v>4.84</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BU12" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BV12" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BW12" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BX12" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.93</v>
+        <v>3.99</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.07</v>
+        <v>4.11</v>
       </c>
       <c r="CC12" t="n">
         <v>2.83</v>
@@ -5655,16 +5655,16 @@
         <v>1.25</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.5</v>
@@ -5685,10 +5685,10 @@
         <v>1.15</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CR12" t="n">
         <v>1.34</v>
@@ -5703,7 +5703,7 @@
         <v>1.7</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CW12" t="n">
         <v>1.5</v>
@@ -5727,82 +5727,82 @@
         <v>1.53</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF12" t="n">
         <v>1.11</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="DH12" t="n">
-        <v>106.55</v>
+        <v>107.42</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.22</v>
+        <v>5.47</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM12" t="n">
-        <v>52.11</v>
+        <v>51.74</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.44</v>
+        <v>12.16</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.33</v>
+        <v>12.31</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>56.67</v>
+        <v>56.05</v>
       </c>
       <c r="DW12" t="n">
         <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.56</v>
+        <v>15.42</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.67</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.89</v>
+        <v>6.63</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.22</v>
+        <v>21.42</v>
       </c>
       <c r="EB12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="EC12" t="n">
         <v>1.84</v>
-      </c>
-      <c r="EC12" t="n">
-        <v>1.89</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0.33</v>
@@ -5902,52 +5902,52 @@
         <v>1.78</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AI13" t="n">
-        <v>74.40000000000001</v>
+        <v>75.73</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AN13" t="n">
-        <v>29.5</v>
+        <v>31.18</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.1</v>
+        <v>10.27</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.8</v>
+        <v>12.27</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.6</v>
+        <v>10.82</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>45</v>
+        <v>45.91</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="BC13" t="n">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="BD13" t="n">
-        <v>15</v>
+        <v>15.73</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.789999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="BO13" t="n">
         <v>1.95</v>
       </c>
       <c r="BP13" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.79</v>
+        <v>4.85</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT13" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU13" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BV13" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW13" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY13" t="n">
         <v>3.72</v>
@@ -6043,31 +6043,31 @@
         <v>3.91</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.31</v>
+        <v>4.34</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="CC13" t="n">
-        <v>6.04</v>
+        <v>6.07</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.44</v>
+        <v>6.43</v>
       </c>
       <c r="CE13" t="n">
         <v>1.27</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.61</v>
@@ -6088,10 +6088,10 @@
         <v>1.16</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6106,7 +6106,7 @@
         <v>1.65</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CW13" t="n">
         <v>1.64</v>
@@ -6124,55 +6124,55 @@
         <v>2</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="DH13" t="n">
-        <v>79.53</v>
+        <v>80</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DK13" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM13" t="n">
-        <v>31.95</v>
+        <v>32.75</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.53</v>
+        <v>10.6</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.74</v>
+        <v>12.45</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.63</v>
+        <v>10.75</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,25 +6184,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>41.79</v>
+        <v>42.45</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX13" t="n">
-        <v>8.369999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.42</v>
+        <v>5.4</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="EA13" t="n">
-        <v>16</v>
+        <v>16.35</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="EC13" t="n">
         <v>1.95</v>
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G14" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="H14" t="n">
-        <v>119.11</v>
+        <v>120</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.89</v>
+        <v>1.2</v>
       </c>
       <c r="K14" t="n">
-        <v>7.44</v>
+        <v>7.7</v>
       </c>
       <c r="L14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M14" t="n">
-        <v>67.56</v>
+        <v>68.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>10.56</v>
+        <v>10.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.109999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="R14" t="n">
-        <v>6.33</v>
+        <v>6.2</v>
       </c>
       <c r="S14" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="T14" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>62.56</v>
+        <v>63.6</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.67</v>
+        <v>20.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.11</v>
+        <v>13</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.56</v>
+        <v>7.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.22</v>
+        <v>18.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.89</v>
+        <v>1.2</v>
       </c>
       <c r="AF14" t="n">
         <v>0.3</v>
@@ -6386,70 +6386,70 @@
         <v>1.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.21</v>
+        <v>11.35</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BL14" t="n">
         <v>0.95</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.42</v>
+        <v>6.55</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT14" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BU14" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BV14" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BW14" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BX14" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY14" t="n">
         <v>1.2</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.51</v>
+        <v>6.45</v>
       </c>
       <c r="CB14" t="n">
-        <v>7.08</v>
+        <v>7</v>
       </c>
       <c r="CC14" t="n">
         <v>1.7</v>
@@ -6461,28 +6461,28 @@
         <v>1.16</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.54</v>
+        <v>4.52</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL14" t="n">
         <v>1.66</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CN14" t="n">
         <v>2.22</v>
@@ -6491,7 +6491,7 @@
         <v>1.06</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CQ14" t="n">
         <v>1.83</v>
@@ -6505,69 +6505,69 @@
         <v>1.94</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
         <v>2.34</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="DH14" t="n">
-        <v>109</v>
+        <v>109.95</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.1</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DM14" t="n">
-        <v>61.11</v>
+        <v>61.9</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.84</v>
+        <v>10.95</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.58</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.52</v>
+        <v>7.4</v>
       </c>
       <c r="DS14" t="n">
         <v>0.1</v>
@@ -6579,28 +6579,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>59.9</v>
+        <v>60.55</v>
       </c>
       <c r="DW14" t="n">
         <v>0.05</v>
       </c>
       <c r="DX14" t="n">
-        <v>17.53</v>
+        <v>17.45</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.26</v>
+        <v>10.35</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7.27</v>
+        <v>7.1</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="15">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0.1</v>
@@ -6700,139 +6700,139 @@
         <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>87.22</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN15" t="n">
-        <v>42.67</v>
+        <v>41.4</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.33</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.44</v>
+        <v>9.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.44</v>
+        <v>10.3</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>46.67</v>
+        <v>46.1</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA15" t="n">
-        <v>14.33</v>
+        <v>13.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.44</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.89</v>
+        <v>4.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>14.67</v>
+        <v>14.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.68</v>
+        <v>11.6</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.84</v>
+        <v>6.75</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV15" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW15" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BX15" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BY15" t="n">
         <v>2.82</v>
@@ -6841,34 +6841,34 @@
         <v>2.93</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.57</v>
+        <v>4.47</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.82</v>
+        <v>4.72</v>
       </c>
       <c r="CE15" t="n">
         <v>1.27</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CK15" t="n">
         <v>1.34</v>
@@ -6877,7 +6877,7 @@
         <v>1.71</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CN15" t="n">
         <v>2.17</v>
@@ -6886,28 +6886,28 @@
         <v>1.18</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
@@ -6921,85 +6921,85 @@
         <v>1.19</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="DH15" t="n">
-        <v>90.53</v>
+        <v>90.7</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.37</v>
+        <v>4.15</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM15" t="n">
-        <v>42.74</v>
+        <v>42.1</v>
       </c>
       <c r="DN15" t="n">
         <v>0.95</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="DP15" t="n">
-        <v>8.68</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.31</v>
+        <v>10.35</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.31</v>
+        <v>9.75</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.11</v>
+        <v>45.85</v>
       </c>
       <c r="DW15" t="n">
         <v>0.1</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.37</v>
+        <v>12.95</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.68</v>
+        <v>8.35</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.68</v>
+        <v>4.6</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.21</v>
+        <v>15.15</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="16">
@@ -7009,61 +7009,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5</v>
+        <v>3.09</v>
       </c>
       <c r="H16" t="n">
-        <v>82.3</v>
+        <v>84.09</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="K16" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="M16" t="n">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="P16" t="n">
-        <v>9.9</v>
+        <v>10.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>10.7</v>
+        <v>11.18</v>
       </c>
       <c r="R16" t="n">
-        <v>6.7</v>
+        <v>6.55</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7075,28 +7075,28 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>44.6</v>
+        <v>45</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.1</v>
+        <v>13.73</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.5</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.6</v>
+        <v>5.36</v>
       </c>
       <c r="AC16" t="n">
-        <v>19</v>
+        <v>19.27</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7180,70 +7180,70 @@
         <v>1.67</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.16</v>
+        <v>10.9</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM16" t="n">
         <v>0.95</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.74</v>
+        <v>5.4</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.42</v>
+        <v>5.1</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS16" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT16" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV16" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX16" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.57</v>
+        <v>4.52</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.71</v>
+        <v>4.66</v>
       </c>
       <c r="CC16" t="n">
         <v>8.56</v>
@@ -7258,7 +7258,7 @@
         <v>2.3</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CH16" t="n">
         <v>1.59</v>
@@ -7273,22 +7273,22 @@
         <v>1.37</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM16" t="n">
         <v>2.84</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
@@ -7306,7 +7306,7 @@
         <v>2.36</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
@@ -7327,49 +7327,49 @@
         <v>1.61</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="DH16" t="n">
-        <v>81.48</v>
+        <v>82.5</v>
       </c>
       <c r="DI16" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.16</v>
+        <v>41.6</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.47</v>
+        <v>10.6</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.58</v>
+        <v>10.85</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.210000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
@@ -7381,28 +7381,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>42.89</v>
+        <v>43.2</v>
       </c>
       <c r="DW16" t="n">
         <v>0.1</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.05</v>
+        <v>12.9</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.58</v>
+        <v>8.5</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.26</v>
+        <v>18.45</v>
       </c>
       <c r="EB16" t="n">
         <v>1.43</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="17">
@@ -7412,94 +7412,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="H17" t="n">
-        <v>124.22</v>
+        <v>126.4</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.33</v>
+        <v>5.9</v>
       </c>
       <c r="L17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M17" t="n">
-        <v>66.44</v>
+        <v>67.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>10.78</v>
+        <v>10.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.22</v>
+        <v>10</v>
       </c>
       <c r="R17" t="n">
-        <v>5.67</v>
+        <v>5.4</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>57.89</v>
+        <v>58.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.67</v>
+        <v>19.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.33</v>
+        <v>13.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="AC17" t="n">
-        <v>21</v>
+        <v>21.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7583,70 +7583,70 @@
         <v>2.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="BH17" t="n">
-        <v>9</v>
+        <v>9.35</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM17" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.58</v>
+        <v>4.7</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.42</v>
+        <v>4.65</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.73999999999999</v>
+        <v>90</v>
       </c>
       <c r="BS17" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT17" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BU17" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV17" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW17" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX17" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.18</v>
+        <v>4.25</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.3</v>
+        <v>4.39</v>
       </c>
       <c r="CC17" t="n">
         <v>2.44</v>
@@ -7667,10 +7667,10 @@
         <v>1.58</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CK17" t="n">
         <v>1.46</v>
@@ -7682,13 +7682,13 @@
         <v>2.52</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO17" t="n">
         <v>1.18</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CQ17" t="n">
         <v>2.45</v>
@@ -7706,10 +7706,10 @@
         <v>1.58</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX17" t="n">
         <v>1.52</v>
@@ -7730,82 +7730,82 @@
         <v>1.64</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="DE17" t="n">
         <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="DH17" t="n">
-        <v>109.16</v>
+        <v>111</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.16</v>
+        <v>5.45</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM17" t="n">
-        <v>58.68</v>
+        <v>59.45</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.26</v>
+        <v>10.15</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.74</v>
+        <v>6.55</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>55.21</v>
+        <v>55.7</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX17" t="n">
-        <v>18.84</v>
+        <v>18.6</v>
       </c>
       <c r="DY17" t="n">
-        <v>12.47</v>
+        <v>12.4</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.37</v>
+        <v>6.2</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.74</v>
+        <v>21.15</v>
       </c>
       <c r="EB17" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18">
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
@@ -7827,49 +7827,49 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="G18" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="H18" t="n">
-        <v>94.11</v>
+        <v>94.7</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J18" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="M18" t="n">
-        <v>37.78</v>
+        <v>39.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>10.22</v>
+        <v>10.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.22</v>
+        <v>13.3</v>
       </c>
       <c r="R18" t="n">
-        <v>6.89</v>
+        <v>6.6</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7881,28 +7881,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>44.89</v>
+        <v>46.3</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.56</v>
+        <v>16.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>10.22</v>
+        <v>10.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>20.33</v>
+        <v>21</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7986,70 +7986,70 @@
         <v>1.78</v>
       </c>
       <c r="BG18" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.67</v>
+        <v>9.68</v>
       </c>
       <c r="BI18" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP18" t="n">
         <v>4.89</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT18" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU18" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV18" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CB18" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CC18" t="n">
         <v>2.98</v>
@@ -8061,49 +8061,49 @@
         <v>1.31</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL18" t="n">
         <v>1.84</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CO18" t="n">
         <v>1.2</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CU18" t="n">
         <v>1.54</v>
@@ -8118,64 +8118,64 @@
         <v>1.5</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.48</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="DB18" t="n">
         <v>1.23</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="DH18" t="n">
-        <v>99.78</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.06</v>
+        <v>5.32</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM18" t="n">
-        <v>38.56</v>
+        <v>39.31</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.66</v>
+        <v>10.68</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.5</v>
+        <v>11.63</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.34</v>
+        <v>7.16</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8187,28 +8187,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.16</v>
+        <v>48.73</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.84</v>
+        <v>15.21</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.66</v>
+        <v>10.05</v>
       </c>
       <c r="DZ18" t="n">
         <v>5.16</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.33</v>
+        <v>20.68</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="19">
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0.2</v>
@@ -8311,136 +8311,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AI19" t="n">
-        <v>79.11</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="AK19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BF19" t="n">
         <v>1</v>
       </c>
-      <c r="AL19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>33</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>44.78</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>17.11</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0.78</v>
-      </c>
       <c r="BG19" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.47</v>
+        <v>10.45</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.74</v>
+        <v>5.8</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT19" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BU19" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV19" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY19" t="n">
         <v>4.01</v>
@@ -8449,16 +8449,16 @@
         <v>4.15</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="CB19" t="n">
-        <v>5.42</v>
+        <v>5.45</v>
       </c>
       <c r="CC19" t="n">
-        <v>8.84</v>
+        <v>8.82</v>
       </c>
       <c r="CD19" t="n">
-        <v>9.82</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="CE19" t="n">
         <v>1.23</v>
@@ -8467,13 +8467,13 @@
         <v>2.16</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.62</v>
@@ -8482,22 +8482,22 @@
         <v>1.37</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CN19" t="n">
         <v>2.16</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
@@ -8512,10 +8512,10 @@
         <v>1.78</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX19" t="n">
         <v>1.51</v>
@@ -8539,46 +8539,46 @@
         <v>2.28</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="DH19" t="n">
-        <v>79.84</v>
+        <v>78.8</v>
       </c>
       <c r="DI19" t="n">
         <v>-0.1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM19" t="n">
-        <v>37.68</v>
+        <v>37.85</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="DP19" t="n">
-        <v>10</v>
+        <v>10.15</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.32</v>
+        <v>11.25</v>
       </c>
       <c r="DR19" t="n">
-        <v>10.26</v>
+        <v>10.2</v>
       </c>
       <c r="DS19" t="n">
         <v>0.05</v>
@@ -8590,28 +8590,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>44.37</v>
+        <v>43.9</v>
       </c>
       <c r="DW19" t="n">
         <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.05</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.58</v>
+        <v>6.4</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="EA19" t="n">
-        <v>14.84</v>
+        <v>14.75</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -6703,7 +6703,7 @@
         <v>0.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
         <v>2</v>
@@ -6715,7 +6715,7 @@
         <v>0.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AL15" t="n">
         <v>3.6</v>
@@ -6778,7 +6778,7 @@
         <v>1.48</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BG15" t="n">
         <v>2.95</v>
@@ -6930,7 +6930,7 @@
         <v>0.1</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="DG15" t="n">
         <v>2.35</v>
@@ -6942,7 +6942,7 @@
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DK15" t="n">
         <v>4.15</v>
@@ -6999,7 +6999,7 @@
         <v>1.45</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="16">

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -5018,82 +5018,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="H11" t="n">
-        <v>88</v>
+        <v>93.73</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M11" t="n">
-        <v>43</v>
+        <v>44.36</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P11" t="n">
-        <v>10.5</v>
+        <v>10.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.6</v>
+        <v>13.27</v>
       </c>
       <c r="R11" t="n">
-        <v>6.6</v>
+        <v>6.45</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>50.4</v>
+        <v>51.55</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.7</v>
+        <v>14.27</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.6</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.1</v>
+        <v>4.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.5</v>
+        <v>18.36</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
         <v>0.1</v>
@@ -5177,70 +5177,70 @@
         <v>1.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.15</v>
+        <v>4.24</v>
       </c>
       <c r="BQ11" t="n">
         <v>5.05</v>
       </c>
       <c r="BR11" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV11" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX11" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.23</v>
+        <v>4.19</v>
       </c>
       <c r="CC11" t="n">
         <v>5.43</v>
@@ -5249,19 +5249,19 @@
         <v>5.74</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.67</v>
@@ -5273,31 +5273,31 @@
         <v>1.87</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV11" t="n">
         <v>2.24</v>
@@ -5312,94 +5312,94 @@
         <v>1.8</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DA11" t="n">
         <v>2.01</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="DE11" t="n">
         <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="DH11" t="n">
-        <v>91.8</v>
+        <v>94.62</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.15</v>
+        <v>5.24</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DM11" t="n">
-        <v>41.55</v>
+        <v>42.33</v>
       </c>
       <c r="DN11" t="n">
         <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.35</v>
+        <v>11.14</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.15</v>
+        <v>13</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.8</v>
+        <v>7.66</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.25</v>
+        <v>48.95</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.05</v>
+        <v>13.38</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.25</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.25</v>
+        <v>20.09</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="12">
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0.1</v>
@@ -7505,136 +7505,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI17" t="n">
-        <v>95.59999999999999</v>
+        <v>94.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AL17" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN17" t="n">
-        <v>51.7</v>
+        <v>50.82</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.9</v>
+        <v>12.64</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.7</v>
+        <v>7.55</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>52.8</v>
+        <v>51.36</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA17" t="n">
-        <v>18.1</v>
+        <v>18.09</v>
       </c>
       <c r="BB17" t="n">
-        <v>11.7</v>
+        <v>11.45</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.4</v>
+        <v>6.64</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.5</v>
+        <v>20.36</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.35</v>
+        <v>9.43</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BM17" t="n">
         <v>0.95</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.7</v>
+        <v>4.76</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="BR17" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT17" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BU17" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV17" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW17" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX17" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY17" t="n">
         <v>1.93</v>
@@ -7643,31 +7643,31 @@
         <v>1.94</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.65</v>
@@ -7676,40 +7676,40 @@
         <v>1.46</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO17" t="n">
         <v>1.18</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX17" t="n">
         <v>1.52</v>
@@ -7718,7 +7718,7 @@
         <v>1.82</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA17" t="n">
         <v>1.99</v>
@@ -7727,85 +7727,85 @@
         <v>1.2</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="DE17" t="n">
         <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="DH17" t="n">
-        <v>111</v>
+        <v>109.72</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.45</v>
+        <v>5.38</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM17" t="n">
-        <v>59.45</v>
+        <v>58.62</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.8</v>
+        <v>11.72</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.15</v>
+        <v>10</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.55</v>
+        <v>6.53</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>55.7</v>
+        <v>54.81</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX17" t="n">
-        <v>18.6</v>
+        <v>18.57</v>
       </c>
       <c r="DY17" t="n">
-        <v>12.4</v>
+        <v>12.24</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.2</v>
+        <v>6.34</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.15</v>
+        <v>21.05</v>
       </c>
       <c r="EB17" t="n">
         <v>2.04</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="G2" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="H2" t="n">
-        <v>105.78</v>
+        <v>103.7</v>
       </c>
       <c r="I2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="K2" t="n">
-        <v>6.56</v>
+        <v>6.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="M2" t="n">
-        <v>54.56</v>
+        <v>52.2</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O2" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="P2" t="n">
-        <v>8.67</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.22</v>
+        <v>10.8</v>
       </c>
       <c r="R2" t="n">
-        <v>6.33</v>
+        <v>6.6</v>
       </c>
       <c r="S2" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="T2" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>53.56</v>
+        <v>53.1</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.11</v>
+        <v>16.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.67</v>
+        <v>10.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.44</v>
+        <v>6</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.22</v>
+        <v>18.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
         <v>0.09</v>
@@ -1550,70 +1550,70 @@
         <v>2.64</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.25</v>
+        <v>10.05</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM2" t="n">
         <v>0.9</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.65</v>
+        <v>5.48</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT2" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BV2" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW2" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX2" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.64</v>
+        <v>4.61</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.76</v>
+        <v>4.73</v>
       </c>
       <c r="CC2" t="n">
         <v>2.03</v>
@@ -1625,16 +1625,16 @@
         <v>1.23</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CH2" t="n">
         <v>1.65</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.58</v>
@@ -1643,19 +1643,19 @@
         <v>1.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CN2" t="n">
         <v>2.04</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CQ2" t="n">
         <v>2.25</v>
@@ -1676,19 +1676,19 @@
         <v>2.42</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CX2" t="n">
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.45</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="DB2" t="n">
         <v>1.16</v>
@@ -1700,79 +1700,79 @@
         <v>2.3</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.6</v>
+        <v>100.81</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="DK2" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.95</v>
+        <v>49.05</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.65</v>
+        <v>10.86</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.8</v>
+        <v>11.05</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.15</v>
+        <v>7.24</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.15</v>
+        <v>53.91</v>
       </c>
       <c r="DW2" t="n">
         <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.2</v>
+        <v>15.95</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.25</v>
+        <v>10.19</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.95</v>
+        <v>5.76</v>
       </c>
       <c r="EA2" t="n">
         <v>16.95</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0.09</v>
@@ -1872,118 +1872,118 @@
         <v>1.45</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="AI3" t="n">
-        <v>97.78</v>
+        <v>97.8</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.89</v>
+        <v>4.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>50.56</v>
+        <v>48.3</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.56</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.22</v>
+        <v>11.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.11</v>
+        <v>6.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>58</v>
+        <v>57.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>14.78</v>
+        <v>14.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="BD3" t="n">
-        <v>16.22</v>
+        <v>16.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.3</v>
+        <v>10.05</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.8</v>
+        <v>4.67</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,19 +1992,19 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BV3" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW3" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX3" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY3" t="n">
         <v>1.62</v>
@@ -2013,16 +2013,16 @@
         <v>1.66</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.67</v>
+        <v>4.63</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="CE3" t="n">
         <v>1.24</v>
@@ -2031,10 +2031,10 @@
         <v>2.18</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI3" t="n">
         <v>2.3</v>
@@ -2046,10 +2046,10 @@
         <v>1.48</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN3" t="n">
         <v>1.96</v>
@@ -2058,7 +2058,7 @@
         <v>1.13</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CQ3" t="n">
         <v>2.27</v>
@@ -2067,7 +2067,7 @@
         <v>1.33</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CT3" t="n">
         <v>3.32</v>
@@ -2082,67 +2082,67 @@
         <v>1.64</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB3" t="n">
         <v>1.16</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.15</v>
+        <v>100.05</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.35</v>
+        <v>5.14</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DM3" t="n">
-        <v>55.15</v>
+        <v>53.86</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.65</v>
+        <v>10.38</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.5</v>
+        <v>12.48</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.65</v>
+        <v>6.52</v>
       </c>
       <c r="DS3" t="n">
         <v>0.05</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.45</v>
+        <v>57.19</v>
       </c>
       <c r="DW3" t="n">
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.85</v>
+        <v>15.53</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.15</v>
+        <v>9</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.7</v>
+        <v>6.52</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.15</v>
+        <v>16.43</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H4" t="n">
-        <v>94.09999999999999</v>
+        <v>95.91</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M4" t="n">
-        <v>35.6</v>
+        <v>36.27</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="P4" t="n">
-        <v>12.9</v>
+        <v>12.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="R4" t="n">
-        <v>9.5</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>46.1</v>
+        <v>46.27</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.2</v>
+        <v>12.09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.8</v>
+        <v>17.82</v>
       </c>
       <c r="AD4" t="n">
         <v>1.31</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF4" t="n">
         <v>0.1</v>
@@ -2356,70 +2356,70 @@
         <v>1.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.65</v>
+        <v>9.43</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.35</v>
+        <v>4.24</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.3</v>
+        <v>5.19</v>
       </c>
       <c r="BR4" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT4" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV4" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW4" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX4" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.29</v>
+        <v>3.34</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.44</v>
+        <v>3.49</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.6</v>
+        <v>4.57</v>
       </c>
       <c r="CC4" t="n">
         <v>6.39</v>
@@ -2434,7 +2434,7 @@
         <v>2.27</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CH4" t="n">
         <v>1.6</v>
@@ -2449,13 +2449,13 @@
         <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO4" t="n">
         <v>1.16</v>
@@ -2476,7 +2476,7 @@
         <v>3.31</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CV4" t="n">
         <v>2.4</v>
@@ -2485,16 +2485,16 @@
         <v>1.62</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB4" t="n">
         <v>1.18</v>
@@ -2506,79 +2506,79 @@
         <v>2.44</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DH4" t="n">
-        <v>92.75</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DK4" t="n">
         <v>4.1</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM4" t="n">
-        <v>37.55</v>
+        <v>37.81</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.95</v>
+        <v>12.91</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.949999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.75</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.8</v>
+        <v>44.95</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.55</v>
+        <v>11.52</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.7</v>
+        <v>7.62</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.35</v>
+        <v>17.38</v>
       </c>
       <c r="EB4" t="n">
         <v>1.28</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.09</v>
@@ -2678,139 +2678,139 @@
         <v>0.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AI5" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AK5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BF5" t="n">
         <v>2</v>
       </c>
-      <c r="AL5" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>57.33</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>54.33</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>19.44</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.89</v>
-      </c>
       <c r="BG5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BH5" t="n">
         <v>11</v>
       </c>
       <c r="BI5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.85</v>
+        <v>5.9</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT5" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BV5" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BW5" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BX5" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY5" t="n">
         <v>1.42</v>
@@ -2819,55 +2819,55 @@
         <v>1.48</v>
       </c>
       <c r="CA5" t="n">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.33</v>
+        <v>5.29</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.86</v>
+        <v>2.13</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="CE5" t="n">
         <v>1.23</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK5" t="n">
         <v>1.41</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CM5" t="n">
         <v>2.71</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CR5" t="n">
         <v>1.33</v>
@@ -2882,10 +2882,10 @@
         <v>1.77</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX5" t="n">
         <v>1.52</v>
@@ -2906,82 +2906,82 @@
         <v>1.5</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DE5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="DI5" t="n">
         <v>0.1</v>
       </c>
-      <c r="DF5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>103.3</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>0.05</v>
-      </c>
       <c r="DJ5" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.55</v>
+        <v>7.33</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DM5" t="n">
-        <v>57.65</v>
+        <v>56.67</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="DP5" t="n">
-        <v>9.449999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.1</v>
+        <v>10.95</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.5</v>
+        <v>53.76</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.85</v>
+        <v>17.38</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.05</v>
+        <v>10.81</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.8</v>
+        <v>6.57</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.55</v>
+        <v>18.33</v>
       </c>
       <c r="EB5" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0.4</v>
@@ -3081,52 +3081,52 @@
         <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AI6" t="n">
-        <v>91</v>
+        <v>90.73</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN6" t="n">
-        <v>33.8</v>
+        <v>32.91</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.2</v>
+        <v>13.27</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.3</v>
+        <v>11.82</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.6</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.2</v>
+        <v>46.91</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.1</v>
+        <v>10.27</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.6</v>
+        <v>5.64</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.2</v>
+        <v>18.73</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BF6" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="BH6" t="n">
-        <v>11.65</v>
+        <v>11.52</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.55</v>
+        <v>5.48</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX6" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY6" t="n">
         <v>3.43</v>
@@ -3222,28 +3222,28 @@
         <v>3.27</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.27</v>
+        <v>4.23</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.76</v>
+        <v>5.53</v>
       </c>
       <c r="CD6" t="n">
-        <v>6.51</v>
+        <v>6.21</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI6" t="n">
         <v>2.16</v>
@@ -3252,37 +3252,37 @@
         <v>1.66</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CO6" t="n">
         <v>1.19</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CT6" t="n">
         <v>3.19</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV6" t="n">
         <v>2.27</v>
@@ -3294,64 +3294,64 @@
         <v>1.49</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.5</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB6" t="n">
         <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.40000000000001</v>
+        <v>89.33</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM6" t="n">
-        <v>37.4</v>
+        <v>36.76</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.6</v>
+        <v>13.62</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.1</v>
+        <v>11.38</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.449999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="DS6" t="n">
         <v>0.1</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.45</v>
+        <v>45.86</v>
       </c>
       <c r="DW6" t="n">
         <v>0.05</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.95</v>
+        <v>12.9</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.4</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.55</v>
+        <v>4.62</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.7</v>
+        <v>17.05</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0.22</v>
@@ -3484,52 +3484,52 @@
         <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AI7" t="n">
-        <v>98.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="AN7" t="n">
-        <v>42.3</v>
+        <v>42.09</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.2</v>
+        <v>10.73</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.6</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.1</v>
+        <v>8.82</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>51</v>
+        <v>49.82</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.6</v>
+        <v>9.91</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.7</v>
+        <v>19.36</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.63</v>
+        <v>10.65</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.84</v>
+        <v>5.9</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT7" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BU7" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BV7" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW7" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX7" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY7" t="n">
         <v>2.85</v>
@@ -3625,43 +3625,43 @@
         <v>3.05</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.77</v>
+        <v>4.52</v>
       </c>
       <c r="CE7" t="n">
         <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CK7" t="n">
         <v>1.35</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CN7" t="n">
         <v>2.2</v>
@@ -3670,25 +3670,25 @@
         <v>1.14</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CR7" t="n">
         <v>1.34</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CW7" t="n">
         <v>1.56</v>
@@ -3709,52 +3709,52 @@
         <v>1.18</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="DG7" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DH7" t="n">
-        <v>97.68000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.31</v>
+        <v>5.3</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.58</v>
+        <v>46.25</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.74</v>
+        <v>10.05</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.84</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.9</v>
+        <v>8.75</v>
       </c>
       <c r="DS7" t="n">
         <v>0.05</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.9</v>
+        <v>51.2</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.26</v>
+        <v>11.35</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.21</v>
+        <v>6.3</v>
       </c>
       <c r="DZ7" t="n">
         <v>5.05</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.53</v>
+        <v>18.4</v>
       </c>
       <c r="EB7" t="n">
         <v>1.41</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0.2</v>
@@ -3887,139 +3887,139 @@
         <v>1.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>103.64</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>41.64</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>47.45</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO8" t="n">
         <v>1.1</v>
       </c>
-      <c r="AH8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BP8" t="n">
-        <v>5.45</v>
+        <v>5.38</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="BR8" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU8" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV8" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW8" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY8" t="n">
         <v>1.99</v>
@@ -4028,46 +4028,46 @@
         <v>2.06</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.72</v>
+        <v>4.53</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.78</v>
+        <v>4.62</v>
       </c>
       <c r="CE8" t="n">
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CH8" t="n">
         <v>1.49</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.72</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CO8" t="n">
         <v>1.23</v>
@@ -4076,7 +4076,7 @@
         <v>1.77</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4091,22 +4091,22 @@
         <v>1.51</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB8" t="n">
         <v>1.25</v>
@@ -4115,82 +4115,82 @@
         <v>1.82</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="DH8" t="n">
-        <v>109.4</v>
+        <v>111</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.6</v>
+        <v>6.57</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.5</v>
+        <v>47.29</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.6</v>
+        <v>0.72</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.1</v>
+        <v>11.33</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.75</v>
+        <v>10.62</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.85</v>
+        <v>6.81</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.95</v>
+        <v>52.05</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.65</v>
+        <v>16.24</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.4</v>
+        <v>10.19</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.3</v>
+        <v>20.81</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="H9" t="n">
-        <v>106.2</v>
+        <v>105.27</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="K9" t="n">
-        <v>5.9</v>
+        <v>5.82</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M9" t="n">
-        <v>55.8</v>
+        <v>59.73</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="O9" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="P9" t="n">
-        <v>9.699999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.8</v>
+        <v>10.73</v>
       </c>
       <c r="R9" t="n">
-        <v>6.3</v>
+        <v>6.55</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>52.7</v>
+        <v>53.36</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.4</v>
+        <v>16.64</v>
       </c>
       <c r="AA9" t="n">
-        <v>11</v>
+        <v>11.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.4</v>
+        <v>5.18</v>
       </c>
       <c r="AC9" t="n">
-        <v>17</v>
+        <v>16.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,67 +4371,67 @@
         <v>1.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.58</v>
+        <v>10.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM9" t="n">
         <v>1</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.42</v>
+        <v>5.45</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT9" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BU9" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV9" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX9" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CB9" t="n">
         <v>3.99</v>
@@ -4443,19 +4443,19 @@
         <v>3.63</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.57</v>
@@ -4464,10 +4464,10 @@
         <v>1.44</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CN9" t="n">
         <v>2.04</v>
@@ -4476,28 +4476,28 @@
         <v>1.17</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX9" t="n">
         <v>1.5</v>
@@ -4506,7 +4506,7 @@
         <v>1.74</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DA9" t="n">
         <v>2.08</v>
@@ -4515,85 +4515,85 @@
         <v>1.19</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="DE9" t="n">
         <v>0.05</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="DH9" t="n">
-        <v>101.84</v>
+        <v>101.55</v>
       </c>
       <c r="DI9" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DM9" t="n">
-        <v>49.95</v>
+        <v>52.4</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.47</v>
+        <v>11.45</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.58</v>
+        <v>10.55</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.79</v>
+        <v>6.9</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.26</v>
+        <v>52.65</v>
       </c>
       <c r="DW9" t="n">
         <v>0.1</v>
       </c>
       <c r="DX9" t="n">
-        <v>16.05</v>
+        <v>16.2</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.47</v>
+        <v>10.75</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.58</v>
+        <v>5.45</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.47</v>
+        <v>18.3</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="H10" t="n">
-        <v>90.22</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="K10" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="M10" t="n">
-        <v>42.11</v>
+        <v>42</v>
       </c>
       <c r="N10" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="P10" t="n">
-        <v>11.67</v>
+        <v>12.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.78</v>
+        <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>7.33</v>
+        <v>7.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>43.89</v>
+        <v>44.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.22</v>
+        <v>13.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.67</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.56</v>
+        <v>5.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.78</v>
+        <v>16.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,37 +4774,37 @@
         <v>2.45</v>
       </c>
       <c r="BG10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.7</v>
+        <v>10.62</v>
       </c>
       <c r="BI10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.55</v>
+        <v>5.48</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4813,31 +4813,31 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BU10" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV10" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BW10" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BX10" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.84</v>
+        <v>3.68</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.05</v>
+        <v>3.87</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.54</v>
+        <v>4.48</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.81</v>
+        <v>4.75</v>
       </c>
       <c r="CC10" t="n">
         <v>6.55</v>
@@ -4846,16 +4846,16 @@
         <v>7.49</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI10" t="n">
         <v>2.2</v>
@@ -4867,7 +4867,7 @@
         <v>1.35</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CM10" t="n">
         <v>2.91</v>
@@ -4876,28 +4876,28 @@
         <v>2.21</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW10" t="n">
         <v>1.67</v>
@@ -4915,25 +4915,25 @@
         <v>2.24</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="DE10" t="n">
         <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="DG10" t="n">
         <v>2.1</v>
       </c>
       <c r="DH10" t="n">
-        <v>85.45</v>
+        <v>86.95</v>
       </c>
       <c r="DI10" t="n">
         <v>0.05</v>
@@ -4942,58 +4942,58 @@
         <v>2.15</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.8</v>
+        <v>37.95</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DP10" t="n">
-        <v>13</v>
+        <v>13.19</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11</v>
+        <v>11.14</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.3</v>
+        <v>43.43</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX10" t="n">
         <v>11.1</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.05</v>
+        <v>6.91</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.05</v>
+        <v>4.19</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.65</v>
+        <v>18</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="EC10" t="n">
         <v>2</v>
@@ -5087,7 +5087,7 @@
         <v>4.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.36</v>
+        <v>18.45</v>
       </c>
       <c r="AD11" t="n">
         <v>1.55</v>
@@ -5240,7 +5240,7 @@
         <v>4.05</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="CC11" t="n">
         <v>5.43</v>
@@ -5291,19 +5291,19 @@
         <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CU11" t="n">
         <v>1.53</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CX11" t="n">
         <v>1.52</v>
@@ -5393,7 +5393,7 @@
         <v>4.1</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.09</v>
+        <v>20.14</v>
       </c>
       <c r="EB11" t="n">
         <v>1.44</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0.33</v>
@@ -5499,52 +5499,52 @@
         <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AI12" t="n">
-        <v>107.3</v>
+        <v>110.09</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AL12" t="n">
-        <v>5.1</v>
+        <v>4.91</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AN12" t="n">
-        <v>56.7</v>
+        <v>56.45</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.4</v>
+        <v>13.64</v>
       </c>
       <c r="AR12" t="n">
-        <v>10.5</v>
+        <v>10.91</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.9</v>
+        <v>5.91</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>60</v>
+        <v>59.18</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA12" t="n">
-        <v>15.8</v>
+        <v>16.09</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.6</v>
+        <v>8.82</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.2</v>
+        <v>7.27</v>
       </c>
       <c r="BD12" t="n">
-        <v>22.4</v>
+        <v>21.45</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="BF12" t="n">
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.789999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="BJ12" t="n">
         <v>1</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.84</v>
+        <v>4.7</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT12" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BU12" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BV12" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BW12" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BX12" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BY12" t="n">
         <v>2.24</v>
@@ -5646,16 +5646,16 @@
         <v>4.11</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="CE12" t="n">
         <v>1.25</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CG12" t="n">
         <v>3.68</v>
@@ -5664,7 +5664,7 @@
         <v>1.63</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.5</v>
@@ -5676,19 +5676,19 @@
         <v>1.71</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO12" t="n">
         <v>1.15</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CR12" t="n">
         <v>1.34</v>
@@ -5709,16 +5709,16 @@
         <v>1.5</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DB12" t="n">
         <v>1.16</v>
@@ -5730,79 +5730,79 @@
         <v>2.3</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="DH12" t="n">
-        <v>107.42</v>
+        <v>108.95</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.47</v>
+        <v>5.35</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="DM12" t="n">
-        <v>51.74</v>
+        <v>51.85</v>
       </c>
       <c r="DN12" t="n">
         <v>0.9</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.16</v>
+        <v>12.35</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.31</v>
+        <v>12.45</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>56.05</v>
+        <v>55.8</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.42</v>
+        <v>15.6</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.789999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.63</v>
+        <v>6.7</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.42</v>
+        <v>20.95</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H13" t="n">
-        <v>85.22</v>
+        <v>88</v>
       </c>
       <c r="I13" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M13" t="n">
-        <v>34.67</v>
+        <v>34.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="P13" t="n">
         <v>11</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.67</v>
+        <v>13</v>
       </c>
       <c r="R13" t="n">
-        <v>10.67</v>
+        <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>38.22</v>
+        <v>40.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.56</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.67</v>
+        <v>5.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.89</v>
+        <v>3.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.11</v>
+        <v>17.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
         <v>0.18</v>
@@ -5983,70 +5983,70 @@
         <v>2.09</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.15</v>
+        <v>9.43</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.3</v>
+        <v>4.57</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BV13" t="n">
-        <v>10</v>
+        <v>14.29</v>
       </c>
       <c r="BW13" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX13" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.72</v>
+        <v>3.59</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.91</v>
+        <v>3.76</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.34</v>
+        <v>4.31</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.56</v>
+        <v>4.52</v>
       </c>
       <c r="CC13" t="n">
         <v>6.07</v>
@@ -6058,16 +6058,16 @@
         <v>1.27</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CH13" t="n">
         <v>1.59</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.61</v>
@@ -6076,10 +6076,10 @@
         <v>1.44</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CN13" t="n">
         <v>2</v>
@@ -6091,7 +6091,7 @@
         <v>1.58</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6106,7 +6106,7 @@
         <v>1.65</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CW13" t="n">
         <v>1.64</v>
@@ -6127,52 +6127,52 @@
         <v>1.18</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DH13" t="n">
-        <v>80</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="DK13" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM13" t="n">
-        <v>32.75</v>
+        <v>32.86</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.6</v>
+        <v>10.62</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.45</v>
+        <v>12.62</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.75</v>
+        <v>10.57</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>42.45</v>
+        <v>43.14</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX13" t="n">
-        <v>8.5</v>
+        <v>8.85</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.4</v>
+        <v>5.48</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.35</v>
+        <v>16.48</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="H14" t="n">
-        <v>120</v>
+        <v>119.55</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="K14" t="n">
-        <v>7.7</v>
+        <v>7.73</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M14" t="n">
-        <v>68.5</v>
+        <v>67.09</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P14" t="n">
-        <v>10.8</v>
+        <v>10.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>63.6</v>
+        <v>63.36</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.2</v>
+        <v>19.64</v>
       </c>
       <c r="AA14" t="n">
-        <v>13</v>
+        <v>12.45</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.2</v>
+        <v>7.18</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.8</v>
+        <v>18.64</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
         <v>0.3</v>
@@ -6386,70 +6386,70 @@
         <v>1.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.35</v>
+        <v>11.33</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.55</v>
+        <v>6.57</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BU14" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BV14" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BW14" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BX14" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.45</v>
+        <v>6.35</v>
       </c>
       <c r="CB14" t="n">
-        <v>7</v>
+        <v>6.88</v>
       </c>
       <c r="CC14" t="n">
         <v>1.7</v>
@@ -6464,16 +6464,16 @@
         <v>1.91</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="CH14" t="n">
         <v>1.91</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CK14" t="n">
         <v>1.35</v>
@@ -6482,30 +6482,30 @@
         <v>1.66</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CN14" t="n">
         <v>2.22</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="CP14" t="n">
         <v>1.32</v>
       </c>
       <c r="CQ14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CW14" t="n">
         <v>1.61</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DB14" t="n">
         <v>1.12</v>
@@ -6525,82 +6525,82 @@
         <v>1.32</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DG14" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="DH14" t="n">
-        <v>109.95</v>
+        <v>110.19</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.1</v>
+        <v>7.14</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DM14" t="n">
-        <v>61.9</v>
+        <v>61.48</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DO14" t="n">
         <v>3.1</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.95</v>
+        <v>10.81</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.4</v>
+        <v>7.24</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>60.55</v>
+        <v>60.57</v>
       </c>
       <c r="DW14" t="n">
         <v>0.05</v>
       </c>
       <c r="DX14" t="n">
-        <v>17.45</v>
+        <v>17.29</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.35</v>
+        <v>10.19</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.4</v>
+        <v>18.34</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="15">
@@ -6610,94 +6610,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="H15" t="n">
-        <v>93.5</v>
+        <v>93.91</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="M15" t="n">
-        <v>42.8</v>
+        <v>41.73</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>8.1</v>
+        <v>8.09</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.1</v>
+        <v>11.55</v>
       </c>
       <c r="R15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>45.6</v>
+        <v>45.64</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.5</v>
+        <v>12.09</v>
       </c>
       <c r="AA15" t="n">
-        <v>8</v>
+        <v>7.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>15.7</v>
+        <v>16.18</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF15" t="n">
         <v>0.1</v>
@@ -6781,70 +6781,70 @@
         <v>2.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.6</v>
+        <v>11.48</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.75</v>
+        <v>6.67</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU15" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV15" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW15" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BX15" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="CC15" t="n">
         <v>4.47</v>
@@ -6856,40 +6856,40 @@
         <v>1.27</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CH15" t="n">
         <v>1.56</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.59</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CO15" t="n">
         <v>1.18</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
@@ -6909,97 +6909,101 @@
       <c r="CW15" t="n">
         <v>1.59</v>
       </c>
-      <c r="CX15" t="inlineStr"/>
+      <c r="CX15" t="n">
+        <v>1.45</v>
+      </c>
       <c r="CY15" t="n">
         <v>1.62</v>
       </c>
-      <c r="CZ15" t="inlineStr"/>
+      <c r="CZ15" t="n">
+        <v>2.6</v>
+      </c>
       <c r="DA15" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC15" t="n">
         <v>1.64</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF15" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="DH15" t="n">
-        <v>90.7</v>
+        <v>91.05</v>
       </c>
       <c r="DI15" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM15" t="n">
-        <v>42.1</v>
+        <v>41.57</v>
       </c>
       <c r="DN15" t="n">
         <v>0.95</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DP15" t="n">
-        <v>8.949999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.35</v>
+        <v>10.62</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.75</v>
+        <v>9.57</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.85</v>
+        <v>45.86</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.95</v>
+        <v>12.71</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.35</v>
+        <v>8.1</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.15</v>
+        <v>15.43</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7013,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0.18</v>
@@ -7102,49 +7106,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AI16" t="n">
-        <v>80.56</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.11</v>
+        <v>-0.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.89</v>
+        <v>5.3</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AN16" t="n">
-        <v>37.44</v>
+        <v>38.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.11</v>
+        <v>11.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.44</v>
+        <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.890000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7156,82 +7160,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.89</v>
+        <v>12.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.67</v>
+        <v>8.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.44</v>
+        <v>17.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.65</v>
+        <v>0.76</v>
       </c>
       <c r="BM16" t="n">
         <v>0.95</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.4</v>
+        <v>5.62</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="BR16" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU16" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BV16" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BW16" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY16" t="n">
         <v>3.2</v>
@@ -7240,25 +7244,25 @@
         <v>3.13</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.52</v>
+        <v>4.48</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.66</v>
+        <v>4.61</v>
       </c>
       <c r="CC16" t="n">
-        <v>8.56</v>
+        <v>7.99</v>
       </c>
       <c r="CD16" t="n">
-        <v>7.65</v>
+        <v>7.18</v>
       </c>
       <c r="CE16" t="n">
         <v>1.27</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CH16" t="n">
         <v>1.59</v>
@@ -7279,7 +7283,7 @@
         <v>2.84</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
@@ -7288,7 +7292,7 @@
         <v>1.59</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
@@ -7324,52 +7328,52 @@
         <v>1.2</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="DH16" t="n">
-        <v>82.5</v>
+        <v>82.33</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.05</v>
+        <v>-0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.2</v>
+        <v>5.38</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.6</v>
+        <v>41.86</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.6</v>
+        <v>10.86</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.85</v>
+        <v>10.86</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.050000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
@@ -7381,28 +7385,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.2</v>
+        <v>43.19</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.9</v>
+        <v>12.95</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.4</v>
+        <v>4.57</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.45</v>
+        <v>18.57</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="17">
@@ -7694,13 +7698,13 @@
         <v>2.49</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CU17" t="n">
         <v>1.57</v>
@@ -7730,7 +7734,7 @@
         <v>1.66</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="DE17" t="n">
         <v>0.05</v>
@@ -7815,13 +7819,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7908,49 +7912,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AI18" t="n">
-        <v>105.44</v>
+        <v>101.8</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="AN18" t="n">
-        <v>39.33</v>
+        <v>41.8</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.779999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.78</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7962,82 +7966,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>51.44</v>
+        <v>50.3</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>14.11</v>
+        <v>13.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>9.109999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="BC18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BD18" t="n">
-        <v>20.33</v>
+        <v>19</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.68</v>
+        <v>9.75</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.79</v>
+        <v>4.85</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT18" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU18" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV18" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY18" t="n">
         <v>2.19</v>
@@ -8046,25 +8050,25 @@
         <v>2.17</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="CB18" t="n">
         <v>3.98</v>
       </c>
       <c r="CC18" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CH18" t="n">
         <v>1.51</v>
@@ -8079,10 +8083,10 @@
         <v>1.42</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CN18" t="n">
         <v>2.03</v>
@@ -8091,25 +8095,25 @@
         <v>1.2</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CW18" t="n">
         <v>1.69</v>
@@ -8121,61 +8125,61 @@
         <v>1.77</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC18" t="n">
         <v>1.77</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DH18" t="n">
-        <v>99.79000000000001</v>
+        <v>98.25</v>
       </c>
       <c r="DI18" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.32</v>
+        <v>5.35</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.31</v>
+        <v>40.55</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.68</v>
+        <v>10.65</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.63</v>
+        <v>11.6</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.16</v>
+        <v>7.4</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8187,28 +8191,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.73</v>
+        <v>48.3</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>15.21</v>
+        <v>15</v>
       </c>
       <c r="DY18" t="n">
-        <v>10.05</v>
+        <v>9.9</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.68</v>
+        <v>20</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="19">
@@ -8218,94 +8222,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="H19" t="n">
-        <v>80.5</v>
+        <v>84.09</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M19" t="n">
-        <v>41.9</v>
+        <v>44.45</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="O19" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P19" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.6</v>
+        <v>12.91</v>
       </c>
       <c r="R19" t="n">
-        <v>10.7</v>
+        <v>10.27</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>44</v>
+        <v>45.64</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>11.6</v>
+        <v>12.36</v>
       </c>
       <c r="AA19" t="n">
-        <v>7</v>
+        <v>7.82</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.8</v>
+        <v>13.45</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8389,70 +8393,70 @@
         <v>1</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.8</v>
+        <v>5.71</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.65</v>
+        <v>4.76</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BU19" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV19" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY19" t="n">
-        <v>4.01</v>
+        <v>3.91</v>
       </c>
       <c r="BZ19" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.17</v>
+        <v>5.09</v>
       </c>
       <c r="CB19" t="n">
-        <v>5.45</v>
+        <v>5.37</v>
       </c>
       <c r="CC19" t="n">
         <v>8.82</v>
@@ -8464,13 +8468,13 @@
         <v>1.23</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI19" t="n">
         <v>2.26</v>
@@ -8491,28 +8495,28 @@
         <v>2.16</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CW19" t="n">
         <v>1.66</v>
@@ -8533,52 +8537,52 @@
         <v>1.17</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="DH19" t="n">
-        <v>78.8</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>-0.1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM19" t="n">
-        <v>37.85</v>
+        <v>39.38</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="DP19" t="n">
-        <v>10.15</v>
+        <v>10</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.25</v>
+        <v>11.48</v>
       </c>
       <c r="DR19" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="DS19" t="n">
         <v>0.05</v>
@@ -8590,28 +8594,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>43.9</v>
+        <v>44.76</v>
       </c>
       <c r="DW19" t="n">
         <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>9.800000000000001</v>
+        <v>10.28</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.4</v>
+        <v>6.86</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="EA19" t="n">
-        <v>14.75</v>
+        <v>15</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.91</v>
+        <v>53.86</v>
       </c>
       <c r="DW2" t="n">
         <v>0.05</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.2</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53.76</v>
+        <v>53.81</v>
       </c>
       <c r="DW5" t="n">
         <v>0.19</v>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>59.18</v>
+        <v>59.27</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.18</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>55.8</v>
+        <v>55.85</v>
       </c>
       <c r="DW12" t="n">
         <v>0.15</v>
@@ -5878,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="Y13" t="n">
         <v>0.2</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>43.14</v>
+        <v>43.19</v>
       </c>
       <c r="DW13" t="n">
         <v>0.19</v>
@@ -6281,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>63.36</v>
+        <v>63.27</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>60.57</v>
+        <v>60.52</v>
       </c>
       <c r="DW14" t="n">
         <v>0.05</v>
@@ -6682,10 +6682,10 @@
         <v>0.09</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.09</v>
+        <v>12.18</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.55</v>
+        <v>7.64</v>
       </c>
       <c r="AB15" t="n">
         <v>4.55</v>
@@ -6988,10 +6988,10 @@
         <v>0.09</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.71</v>
+        <v>12.76</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.1</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ15" t="n">
         <v>4.62</v>
@@ -7160,7 +7160,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.1</v>
@@ -7385,7 +7385,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.19</v>
+        <v>43.14</v>
       </c>
       <c r="DW16" t="n">
         <v>0.09</v>
@@ -8297,16 +8297,16 @@
         <v>12.36</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.82</v>
+        <v>7.73</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.55</v>
+        <v>4.64</v>
       </c>
       <c r="AC19" t="n">
         <v>13.45</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE19" t="n">
         <v>1.91</v>
@@ -8603,10 +8603,10 @@
         <v>10.28</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.86</v>
+        <v>6.81</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.43</v>
+        <v>3.48</v>
       </c>
       <c r="EA19" t="n">
         <v>15</v>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0.27</v>
@@ -2275,139 +2275,139 @@
         <v>1.55</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>91.40000000000001</v>
+        <v>91.91</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.4</v>
+        <v>4.27</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>39.5</v>
+        <v>39.36</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>13.18</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS4" t="n">
-        <v>8</v>
+        <v>8.18</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AU4" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>43.5</v>
+        <v>44.18</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.9</v>
+        <v>10.73</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.1</v>
+        <v>6.73</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.9</v>
+        <v>16.55</v>
       </c>
       <c r="BE4" t="n">
         <v>1.25</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.43</v>
+        <v>9.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.24</v>
+        <v>4.32</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS4" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT4" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU4" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV4" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX4" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY4" t="n">
         <v>3.34</v>
@@ -2416,31 +2416,31 @@
         <v>3.49</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.37</v>
+        <v>4.34</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.57</v>
+        <v>4.53</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.39</v>
+        <v>6.19</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.86</v>
+        <v>6.62</v>
       </c>
       <c r="CE4" t="n">
         <v>1.26</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.6</v>
@@ -2449,22 +2449,22 @@
         <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CN4" t="n">
         <v>2.05</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
@@ -2479,10 +2479,10 @@
         <v>1.62</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX4" t="n">
         <v>1.5</v>
@@ -2491,61 +2491,61 @@
         <v>1.76</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DB4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="DF4" t="n">
         <v>1.18</v>
       </c>
-      <c r="DC4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="DD4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="DE4" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="DF4" t="n">
-        <v>1.14</v>
-      </c>
       <c r="DG4" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="DH4" t="n">
-        <v>93.76000000000001</v>
+        <v>93.91</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.1</v>
+        <v>4.04</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM4" t="n">
-        <v>37.81</v>
+        <v>37.82</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.91</v>
+        <v>13</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.76</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.710000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="DS4" t="n">
         <v>0.09</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.95</v>
+        <v>45.22</v>
       </c>
       <c r="DW4" t="n">
         <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.52</v>
+        <v>11.41</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.62</v>
+        <v>7.41</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.38</v>
+        <v>17.19</v>
       </c>
       <c r="EB4" t="n">
         <v>1.28</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
-        <v>87.8</v>
+        <v>87</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="K6" t="n">
-        <v>5.4</v>
+        <v>5.18</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M6" t="n">
-        <v>41</v>
+        <v>40.18</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="P6" t="n">
-        <v>14</v>
+        <v>13.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.9</v>
+        <v>10.82</v>
       </c>
       <c r="R6" t="n">
-        <v>7.3</v>
+        <v>7.36</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>44.7</v>
+        <v>43.91</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.8</v>
+        <v>15.36</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.2</v>
+        <v>10.91</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AF6" t="n">
         <v>0.09</v>
@@ -3162,34 +3162,34 @@
         <v>2.09</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="BH6" t="n">
-        <v>11.52</v>
+        <v>11.73</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="BJ6" t="n">
         <v>1.14</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.48</v>
+        <v>5.68</v>
       </c>
       <c r="BQ6" t="n">
         <v>6</v>
@@ -3198,34 +3198,34 @@
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU6" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV6" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX6" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.43</v>
+        <v>3.39</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.06</v>
+        <v>4.02</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="CC6" t="n">
         <v>5.53</v>
@@ -3237,10 +3237,10 @@
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CH6" t="n">
         <v>1.53</v>
@@ -3252,16 +3252,16 @@
         <v>1.66</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CO6" t="n">
         <v>1.19</v>
@@ -3276,13 +3276,13 @@
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV6" t="n">
         <v>2.27</v>
@@ -3294,97 +3294,97 @@
         <v>1.49</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.5</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB6" t="n">
         <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD6" t="n">
         <v>2.78</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.33</v>
+        <v>88.86</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.62</v>
+        <v>4.55</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.76</v>
+        <v>36.54</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.62</v>
+        <v>13.59</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.38</v>
+        <v>11.32</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.43</v>
+        <v>8.4</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.86</v>
+        <v>45.41</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.9</v>
+        <v>12.81</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.62</v>
+        <v>4.55</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.05</v>
+        <v>16.86</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="7">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.09</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AM9" t="n">
         <v>1</v>
       </c>
-      <c r="AH9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>97</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AN9" t="n">
-        <v>43.44</v>
+        <v>42.1</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.44</v>
+        <v>13.1</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.33</v>
+        <v>10.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.33</v>
+        <v>7.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>51.78</v>
+        <v>50.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.67</v>
+        <v>14.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.890000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.78</v>
+        <v>5.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>20.11</v>
+        <v>19.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.15</v>
+        <v>3.24</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.6</v>
+        <v>10.43</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.15</v>
+        <v>3.24</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="BM9" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BP9" t="n">
         <v>5.1</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.45</v>
+        <v>5.29</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BV9" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BW9" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX9" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BY9" t="n">
         <v>2.33</v>
@@ -4431,22 +4431,22 @@
         <v>2.27</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.33</v>
+        <v>3.52</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.63</v>
+        <v>3.83</v>
       </c>
       <c r="CE9" t="n">
         <v>1.28</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CG9" t="n">
         <v>3.39</v>
@@ -4455,7 +4455,7 @@
         <v>1.58</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.57</v>
@@ -4467,7 +4467,7 @@
         <v>1.82</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CN9" t="n">
         <v>2.04</v>
@@ -4479,7 +4479,7 @@
         <v>1.64</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
@@ -4494,7 +4494,7 @@
         <v>1.61</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CW9" t="n">
         <v>1.58</v>
@@ -4515,7 +4515,7 @@
         <v>1.19</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD9" t="n">
         <v>2.53</v>
@@ -4524,76 +4524,76 @@
         <v>0.05</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="DH9" t="n">
-        <v>101.55</v>
+        <v>101</v>
       </c>
       <c r="DI9" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.05</v>
+        <v>5.76</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DM9" t="n">
-        <v>52.4</v>
+        <v>51.33</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.45</v>
+        <v>11.38</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.55</v>
+        <v>10.43</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.9</v>
+        <v>7.19</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.65</v>
+        <v>52.05</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>16.2</v>
+        <v>15.76</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.75</v>
+        <v>10.57</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.45</v>
+        <v>5.19</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0.2</v>
@@ -4696,115 +4696,115 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AI10" t="n">
-        <v>81.55</v>
+        <v>78.33</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>34.27</v>
+        <v>32.92</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.09</v>
+        <v>14.42</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.36</v>
+        <v>10.33</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.359999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>42.82</v>
+        <v>41.83</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.550000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.73</v>
+        <v>5.92</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.18</v>
+        <v>18.67</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.62</v>
+        <v>10.55</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BN10" t="n">
         <v>2.14</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.48</v>
+        <v>5.36</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.14</v>
+        <v>5.18</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4813,19 +4813,19 @@
         <v>100</v>
       </c>
       <c r="BT10" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BU10" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV10" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BW10" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BX10" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY10" t="n">
         <v>3.68</v>
@@ -4834,10 +4834,10 @@
         <v>3.87</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="CC10" t="n">
         <v>6.55</v>
@@ -4846,16 +4846,16 @@
         <v>7.49</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CI10" t="n">
         <v>2.2</v>
@@ -4870,7 +4870,7 @@
         <v>1.66</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CN10" t="n">
         <v>2.21</v>
@@ -4882,7 +4882,7 @@
         <v>1.6</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4897,25 +4897,25 @@
         <v>1.62</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX10" t="n">
         <v>1.46</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.59</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC10" t="n">
         <v>1.61</v>
@@ -4924,46 +4924,46 @@
         <v>2.51</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DH10" t="n">
-        <v>86.95</v>
+        <v>84.95</v>
       </c>
       <c r="DI10" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.28</v>
+        <v>4.36</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.95</v>
+        <v>37.05</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.19</v>
+        <v>13.41</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.14</v>
+        <v>11.09</v>
       </c>
       <c r="DR10" t="n">
-        <v>8</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DS10" t="n">
         <v>0.14</v>
@@ -4975,25 +4975,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.43</v>
+        <v>42.86</v>
       </c>
       <c r="DW10" t="n">
         <v>0.09</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.1</v>
+        <v>11.05</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.91</v>
+        <v>6.96</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.19</v>
+        <v>4.09</v>
       </c>
       <c r="EA10" t="n">
-        <v>18</v>
+        <v>17.77</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="EC10" t="n">
         <v>2</v>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
@@ -5018,82 +5018,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="H11" t="n">
-        <v>93.73</v>
+        <v>96.83</v>
       </c>
       <c r="I11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J11" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="K11" t="n">
-        <v>5.09</v>
+        <v>5.33</v>
       </c>
       <c r="L11" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="M11" t="n">
-        <v>44.36</v>
+        <v>44.67</v>
       </c>
       <c r="N11" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="O11" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="P11" t="n">
-        <v>10.18</v>
+        <v>9.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.27</v>
+        <v>13.42</v>
       </c>
       <c r="R11" t="n">
-        <v>6.45</v>
+        <v>6.17</v>
       </c>
       <c r="S11" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51.55</v>
+        <v>51.33</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.27</v>
+        <v>14.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.640000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.64</v>
+        <v>4.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.45</v>
+        <v>19.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
         <v>0.1</v>
@@ -5177,70 +5177,70 @@
         <v>1.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.289999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.24</v>
+        <v>4.32</v>
       </c>
       <c r="BQ11" t="n">
         <v>5.05</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS11" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU11" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV11" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX11" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.01</v>
+        <v>2.91</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.18</v>
+        <v>4.16</v>
       </c>
       <c r="CC11" t="n">
         <v>5.43</v>
@@ -5252,40 +5252,40 @@
         <v>1.3</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CH11" t="n">
         <v>1.52</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.67</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL11" t="n">
         <v>1.87</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO11" t="n">
         <v>1.2</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
@@ -5306,13 +5306,13 @@
         <v>1.71</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY11" t="n">
         <v>1.8</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA11" t="n">
         <v>2.01</v>
@@ -5321,52 +5321,52 @@
         <v>1.23</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="DE11" t="n">
         <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="DH11" t="n">
-        <v>94.62</v>
+        <v>96.27</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.24</v>
+        <v>5.36</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.33</v>
+        <v>42.59</v>
       </c>
       <c r="DN11" t="n">
         <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.14</v>
+        <v>10.91</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13</v>
+        <v>13.09</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.66</v>
+        <v>7.46</v>
       </c>
       <c r="DS11" t="n">
         <v>0.09</v>
@@ -5381,25 +5381,25 @@
         <v>48.95</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.38</v>
+        <v>13.45</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.289999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.14</v>
+        <v>20.68</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="12">
@@ -5409,76 +5409,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F12" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="G12" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>107.56</v>
+        <v>109.3</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="K12" t="n">
-        <v>5.89</v>
+        <v>5.6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="M12" t="n">
-        <v>46.22</v>
+        <v>46.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O12" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="P12" t="n">
-        <v>10.78</v>
+        <v>10.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.33</v>
+        <v>14.6</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="U12" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>51.67</v>
+        <v>53.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z12" t="n">
         <v>15</v>
@@ -5490,13 +5490,13 @@
         <v>6</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.33</v>
+        <v>19.6</v>
       </c>
       <c r="AD12" t="n">
         <v>1.71</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
         <v>0.27</v>
@@ -5580,70 +5580,70 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.6</v>
+        <v>9.57</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.9</v>
+        <v>4.81</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.7</v>
+        <v>4.76</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BU12" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BV12" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BW12" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BX12" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.11</v>
+        <v>4.15</v>
       </c>
       <c r="CC12" t="n">
         <v>2.92</v>
@@ -5652,22 +5652,22 @@
         <v>2.92</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CK12" t="n">
         <v>1.4</v>
@@ -5676,10 +5676,10 @@
         <v>1.71</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO12" t="n">
         <v>1.15</v>
@@ -5688,13 +5688,13 @@
         <v>1.53</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CR12" t="n">
         <v>1.34</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CT12" t="n">
         <v>3.34</v>
@@ -5703,22 +5703,22 @@
         <v>1.7</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CX12" t="n">
         <v>1.5</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.48</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="DB12" t="n">
         <v>1.16</v>
@@ -5727,82 +5727,82 @@
         <v>1.53</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="DH12" t="n">
-        <v>108.95</v>
+        <v>109.71</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.35</v>
+        <v>5.24</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DM12" t="n">
         <v>51.85</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.35</v>
+        <v>12.24</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.45</v>
+        <v>12.67</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>55.85</v>
+        <v>56.47</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.6</v>
+        <v>15.57</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.7</v>
+        <v>6.67</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.95</v>
+        <v>20.57</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="13">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="H13" t="n">
-        <v>88</v>
+        <v>89.27</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="M13" t="n">
-        <v>34.7</v>
+        <v>36.82</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="O13" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="P13" t="n">
-        <v>11</v>
+        <v>11.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>12.73</v>
       </c>
       <c r="R13" t="n">
-        <v>10.3</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>40.2</v>
+        <v>41.82</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>9.300000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.8</v>
+        <v>6.18</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.3</v>
+        <v>17.27</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
         <v>0.18</v>
@@ -5983,70 +5983,70 @@
         <v>2.09</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.43</v>
+        <v>9.5</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.57</v>
+        <v>4.64</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU13" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BV13" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX13" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.59</v>
+        <v>3.42</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.76</v>
+        <v>3.56</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="CC13" t="n">
         <v>6.07</v>
@@ -6061,16 +6061,16 @@
         <v>2.3</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI13" t="n">
         <v>2.22</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK13" t="n">
         <v>1.44</v>
@@ -6088,7 +6088,7 @@
         <v>1.16</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CQ13" t="n">
         <v>2.43</v>
@@ -6097,16 +6097,16 @@
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CT13" t="n">
         <v>3.34</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CW13" t="n">
         <v>1.64</v>
@@ -6124,7 +6124,7 @@
         <v>2</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="DC13" t="n">
         <v>1.6</v>
@@ -6133,46 +6133,46 @@
         <v>2.47</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="DH13" t="n">
-        <v>81.56999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="DK13" t="n">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM13" t="n">
-        <v>32.86</v>
+        <v>34</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.62</v>
+        <v>10.96</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.62</v>
+        <v>12.5</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.57</v>
+        <v>10.23</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>43.19</v>
+        <v>43.86</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX13" t="n">
-        <v>8.85</v>
+        <v>9.09</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.48</v>
+        <v>5.68</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.48</v>
+        <v>16.5</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="14">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0.09</v>
@@ -6700,139 +6700,139 @@
         <v>1.09</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="AI15" t="n">
-        <v>87.90000000000001</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.6</v>
+        <v>4.45</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.4</v>
+        <v>45.73</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.6</v>
+        <v>9.91</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.3</v>
+        <v>9.73</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>46.1</v>
+        <v>47.73</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.4</v>
+        <v>13.64</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="BD15" t="n">
-        <v>14.6</v>
+        <v>14.73</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.48</v>
+        <v>11.68</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="BO15" t="n">
         <v>1.05</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.81</v>
+        <v>5.05</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.67</v>
+        <v>6.64</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV15" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW15" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BX15" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BY15" t="n">
         <v>2.78</v>
@@ -6841,28 +6841,28 @@
         <v>2.89</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.47</v>
+        <v>4.27</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.72</v>
+        <v>4.5</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF15" t="n">
         <v>2.32</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CI15" t="n">
         <v>2.3</v>
@@ -6871,16 +6871,16 @@
         <v>1.59</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM15" t="n">
         <v>2.92</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CO15" t="n">
         <v>1.18</v>
@@ -6889,19 +6889,19 @@
         <v>1.64</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV15" t="n">
         <v>2.46</v>
@@ -6919,91 +6919,91 @@
         <v>2.6</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DB15" t="n">
         <v>1.2</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="DE15" t="n">
         <v>0.09</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="DH15" t="n">
-        <v>91.05</v>
+        <v>93.86</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="DM15" t="n">
-        <v>41.57</v>
+        <v>43.73</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO15" t="n">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="DP15" t="n">
-        <v>8.9</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.62</v>
+        <v>10.73</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.57</v>
+        <v>9.32</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.86</v>
+        <v>46.68</v>
       </c>
       <c r="DW15" t="n">
         <v>0.09</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.76</v>
+        <v>12.91</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.140000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.62</v>
+        <v>4.64</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.43</v>
+        <v>15.46</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="16">
@@ -7416,94 +7416,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="H17" t="n">
-        <v>126.4</v>
+        <v>124.64</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="K17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="M17" t="n">
-        <v>67.2</v>
+        <v>66.27</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="P17" t="n">
-        <v>10.7</v>
+        <v>10.45</v>
       </c>
       <c r="Q17" t="n">
         <v>10</v>
       </c>
       <c r="R17" t="n">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>58.6</v>
+        <v>58.73</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.1</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.1</v>
+        <v>13.27</v>
       </c>
       <c r="AB17" t="n">
-        <v>6</v>
+        <v>6.73</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.8</v>
+        <v>21.09</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7587,70 +7587,70 @@
         <v>2.09</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.43</v>
+        <v>9.32</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.67</v>
+        <v>4.55</v>
       </c>
       <c r="BR17" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT17" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU17" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BV17" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX17" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.23</v>
+        <v>4.22</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="CC17" t="n">
         <v>2.39</v>
@@ -7659,7 +7659,7 @@
         <v>2.37</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF17" t="n">
         <v>2.33</v>
@@ -7677,16 +7677,16 @@
         <v>1.65</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL17" t="n">
         <v>1.81</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO17" t="n">
         <v>1.18</v>
@@ -7695,7 +7695,7 @@
         <v>1.61</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CR17" t="n">
         <v>1.37</v>
@@ -7719,13 +7719,13 @@
         <v>1.52</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.46</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB17" t="n">
         <v>1.2</v>
@@ -7734,82 +7734,82 @@
         <v>1.66</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DH17" t="n">
-        <v>109.72</v>
+        <v>109.6</v>
       </c>
       <c r="DI17" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.38</v>
+        <v>5.46</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="DM17" t="n">
-        <v>58.62</v>
+        <v>58.54</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.72</v>
+        <v>11.54</v>
       </c>
       <c r="DQ17" t="n">
         <v>10</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.53</v>
+        <v>6.55</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.81</v>
+        <v>55.04</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>18.57</v>
+        <v>19.05</v>
       </c>
       <c r="DY17" t="n">
-        <v>12.24</v>
+        <v>12.36</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.34</v>
+        <v>6.68</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.05</v>
+        <v>20.72</v>
       </c>
       <c r="EB17" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="18">
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0.18</v>
@@ -8315,49 +8315,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AI19" t="n">
-        <v>77.09999999999999</v>
+        <v>77.09</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN19" t="n">
-        <v>33.8</v>
+        <v>34.55</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AQ19" t="n">
         <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.9</v>
+        <v>10.64</v>
       </c>
       <c r="AS19" t="n">
-        <v>9.699999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8369,82 +8369,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>43.8</v>
+        <v>43.64</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA19" t="n">
-        <v>8</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="BD19" t="n">
-        <v>16.7</v>
+        <v>17.09</v>
       </c>
       <c r="BE19" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="BF19" t="n">
         <v>0.91</v>
       </c>
-      <c r="BF19" t="n">
-        <v>1</v>
-      </c>
       <c r="BG19" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.48</v>
+        <v>10.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.71</v>
+        <v>5.73</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT19" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU19" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV19" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY19" t="n">
         <v>3.91</v>
@@ -8453,31 +8453,31 @@
         <v>4.1</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.09</v>
+        <v>5.04</v>
       </c>
       <c r="CB19" t="n">
-        <v>5.37</v>
+        <v>5.31</v>
       </c>
       <c r="CC19" t="n">
-        <v>8.82</v>
+        <v>8.49</v>
       </c>
       <c r="CD19" t="n">
-        <v>9.710000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="CE19" t="n">
         <v>1.23</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.62</v>
@@ -8486,10 +8486,10 @@
         <v>1.37</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CN19" t="n">
         <v>2.16</v>
@@ -8498,7 +8498,7 @@
         <v>1.15</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CQ19" t="n">
         <v>2.25</v>
@@ -8507,16 +8507,16 @@
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CT19" t="n">
         <v>3.35</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CW19" t="n">
         <v>1.66</v>
@@ -8531,7 +8531,7 @@
         <v>2.44</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DB19" t="n">
         <v>1.17</v>
@@ -8540,82 +8540,82 @@
         <v>1.53</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DE19" t="n">
         <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="DH19" t="n">
-        <v>80.76000000000001</v>
+        <v>80.59</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM19" t="n">
-        <v>39.38</v>
+        <v>39.5</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="DP19" t="n">
         <v>10</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.48</v>
+        <v>11.78</v>
       </c>
       <c r="DR19" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>44.76</v>
+        <v>44.64</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.28</v>
+        <v>10.5</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.81</v>
+        <v>6.86</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.48</v>
+        <v>3.64</v>
       </c>
       <c r="EA19" t="n">
-        <v>15</v>
+        <v>15.27</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6</v>
+        <v>3.27</v>
       </c>
       <c r="H2" t="n">
-        <v>103.7</v>
+        <v>102.73</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="K2" t="n">
-        <v>6.2</v>
+        <v>5.82</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>52.2</v>
+        <v>50.18</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="O2" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.8</v>
+        <v>10.91</v>
       </c>
       <c r="R2" t="n">
-        <v>6.6</v>
+        <v>6.91</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>53</v>
+        <v>51.64</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.5</v>
+        <v>16.27</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.5</v>
+        <v>10.27</v>
       </c>
       <c r="AB2" t="n">
         <v>6</v>
       </c>
       <c r="AC2" t="n">
-        <v>18.1</v>
+        <v>17.91</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF2" t="n">
         <v>0.09</v>
@@ -1550,70 +1550,70 @@
         <v>2.64</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.05</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.48</v>
+        <v>5.32</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT2" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BU2" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BV2" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX2" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.61</v>
+        <v>4.57</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.73</v>
+        <v>4.68</v>
       </c>
       <c r="CC2" t="n">
         <v>2.03</v>
@@ -1625,19 +1625,19 @@
         <v>1.23</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CK2" t="n">
         <v>1.43</v>
@@ -1646,19 +1646,19 @@
         <v>1.82</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO2" t="n">
         <v>1.13</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CR2" t="n">
         <v>1.33</v>
@@ -1673,7 +1673,7 @@
         <v>1.71</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CW2" t="n">
         <v>1.63</v>
@@ -1682,97 +1682,97 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB2" t="n">
         <v>1.16</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.33</v>
+        <v>3.18</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.81</v>
+        <v>100.46</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.86</v>
+        <v>5.68</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.05</v>
+        <v>48.18</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DP2" t="n">
         <v>10.86</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.05</v>
+        <v>11.09</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.24</v>
+        <v>7.37</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.86</v>
+        <v>53.14</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.95</v>
+        <v>15.86</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.19</v>
+        <v>10.09</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.76</v>
+        <v>5.78</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.95</v>
+        <v>16.91</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0.09</v>
@@ -1872,118 +1872,118 @@
         <v>1.45</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="AI3" t="n">
-        <v>97.8</v>
+        <v>100</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN3" t="n">
-        <v>48.3</v>
+        <v>50.36</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>10.18</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.3</v>
+        <v>11.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.8</v>
+        <v>6.64</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>57.4</v>
+        <v>57.82</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA3" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>6</v>
+        <v>5.64</v>
       </c>
       <c r="BD3" t="n">
-        <v>16.8</v>
+        <v>16.55</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.05</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.67</v>
+        <v>4.64</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.38</v>
+        <v>5.23</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,19 +1992,19 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU3" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BV3" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX3" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BY3" t="n">
         <v>1.62</v>
@@ -2013,31 +2013,31 @@
         <v>1.66</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.63</v>
+        <v>4.59</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="CE3" t="n">
         <v>1.24</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CH3" t="n">
         <v>1.67</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.6</v>
@@ -2049,10 +2049,10 @@
         <v>1.83</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO3" t="n">
         <v>1.13</v>
@@ -2061,7 +2061,7 @@
         <v>1.49</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
@@ -2076,106 +2076,106 @@
         <v>1.72</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CX3" t="n">
         <v>1.52</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB3" t="n">
         <v>1.16</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="DE3" t="n">
         <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.05</v>
+        <v>101.04</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.14</v>
+        <v>5.09</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM3" t="n">
-        <v>53.86</v>
+        <v>54.64</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.38</v>
+        <v>10.46</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.48</v>
+        <v>12.41</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.52</v>
+        <v>6.45</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.19</v>
+        <v>57.41</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.53</v>
+        <v>15.36</v>
       </c>
       <c r="DY3" t="n">
-        <v>9</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.52</v>
+        <v>6.32</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.43</v>
+        <v>16.32</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0.09</v>
@@ -2678,139 +2678,139 @@
         <v>0.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AI5" t="n">
-        <v>101</v>
+        <v>102.27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.8</v>
+        <v>6.82</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN5" t="n">
-        <v>55.3</v>
+        <v>54.36</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AP5" t="n">
         <v>3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.3</v>
+        <v>10.45</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.2</v>
+        <v>6.91</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52.9</v>
+        <v>52.91</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA5" t="n">
-        <v>15.4</v>
+        <v>14.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.6</v>
+        <v>9.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.8</v>
+        <v>5.64</v>
       </c>
       <c r="BD5" t="n">
-        <v>18.9</v>
+        <v>19.09</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="BF5" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="BH5" t="n">
-        <v>11</v>
+        <v>10.91</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="BJ5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BL5" t="n">
         <v>1</v>
       </c>
-      <c r="BK5" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1.05</v>
-      </c>
       <c r="BM5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.9</v>
+        <v>5.82</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>90.48</v>
+        <v>86.36</v>
       </c>
       <c r="BT5" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU5" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BV5" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BW5" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BX5" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY5" t="n">
         <v>1.42</v>
@@ -2819,31 +2819,31 @@
         <v>1.48</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.97</v>
+        <v>4.91</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.29</v>
+        <v>5.21</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CE5" t="n">
         <v>1.23</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.64</v>
@@ -2852,103 +2852,103 @@
         <v>1.41</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CM5" t="n">
         <v>2.71</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO5" t="n">
         <v>1.13</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CR5" t="n">
         <v>1.33</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX5" t="n">
         <v>1.52</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.45</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="DE5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="DI5" t="n">
         <v>0.09</v>
       </c>
-      <c r="DF5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>0.1</v>
-      </c>
       <c r="DJ5" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.33</v>
+        <v>7.32</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DM5" t="n">
-        <v>56.67</v>
+        <v>56.14</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="DP5" t="n">
-        <v>9.380000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.95</v>
+        <v>11</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.71</v>
+        <v>6.59</v>
       </c>
       <c r="DS5" t="n">
         <v>0.09</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53.81</v>
+        <v>53.78</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.38</v>
+        <v>17.05</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.81</v>
+        <v>10.59</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.57</v>
+        <v>6.45</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.33</v>
+        <v>18.45</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="6">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="H7" t="n">
-        <v>97.22</v>
+        <v>96.3</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
-        <v>6.44</v>
+        <v>7.1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>51.33</v>
+        <v>53</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>9.220000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.22</v>
+        <v>11.5</v>
       </c>
       <c r="R7" t="n">
-        <v>8.67</v>
+        <v>8.9</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52.89</v>
+        <v>53.4</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.11</v>
+        <v>14.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.33</v>
+        <v>7.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.78</v>
+        <v>6.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.22</v>
+        <v>17.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
         <v>0.27</v>
@@ -3565,70 +3565,70 @@
         <v>2.09</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.65</v>
+        <v>10.86</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.65</v>
+        <v>4.81</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BU7" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BV7" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW7" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX7" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="CA7" t="n">
         <v>4.07</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="CC7" t="n">
         <v>4.14</v>
@@ -3643,7 +3643,7 @@
         <v>2.24</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CH7" t="n">
         <v>1.62</v>
@@ -3655,16 +3655,16 @@
         <v>1.53</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CO7" t="n">
         <v>1.14</v>
@@ -3688,22 +3688,22 @@
         <v>1.67</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX7" t="n">
         <v>1.44</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.62</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DB7" t="n">
         <v>1.18</v>
@@ -3715,46 +3715,46 @@
         <v>2.44</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF7" t="n">
         <v>1</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.95</v>
+        <v>3.09</v>
       </c>
       <c r="DH7" t="n">
-        <v>96.55</v>
+        <v>96.14</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.3</v>
+        <v>5.66</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.25</v>
+        <v>47.29</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.05</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.75</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0.05</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.2</v>
+        <v>51.52</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.35</v>
+        <v>11.95</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.3</v>
+        <v>6.62</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.05</v>
+        <v>5.33</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.4</v>
+        <v>18.66</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="H8" t="n">
-        <v>119.1</v>
+        <v>116.91</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="K8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>53.5</v>
+        <v>52.27</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O8" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="P8" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.4</v>
+        <v>10.27</v>
       </c>
       <c r="R8" t="n">
-        <v>6.2</v>
+        <v>6.09</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>57.1</v>
+        <v>55.27</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.9</v>
+        <v>17.91</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.1</v>
+        <v>12.27</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.8</v>
+        <v>5.64</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.7</v>
+        <v>21.36</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AF8" t="n">
         <v>0.09</v>
@@ -3968,70 +3968,70 @@
         <v>1.82</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.62</v>
+        <v>10.91</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.38</v>
+        <v>5.55</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.24</v>
+        <v>5.36</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS8" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT8" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU8" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX8" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
       <c r="CC8" t="n">
         <v>4.53</v>
@@ -4043,70 +4043,70 @@
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="CH8" t="n">
         <v>1.49</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK8" t="n">
         <v>1.52</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO8" t="n">
         <v>1.23</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="CT8" t="n">
         <v>3.2</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX8" t="n">
         <v>1.56</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.36</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB8" t="n">
         <v>1.25</v>
@@ -4118,79 +4118,79 @@
         <v>2.98</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="DH8" t="n">
-        <v>111</v>
+        <v>110.28</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.57</v>
+        <v>6.55</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="DM8" t="n">
-        <v>47.29</v>
+        <v>46.96</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.33</v>
+        <v>11.18</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.62</v>
+        <v>10.54</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.81</v>
+        <v>6.72</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>52.05</v>
+        <v>51.36</v>
       </c>
       <c r="DW8" t="n">
         <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.24</v>
+        <v>15.86</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.19</v>
+        <v>9.91</v>
       </c>
       <c r="DZ8" t="n">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.81</v>
+        <v>20.68</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="9">
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>41.83</v>
+        <v>41.92</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.08</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>42.86</v>
+        <v>42.91</v>
       </c>
       <c r="DW10" t="n">
         <v>0.09</v>
@@ -5475,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
       <c r="Y12" t="n">
         <v>0.1</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>56.47</v>
+        <v>56.43</v>
       </c>
       <c r="DW12" t="n">
         <v>0.14</v>
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0.45</v>
@@ -6305,52 +6305,52 @@
         <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.9</v>
+        <v>4.09</v>
       </c>
       <c r="AI14" t="n">
-        <v>99.90000000000001</v>
+        <v>100.55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AL14" t="n">
-        <v>6.5</v>
+        <v>6.91</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AN14" t="n">
-        <v>55.3</v>
+        <v>56.09</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.1</v>
+        <v>10.91</v>
       </c>
       <c r="AR14" t="n">
-        <v>9</v>
+        <v>8.91</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.6</v>
+        <v>8.18</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6362,82 +6362,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>57.5</v>
+        <v>58</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.7</v>
+        <v>14.73</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.7</v>
+        <v>7.91</v>
       </c>
       <c r="BC14" t="n">
-        <v>7</v>
+        <v>6.82</v>
       </c>
       <c r="BD14" t="n">
-        <v>18</v>
+        <v>18.27</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.33</v>
+        <v>11.59</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BN14" t="n">
         <v>1.95</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.76</v>
+        <v>4.95</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.57</v>
+        <v>6.64</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BT14" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BU14" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BW14" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BX14" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY14" t="n">
         <v>1.24</v>
@@ -6446,28 +6446,28 @@
         <v>1.25</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.35</v>
+        <v>6.26</v>
       </c>
       <c r="CB14" t="n">
-        <v>6.88</v>
+        <v>6.78</v>
       </c>
       <c r="CC14" t="n">
         <v>1.7</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CI14" t="n">
         <v>2.38</v>
@@ -6485,24 +6485,24 @@
         <v>2.93</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CO14" t="n">
         <v>1.07</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CQ14" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CV14" t="n">
         <v>2.49</v>
@@ -6512,11 +6512,11 @@
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DB14" t="n">
         <v>1.12</v>
@@ -6528,46 +6528,46 @@
         <v>1.83</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DF14" t="n">
         <v>1.14</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="DH14" t="n">
-        <v>110.19</v>
+        <v>110.05</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.09</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.14</v>
+        <v>7.32</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="DM14" t="n">
-        <v>61.48</v>
+        <v>61.59</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.81</v>
+        <v>10.73</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.76</v>
+        <v>8.73</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.24</v>
+        <v>7.09</v>
       </c>
       <c r="DS14" t="n">
         <v>0.09</v>
@@ -6579,28 +6579,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>60.52</v>
+        <v>60.64</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX14" t="n">
-        <v>17.29</v>
+        <v>17.19</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.34</v>
+        <v>18.45</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="15">
@@ -7013,13 +7013,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0.18</v>
@@ -7106,49 +7106,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AI16" t="n">
-        <v>80.40000000000001</v>
+        <v>78.73</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN16" t="n">
-        <v>38.4</v>
+        <v>38</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.6</v>
+        <v>11.82</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.5</v>
+        <v>10.09</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.5</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7160,82 +7160,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>41.1</v>
+        <v>41.18</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA16" t="n">
-        <v>12.1</v>
+        <v>12.09</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.1</v>
+        <v>11.27</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM16" t="n">
         <v>0.95</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.62</v>
+        <v>5.73</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.05</v>
+        <v>5.14</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS16" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BV16" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY16" t="n">
         <v>3.2</v>
@@ -7244,25 +7244,25 @@
         <v>3.13</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.61</v>
+        <v>4.59</v>
       </c>
       <c r="CC16" t="n">
-        <v>7.99</v>
+        <v>7.63</v>
       </c>
       <c r="CD16" t="n">
-        <v>7.18</v>
+        <v>6.9</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF16" t="n">
         <v>2.31</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CH16" t="n">
         <v>1.59</v>
@@ -7277,13 +7277,13 @@
         <v>1.37</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
@@ -7316,13 +7316,13 @@
         <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.37</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DB16" t="n">
         <v>1.2</v>
@@ -7337,43 +7337,43 @@
         <v>0.09</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="DH16" t="n">
-        <v>82.33</v>
+        <v>81.41</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.38</v>
+        <v>5.22</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.86</v>
+        <v>41.5</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.86</v>
+        <v>11</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.86</v>
+        <v>10.63</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.95</v>
+        <v>8</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
@@ -7385,28 +7385,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.14</v>
+        <v>43.09</v>
       </c>
       <c r="DW16" t="n">
         <v>0.09</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.95</v>
+        <v>12.91</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.380000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.57</v>
+        <v>4.45</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.57</v>
+        <v>18.64</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="17">
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
@@ -7831,49 +7831,49 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="H18" t="n">
-        <v>94.7</v>
+        <v>96.27</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="K18" t="n">
-        <v>5.5</v>
+        <v>5.18</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M18" t="n">
-        <v>39.3</v>
+        <v>37.91</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="P18" t="n">
-        <v>10.3</v>
+        <v>10.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.3</v>
+        <v>13.36</v>
       </c>
       <c r="R18" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7885,28 +7885,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>46.3</v>
+        <v>46.36</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.2</v>
+        <v>15.27</v>
       </c>
       <c r="AA18" t="n">
-        <v>10.9</v>
+        <v>10</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.3</v>
+        <v>5.27</v>
       </c>
       <c r="AC18" t="n">
-        <v>21</v>
+        <v>20.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AE18" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7990,70 +7990,70 @@
         <v>1.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.75</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP18" t="n">
         <v>4.9</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT18" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU18" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="CC18" t="n">
         <v>3.1</v>
@@ -8062,13 +8062,13 @@
         <v>3.42</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CH18" t="n">
         <v>1.51</v>
@@ -8083,10 +8083,10 @@
         <v>1.42</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CN18" t="n">
         <v>2.03</v>
@@ -8107,7 +8107,7 @@
         <v>2.61</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CU18" t="n">
         <v>1.53</v>
@@ -8128,58 +8128,58 @@
         <v>2.5</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DB18" t="n">
         <v>1.24</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="DH18" t="n">
-        <v>98.25</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="DI18" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.35</v>
+        <v>5.19</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.55</v>
+        <v>39.76</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.65</v>
+        <v>10.71</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.6</v>
+        <v>11.71</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.4</v>
+        <v>7.57</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8191,28 +8191,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.3</v>
+        <v>48.24</v>
       </c>
       <c r="DW18" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DX18" t="n">
-        <v>15</v>
+        <v>14.57</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.9</v>
+        <v>9.48</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="EA18" t="n">
         <v>20</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9</v>
+        <v>4.09</v>
       </c>
       <c r="H7" t="n">
-        <v>96.3</v>
+        <v>95.55</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
-        <v>7.1</v>
+        <v>7.18</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>53</v>
+        <v>51.91</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="P7" t="n">
-        <v>8.9</v>
+        <v>8.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.5</v>
+        <v>11.73</v>
       </c>
       <c r="R7" t="n">
-        <v>8.9</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>53.4</v>
+        <v>52.73</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.2</v>
+        <v>14.09</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.9</v>
+        <v>7.82</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.3</v>
+        <v>6.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.9</v>
+        <v>17.55</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF7" t="n">
         <v>0.27</v>
@@ -3565,70 +3565,70 @@
         <v>2.09</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.86</v>
+        <v>10.91</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL7" t="n">
         <v>0.86</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.81</v>
+        <v>4.77</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.95</v>
+        <v>6.05</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BT7" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU7" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX7" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="CC7" t="n">
         <v>4.14</v>
@@ -3640,13 +3640,13 @@
         <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CG7" t="n">
         <v>3.61</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CI7" t="n">
         <v>2.41</v>
@@ -3667,19 +3667,19 @@
         <v>2.21</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP7" t="n">
         <v>1.57</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CR7" t="n">
         <v>1.34</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
@@ -3691,7 +3691,7 @@
         <v>2.53</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CX7" t="n">
         <v>1.44</v>
@@ -3703,7 +3703,7 @@
         <v>2.62</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DB7" t="n">
         <v>1.18</v>
@@ -3715,79 +3715,79 @@
         <v>2.44</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF7" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.09</v>
+        <v>3.22</v>
       </c>
       <c r="DH7" t="n">
-        <v>96.14</v>
+        <v>95.78</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.66</v>
+        <v>5.77</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DM7" t="n">
-        <v>47.29</v>
+        <v>47</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.859999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.9</v>
+        <v>10.09</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.859999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.52</v>
+        <v>51.28</v>
       </c>
       <c r="DW7" t="n">
         <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.95</v>
+        <v>12</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.62</v>
+        <v>6.64</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.33</v>
+        <v>5.36</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.66</v>
+        <v>18.45</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="8">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.09</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AI9" t="n">
-        <v>96.3</v>
+        <v>95.55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="AM9" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AN9" t="n">
-        <v>42.1</v>
+        <v>41.73</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.1</v>
+        <v>13.18</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.1</v>
+        <v>9.91</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>50.6</v>
+        <v>50.91</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA9" t="n">
-        <v>14.8</v>
+        <v>15.18</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.6</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.2</v>
+        <v>5.64</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.5</v>
+        <v>19.64</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.43</v>
+        <v>10.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL9" t="n">
         <v>0.86</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.29</v>
+        <v>5.41</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BT9" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV9" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX9" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY9" t="n">
         <v>2.33</v>
@@ -4431,22 +4431,22 @@
         <v>2.27</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CB9" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="CE9" t="n">
         <v>1.28</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CG9" t="n">
         <v>3.39</v>
@@ -4455,22 +4455,22 @@
         <v>1.58</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.57</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CO9" t="n">
         <v>1.17</v>
@@ -4479,7 +4479,7 @@
         <v>1.64</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
@@ -4503,13 +4503,13 @@
         <v>1.5</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.5</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB9" t="n">
         <v>1.19</v>
@@ -4521,79 +4521,79 @@
         <v>2.53</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="DG9" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DH9" t="n">
-        <v>101</v>
+        <v>100.41</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.76</v>
+        <v>5.68</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DM9" t="n">
-        <v>51.33</v>
+        <v>50.73</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.38</v>
+        <v>11.5</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.43</v>
+        <v>10.32</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.19</v>
+        <v>7.23</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.05</v>
+        <v>52.14</v>
       </c>
       <c r="DW9" t="n">
         <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.76</v>
+        <v>15.91</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.57</v>
+        <v>10.5</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.19</v>
+        <v>5.41</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.1</v>
+        <v>18.23</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="H12" t="n">
-        <v>109.3</v>
+        <v>113.09</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="K12" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="M12" t="n">
-        <v>46.8</v>
+        <v>51.55</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="O12" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="P12" t="n">
-        <v>10.7</v>
+        <v>10.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.6</v>
+        <v>14.73</v>
       </c>
       <c r="R12" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>53.3</v>
+        <v>55.27</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>15</v>
+        <v>15.91</v>
       </c>
       <c r="AA12" t="n">
-        <v>9</v>
+        <v>9.91</v>
       </c>
       <c r="AB12" t="n">
         <v>6</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.6</v>
+        <v>20.09</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AF12" t="n">
         <v>0.27</v>
@@ -5580,70 +5580,70 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.57</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.81</v>
+        <v>4.59</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BT12" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BU12" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BV12" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BW12" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BX12" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="CA12" t="n">
         <v>4.04</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="CC12" t="n">
         <v>2.92</v>
@@ -5652,31 +5652,31 @@
         <v>2.92</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.51</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CN12" t="n">
         <v>2.07</v>
@@ -5685,25 +5685,25 @@
         <v>1.15</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CR12" t="n">
         <v>1.34</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CT12" t="n">
         <v>3.34</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CW12" t="n">
         <v>1.52</v>
@@ -5721,88 +5721,88 @@
         <v>2.13</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF12" t="n">
         <v>1.05</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="DH12" t="n">
-        <v>109.71</v>
+        <v>111.59</v>
       </c>
       <c r="DI12" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DM12" t="n">
-        <v>51.85</v>
+        <v>54</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.24</v>
+        <v>11.96</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.67</v>
+        <v>12.82</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.62</v>
+        <v>5.46</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>56.43</v>
+        <v>57.27</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.57</v>
+        <v>16</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.91</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.67</v>
+        <v>6.64</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.57</v>
+        <v>20.77</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="13">
@@ -7819,13 +7819,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7909,52 +7909,52 @@
         <v>1.09</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AI18" t="n">
-        <v>101.8</v>
+        <v>98.64</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.2</v>
+        <v>4.73</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.8</v>
+        <v>39.18</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>11.45</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.9</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7966,82 +7966,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>50.3</v>
+        <v>48</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.8</v>
+        <v>13.55</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="BD18" t="n">
-        <v>19</v>
+        <v>18.45</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.710000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.9</v>
+        <v>4.68</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT18" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU18" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BV18" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY18" t="n">
         <v>2.3</v>
@@ -8050,16 +8050,16 @@
         <v>2.29</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="CB18" t="n">
         <v>3.96</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="CE18" t="n">
         <v>1.31</v>
@@ -8083,13 +8083,13 @@
         <v>1.42</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM18" t="n">
         <v>2.67</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO18" t="n">
         <v>1.2</v>
@@ -8098,13 +8098,13 @@
         <v>1.71</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CT18" t="n">
         <v>3.24</v>
@@ -8122,7 +8122,7 @@
         <v>1.5</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.5</v>
@@ -8134,52 +8134,52 @@
         <v>1.24</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DF18" t="n">
         <v>1.14</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="DH18" t="n">
-        <v>98.90000000000001</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.19</v>
+        <v>4.95</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.76</v>
+        <v>38.54</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.71</v>
+        <v>10.95</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.71</v>
+        <v>11.46</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.57</v>
+        <v>7.72</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8191,28 +8191,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.24</v>
+        <v>47.18</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.57</v>
+        <v>14.41</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.48</v>
+        <v>9.32</v>
       </c>
       <c r="DZ18" t="n">
         <v>5.09</v>
       </c>
       <c r="EA18" t="n">
-        <v>20</v>
+        <v>19.68</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0.27</v>
@@ -1469,139 +1469,139 @@
         <v>1.91</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="AI2" t="n">
-        <v>98.18000000000001</v>
+        <v>99.92</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AN2" t="n">
-        <v>46.18</v>
+        <v>45.58</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.27</v>
+        <v>11.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.27</v>
+        <v>10.92</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.82</v>
+        <v>7.67</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>54.64</v>
+        <v>54.67</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA2" t="n">
-        <v>15.45</v>
+        <v>15.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.91</v>
+        <v>9.83</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.55</v>
+        <v>5.67</v>
       </c>
       <c r="BD2" t="n">
-        <v>15.91</v>
+        <v>15.92</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.859999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="BJ2" t="n">
         <v>1.09</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.18</v>
+        <v>4.3</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.32</v>
+        <v>5.3</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BV2" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX2" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BY2" t="n">
         <v>1.74</v>
@@ -1610,31 +1610,31 @@
         <v>1.8</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.57</v>
+        <v>4.53</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.68</v>
+        <v>4.63</v>
       </c>
       <c r="CC2" t="n">
         <v>2.03</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CH2" t="n">
         <v>1.64</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.57</v>
@@ -1643,37 +1643,37 @@
         <v>1.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CQ2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CS2" t="n">
         <v>2.26</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>2.23</v>
       </c>
       <c r="CT2" t="n">
         <v>3.32</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW2" t="n">
         <v>1.63</v>
@@ -1682,7 +1682,7 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.44</v>
@@ -1691,88 +1691,88 @@
         <v>2.04</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.46</v>
+        <v>101.26</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.68</v>
+        <v>5.65</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="DM2" t="n">
-        <v>48.18</v>
+        <v>47.78</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.86</v>
+        <v>10.65</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.09</v>
+        <v>10.92</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.37</v>
+        <v>7.31</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.14</v>
+        <v>53.22</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.86</v>
+        <v>15.87</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.09</v>
+        <v>10.04</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.78</v>
+        <v>5.83</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.91</v>
+        <v>16.87</v>
       </c>
       <c r="EB2" t="n">
         <v>1.76</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="F3" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="G3" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="H3" t="n">
-        <v>102.09</v>
+        <v>103.83</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09</v>
+        <v>-0.17</v>
       </c>
       <c r="J3" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="K3" t="n">
-        <v>5.73</v>
+        <v>5.58</v>
       </c>
       <c r="L3" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M3" t="n">
-        <v>58.91</v>
+        <v>58.25</v>
       </c>
       <c r="N3" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>10.73</v>
+        <v>10.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.55</v>
+        <v>13.25</v>
       </c>
       <c r="R3" t="n">
-        <v>6.27</v>
+        <v>6.08</v>
       </c>
       <c r="S3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="T3" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>57</v>
+        <v>56.92</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.73</v>
+        <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.73</v>
+        <v>9.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>7</v>
+        <v>7.08</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.09</v>
+        <v>16</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AF3" t="n">
         <v>0.09</v>
@@ -1953,37 +1953,37 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.859999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.95</v>
+        <v>1.04</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.64</v>
+        <v>4.57</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.23</v>
+        <v>5.04</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,31 +1992,31 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU3" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BV3" t="n">
-        <v>13.64</v>
+        <v>17.39</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX3" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.59</v>
+        <v>4.63</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="CC3" t="n">
         <v>2.34</v>
@@ -2037,22 +2037,22 @@
         <v>1.67</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO3" t="n">
         <v>1.13</v>
@@ -2076,73 +2076,73 @@
         <v>1.72</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX3" t="n">
         <v>1.52</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.44</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="DB3" t="n">
         <v>1.16</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.04</v>
+        <v>102</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.09</v>
+        <v>5.04</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM3" t="n">
-        <v>54.64</v>
+        <v>54.48</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.46</v>
+        <v>10.48</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.41</v>
+        <v>12.3</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.45</v>
+        <v>6.35</v>
       </c>
       <c r="DS3" t="n">
         <v>0.04</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.41</v>
+        <v>57.35</v>
       </c>
       <c r="DW3" t="n">
         <v>0.04</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.36</v>
+        <v>15.57</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.039999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.32</v>
+        <v>6.39</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.32</v>
+        <v>16.26</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F4" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="G4" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="n">
-        <v>95.91</v>
+        <v>99</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M4" t="n">
-        <v>36.27</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.64</v>
-      </c>
       <c r="P4" t="n">
-        <v>12.82</v>
+        <v>12.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.27</v>
+        <v>9</v>
       </c>
       <c r="R4" t="n">
-        <v>9.359999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="S4" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>46.27</v>
+        <v>46.17</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.09</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.09</v>
+        <v>8.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.82</v>
+        <v>17.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AF4" t="n">
         <v>0.09</v>
@@ -2356,70 +2356,70 @@
         <v>1.45</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.5</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.32</v>
+        <v>4.43</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS4" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU4" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV4" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX4" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.34</v>
+        <v>4.31</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.53</v>
+        <v>4.49</v>
       </c>
       <c r="CC4" t="n">
         <v>6.19</v>
@@ -2428,13 +2428,13 @@
         <v>6.62</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CH4" t="n">
         <v>1.59</v>
@@ -2446,31 +2446,31 @@
         <v>1.6</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL4" t="n">
         <v>1.76</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CO4" t="n">
         <v>1.17</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CT4" t="n">
         <v>3.31</v>
@@ -2488,7 +2488,7 @@
         <v>1.5</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.48</v>
@@ -2500,58 +2500,58 @@
         <v>1.19</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="DH4" t="n">
-        <v>93.91</v>
+        <v>95.61</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.04</v>
+        <v>4.17</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="DM4" t="n">
-        <v>37.82</v>
+        <v>37.74</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="DP4" t="n">
-        <v>13</v>
+        <v>12.74</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.77</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2560,25 +2560,25 @@
         <v>45.22</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.41</v>
+        <v>11.39</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.41</v>
+        <v>7.48</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.19</v>
+        <v>17.18</v>
       </c>
       <c r="EB4" t="n">
         <v>1.28</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0.36</v>
@@ -3081,52 +3081,52 @@
         <v>2.55</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AI6" t="n">
-        <v>90.73</v>
+        <v>90.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.91</v>
+        <v>3.58</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN6" t="n">
-        <v>32.91</v>
+        <v>32.17</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13.27</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.82</v>
+        <v>11.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.449999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.91</v>
+        <v>46.67</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.27</v>
+        <v>10.08</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.64</v>
+        <v>5.75</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.64</v>
+        <v>4.33</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.73</v>
+        <v>17.83</v>
       </c>
       <c r="BE6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>1.22</v>
       </c>
-      <c r="BF6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BK6" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.68</v>
+        <v>5.57</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>5.78</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT6" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU6" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BV6" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX6" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BY6" t="n">
         <v>3.39</v>
@@ -3222,31 +3222,31 @@
         <v>3.26</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.02</v>
+        <v>4.08</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.53</v>
+        <v>5.82</v>
       </c>
       <c r="CD6" t="n">
-        <v>6.21</v>
+        <v>6.49</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="CH6" t="n">
         <v>1.53</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.66</v>
@@ -3255,34 +3255,34 @@
         <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CO6" t="n">
         <v>1.19</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="CT6" t="n">
         <v>3.21</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CV6" t="n">
         <v>2.27</v>
@@ -3294,64 +3294,64 @@
         <v>1.49</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.5</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DB6" t="n">
         <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.86</v>
+        <v>88.7</v>
       </c>
       <c r="DI6" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.54</v>
+        <v>36</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.59</v>
+        <v>13.44</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.32</v>
+        <v>11.31</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.4</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DS6" t="n">
         <v>0.09</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.41</v>
+        <v>45.35</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.81</v>
+        <v>12.61</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.279999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.55</v>
+        <v>4.39</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.86</v>
+        <v>16.48</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="7">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F8" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="H8" t="n">
-        <v>116.91</v>
+        <v>115.42</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="K8" t="n">
-        <v>8.09</v>
+        <v>7.58</v>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>52.27</v>
+        <v>51.25</v>
       </c>
       <c r="N8" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O8" t="n">
-        <v>4.27</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.27</v>
+        <v>9.92</v>
       </c>
       <c r="R8" t="n">
-        <v>6.09</v>
+        <v>5.92</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="T8" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>55.27</v>
+        <v>54.67</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>17.91</v>
+        <v>17.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.27</v>
+        <v>12</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.64</v>
+        <v>5.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.36</v>
+        <v>21.42</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AF8" t="n">
         <v>0.09</v>
@@ -3968,70 +3968,70 @@
         <v>1.82</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.91</v>
+        <v>10.87</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.55</v>
+        <v>5.52</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.36</v>
+        <v>5.35</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU8" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX8" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="CC8" t="n">
         <v>4.53</v>
@@ -4043,16 +4043,16 @@
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CH8" t="n">
         <v>1.49</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.71</v>
@@ -4061,22 +4061,22 @@
         <v>1.52</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM8" t="n">
         <v>2.41</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO8" t="n">
         <v>1.23</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4091,10 +4091,10 @@
         <v>1.52</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX8" t="n">
         <v>1.56</v>
@@ -4103,7 +4103,7 @@
         <v>1.89</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA8" t="n">
         <v>1.92</v>
@@ -4112,52 +4112,52 @@
         <v>1.25</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="DE8" t="n">
         <v>0.13</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="DG8" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="DH8" t="n">
-        <v>110.28</v>
+        <v>109.79</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.55</v>
+        <v>6.35</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.96</v>
+        <v>46.65</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.18</v>
+        <v>11.22</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.54</v>
+        <v>10.35</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.72</v>
+        <v>6.61</v>
       </c>
       <c r="DS8" t="n">
         <v>0.13</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.36</v>
+        <v>51.22</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.86</v>
+        <v>15.65</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.91</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.95</v>
+        <v>5.78</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.68</v>
+        <v>20.74</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="9">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="H10" t="n">
-        <v>92.90000000000001</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="M10" t="n">
-        <v>42</v>
+        <v>40.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O10" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="P10" t="n">
-        <v>12.2</v>
+        <v>12.18</v>
       </c>
       <c r="Q10" t="n">
         <v>12</v>
       </c>
       <c r="R10" t="n">
-        <v>7.6</v>
+        <v>7.64</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>44.1</v>
+        <v>44.91</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.9</v>
+        <v>13.91</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.7</v>
+        <v>5.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.7</v>
+        <v>17.27</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.42</v>
       </c>
       <c r="BG10" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.55</v>
+        <v>10.39</v>
       </c>
       <c r="BI10" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.36</v>
+        <v>5.26</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.18</v>
+        <v>5.13</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>100</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BT10" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BU10" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV10" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BW10" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BX10" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.87</v>
+        <v>3.78</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.77</v>
+        <v>4.71</v>
       </c>
       <c r="CC10" t="n">
         <v>6.55</v>
@@ -4846,16 +4846,16 @@
         <v>7.49</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI10" t="n">
         <v>2.2</v>
@@ -4870,7 +4870,7 @@
         <v>1.66</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CN10" t="n">
         <v>2.21</v>
@@ -4879,25 +4879,25 @@
         <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW10" t="n">
         <v>1.68</v>
@@ -4915,88 +4915,88 @@
         <v>2.25</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="DE10" t="n">
         <v>0.09</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DH10" t="n">
-        <v>84.95</v>
+        <v>86.22</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.05</v>
+        <v>36.57</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.41</v>
+        <v>13.35</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.09</v>
+        <v>11.13</v>
       </c>
       <c r="DR10" t="n">
         <v>8.130000000000001</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>42.91</v>
+        <v>43.35</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.05</v>
+        <v>11.18</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.96</v>
+        <v>7.13</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.09</v>
+        <v>4.04</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.77</v>
+        <v>18</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC10" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5096,139 +5096,139 @@
         <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG11" t="n">
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AI11" t="n">
-        <v>95.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AL11" t="n">
-        <v>5.4</v>
+        <v>5.18</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AN11" t="n">
-        <v>40.1</v>
+        <v>40.64</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.2</v>
+        <v>12.18</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.7</v>
+        <v>12.55</v>
       </c>
       <c r="AS11" t="n">
-        <v>9</v>
+        <v>8.82</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>46.1</v>
+        <v>46.18</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.4</v>
+        <v>12.45</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.9</v>
+        <v>8.82</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="BD11" t="n">
-        <v>22</v>
+        <v>21.91</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.359999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.32</v>
+        <v>4.26</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS11" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BT11" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU11" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV11" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX11" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY11" t="n">
         <v>2.91</v>
@@ -5237,70 +5237,70 @@
         <v>3.04</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.16</v>
+        <v>4.13</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.43</v>
+        <v>5.16</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.74</v>
+        <v>5.45</v>
       </c>
       <c r="CE11" t="n">
         <v>1.3</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI11" t="n">
         <v>2.13</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK11" t="n">
         <v>1.45</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CW11" t="n">
         <v>1.71</v>
@@ -5315,91 +5315,91 @@
         <v>2.46</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB11" t="n">
         <v>1.23</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF11" t="n">
         <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="DH11" t="n">
-        <v>96.27</v>
+        <v>95.95</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.36</v>
+        <v>5.26</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.59</v>
+        <v>42.74</v>
       </c>
       <c r="DN11" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.91</v>
+        <v>10.95</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13.09</v>
+        <v>13</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.46</v>
+        <v>7.44</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.95</v>
+        <v>48.87</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.45</v>
+        <v>13.43</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.27</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.68</v>
+        <v>20.69</v>
       </c>
       <c r="EB11" t="n">
         <v>1.45</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="12">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0.45</v>
@@ -6305,139 +6305,139 @@
         <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="AI14" t="n">
-        <v>100.55</v>
+        <v>102.75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AL14" t="n">
-        <v>6.91</v>
+        <v>7</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AN14" t="n">
-        <v>56.09</v>
+        <v>57.17</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.82</v>
+        <v>3.08</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10.91</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.91</v>
+        <v>8.92</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.18</v>
+        <v>7.92</v>
       </c>
       <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BL14" t="n">
         <v>0.91</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>58</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>14.73</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>18.27</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>11.59</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.86</v>
       </c>
       <c r="BM14" t="n">
         <v>1.09</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.64</v>
+        <v>6.52</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BV14" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BW14" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BX14" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY14" t="n">
         <v>1.24</v>
@@ -6446,16 +6446,16 @@
         <v>1.25</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.26</v>
+        <v>6.27</v>
       </c>
       <c r="CB14" t="n">
         <v>6.78</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="CE14" t="n">
         <v>1.17</v>
@@ -6470,7 +6470,7 @@
         <v>1.9</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.57</v>
@@ -6479,7 +6479,7 @@
         <v>1.35</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CM14" t="n">
         <v>2.93</v>
@@ -6502,72 +6502,72 @@
       </c>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CW14" t="n">
         <v>1.61</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DB14" t="n">
         <v>1.12</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.14</v>
+        <v>4.04</v>
       </c>
       <c r="DH14" t="n">
-        <v>110.05</v>
+        <v>110.78</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.32</v>
+        <v>7.35</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DM14" t="n">
-        <v>61.59</v>
+        <v>61.91</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.73</v>
+        <v>10.78</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.73</v>
+        <v>8.74</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="DS14" t="n">
         <v>0.09</v>
@@ -6579,28 +6579,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>60.64</v>
+        <v>60.91</v>
       </c>
       <c r="DW14" t="n">
         <v>0.04</v>
       </c>
       <c r="DX14" t="n">
-        <v>17.19</v>
+        <v>17.26</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.18</v>
+        <v>10.35</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7</v>
+        <v>6.91</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.45</v>
+        <v>18.7</v>
       </c>
       <c r="EB14" t="n">
         <v>2.02</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="15">
@@ -7819,13 +7819,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7909,52 +7909,52 @@
         <v>1.09</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="AI18" t="n">
-        <v>98.64</v>
+        <v>99.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AN18" t="n">
-        <v>39.18</v>
+        <v>40</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.45</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.550000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.449999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7966,82 +7966,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>48</v>
+        <v>48.33</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.55</v>
+        <v>13.67</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.640000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.91</v>
+        <v>5.08</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.45</v>
+        <v>18.17</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.5</v>
+        <v>9.52</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL18" t="n">
         <v>0.91</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU18" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV18" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY18" t="n">
         <v>2.3</v>
@@ -8050,31 +8050,31 @@
         <v>2.29</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.24</v>
+        <v>3.31</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.65</v>
@@ -8083,22 +8083,22 @@
         <v>1.42</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8113,73 +8113,73 @@
         <v>1.53</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX18" t="n">
         <v>1.5</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.5</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB18" t="n">
         <v>1.24</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="DE18" t="n">
         <v>0.04</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="DH18" t="n">
-        <v>97.45999999999999</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0.04</v>
+        <v>-0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="DM18" t="n">
-        <v>38.54</v>
+        <v>39</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.95</v>
+        <v>10.74</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.46</v>
+        <v>11.48</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.72</v>
+        <v>7.74</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8191,28 +8191,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.18</v>
+        <v>47.39</v>
       </c>
       <c r="DW18" t="n">
         <v>0.04</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.41</v>
+        <v>14.44</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.32</v>
+        <v>9.26</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.09</v>
+        <v>5.17</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.68</v>
+        <v>19.48</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="19">
@@ -8222,94 +8222,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="G19" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
-        <v>84.09</v>
+        <v>83.42</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="K19" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="L19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M19" t="n">
-        <v>44.45</v>
+        <v>43.08</v>
       </c>
       <c r="N19" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="P19" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.91</v>
+        <v>12.83</v>
       </c>
       <c r="R19" t="n">
-        <v>10.27</v>
+        <v>10.33</v>
       </c>
       <c r="S19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>45.64</v>
+        <v>44.58</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.36</v>
+        <v>12.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.73</v>
+        <v>7.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="AC19" t="n">
-        <v>13.45</v>
+        <v>13.58</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8393,70 +8393,70 @@
         <v>0.91</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.5</v>
+        <v>10.57</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.73</v>
+        <v>5.83</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU19" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV19" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY19" t="n">
-        <v>3.91</v>
+        <v>4.4</v>
       </c>
       <c r="BZ19" t="n">
-        <v>4.1</v>
+        <v>4.59</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.04</v>
+        <v>5.11</v>
       </c>
       <c r="CB19" t="n">
-        <v>5.31</v>
+        <v>5.37</v>
       </c>
       <c r="CC19" t="n">
         <v>8.49</v>
@@ -8468,13 +8468,13 @@
         <v>1.23</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CI19" t="n">
         <v>2.25</v>
@@ -8486,10 +8486,10 @@
         <v>1.37</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CN19" t="n">
         <v>2.16</v>
@@ -8498,22 +8498,22 @@
         <v>1.15</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CT19" t="n">
         <v>3.35</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CV19" t="n">
         <v>2.33</v>
@@ -8525,13 +8525,13 @@
         <v>1.51</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.44</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="DB19" t="n">
         <v>1.17</v>
@@ -8540,7 +8540,7 @@
         <v>1.53</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DE19" t="n">
         <v>0.09</v>
@@ -8552,37 +8552,37 @@
         <v>1.91</v>
       </c>
       <c r="DH19" t="n">
-        <v>80.59</v>
+        <v>80.39</v>
       </c>
       <c r="DI19" t="n">
         <v>-0.09</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM19" t="n">
-        <v>39.5</v>
+        <v>39</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DP19" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DQ19" t="n">
         <v>11.78</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.960000000000001</v>
+        <v>10</v>
       </c>
       <c r="DS19" t="n">
         <v>0.04</v>
@@ -8594,28 +8594,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>44.64</v>
+        <v>44.13</v>
       </c>
       <c r="DW19" t="n">
         <v>0.04</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.5</v>
+        <v>10.57</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.86</v>
+        <v>6.91</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="EA19" t="n">
-        <v>15.27</v>
+        <v>15.26</v>
       </c>
       <c r="EB19" t="n">
         <v>1.2</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>56.92</v>
+        <v>56.83</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.35</v>
+        <v>57.3</v>
       </c>
       <c r="DW3" t="n">
         <v>0.04</v>
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="G5" t="n">
-        <v>3.64</v>
+        <v>4.25</v>
       </c>
       <c r="H5" t="n">
-        <v>102.73</v>
+        <v>105.42</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="K5" t="n">
-        <v>7.82</v>
+        <v>8.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="M5" t="n">
-        <v>57.91</v>
+        <v>62.33</v>
       </c>
       <c r="N5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O5" t="n">
-        <v>4.18</v>
+        <v>4.5</v>
       </c>
       <c r="P5" t="n">
-        <v>9.73</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.55</v>
+        <v>11.58</v>
       </c>
       <c r="R5" t="n">
-        <v>6.27</v>
+        <v>6.17</v>
       </c>
       <c r="S5" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>54.64</v>
+        <v>56.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.18</v>
+        <v>20.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>11.91</v>
+        <v>13</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.27</v>
+        <v>7.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>17.82</v>
+        <v>17.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AF5" t="n">
         <v>0.18</v>
@@ -2759,70 +2759,70 @@
         <v>2.18</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.91</v>
+        <v>11.35</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BL5" t="n">
         <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.09</v>
+        <v>5.26</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.82</v>
+        <v>6.09</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>86.36</v>
+        <v>82.61</v>
       </c>
       <c r="BT5" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BU5" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BV5" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BW5" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BX5" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY5" t="n">
         <v>1.42</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="CC5" t="n">
         <v>2.12</v>
@@ -2831,40 +2831,40 @@
         <v>2.17</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="CH5" t="n">
         <v>1.68</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.64</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL5" t="n">
         <v>1.76</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO5" t="n">
         <v>1.13</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CQ5" t="n">
         <v>2.19</v>
@@ -2897,13 +2897,13 @@
         <v>2.45</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DB5" t="n">
         <v>1.17</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="DD5" t="n">
         <v>2.28</v>
@@ -2912,76 +2912,76 @@
         <v>0.13</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.73</v>
+        <v>4.04</v>
       </c>
       <c r="DH5" t="n">
-        <v>102.5</v>
+        <v>103.91</v>
       </c>
       <c r="DI5" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.32</v>
+        <v>7.83</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM5" t="n">
-        <v>56.14</v>
+        <v>58.52</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.59</v>
+        <v>3.78</v>
       </c>
       <c r="DP5" t="n">
-        <v>9.59</v>
+        <v>9.74</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11</v>
+        <v>11.04</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.59</v>
+        <v>6.52</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53.78</v>
+        <v>54.69</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.05</v>
+        <v>17.74</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.59</v>
+        <v>11.22</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.45</v>
+        <v>6.52</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.45</v>
+        <v>18.39</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="6">
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.67</v>
+        <v>46.75</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.35</v>
+        <v>45.39</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0.18</v>
@@ -3484,52 +3484,52 @@
         <v>1.09</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AI7" t="n">
-        <v>96</v>
+        <v>93.17</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.36</v>
+        <v>4.17</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN7" t="n">
-        <v>42.09</v>
+        <v>39.75</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AP7" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.73</v>
+        <v>10.92</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.449999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.82</v>
+        <v>10.08</v>
       </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>49.82</v>
+        <v>47.75</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.91</v>
+        <v>9.42</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.45</v>
+        <v>5.33</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.45</v>
+        <v>4.08</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.36</v>
+        <v>19.25</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.91</v>
+        <v>11.35</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.77</v>
+        <v>4.96</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.05</v>
+        <v>6.3</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="BT7" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BU7" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX7" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY7" t="n">
         <v>2.71</v>
@@ -3625,31 +3625,31 @@
         <v>2.91</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.04</v>
+        <v>4.09</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.22</v>
+        <v>4.27</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.14</v>
+        <v>4.38</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.52</v>
+        <v>4.76</v>
       </c>
       <c r="CE7" t="n">
         <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.53</v>
@@ -3664,22 +3664,22 @@
         <v>2.99</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CR7" t="n">
         <v>1.34</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
@@ -3688,10 +3688,10 @@
         <v>1.67</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX7" t="n">
         <v>1.44</v>
@@ -3718,43 +3718,43 @@
         <v>0.22</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="DH7" t="n">
-        <v>95.78</v>
+        <v>94.31</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.77</v>
+        <v>5.61</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DM7" t="n">
-        <v>47</v>
+        <v>45.57</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.779999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.09</v>
+        <v>10.22</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.68</v>
+        <v>9.35</v>
       </c>
       <c r="DS7" t="n">
         <v>0.04</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.28</v>
+        <v>50.13</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DX7" t="n">
-        <v>12</v>
+        <v>11.65</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.64</v>
+        <v>6.52</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.36</v>
+        <v>5.13</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.45</v>
+        <v>18.44</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="8">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="H9" t="n">
-        <v>105.27</v>
+        <v>104.92</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="K9" t="n">
-        <v>5.82</v>
+        <v>5.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M9" t="n">
-        <v>59.73</v>
+        <v>58.42</v>
       </c>
       <c r="N9" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="O9" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>9.82</v>
+        <v>9.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.73</v>
+        <v>10.33</v>
       </c>
       <c r="R9" t="n">
-        <v>6.55</v>
+        <v>6.58</v>
       </c>
       <c r="S9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="T9" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>53.36</v>
+        <v>52.58</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.64</v>
+        <v>16.17</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.45</v>
+        <v>11</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.82</v>
+        <v>17.42</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>1.64</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.27</v>
+        <v>3.39</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.5</v>
+        <v>10.35</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.27</v>
+        <v>3.39</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.05</v>
+        <v>4.96</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.41</v>
+        <v>5.35</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BV9" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.55</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX9" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="CC9" t="n">
         <v>3.44</v>
@@ -4443,13 +4443,13 @@
         <v>3.71</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CH9" t="n">
         <v>1.58</v>
@@ -4464,7 +4464,7 @@
         <v>1.43</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM9" t="n">
         <v>2.65</v>
@@ -4476,25 +4476,25 @@
         <v>1.17</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CT9" t="n">
         <v>3.26</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CW9" t="n">
         <v>1.58</v>
@@ -4518,49 +4518,49 @@
         <v>1.62</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="DE9" t="n">
         <v>0.04</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="DH9" t="n">
-        <v>100.41</v>
+        <v>100.44</v>
       </c>
       <c r="DI9" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.68</v>
+        <v>5.52</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DM9" t="n">
-        <v>50.73</v>
+        <v>50.44</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.5</v>
+        <v>11.35</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.32</v>
+        <v>10.13</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.23</v>
+        <v>7.22</v>
       </c>
       <c r="DS9" t="n">
         <v>0.13</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.14</v>
+        <v>51.78</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.91</v>
+        <v>15.7</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.5</v>
+        <v>10.31</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.41</v>
+        <v>5.39</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.23</v>
+        <v>18.48</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="10">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0.36</v>
@@ -5902,52 +5902,52 @@
         <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AI13" t="n">
-        <v>75.73</v>
+        <v>77.08</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AN13" t="n">
-        <v>31.18</v>
+        <v>32.67</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.27</v>
+        <v>9.92</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.27</v>
+        <v>11.92</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.82</v>
+        <v>10.58</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>45.91</v>
+        <v>46.75</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.449999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.18</v>
+        <v>5.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>15.73</v>
+        <v>15.92</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.45</v>
+        <v>3.57</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.5</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.45</v>
+        <v>3.57</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.64</v>
+        <v>4.57</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU13" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BV13" t="n">
-        <v>13.64</v>
+        <v>17.39</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BX13" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY13" t="n">
         <v>3.42</v>
@@ -6043,19 +6043,19 @@
         <v>3.56</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="CC13" t="n">
-        <v>6.07</v>
+        <v>6.02</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.43</v>
+        <v>6.28</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF13" t="n">
         <v>2.3</v>
@@ -6064,13 +6064,13 @@
         <v>3.48</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK13" t="n">
         <v>1.44</v>
@@ -6082,31 +6082,31 @@
         <v>2.6</v>
       </c>
       <c r="CN13" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CO13" t="n">
         <v>1.16</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CT13" t="n">
         <v>3.34</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CW13" t="n">
         <v>1.64</v>
@@ -6115,16 +6115,16 @@
         <v>1.5</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.47</v>
       </c>
       <c r="DA13" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DC13" t="n">
         <v>1.6</v>
@@ -6133,46 +6133,46 @@
         <v>2.47</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="DH13" t="n">
-        <v>82.5</v>
+        <v>82.91</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="DK13" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM13" t="n">
-        <v>34</v>
+        <v>34.65</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.96</v>
+        <v>10.74</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.5</v>
+        <v>12.31</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.23</v>
+        <v>10.13</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>43.86</v>
+        <v>44.39</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.09</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.68</v>
+        <v>5.69</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.41</v>
+        <v>3.52</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.5</v>
+        <v>16.57</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="14">
@@ -7013,61 +7013,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F16" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="G16" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="H16" t="n">
-        <v>84.09</v>
+        <v>85.75</v>
       </c>
       <c r="I16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J16" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="K16" t="n">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="L16" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M16" t="n">
-        <v>45</v>
+        <v>44.67</v>
       </c>
       <c r="N16" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="O16" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="P16" t="n">
-        <v>10.18</v>
+        <v>10.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.18</v>
+        <v>10.92</v>
       </c>
       <c r="R16" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7079,28 +7079,28 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>45</v>
+        <v>45.17</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.73</v>
+        <v>13.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.359999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.36</v>
+        <v>5.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.27</v>
+        <v>19.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7184,67 +7184,67 @@
         <v>1.36</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.27</v>
+        <v>11.17</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.73</v>
+        <v>5.74</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.14</v>
+        <v>5.04</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS16" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU16" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV16" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX16" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.13</v>
+        <v>3.39</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.46</v>
+        <v>4.47</v>
       </c>
       <c r="CB16" t="n">
         <v>4.59</v>
@@ -7262,7 +7262,7 @@
         <v>2.31</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="CH16" t="n">
         <v>1.59</v>
@@ -7274,7 +7274,7 @@
         <v>1.63</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL16" t="n">
         <v>1.7</v>
@@ -7331,49 +7331,49 @@
         <v>1.62</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="DE16" t="n">
         <v>0.09</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="DH16" t="n">
-        <v>81.41</v>
+        <v>82.39</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.22</v>
+        <v>5.13</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.5</v>
+        <v>41.48</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DP16" t="n">
         <v>11</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.63</v>
+        <v>10.52</v>
       </c>
       <c r="DR16" t="n">
-        <v>8</v>
+        <v>7.91</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
@@ -7385,28 +7385,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.09</v>
+        <v>43.26</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.91</v>
+        <v>12.96</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.460000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.64</v>
+        <v>18.69</v>
       </c>
       <c r="EB16" t="n">
         <v>1.43</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="17">
@@ -7416,13 +7416,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>0.09</v>
@@ -7509,136 +7509,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>94.55</v>
+        <v>97</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.91</v>
+        <v>5</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AN17" t="n">
-        <v>50.82</v>
+        <v>53.58</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.64</v>
+        <v>12.25</v>
       </c>
       <c r="AR17" t="n">
-        <v>10</v>
+        <v>10.08</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.55</v>
+        <v>7.67</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>51.36</v>
+        <v>51.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA17" t="n">
-        <v>18.09</v>
+        <v>18.25</v>
       </c>
       <c r="BB17" t="n">
-        <v>11.45</v>
+        <v>11.58</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.64</v>
+        <v>6.67</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.36</v>
+        <v>19.92</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.32</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL17" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM17" t="n">
         <v>0.91</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.77</v>
+        <v>4.83</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="BR17" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS17" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU17" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV17" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX17" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY17" t="n">
         <v>1.9</v>
@@ -7647,28 +7647,28 @@
         <v>1.91</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="CE17" t="n">
         <v>1.26</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CI17" t="n">
         <v>2.19</v>
@@ -7677,13 +7677,13 @@
         <v>1.65</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CN17" t="n">
         <v>1.95</v>
@@ -7692,7 +7692,7 @@
         <v>1.18</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ17" t="n">
         <v>2.48</v>
@@ -7731,85 +7731,85 @@
         <v>1.2</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="DE17" t="n">
         <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DH17" t="n">
-        <v>109.6</v>
+        <v>110.22</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.46</v>
+        <v>5.48</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM17" t="n">
-        <v>58.54</v>
+        <v>59.65</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.54</v>
+        <v>11.39</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10</v>
+        <v>10.04</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.55</v>
+        <v>6.66</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>55.04</v>
+        <v>54.96</v>
       </c>
       <c r="DW17" t="n">
         <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>19.05</v>
+        <v>19.09</v>
       </c>
       <c r="DY17" t="n">
-        <v>12.36</v>
+        <v>12.39</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.68</v>
+        <v>6.7</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.72</v>
+        <v>20.48</v>
       </c>
       <c r="EB17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="18">
@@ -7972,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.67</v>
+        <v>13.58</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.58</v>
+        <v>8.5</v>
       </c>
       <c r="BC18" t="n">
         <v>5.08</v>
@@ -8197,10 +8197,10 @@
         <v>0.04</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.44</v>
+        <v>14.39</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.26</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ18" t="n">
         <v>5.17</v>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0.27</v>
@@ -5499,52 +5499,52 @@
         <v>1.64</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AI12" t="n">
-        <v>110.09</v>
+        <v>109.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AN12" t="n">
-        <v>56.45</v>
+        <v>56.42</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.64</v>
+        <v>13.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>10.91</v>
+        <v>11.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.91</v>
+        <v>5.92</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>59.27</v>
+        <v>59.25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA12" t="n">
-        <v>16.09</v>
+        <v>15.75</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.82</v>
+        <v>8.67</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.27</v>
+        <v>7.08</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.45</v>
+        <v>22.08</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.32</v>
+        <v>4.22</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.359999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.32</v>
+        <v>4.22</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BM12" t="n">
         <v>1.09</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.59</v>
+        <v>4.65</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.77</v>
+        <v>4.87</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>86.36</v>
+        <v>82.61</v>
       </c>
       <c r="BU12" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BV12" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BW12" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BX12" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BY12" t="n">
         <v>2.12</v>
@@ -5640,13 +5640,13 @@
         <v>2.26</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CD12" t="n">
         <v>2.92</v>
@@ -5673,13 +5673,13 @@
         <v>1.39</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CO12" t="n">
         <v>1.15</v>
@@ -5688,7 +5688,7 @@
         <v>1.54</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CR12" t="n">
         <v>1.34</v>
@@ -5712,13 +5712,13 @@
         <v>1.5</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.48</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DB12" t="n">
         <v>1.17</v>
@@ -5727,82 +5727,82 @@
         <v>1.54</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DH12" t="n">
-        <v>111.59</v>
+        <v>111.22</v>
       </c>
       <c r="DI12" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.23</v>
+        <v>5.22</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="DM12" t="n">
-        <v>54</v>
+        <v>54.09</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DP12" t="n">
         <v>11.96</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.82</v>
+        <v>13.04</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.46</v>
+        <v>5.48</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.27</v>
+        <v>57.35</v>
       </c>
       <c r="DW12" t="n">
         <v>0.13</v>
       </c>
       <c r="DX12" t="n">
-        <v>16</v>
+        <v>15.83</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.369999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.64</v>
+        <v>6.56</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.77</v>
+        <v>21.13</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="13">
@@ -6610,94 +6610,94 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F15" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="G15" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="H15" t="n">
-        <v>93.91</v>
+        <v>92.58</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="K15" t="n">
-        <v>4.55</v>
+        <v>4.83</v>
       </c>
       <c r="L15" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="M15" t="n">
-        <v>41.73</v>
+        <v>41.42</v>
       </c>
       <c r="N15" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="P15" t="n">
-        <v>8.09</v>
+        <v>8.92</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.55</v>
+        <v>11.58</v>
       </c>
       <c r="R15" t="n">
-        <v>8.91</v>
+        <v>8.42</v>
       </c>
       <c r="S15" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="T15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="U15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>45.64</v>
+        <v>45.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.18</v>
+        <v>12.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.64</v>
+        <v>7.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.18</v>
+        <v>16.58</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AF15" t="n">
         <v>0.09</v>
@@ -6781,70 +6781,70 @@
         <v>2.45</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.68</v>
+        <v>11.74</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BN15" t="n">
         <v>1.91</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.64</v>
+        <v>6.65</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU15" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV15" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW15" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BX15" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="CB15" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CC15" t="n">
         <v>4.27</v>
@@ -6859,28 +6859,28 @@
         <v>2.32</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CH15" t="n">
         <v>1.55</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CK15" t="n">
         <v>1.34</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CO15" t="n">
         <v>1.18</v>
@@ -6904,7 +6904,7 @@
         <v>1.61</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CW15" t="n">
         <v>1.59</v>
@@ -6931,46 +6931,46 @@
         <v>2.58</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="DH15" t="n">
-        <v>93.86</v>
+        <v>93.17</v>
       </c>
       <c r="DI15" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.73</v>
+        <v>43.48</v>
       </c>
       <c r="DN15" t="n">
         <v>0.91</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DP15" t="n">
-        <v>8.960000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.73</v>
+        <v>10.78</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.32</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DS15" t="n">
         <v>0.13</v>
@@ -6982,28 +6982,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.68</v>
+        <v>46.44</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX15" t="n">
         <v>12.91</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.279999999999999</v>
+        <v>8.26</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.46</v>
+        <v>15.7</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="16">

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="H2" t="n">
-        <v>102.73</v>
+        <v>102.67</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="K2" t="n">
-        <v>5.82</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M2" t="n">
-        <v>50.18</v>
+        <v>49.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="O2" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="P2" t="n">
-        <v>9.449999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.91</v>
+        <v>11</v>
       </c>
       <c r="R2" t="n">
-        <v>6.91</v>
+        <v>7.08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51.64</v>
+        <v>51.08</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.27</v>
+        <v>15.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.27</v>
+        <v>9.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>6</v>
+        <v>5.92</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.91</v>
+        <v>17.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AF2" t="n">
         <v>0.08</v>
@@ -1550,70 +1550,70 @@
         <v>2.58</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="BM2" t="n">
         <v>0.96</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.3</v>
+        <v>4.42</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.3</v>
+        <v>5.17</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT2" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BV2" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.63</v>
+        <v>4.59</v>
       </c>
       <c r="CC2" t="n">
         <v>2.03</v>
@@ -1625,13 +1625,13 @@
         <v>1.24</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CI2" t="n">
         <v>2.33</v>
@@ -1643,10 +1643,10 @@
         <v>1.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CN2" t="n">
         <v>2.02</v>
@@ -1658,7 +1658,7 @@
         <v>1.51</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CR2" t="n">
         <v>1.34</v>
@@ -1673,7 +1673,7 @@
         <v>1.7</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CW2" t="n">
         <v>1.63</v>
@@ -1682,7 +1682,7 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.44</v>
@@ -1700,79 +1700,79 @@
         <v>2.34</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.26</v>
+        <v>101.3</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DM2" t="n">
-        <v>47.78</v>
+        <v>47.54</v>
       </c>
       <c r="DN2" t="n">
         <v>0.83</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.65</v>
+        <v>10.58</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.92</v>
+        <v>10.96</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.31</v>
+        <v>7.38</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.22</v>
+        <v>52.88</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.87</v>
+        <v>15.66</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.04</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.83</v>
+        <v>5.79</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.87</v>
+        <v>16.88</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F3" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="G3" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H3" t="n">
-        <v>103.83</v>
+        <v>101.46</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="J3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="K3" t="n">
-        <v>5.58</v>
+        <v>5.62</v>
       </c>
       <c r="L3" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>58.25</v>
+        <v>55.69</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>10.75</v>
+        <v>10.46</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.25</v>
+        <v>13.46</v>
       </c>
       <c r="R3" t="n">
-        <v>6.08</v>
+        <v>6.23</v>
       </c>
       <c r="S3" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="T3" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>56.83</v>
+        <v>56.15</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>16.38</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.92</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.08</v>
+        <v>6.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>16</v>
+        <v>15.77</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF3" t="n">
         <v>0.09</v>
@@ -1953,34 +1953,34 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.609999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BJ3" t="n">
         <v>1.04</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.57</v>
+        <v>4.71</v>
       </c>
       <c r="BQ3" t="n">
         <v>5.04</v>
@@ -1992,31 +1992,31 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BV3" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX3" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="CC3" t="n">
         <v>2.34</v>
@@ -2031,16 +2031,16 @@
         <v>2.19</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CH3" t="n">
         <v>1.67</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK3" t="n">
         <v>1.47</v>
@@ -2061,13 +2061,13 @@
         <v>1.49</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CT3" t="n">
         <v>3.32</v>
@@ -2076,10 +2076,10 @@
         <v>1.72</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CX3" t="n">
         <v>1.52</v>
@@ -2091,7 +2091,7 @@
         <v>2.44</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB3" t="n">
         <v>1.16</v>
@@ -2100,49 +2100,49 @@
         <v>1.52</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="DH3" t="n">
-        <v>102</v>
+        <v>100.79</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.04</v>
+        <v>5.08</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DM3" t="n">
-        <v>54.48</v>
+        <v>53.25</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.48</v>
+        <v>10.33</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.3</v>
+        <v>12.46</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.35</v>
+        <v>6.42</v>
       </c>
       <c r="DS3" t="n">
         <v>0.04</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.3</v>
+        <v>56.92</v>
       </c>
       <c r="DW3" t="n">
         <v>0.04</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.57</v>
+        <v>15.29</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.17</v>
+        <v>9</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.39</v>
+        <v>6.3</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.26</v>
+        <v>16.13</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0.25</v>
@@ -2275,139 +2275,139 @@
         <v>1.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG4" t="n">
         <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>91.91</v>
+        <v>94</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>39.36</v>
+        <v>40.67</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.18</v>
+        <v>13.33</v>
       </c>
       <c r="AR4" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.18</v>
+        <v>7.83</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>44.18</v>
+        <v>45</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.73</v>
+        <v>10.67</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.73</v>
+        <v>6.67</v>
       </c>
       <c r="BC4" t="n">
         <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>16.55</v>
+        <v>17.5</v>
       </c>
       <c r="BE4" t="n">
         <v>1.25</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.609999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
         <v>0.83</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="BQ4" t="n">
         <v>5.17</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS4" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT4" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX4" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY4" t="n">
         <v>3.32</v>
@@ -2416,34 +2416,34 @@
         <v>3.45</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.49</v>
+        <v>4.45</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.19</v>
+        <v>5.92</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.62</v>
+        <v>6.34</v>
       </c>
       <c r="CE4" t="n">
         <v>1.27</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CH4" t="n">
         <v>1.59</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CK4" t="n">
         <v>1.41</v>
@@ -2461,25 +2461,25 @@
         <v>1.17</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CW4" t="n">
         <v>1.63</v>
@@ -2497,55 +2497,55 @@
         <v>2.06</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="DH4" t="n">
-        <v>95.61</v>
+        <v>96.5</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.17</v>
+        <v>4.12</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DM4" t="n">
-        <v>37.74</v>
+        <v>38.46</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DO4" t="n">
         <v>1.96</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.74</v>
+        <v>12.83</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.52</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.779999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="DS4" t="n">
         <v>0.08</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.22</v>
+        <v>45.58</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.39</v>
+        <v>11.34</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.48</v>
+        <v>7.42</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.18</v>
+        <v>17.62</v>
       </c>
       <c r="EB4" t="n">
         <v>1.28</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
@@ -2600,79 +2600,79 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="G5" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>105.42</v>
+        <v>105.31</v>
       </c>
       <c r="I5" t="n">
         <v>-0.08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="K5" t="n">
-        <v>8.75</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="M5" t="n">
-        <v>62.33</v>
+        <v>62.38</v>
       </c>
       <c r="N5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="O5" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>9.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.58</v>
+        <v>11.92</v>
       </c>
       <c r="R5" t="n">
-        <v>6.17</v>
+        <v>5.85</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="U5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>56.33</v>
+        <v>56.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>20.33</v>
+        <v>20.23</v>
       </c>
       <c r="AA5" t="n">
-        <v>13</v>
+        <v>12.69</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.33</v>
+        <v>7.54</v>
       </c>
       <c r="AC5" t="n">
-        <v>17.75</v>
+        <v>18.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AE5" t="n">
         <v>0.92</v>
@@ -2759,70 +2759,70 @@
         <v>2.18</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.35</v>
+        <v>11.12</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BL5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BM5" t="n">
         <v>1</v>
       </c>
-      <c r="BM5" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BN5" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.26</v>
+        <v>5.25</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.09</v>
+        <v>5.88</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BU5" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BV5" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BW5" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BX5" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.92</v>
+        <v>4.98</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.22</v>
+        <v>5.31</v>
       </c>
       <c r="CC5" t="n">
         <v>2.12</v>
@@ -2837,13 +2837,13 @@
         <v>2.14</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="CH5" t="n">
         <v>1.68</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.64</v>
@@ -2855,10 +2855,10 @@
         <v>1.76</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CO5" t="n">
         <v>1.13</v>
@@ -2867,22 +2867,22 @@
         <v>1.48</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CR5" t="n">
         <v>1.33</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CT5" t="n">
         <v>3.24</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CW5" t="n">
         <v>1.67</v>
@@ -2891,22 +2891,22 @@
         <v>1.52</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.45</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DC5" t="n">
         <v>1.51</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DE5" t="n">
         <v>0.13</v>
@@ -2915,73 +2915,73 @@
         <v>1.13</v>
       </c>
       <c r="DG5" t="n">
-        <v>4.04</v>
+        <v>3.92</v>
       </c>
       <c r="DH5" t="n">
-        <v>103.91</v>
+        <v>103.92</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.83</v>
+        <v>7.71</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DM5" t="n">
-        <v>58.52</v>
+        <v>58.7</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="DP5" t="n">
-        <v>9.74</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.04</v>
+        <v>11.25</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.52</v>
+        <v>6.34</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.69</v>
+        <v>54.63</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.74</v>
+        <v>17.79</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.22</v>
+        <v>11.12</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.52</v>
+        <v>6.67</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.39</v>
+        <v>18.58</v>
       </c>
       <c r="EB5" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="F6" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="G6" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
-        <v>87</v>
+        <v>88.17</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="K6" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="L6" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M6" t="n">
-        <v>40.18</v>
+        <v>40.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O6" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="P6" t="n">
-        <v>13.91</v>
+        <v>13.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.82</v>
+        <v>11.08</v>
       </c>
       <c r="R6" t="n">
-        <v>7.36</v>
+        <v>7.33</v>
       </c>
       <c r="S6" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>43.91</v>
+        <v>44.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.36</v>
+        <v>15.42</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.91</v>
+        <v>10.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.45</v>
+        <v>4.58</v>
       </c>
       <c r="AC6" t="n">
-        <v>15</v>
+        <v>14.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AF6" t="n">
         <v>0.08</v>
@@ -3162,70 +3162,70 @@
         <v>1.92</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="BH6" t="n">
-        <v>11.39</v>
+        <v>11.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM6" t="n">
         <v>0.83</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.57</v>
+        <v>5.46</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.78</v>
+        <v>5.75</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT6" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BU6" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX6" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.39</v>
+        <v>3.29</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.26</v>
+        <v>3.17</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="CC6" t="n">
         <v>5.82</v>
@@ -3240,7 +3240,7 @@
         <v>2.44</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CH6" t="n">
         <v>1.53</v>
@@ -3267,16 +3267,16 @@
         <v>1.19</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CT6" t="n">
         <v>3.21</v>
@@ -3306,85 +3306,85 @@
         <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DG6" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.7</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM6" t="n">
-        <v>36</v>
+        <v>36.21</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.44</v>
+        <v>13.16</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.31</v>
+        <v>11.42</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.390000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.39</v>
+        <v>45.42</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.61</v>
+        <v>12.75</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.220000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.39</v>
+        <v>4.46</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.48</v>
+        <v>16.38</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F7" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="H7" t="n">
-        <v>95.55</v>
+        <v>94.42</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.18</v>
+        <v>6.92</v>
       </c>
       <c r="L7" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="M7" t="n">
-        <v>51.91</v>
+        <v>51.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="O7" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>8.82</v>
+        <v>8.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.73</v>
+        <v>11.83</v>
       </c>
       <c r="R7" t="n">
-        <v>8.550000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52.73</v>
+        <v>52.58</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>14.09</v>
+        <v>13.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.82</v>
+        <v>7.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.27</v>
+        <v>6.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.55</v>
+        <v>17.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
         <v>0.25</v>
@@ -3565,70 +3565,70 @@
         <v>2.17</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.35</v>
+        <v>11.25</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.87</v>
+        <v>0.96</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="CC7" t="n">
         <v>4.38</v>
@@ -3643,16 +3643,16 @@
         <v>2.24</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CI7" t="n">
         <v>2.4</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CK7" t="n">
         <v>1.34</v>
@@ -3661,31 +3661,31 @@
         <v>1.62</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CR7" t="n">
         <v>1.34</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CV7" t="n">
         <v>2.52</v>
@@ -3715,46 +3715,46 @@
         <v>2.44</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF7" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="DH7" t="n">
-        <v>94.31</v>
+        <v>93.8</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.61</v>
+        <v>5.54</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.57</v>
+        <v>45.75</v>
       </c>
       <c r="DN7" t="n">
         <v>0.83</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.92</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.22</v>
+        <v>10.33</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.35</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DS7" t="n">
         <v>0.04</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.13</v>
+        <v>50.16</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.65</v>
+        <v>11.67</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.52</v>
+        <v>6.5</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.13</v>
+        <v>5.16</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.44</v>
+        <v>18.29</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0.17</v>
@@ -3887,139 +3887,139 @@
         <v>1.58</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>103.64</v>
+        <v>104.17</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL8" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN8" t="n">
-        <v>41.64</v>
+        <v>40.92</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.36</v>
+        <v>11.83</v>
       </c>
       <c r="AR8" t="n">
-        <v>10.82</v>
+        <v>10.58</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.36</v>
+        <v>7.33</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>47.45</v>
+        <v>47.75</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.82</v>
+        <v>13.58</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.55</v>
+        <v>7.58</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.27</v>
+        <v>6</v>
       </c>
       <c r="BD8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.87</v>
+        <v>10.75</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL8" t="n">
         <v>0.83</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.52</v>
+        <v>5.46</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS8" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>2.1</v>
@@ -4028,25 +4028,25 @@
         <v>2.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.53</v>
+        <v>4.65</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.62</v>
+        <v>4.7</v>
       </c>
       <c r="CE8" t="n">
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CH8" t="n">
         <v>1.49</v>
@@ -4058,13 +4058,13 @@
         <v>1.71</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CN8" t="n">
         <v>1.88</v>
@@ -4076,34 +4076,34 @@
         <v>1.77</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CT8" t="n">
         <v>3.2</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY8" t="n">
         <v>1.89</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA8" t="n">
         <v>1.92</v>
@@ -4112,85 +4112,85 @@
         <v>1.25</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="DG8" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="DH8" t="n">
-        <v>109.79</v>
+        <v>109.8</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.35</v>
+        <v>6.25</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.65</v>
+        <v>46.08</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.22</v>
+        <v>11</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.35</v>
+        <v>10.25</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.61</v>
+        <v>6.62</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.22</v>
+        <v>51.21</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.65</v>
+        <v>15.45</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.869999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.78</v>
+        <v>5.66</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.74</v>
+        <v>20.46</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0.08</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>95.55</v>
+        <v>92.42</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.55</v>
+        <v>5.33</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AN9" t="n">
-        <v>41.73</v>
+        <v>41.67</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP9" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.18</v>
+        <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.91</v>
+        <v>8.92</v>
       </c>
       <c r="AT9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.64</v>
       </c>
-      <c r="AU9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>50.91</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>15.18</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>19.64</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.66</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.35</v>
+        <v>10.42</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM9" t="n">
         <v>0.96</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1</v>
       </c>
       <c r="BN9" t="n">
         <v>1.96</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.35</v>
+        <v>5.46</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BT9" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BU9" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BV9" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX9" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BY9" t="n">
         <v>2.27</v>
@@ -4431,28 +4431,28 @@
         <v>2.22</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="CB9" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.44</v>
+        <v>3.74</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.71</v>
+        <v>4.27</v>
       </c>
       <c r="CE9" t="n">
         <v>1.27</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CI9" t="n">
         <v>2.38</v>
@@ -4467,19 +4467,19 @@
         <v>1.8</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CO9" t="n">
         <v>1.17</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
@@ -4494,7 +4494,7 @@
         <v>1.62</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CW9" t="n">
         <v>1.58</v>
@@ -4503,22 +4503,22 @@
         <v>1.5</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.5</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DB9" t="n">
         <v>1.19</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="DE9" t="n">
         <v>0.04</v>
@@ -4527,73 +4527,73 @@
         <v>1.08</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="DH9" t="n">
-        <v>100.44</v>
+        <v>98.67</v>
       </c>
       <c r="DI9" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.52</v>
+        <v>5.42</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="DM9" t="n">
-        <v>50.44</v>
+        <v>50.04</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.35</v>
+        <v>11.08</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.13</v>
+        <v>10.17</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.22</v>
+        <v>7.75</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.78</v>
+        <v>51.08</v>
       </c>
       <c r="DW9" t="n">
         <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.7</v>
+        <v>15.62</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.31</v>
+        <v>10.29</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.39</v>
+        <v>5.34</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.48</v>
+        <v>18.34</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>0.18</v>
@@ -4696,136 +4696,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>78.33</v>
+        <v>78.38</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN10" t="n">
         <v>32.92</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.42</v>
+        <v>14.31</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.33</v>
+        <v>10.08</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.58</v>
+        <v>8.31</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>41.92</v>
+        <v>42.46</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.08</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.67</v>
+        <v>8.69</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.92</v>
+        <v>6</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.67</v>
+        <v>18.77</v>
       </c>
       <c r="BE10" t="n">
         <v>0.98</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.39</v>
+        <v>10.33</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.26</v>
+        <v>5.21</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.13</v>
+        <v>5.12</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BT10" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BU10" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BV10" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BW10" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BX10" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY10" t="n">
         <v>3.6</v>
@@ -4834,16 +4834,16 @@
         <v>3.78</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="CC10" t="n">
-        <v>6.55</v>
+        <v>6.39</v>
       </c>
       <c r="CD10" t="n">
-        <v>7.49</v>
+        <v>7.21</v>
       </c>
       <c r="CE10" t="n">
         <v>1.27</v>
@@ -4852,7 +4852,7 @@
         <v>2.29</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CH10" t="n">
         <v>1.59</v>
@@ -4867,13 +4867,13 @@
         <v>1.35</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CO10" t="n">
         <v>1.17</v>
@@ -4882,7 +4882,7 @@
         <v>1.61</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CR10" t="n">
         <v>1.36</v>
@@ -4897,7 +4897,7 @@
         <v>1.61</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CW10" t="n">
         <v>1.68</v>
@@ -4921,82 +4921,82 @@
         <v>1.63</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="DH10" t="n">
-        <v>86.22</v>
+        <v>85.92</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.34</v>
+        <v>4.37</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.57</v>
+        <v>36.42</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.35</v>
+        <v>13.33</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.13</v>
+        <v>10.96</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.130000000000001</v>
+        <v>8</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.35</v>
+        <v>43.58</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.18</v>
+        <v>11.08</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.13</v>
+        <v>7.12</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="EA10" t="n">
-        <v>18</v>
+        <v>18.08</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="11">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
@@ -5018,49 +5018,49 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G11" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="H11" t="n">
-        <v>96.83</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="L11" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="M11" t="n">
-        <v>44.67</v>
+        <v>46.08</v>
       </c>
       <c r="N11" t="n">
         <v>0.92</v>
       </c>
       <c r="O11" t="n">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="P11" t="n">
-        <v>9.83</v>
+        <v>10.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.42</v>
+        <v>13.38</v>
       </c>
       <c r="R11" t="n">
-        <v>6.17</v>
+        <v>6.31</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="T11" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="U11" t="n">
         <v>0.08</v>
@@ -5072,28 +5072,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51.33</v>
+        <v>51.46</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.33</v>
+        <v>14.54</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.58</v>
+        <v>9.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.58</v>
+        <v>19.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AF11" t="n">
         <v>0.09</v>
@@ -5177,64 +5177,64 @@
         <v>1.73</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.26</v>
+        <v>9.25</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.26</v>
+        <v>4.29</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS11" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="CA11" t="n">
         <v>4</v>
@@ -5267,13 +5267,13 @@
         <v>1.68</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CN11" t="n">
         <v>1.96</v>
@@ -5285,16 +5285,16 @@
         <v>1.73</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CU11" t="n">
         <v>1.52</v>
@@ -5309,7 +5309,7 @@
         <v>1.51</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.46</v>
@@ -5324,49 +5324,49 @@
         <v>1.76</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="DE11" t="n">
         <v>0.04</v>
       </c>
       <c r="DF11" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="DH11" t="n">
-        <v>95.95</v>
+        <v>96.87</v>
       </c>
       <c r="DI11" t="n">
         <v>0.17</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.26</v>
+        <v>5.29</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="DM11" t="n">
-        <v>42.74</v>
+        <v>43.59</v>
       </c>
       <c r="DN11" t="n">
         <v>0.96</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.95</v>
+        <v>11.04</v>
       </c>
       <c r="DQ11" t="n">
         <v>13</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.44</v>
+        <v>7.46</v>
       </c>
       <c r="DS11" t="n">
         <v>0.13</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.87</v>
+        <v>49.04</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.43</v>
+        <v>13.58</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.220000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.69</v>
+        <v>20.54</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
         <v>0.27</v>
@@ -5499,52 +5499,52 @@
         <v>1.64</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>109.5</v>
+        <v>109.77</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.92</v>
+        <v>5.08</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AN12" t="n">
-        <v>56.42</v>
+        <v>55.69</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.5</v>
+        <v>13.69</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.5</v>
+        <v>11.15</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.92</v>
+        <v>5.77</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5556,82 +5556,82 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>59.25</v>
+        <v>58.69</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA12" t="n">
-        <v>15.75</v>
+        <v>15.85</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.67</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.08</v>
+        <v>7.23</v>
       </c>
       <c r="BD12" t="n">
-        <v>22.08</v>
+        <v>21.38</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.22</v>
+        <v>4.12</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.52</v>
+        <v>9.67</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.22</v>
+        <v>4.12</v>
       </c>
       <c r="BJ12" t="n">
         <v>0.96</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.65</v>
+        <v>4.79</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.87</v>
+        <v>4.88</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BT12" t="n">
-        <v>82.61</v>
+        <v>79.17</v>
       </c>
       <c r="BU12" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BW12" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BX12" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BY12" t="n">
         <v>2.12</v>
@@ -5640,16 +5640,16 @@
         <v>2.26</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="CB12" t="n">
         <v>4.12</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="CE12" t="n">
         <v>1.25</v>
@@ -5661,10 +5661,10 @@
         <v>3.67</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.51</v>
@@ -5676,16 +5676,16 @@
         <v>1.71</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO12" t="n">
         <v>1.15</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CQ12" t="n">
         <v>2.3</v>
@@ -5694,13 +5694,13 @@
         <v>1.34</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CT12" t="n">
         <v>3.34</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CV12" t="n">
         <v>2.66</v>
@@ -5712,13 +5712,13 @@
         <v>1.5</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DB12" t="n">
         <v>1.17</v>
@@ -5727,82 +5727,82 @@
         <v>1.54</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF12" t="n">
         <v>1.17</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DH12" t="n">
-        <v>111.22</v>
+        <v>111.29</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.22</v>
+        <v>5.3</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="DM12" t="n">
-        <v>54.09</v>
+        <v>53.79</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.96</v>
+        <v>12.12</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.04</v>
+        <v>12.79</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.48</v>
+        <v>5.42</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.35</v>
+        <v>57.12</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.83</v>
+        <v>15.88</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.26</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.56</v>
+        <v>6.67</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.13</v>
+        <v>20.79</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
         <v>0.36</v>
@@ -5902,16 +5902,16 @@
         <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AI13" t="n">
-        <v>77.08</v>
+        <v>77.38</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -5920,121 +5920,121 @@
         <v>2.08</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AM13" t="n">
         <v>0.08</v>
       </c>
       <c r="AN13" t="n">
-        <v>32.67</v>
+        <v>31.54</v>
       </c>
       <c r="AO13" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BM13" t="n">
         <v>0.75</v>
       </c>
-      <c r="AP13" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>9.92</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>10.58</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>46.75</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>15.92</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BF13" t="n">
+      <c r="BN13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO13" t="n">
         <v>1.92</v>
       </c>
-      <c r="BG13" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1.96</v>
-      </c>
       <c r="BP13" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BV13" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW13" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX13" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BY13" t="n">
         <v>3.42</v>
@@ -6043,34 +6043,34 @@
         <v>3.56</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="CC13" t="n">
-        <v>6.02</v>
+        <v>5.94</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.28</v>
+        <v>6.21</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF13" t="n">
         <v>2.3</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK13" t="n">
         <v>1.44</v>
@@ -6088,25 +6088,25 @@
         <v>1.16</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CT13" t="n">
         <v>3.34</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CW13" t="n">
         <v>1.64</v>
@@ -6124,25 +6124,25 @@
         <v>2.01</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="DC13" t="n">
         <v>1.6</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="DH13" t="n">
-        <v>82.91</v>
+        <v>82.83</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
@@ -6151,28 +6151,28 @@
         <v>2.08</v>
       </c>
       <c r="DK13" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DM13" t="n">
-        <v>34.65</v>
+        <v>33.96</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.74</v>
+        <v>11</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.31</v>
+        <v>12.25</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.13</v>
+        <v>10.33</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.39</v>
+        <v>44.46</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.220000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.69</v>
+        <v>5.67</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.57</v>
+        <v>16.46</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="F14" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="G14" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="H14" t="n">
-        <v>119.55</v>
+        <v>121.67</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="K14" t="n">
-        <v>7.73</v>
+        <v>7.83</v>
       </c>
       <c r="L14" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="M14" t="n">
-        <v>67.09</v>
+        <v>67.92</v>
       </c>
       <c r="N14" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="O14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>10.55</v>
+        <v>10.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.550000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="R14" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="S14" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>63.27</v>
+        <v>63.42</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.64</v>
+        <v>20.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>12.45</v>
+        <v>13.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.64</v>
+        <v>18.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF14" t="n">
         <v>0.25</v>
@@ -6386,13 +6386,13 @@
         <v>1.67</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.61</v>
+        <v>11.62</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="BJ14" t="n">
         <v>1.17</v>
@@ -6401,55 +6401,55 @@
         <v>0.96</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
         <v>2</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.09</v>
+        <v>5.04</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.52</v>
+        <v>6.58</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BT14" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BW14" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BX14" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BZ14" t="n">
         <v>1.25</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.27</v>
+        <v>6.23</v>
       </c>
       <c r="CB14" t="n">
-        <v>6.78</v>
+        <v>6.77</v>
       </c>
       <c r="CC14" t="n">
         <v>1.66</v>
@@ -6482,19 +6482,19 @@
         <v>1.65</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CO14" t="n">
         <v>1.07</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CQ14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
@@ -6516,91 +6516,91 @@
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DB14" t="n">
         <v>1.12</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.04</v>
+        <v>4.12</v>
       </c>
       <c r="DH14" t="n">
-        <v>110.78</v>
+        <v>112.21</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.35</v>
+        <v>7.42</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="DM14" t="n">
-        <v>61.91</v>
+        <v>62.54</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.78</v>
+        <v>10.84</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.74</v>
+        <v>8.58</v>
       </c>
       <c r="DR14" t="n">
-        <v>7</v>
+        <v>7.04</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>60.91</v>
+        <v>61.08</v>
       </c>
       <c r="DW14" t="n">
         <v>0.04</v>
       </c>
       <c r="DX14" t="n">
-        <v>17.26</v>
+        <v>17.7</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.35</v>
+        <v>10.8</v>
       </c>
       <c r="DZ14" t="n">
-        <v>6.91</v>
+        <v>6.92</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.7</v>
+        <v>18.58</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="15">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
         <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0.08</v>
@@ -6700,139 +6700,139 @@
         <v>1.25</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AI15" t="n">
-        <v>93.81999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.45</v>
+        <v>4.67</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AN15" t="n">
-        <v>45.73</v>
+        <v>46.25</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.82</v>
+        <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.91</v>
+        <v>9.83</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.73</v>
+        <v>9.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>47.73</v>
+        <v>48.33</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.64</v>
+        <v>13.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.91</v>
+        <v>8.83</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="BD15" t="n">
-        <v>14.73</v>
+        <v>15.5</v>
       </c>
       <c r="BE15" t="n">
         <v>1.52</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.74</v>
+        <v>11.62</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="BM15" t="n">
         <v>1.17</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BO15" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.09</v>
+        <v>5.17</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.65</v>
+        <v>6.46</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW15" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BX15" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BY15" t="n">
         <v>2.75</v>
@@ -6841,16 +6841,16 @@
         <v>2.85</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.5</v>
+        <v>4.42</v>
       </c>
       <c r="CE15" t="n">
         <v>1.28</v>
@@ -6874,13 +6874,13 @@
         <v>1.34</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CO15" t="n">
         <v>1.18</v>
@@ -6889,7 +6889,7 @@
         <v>1.64</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
@@ -6907,7 +6907,7 @@
         <v>2.47</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CX15" t="n">
         <v>1.45</v>
@@ -6919,7 +6919,7 @@
         <v>2.6</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DB15" t="n">
         <v>1.2</v>
@@ -6937,10 +6937,10 @@
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="DH15" t="n">
-        <v>93.17</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="DI15" t="n">
         <v>0.04</v>
@@ -6949,61 +6949,61 @@
         <v>1.96</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.48</v>
+        <v>43.84</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.35</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.78</v>
+        <v>10.7</v>
       </c>
       <c r="DR15" t="n">
-        <v>9.050000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.44</v>
+        <v>46.79</v>
       </c>
       <c r="DW15" t="n">
         <v>0.08</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.91</v>
+        <v>12.88</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.26</v>
+        <v>8.25</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.65</v>
+        <v>4.62</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.7</v>
+        <v>16.04</v>
       </c>
       <c r="EB15" t="n">
         <v>1.46</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="16">
@@ -7013,13 +7013,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>0.17</v>
@@ -7106,49 +7106,49 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>78.73</v>
+        <v>79.75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>38</v>
+        <v>36.58</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.82</v>
+        <v>12.08</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.09</v>
+        <v>9.83</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.449999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7160,82 +7160,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>41.18</v>
+        <v>41.67</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA16" t="n">
-        <v>12.09</v>
+        <v>11.75</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.550000000000001</v>
+        <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BD16" t="n">
-        <v>18</v>
+        <v>17.92</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.17</v>
+        <v>10.96</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.74</v>
+        <v>5.71</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.04</v>
+        <v>4.88</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS16" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV16" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX16" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BY16" t="n">
         <v>3.4</v>
@@ -7244,31 +7244,31 @@
         <v>3.39</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.47</v>
+        <v>4.55</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.59</v>
+        <v>4.72</v>
       </c>
       <c r="CC16" t="n">
-        <v>7.63</v>
+        <v>7.74</v>
       </c>
       <c r="CD16" t="n">
-        <v>6.9</v>
+        <v>7.39</v>
       </c>
       <c r="CE16" t="n">
         <v>1.26</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CG16" t="n">
         <v>3.55</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.63</v>
@@ -7280,100 +7280,100 @@
         <v>1.7</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CO16" t="n">
         <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CT16" t="n">
         <v>3.31</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.37</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF16" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="DH16" t="n">
-        <v>82.39</v>
+        <v>82.75</v>
       </c>
       <c r="DI16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.13</v>
+        <v>4.96</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.48</v>
+        <v>40.62</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="DP16" t="n">
-        <v>11</v>
+        <v>11.16</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.52</v>
+        <v>10.38</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.91</v>
+        <v>8.08</v>
       </c>
       <c r="DS16" t="n">
         <v>0</v>
@@ -7385,28 +7385,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.26</v>
+        <v>43.42</v>
       </c>
       <c r="DW16" t="n">
         <v>0.08</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.96</v>
+        <v>12.75</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.52</v>
+        <v>8.25</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.69</v>
+        <v>18.62</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="17">
@@ -7416,94 +7416,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G17" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="H17" t="n">
-        <v>124.64</v>
+        <v>123.58</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="L17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M17" t="n">
-        <v>66.27</v>
+        <v>65.42</v>
       </c>
       <c r="N17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O17" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="P17" t="n">
-        <v>10.45</v>
+        <v>10.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="R17" t="n">
-        <v>5.55</v>
+        <v>6.25</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>58.73</v>
+        <v>57.92</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>20</v>
+        <v>18.83</v>
       </c>
       <c r="AA17" t="n">
-        <v>13.27</v>
+        <v>12.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.73</v>
+        <v>6.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.09</v>
+        <v>21</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7587,70 +7587,70 @@
         <v>2</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.300000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
         <v>0.96</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.83</v>
+        <v>4.79</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS17" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT17" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BU17" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV17" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX17" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.35</v>
+        <v>4.37</v>
       </c>
       <c r="CC17" t="n">
         <v>2.32</v>
@@ -7662,13 +7662,13 @@
         <v>1.26</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CI17" t="n">
         <v>2.19</v>
@@ -7698,10 +7698,10 @@
         <v>2.48</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CT17" t="n">
         <v>3.24</v>
@@ -7713,7 +7713,7 @@
         <v>2.28</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX17" t="n">
         <v>1.52</v>
@@ -7722,10 +7722,10 @@
         <v>1.81</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DA17" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DB17" t="n">
         <v>1.2</v>
@@ -7734,82 +7734,82 @@
         <v>1.65</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="DE17" t="n">
         <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DH17" t="n">
-        <v>110.22</v>
+        <v>110.29</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.48</v>
+        <v>5.42</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM17" t="n">
-        <v>59.65</v>
+        <v>59.5</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.39</v>
+        <v>11.25</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.04</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.66</v>
+        <v>6.96</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.96</v>
+        <v>54.71</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>19.09</v>
+        <v>18.54</v>
       </c>
       <c r="DY17" t="n">
-        <v>12.39</v>
+        <v>11.96</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.7</v>
+        <v>6.58</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.48</v>
+        <v>20.46</v>
       </c>
       <c r="EB17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="18">
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
@@ -7834,46 +7834,46 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>96.27</v>
+        <v>95.75</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="K18" t="n">
-        <v>5.18</v>
+        <v>5.25</v>
       </c>
       <c r="L18" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="M18" t="n">
-        <v>37.91</v>
+        <v>40</v>
       </c>
       <c r="N18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="O18" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>10.45</v>
+        <v>10.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.36</v>
+        <v>13.67</v>
       </c>
       <c r="R18" t="n">
-        <v>7</v>
+        <v>7.08</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -7885,28 +7885,28 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>46.36</v>
+        <v>47</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.27</v>
+        <v>16.08</v>
       </c>
       <c r="AA18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.27</v>
+        <v>5.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>20.91</v>
+        <v>20.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF18" t="n">
         <v>0.08</v>
@@ -7990,34 +7990,34 @@
         <v>1.75</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.52</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="BQ18" t="n">
         <v>4.83</v>
@@ -8026,34 +8026,34 @@
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT18" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU18" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="CA18" t="n">
         <v>3.81</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="CC18" t="n">
         <v>3.31</v>
@@ -8065,31 +8065,31 @@
         <v>1.32</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH18" t="n">
         <v>1.5</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK18" t="n">
         <v>1.42</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CO18" t="n">
         <v>1.21</v>
@@ -8107,7 +8107,7 @@
         <v>2.6</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CU18" t="n">
         <v>1.53</v>
@@ -8134,7 +8134,7 @@
         <v>1.24</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DD18" t="n">
         <v>2.9</v>
@@ -8143,43 +8143,43 @@
         <v>0.04</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="DH18" t="n">
-        <v>97.81999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.09</v>
+        <v>5.12</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="DM18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.74</v>
+        <v>10.75</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.48</v>
+        <v>11.71</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.74</v>
+        <v>7.75</v>
       </c>
       <c r="DS18" t="n">
         <v>0</v>
@@ -8191,28 +8191,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.39</v>
+        <v>47.66</v>
       </c>
       <c r="DW18" t="n">
         <v>0.04</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.39</v>
+        <v>14.83</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.220000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.17</v>
+        <v>5.08</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.48</v>
+        <v>19.46</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="19">
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
         <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
         <v>0.17</v>
@@ -8315,49 +8315,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AI19" t="n">
-        <v>77.09</v>
+        <v>78.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN19" t="n">
-        <v>34.55</v>
+        <v>33.67</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ19" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="AS19" t="n">
         <v>10</v>
       </c>
-      <c r="AR19" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>9.640000000000001</v>
-      </c>
       <c r="AT19" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8369,82 +8369,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>43.64</v>
+        <v>43.92</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.640000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="BB19" t="n">
-        <v>6</v>
+        <v>6.08</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>17.09</v>
+        <v>17</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.57</v>
+        <v>10.5</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.83</v>
+        <v>5.79</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>86.95999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BU19" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV19" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BY19" t="n">
         <v>4.4</v>
@@ -8453,34 +8453,34 @@
         <v>4.59</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="CB19" t="n">
-        <v>5.37</v>
+        <v>5.32</v>
       </c>
       <c r="CC19" t="n">
-        <v>8.49</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CD19" t="n">
-        <v>9.380000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="CE19" t="n">
         <v>1.23</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CH19" t="n">
         <v>1.67</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK19" t="n">
         <v>1.37</v>
@@ -8501,25 +8501,25 @@
         <v>1.53</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX19" t="n">
         <v>1.51</v>
@@ -8537,52 +8537,52 @@
         <v>1.17</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="DH19" t="n">
-        <v>80.39</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="DI19" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="DL19" t="n">
         <v>0.17</v>
       </c>
       <c r="DM19" t="n">
-        <v>39</v>
+        <v>38.38</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="DP19" t="n">
-        <v>9.960000000000001</v>
+        <v>10.08</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.78</v>
+        <v>11.83</v>
       </c>
       <c r="DR19" t="n">
-        <v>10</v>
+        <v>10.17</v>
       </c>
       <c r="DS19" t="n">
         <v>0.04</v>
@@ -8594,28 +8594,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>44.13</v>
+        <v>44.25</v>
       </c>
       <c r="DW19" t="n">
         <v>0.04</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.57</v>
+        <v>10.46</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.91</v>
+        <v>6.92</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="EA19" t="n">
-        <v>15.26</v>
+        <v>15.29</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
         <v>0.33</v>
@@ -3084,49 +3084,49 @@
         <v>0.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AI6" t="n">
-        <v>90.25</v>
+        <v>87.69</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AN6" t="n">
-        <v>32.17</v>
+        <v>31.46</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
         <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.75</v>
+        <v>11.62</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.33</v>
+        <v>8.85</v>
       </c>
       <c r="AT6" t="n">
         <v>2.08</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.75</v>
+        <v>45.62</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.08</v>
+        <v>10.31</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.75</v>
+        <v>5.62</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.33</v>
+        <v>4.69</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.83</v>
+        <v>18.08</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="BH6" t="n">
-        <v>11.25</v>
+        <v>11.4</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.46</v>
+        <v>5.6</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.75</v>
+        <v>5.76</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT6" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BU6" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BV6" t="n">
-        <v>20.83</v>
+        <v>24</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BY6" t="n">
         <v>3.29</v>
@@ -3222,31 +3222,31 @@
         <v>3.17</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.82</v>
+        <v>5.91</v>
       </c>
       <c r="CD6" t="n">
-        <v>6.49</v>
+        <v>6.51</v>
       </c>
       <c r="CE6" t="n">
         <v>1.3</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.66</v>
@@ -3255,103 +3255,103 @@
         <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM6" t="n">
         <v>2.7</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO6" t="n">
         <v>1.19</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="CT6" t="n">
         <v>3.21</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CV6" t="n">
         <v>2.27</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX6" t="n">
         <v>1.49</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.5</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="DB6" t="n">
         <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="DE6" t="n">
         <v>0.2</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DG6" t="n">
         <v>2.08</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.20999999999999</v>
+        <v>87.92</v>
       </c>
       <c r="DI6" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.21</v>
+        <v>35.68</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="DP6" t="n">
         <v>13.16</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.42</v>
+        <v>11.36</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.33</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS6" t="n">
         <v>0.12</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.42</v>
+        <v>44.88</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.75</v>
+        <v>12.76</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.289999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.46</v>
+        <v>4.64</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.38</v>
+        <v>16.56</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="7">
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
@@ -4212,49 +4212,49 @@
         <v>0.08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="G9" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>104.92</v>
+        <v>104.69</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="K9" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="M9" t="n">
-        <v>58.42</v>
+        <v>56.69</v>
       </c>
       <c r="N9" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="O9" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="P9" t="n">
-        <v>9.67</v>
+        <v>9.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.33</v>
+        <v>9.92</v>
       </c>
       <c r="R9" t="n">
-        <v>6.58</v>
+        <v>6.62</v>
       </c>
       <c r="S9" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="T9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
         <v>0.08</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>52.58</v>
+        <v>52</v>
       </c>
       <c r="Y9" t="n">
         <v>0.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.17</v>
+        <v>16.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>11</v>
+        <v>11.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.17</v>
+        <v>5.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.42</v>
+        <v>17.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,19 +4371,19 @@
         <v>1.58</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.42</v>
+        <v>10.44</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL9" t="n">
         <v>1</v>
@@ -4395,46 +4395,46 @@
         <v>1.96</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.46</v>
+        <v>5.4</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BT9" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BU9" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BV9" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX9" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="CC9" t="n">
         <v>3.74</v>
@@ -4455,28 +4455,28 @@
         <v>1.6</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.57</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO9" t="n">
         <v>1.17</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CQ9" t="n">
         <v>2.46</v>
@@ -4494,7 +4494,7 @@
         <v>1.62</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CW9" t="n">
         <v>1.58</v>
@@ -4509,7 +4509,7 @@
         <v>2.5</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DB9" t="n">
         <v>1.19</v>
@@ -4524,43 +4524,43 @@
         <v>0.04</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="DH9" t="n">
-        <v>98.67</v>
+        <v>98.8</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.42</v>
+        <v>5.4</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="DM9" t="n">
-        <v>50.04</v>
+        <v>49.48</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="DP9" t="n">
         <v>11.08</v>
       </c>
       <c r="DQ9" t="n">
-        <v>10.17</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.75</v>
+        <v>7.72</v>
       </c>
       <c r="DS9" t="n">
         <v>0.12</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.08</v>
+        <v>50.84</v>
       </c>
       <c r="DW9" t="n">
         <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.62</v>
+        <v>15.64</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.29</v>
+        <v>10.36</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.34</v>
+        <v>5.28</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.34</v>
+        <v>18.28</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F10" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="H10" t="n">
-        <v>94.81999999999999</v>
+        <v>94.42</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M10" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P10" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.55</v>
       </c>
-      <c r="K10" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="M10" t="n">
-        <v>40.55</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="P10" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>12</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>44.91</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>17.27</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4777,67 +4777,67 @@
         <v>3.88</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.33</v>
+        <v>10.24</v>
       </c>
       <c r="BI10" t="n">
         <v>3.88</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.12</v>
+        <v>5.04</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BT10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BU10" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BV10" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BW10" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BX10" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.78</v>
+        <v>4.18</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.67</v>
+        <v>4.75</v>
       </c>
       <c r="CC10" t="n">
         <v>6.39</v>
@@ -4846,61 +4846,61 @@
         <v>7.21</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.51</v>
+        <v>3.57</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.64</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL10" t="n">
         <v>1.65</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CO10" t="n">
         <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="CR10" t="n">
         <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CT10" t="n">
         <v>3.3</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CV10" t="n">
         <v>2.29</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX10" t="n">
         <v>1.46</v>
@@ -4918,52 +4918,52 @@
         <v>1.2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="DG10" t="n">
         <v>2.16</v>
       </c>
       <c r="DH10" t="n">
-        <v>85.92</v>
+        <v>86.08</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.37</v>
+        <v>4.32</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.42</v>
+        <v>36.88</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.33</v>
+        <v>13.4</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.96</v>
+        <v>11.08</v>
       </c>
       <c r="DR10" t="n">
-        <v>8</v>
+        <v>7.96</v>
       </c>
       <c r="DS10" t="n">
         <v>0.12</v>
@@ -4975,22 +4975,22 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.58</v>
+        <v>43.36</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.08</v>
+        <v>11.24</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.12</v>
+        <v>7.32</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.08</v>
+        <v>17.96</v>
       </c>
       <c r="EB10" t="n">
         <v>1.25</v>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5096,139 +5096,139 @@
         <v>1.69</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AI11" t="n">
-        <v>95</v>
+        <v>93.58</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AL11" t="n">
-        <v>5.18</v>
+        <v>5.08</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AN11" t="n">
-        <v>40.64</v>
+        <v>40.42</v>
       </c>
       <c r="AO11" t="n">
         <v>1</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.18</v>
+        <v>12.25</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.55</v>
+        <v>12.42</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.82</v>
+        <v>8.58</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>46.18</v>
+        <v>45.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.45</v>
+        <v>12.25</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.64</v>
+        <v>3.33</v>
       </c>
       <c r="BD11" t="n">
-        <v>21.91</v>
+        <v>21.17</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.25</v>
+        <v>9.44</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="BO11" t="n">
         <v>1.12</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.29</v>
+        <v>4.36</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.96</v>
+        <v>5.08</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS11" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV11" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY11" t="n">
         <v>2.81</v>
@@ -5237,16 +5237,16 @@
         <v>2.93</v>
       </c>
       <c r="CA11" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.16</v>
+        <v>4.95</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.45</v>
+        <v>5.21</v>
       </c>
       <c r="CE11" t="n">
         <v>1.3</v>
@@ -5255,7 +5255,7 @@
         <v>2.51</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CH11" t="n">
         <v>1.51</v>
@@ -5270,13 +5270,13 @@
         <v>1.44</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO11" t="n">
         <v>1.21</v>
@@ -5285,7 +5285,7 @@
         <v>1.73</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CR11" t="n">
         <v>1.37</v>
@@ -5294,13 +5294,13 @@
         <v>2.65</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CU11" t="n">
         <v>1.52</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CW11" t="n">
         <v>1.71</v>
@@ -5315,13 +5315,13 @@
         <v>2.46</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DB11" t="n">
         <v>1.23</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DD11" t="n">
         <v>2.84</v>
@@ -5330,76 +5330,76 @@
         <v>0.04</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DH11" t="n">
-        <v>96.87</v>
+        <v>96.12</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.29</v>
+        <v>5.24</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.59</v>
+        <v>43.36</v>
       </c>
       <c r="DN11" t="n">
         <v>0.96</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.04</v>
+        <v>11.12</v>
       </c>
       <c r="DQ11" t="n">
-        <v>13</v>
+        <v>12.92</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.46</v>
+        <v>7.4</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.04</v>
+        <v>48.6</v>
       </c>
       <c r="DW11" t="n">
         <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.58</v>
+        <v>13.44</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.42</v>
+        <v>9.44</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.54</v>
+        <v>20.24</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F12" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="G12" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="H12" t="n">
-        <v>113.09</v>
+        <v>115.25</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="K12" t="n">
-        <v>5.55</v>
+        <v>5.92</v>
       </c>
       <c r="L12" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="M12" t="n">
-        <v>51.55</v>
+        <v>54.75</v>
       </c>
       <c r="N12" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="O12" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>10.27</v>
+        <v>10.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.73</v>
+        <v>14.58</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="S12" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="T12" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="U12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>55.27</v>
+        <v>56.33</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.91</v>
+        <v>15.83</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="AB12" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.09</v>
+        <v>21.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AF12" t="n">
         <v>0.23</v>
@@ -5580,70 +5580,70 @@
         <v>2.08</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.12</v>
+        <v>4.16</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.67</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.12</v>
+        <v>4.16</v>
       </c>
       <c r="BJ12" t="n">
         <v>0.96</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.79</v>
+        <v>4.96</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.88</v>
+        <v>4.92</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BT12" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BU12" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BV12" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BW12" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BX12" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.02</v>
+        <v>4.06</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.12</v>
+        <v>4.17</v>
       </c>
       <c r="CC12" t="n">
         <v>2.98</v>
@@ -5652,13 +5652,13 @@
         <v>3</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CH12" t="n">
         <v>1.64</v>
@@ -5673,13 +5673,13 @@
         <v>1.39</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CM12" t="n">
         <v>2.77</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CO12" t="n">
         <v>1.15</v>
@@ -5688,13 +5688,13 @@
         <v>1.53</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CR12" t="n">
         <v>1.34</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CT12" t="n">
         <v>3.34</v>
@@ -5718,58 +5718,58 @@
         <v>2.47</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="DH12" t="n">
-        <v>111.29</v>
+        <v>112.4</v>
       </c>
       <c r="DI12" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.3</v>
+        <v>5.48</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="DM12" t="n">
-        <v>53.79</v>
+        <v>55.24</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.12</v>
+        <v>12.04</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.79</v>
+        <v>12.8</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.42</v>
+        <v>5.48</v>
       </c>
       <c r="DS12" t="n">
         <v>0.16</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.12</v>
+        <v>57.56</v>
       </c>
       <c r="DW12" t="n">
         <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.88</v>
+        <v>15.84</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.210000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.67</v>
+        <v>6.56</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.79</v>
+        <v>21.24</v>
       </c>
       <c r="EB12" t="n">
         <v>1.86</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="13">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
         <v>0.42</v>
@@ -6305,139 +6305,139 @@
         <v>1.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.92</v>
+        <v>3.69</v>
       </c>
       <c r="AI14" t="n">
-        <v>102.75</v>
+        <v>102.69</v>
       </c>
       <c r="AJ14" t="n">
         <v>-0.08</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AL14" t="n">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AN14" t="n">
-        <v>57.17</v>
+        <v>57.69</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11</v>
+        <v>11.23</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.92</v>
+        <v>9.31</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.92</v>
+        <v>8.23</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>58.75</v>
+        <v>59</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.08</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.08</v>
+        <v>15.77</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.42</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.67</v>
+        <v>7.31</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.75</v>
+        <v>18.31</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BG14" t="n">
         <v>4.12</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.62</v>
+        <v>11.48</v>
       </c>
       <c r="BI14" t="n">
         <v>4.12</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>0.96</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BN14" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BP14" t="n">
         <v>5.04</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.58</v>
+        <v>6.44</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BT14" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BV14" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BW14" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BX14" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BY14" t="n">
         <v>1.25</v>
@@ -6446,25 +6446,25 @@
         <v>1.25</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.23</v>
+        <v>6.24</v>
       </c>
       <c r="CB14" t="n">
         <v>6.77</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="CD14" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="CH14" t="n">
         <v>1.9</v>
@@ -6476,13 +6476,13 @@
         <v>1.57</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL14" t="n">
         <v>1.65</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CN14" t="n">
         <v>2.22</v>
@@ -6498,21 +6498,21 @@
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CW14" t="n">
         <v>1.61</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
@@ -6528,79 +6528,79 @@
         <v>1.83</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="DF14" t="n">
         <v>1.12</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="DH14" t="n">
-        <v>112.21</v>
+        <v>111.8</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.42</v>
+        <v>7.32</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="DM14" t="n">
-        <v>62.54</v>
+        <v>62.6</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.84</v>
+        <v>10.96</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.58</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.04</v>
+        <v>7.24</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>61.08</v>
+        <v>61.12</v>
       </c>
       <c r="DW14" t="n">
         <v>0.04</v>
       </c>
       <c r="DX14" t="n">
-        <v>17.7</v>
+        <v>17.96</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.8</v>
+        <v>10.72</v>
       </c>
       <c r="DZ14" t="n">
-        <v>6.92</v>
+        <v>7.24</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.58</v>
+        <v>18.36</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="15">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" t="n">
         <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
         <v>0.08</v>
@@ -6703,49 +6703,49 @@
         <v>0.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AI15" t="n">
-        <v>96.5</v>
+        <v>98.08</v>
       </c>
       <c r="AJ15" t="n">
         <v>0.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.25</v>
+        <v>46.69</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.83</v>
+        <v>9.92</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.5</v>
+        <v>9.31</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AV15" t="n">
         <v>0.08</v>
@@ -6757,49 +6757,49 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>48.33</v>
+        <v>48.85</v>
       </c>
       <c r="AZ15" t="n">
         <v>0.08</v>
       </c>
       <c r="BA15" t="n">
-        <v>13.5</v>
+        <v>13.46</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.83</v>
+        <v>8.92</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.67</v>
+        <v>4.54</v>
       </c>
       <c r="BD15" t="n">
-        <v>15.5</v>
+        <v>15.38</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="BG15" t="n">
         <v>2.96</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.62</v>
+        <v>11.6</v>
       </c>
       <c r="BI15" t="n">
         <v>2.96</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BN15" t="n">
         <v>2</v>
@@ -6808,31 +6808,31 @@
         <v>0.96</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.17</v>
+        <v>5.24</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.46</v>
+        <v>6.36</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BV15" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW15" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BX15" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BY15" t="n">
         <v>2.75</v>
@@ -6847,16 +6847,16 @@
         <v>3.97</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.25</v>
+        <v>4.17</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="CE15" t="n">
         <v>1.28</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CG15" t="n">
         <v>3.33</v>
@@ -6877,16 +6877,16 @@
         <v>1.71</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CO15" t="n">
         <v>1.18</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ15" t="n">
         <v>2.54</v>
@@ -6901,10 +6901,10 @@
         <v>3.26</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CW15" t="n">
         <v>1.58</v>
@@ -6919,28 +6919,28 @@
         <v>2.6</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DB15" t="n">
         <v>1.2</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="DE15" t="n">
         <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="DH15" t="n">
-        <v>94.54000000000001</v>
+        <v>95.44</v>
       </c>
       <c r="DI15" t="n">
         <v>0.04</v>
@@ -6949,28 +6949,28 @@
         <v>1.96</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.84</v>
+        <v>44.16</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.460000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.7</v>
+        <v>10.72</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.960000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DS15" t="n">
         <v>0.12</v>
@@ -6982,7 +6982,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.79</v>
+        <v>47.12</v>
       </c>
       <c r="DW15" t="n">
         <v>0.08</v>
@@ -6991,13 +6991,13 @@
         <v>12.88</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.25</v>
+        <v>8.32</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="EA15" t="n">
-        <v>16.04</v>
+        <v>15.96</v>
       </c>
       <c r="EB15" t="n">
         <v>1.46</v>
@@ -7013,61 +7013,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
         <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="G16" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>85.75</v>
+        <v>88.31</v>
       </c>
       <c r="I16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="K16" t="n">
-        <v>5.25</v>
+        <v>5.62</v>
       </c>
       <c r="L16" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="M16" t="n">
-        <v>44.67</v>
+        <v>46.54</v>
       </c>
       <c r="N16" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="O16" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="P16" t="n">
-        <v>10.25</v>
+        <v>10.31</v>
       </c>
       <c r="Q16" t="n">
-        <v>10.92</v>
+        <v>11.08</v>
       </c>
       <c r="R16" t="n">
-        <v>6.5</v>
+        <v>6.62</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7079,28 +7079,28 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>45.17</v>
+        <v>46.46</v>
       </c>
       <c r="Y16" t="n">
         <v>0.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.75</v>
+        <v>13.77</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.25</v>
+        <v>5.38</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.33</v>
+        <v>18.92</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7187,67 +7187,67 @@
         <v>2.88</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.96</v>
+        <v>11.08</v>
       </c>
       <c r="BI16" t="n">
         <v>2.88</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.71</v>
+        <v>5.72</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS16" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BU16" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BV16" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BY16" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="BZ16" t="n">
-        <v>3.39</v>
+        <v>3.33</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.55</v>
+        <v>4.51</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.72</v>
+        <v>4.67</v>
       </c>
       <c r="CC16" t="n">
         <v>7.74</v>
@@ -7262,10 +7262,10 @@
         <v>2.3</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI16" t="n">
         <v>2.23</v>
@@ -7277,7 +7277,7 @@
         <v>1.36</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CM16" t="n">
         <v>2.88</v>
@@ -7289,25 +7289,25 @@
         <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="CR16" t="n">
         <v>1.35</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CW16" t="n">
         <v>1.65</v>
@@ -7316,7 +7316,7 @@
         <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.37</v>
@@ -7340,37 +7340,37 @@
         <v>0.96</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="DH16" t="n">
-        <v>82.75</v>
+        <v>84.2</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.96</v>
+        <v>5.16</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="DM16" t="n">
-        <v>40.62</v>
+        <v>41.76</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="DP16" t="n">
         <v>11.16</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.38</v>
+        <v>10.48</v>
       </c>
       <c r="DR16" t="n">
         <v>8.08</v>
@@ -7385,28 +7385,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>43.42</v>
+        <v>44.16</v>
       </c>
       <c r="DW16" t="n">
         <v>0.08</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.75</v>
+        <v>12.8</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.62</v>
+        <v>18.44</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
         <v>0.25</v>
@@ -1472,49 +1472,49 @@
         <v>0.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>99.92</v>
+        <v>98.62</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AN2" t="n">
-        <v>45.58</v>
+        <v>45.23</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.75</v>
+        <v>11.85</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.92</v>
+        <v>11.08</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.67</v>
+        <v>7.69</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AV2" t="n">
         <v>0.08</v>
@@ -1526,82 +1526,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>54.67</v>
+        <v>55</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.08</v>
       </c>
       <c r="BA2" t="n">
-        <v>15.5</v>
+        <v>15.08</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.83</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="BD2" t="n">
         <v>15.92</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.92</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.17</v>
+        <v>5.12</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT2" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BV2" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX2" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="BY2" t="n">
         <v>1.75</v>
@@ -1610,25 +1610,25 @@
         <v>1.83</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.59</v>
+        <v>4.55</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="CE2" t="n">
         <v>1.24</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CH2" t="n">
         <v>1.63</v>
@@ -1643,10 +1643,10 @@
         <v>1.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CN2" t="n">
         <v>2.02</v>
@@ -1655,10 +1655,10 @@
         <v>1.14</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CR2" t="n">
         <v>1.34</v>
@@ -1673,7 +1673,7 @@
         <v>1.7</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW2" t="n">
         <v>1.63</v>
@@ -1682,64 +1682,64 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.44</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DB2" t="n">
         <v>1.17</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="DE2" t="n">
         <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="DG2" t="n">
         <v>3.12</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.3</v>
+        <v>100.56</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DM2" t="n">
-        <v>47.54</v>
+        <v>47.28</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.58</v>
+        <v>10.68</v>
       </c>
       <c r="DQ2" t="n">
-        <v>10.96</v>
+        <v>11.04</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.38</v>
+        <v>7.4</v>
       </c>
       <c r="DS2" t="n">
         <v>0.16</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.88</v>
+        <v>53.12</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.66</v>
+        <v>15.44</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.880000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.88</v>
+        <v>16.84</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0.15</v>
@@ -1872,139 +1872,139 @@
         <v>1.31</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AI3" t="n">
-        <v>100</v>
+        <v>100.42</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>50.36</v>
+        <v>49.42</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.18</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.27</v>
+        <v>11.33</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.64</v>
+        <v>6.92</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>57.82</v>
+        <v>58</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA3" t="n">
-        <v>14</v>
+        <v>13.33</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.359999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.64</v>
+        <v>5.33</v>
       </c>
       <c r="BD3" t="n">
-        <v>16.55</v>
+        <v>17.08</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="BF3" t="n">
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.75</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.71</v>
+        <v>4.88</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.04</v>
+        <v>5.08</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="BS3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="BT3" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BU3" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BV3" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX3" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="BY3" t="n">
         <v>1.61</v>
@@ -2013,16 +2013,16 @@
         <v>1.65</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.78</v>
+        <v>4.75</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="CE3" t="n">
         <v>1.24</v>
@@ -2031,13 +2031,13 @@
         <v>2.19</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CH3" t="n">
         <v>1.67</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.6</v>
@@ -2067,7 +2067,7 @@
         <v>1.33</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CT3" t="n">
         <v>3.32</v>
@@ -2076,19 +2076,19 @@
         <v>1.72</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CX3" t="n">
         <v>1.52</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA3" t="n">
         <v>2.02</v>
@@ -2100,49 +2100,49 @@
         <v>1.52</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DE3" t="n">
         <v>0.12</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.79</v>
+        <v>100.96</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM3" t="n">
-        <v>53.25</v>
+        <v>52.68</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.33</v>
+        <v>10.24</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.46</v>
+        <v>12.44</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.42</v>
+        <v>6.56</v>
       </c>
       <c r="DS3" t="n">
         <v>0.04</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>56.92</v>
+        <v>57.04</v>
       </c>
       <c r="DW3" t="n">
         <v>0.04</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.29</v>
+        <v>14.92</v>
       </c>
       <c r="DY3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.3</v>
+        <v>6.12</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.13</v>
+        <v>16.4</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="4">
@@ -2185,61 +2185,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="G4" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>99</v>
+        <v>101.38</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="K4" t="n">
-        <v>4.08</v>
+        <v>4.23</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="M4" t="n">
-        <v>36.25</v>
+        <v>39.54</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="P4" t="n">
-        <v>12.33</v>
+        <v>12.23</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>8.77</v>
       </c>
       <c r="R4" t="n">
-        <v>9.33</v>
+        <v>9.08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T4" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0.08</v>
@@ -2251,28 +2251,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>46.17</v>
+        <v>47.15</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>12</v>
+        <v>12.54</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.17</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.83</v>
+        <v>4.08</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.75</v>
+        <v>18</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AF4" t="n">
         <v>0.08</v>
@@ -2356,70 +2356,70 @@
         <v>1.42</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.539999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.17</v>
+        <v>5.08</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS4" t="n">
-        <v>79.17</v>
+        <v>76</v>
       </c>
       <c r="BT4" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX4" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="CC4" t="n">
         <v>5.92</v>
@@ -2434,16 +2434,16 @@
         <v>2.3</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI4" t="n">
         <v>2.25</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK4" t="n">
         <v>1.41</v>
@@ -2452,10 +2452,10 @@
         <v>1.76</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CO4" t="n">
         <v>1.17</v>
@@ -2464,13 +2464,13 @@
         <v>1.62</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CR4" t="n">
         <v>1.35</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CT4" t="n">
         <v>3.3</v>
@@ -2479,7 +2479,7 @@
         <v>1.61</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CW4" t="n">
         <v>1.63</v>
@@ -2488,13 +2488,13 @@
         <v>1.5</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.48</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DB4" t="n">
         <v>1.2</v>
@@ -2512,40 +2512,40 @@
         <v>1.12</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="DH4" t="n">
-        <v>96.5</v>
+        <v>97.84</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM4" t="n">
-        <v>38.46</v>
+        <v>40.08</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.83</v>
+        <v>12.76</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.460000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.58</v>
+        <v>8.48</v>
       </c>
       <c r="DS4" t="n">
         <v>0.08</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.58</v>
+        <v>46.12</v>
       </c>
       <c r="DW4" t="n">
         <v>0.12</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.34</v>
+        <v>11.64</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.42</v>
+        <v>7.6</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.92</v>
+        <v>4.04</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.62</v>
+        <v>17.76</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -2678,139 +2678,139 @@
         <v>0.92</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>102.27</v>
+        <v>103.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.82</v>
+        <v>6.42</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>54.36</v>
+        <v>53.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.449999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.45</v>
+        <v>10.67</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.91</v>
+        <v>7.25</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52.91</v>
+        <v>52.42</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.91</v>
+        <v>14.33</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.27</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.64</v>
+        <v>5.33</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.09</v>
+        <v>19.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.12</v>
+        <v>10.92</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.96</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BL5" t="n">
         <v>0.96</v>
       </c>
       <c r="BM5" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.25</v>
+        <v>5.16</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.88</v>
+        <v>5.76</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT5" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BU5" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BV5" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BW5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BX5" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BY5" t="n">
         <v>1.4</v>
@@ -2819,70 +2819,70 @@
         <v>1.45</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.31</v>
+        <v>5.26</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CH5" t="n">
         <v>1.68</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.64</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL5" t="n">
         <v>1.76</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO5" t="n">
         <v>1.13</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CR5" t="n">
         <v>1.33</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CT5" t="n">
         <v>3.24</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CW5" t="n">
         <v>1.67</v>
@@ -2891,13 +2891,13 @@
         <v>1.52</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DB5" t="n">
         <v>1.16</v>
@@ -2906,49 +2906,49 @@
         <v>1.51</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.92</v>
+        <v>3.76</v>
       </c>
       <c r="DH5" t="n">
-        <v>103.92</v>
+        <v>104.44</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.71</v>
+        <v>7.48</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DM5" t="n">
-        <v>58.7</v>
+        <v>58.12</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="DP5" t="n">
-        <v>9.619999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.25</v>
+        <v>11.32</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.34</v>
+        <v>6.52</v>
       </c>
       <c r="DS5" t="n">
         <v>0.12</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.63</v>
+        <v>54.32</v>
       </c>
       <c r="DW5" t="n">
         <v>0.16</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.79</v>
+        <v>17.4</v>
       </c>
       <c r="DY5" t="n">
-        <v>11.12</v>
+        <v>10.92</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.67</v>
+        <v>6.48</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.58</v>
+        <v>18.8</v>
       </c>
       <c r="EB5" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="6">
@@ -3084,7 +3084,7 @@
         <v>0.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
         <v>1.69</v>
@@ -3096,7 +3096,7 @@
         <v>-0.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AL6" t="n">
         <v>3.69</v>
@@ -3159,7 +3159,7 @@
         <v>1.21</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="BG6" t="n">
         <v>3.36</v>
@@ -3315,7 +3315,7 @@
         <v>0.2</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="DG6" t="n">
         <v>2.08</v>
@@ -3327,7 +3327,7 @@
         <v>-0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="DK6" t="n">
         <v>4.4</v>
@@ -3384,7 +3384,7 @@
         <v>1.39</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>0.17</v>
@@ -3484,52 +3484,52 @@
         <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AI7" t="n">
-        <v>93.17</v>
+        <v>92.31</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>39.75</v>
+        <v>39.38</v>
       </c>
       <c r="AO7" t="n">
         <v>1.08</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.92</v>
+        <v>10.54</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.83</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.08</v>
+        <v>10.38</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,82 +3541,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47.75</v>
+        <v>47.23</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.42</v>
+        <v>9.23</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.08</v>
+        <v>3.85</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.25</v>
+        <v>19.08</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.25</v>
+        <v>11.16</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.92</v>
+        <v>4.96</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6.25</v>
+        <v>6.12</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>91.67</v>
+        <v>88</v>
       </c>
       <c r="BT7" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BU7" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BY7" t="n">
         <v>2.63</v>
@@ -3625,31 +3625,31 @@
         <v>2.83</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.76</v>
+        <v>4.63</v>
       </c>
       <c r="CE7" t="n">
         <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CH7" t="n">
         <v>1.61</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.54</v>
@@ -3658,13 +3658,13 @@
         <v>1.34</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CM7" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CO7" t="n">
         <v>1.15</v>
@@ -3673,13 +3673,13 @@
         <v>1.57</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CR7" t="n">
         <v>1.34</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
@@ -3709,52 +3709,52 @@
         <v>1.18</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="DH7" t="n">
-        <v>93.8</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.54</v>
+        <v>5.44</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.75</v>
+        <v>45.32</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.33</v>
+        <v>10.36</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.380000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="DS7" t="n">
         <v>0.04</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.16</v>
+        <v>49.8</v>
       </c>
       <c r="DW7" t="n">
         <v>0.16</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.67</v>
+        <v>11.48</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.5</v>
+        <v>6.48</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.16</v>
+        <v>5</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.29</v>
+        <v>18.24</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
         <v>0.17</v>
@@ -3890,13 +3890,13 @@
         <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AI8" t="n">
-        <v>104.17</v>
+        <v>104.31</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -3905,34 +3905,34 @@
         <v>1.92</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.92</v>
+        <v>5.31</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.92</v>
+        <v>41.92</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.67</v>
+        <v>3.08</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.83</v>
+        <v>11.92</v>
       </c>
       <c r="AR8" t="n">
-        <v>10.58</v>
+        <v>10.38</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.33</v>
+        <v>7.31</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AV8" t="n">
         <v>0.08</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>47.75</v>
+        <v>48.08</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.58</v>
+        <v>14.69</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.58</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>6.23</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.5</v>
+        <v>19.69</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.75</v>
+        <v>10.8</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.46</v>
+        <v>5.64</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.29</v>
+        <v>5.16</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS8" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BU8" t="n">
-        <v>16.67</v>
+        <v>20</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.33</v>
+        <v>12</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BY8" t="n">
         <v>2.1</v>
@@ -4028,16 +4028,16 @@
         <v>2.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.65</v>
+        <v>4.44</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.7</v>
+        <v>4.49</v>
       </c>
       <c r="CE8" t="n">
         <v>1.33</v>
@@ -4052,7 +4052,7 @@
         <v>1.49</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.71</v>
@@ -4061,22 +4061,22 @@
         <v>1.51</v>
       </c>
       <c r="CL8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CM8" t="n">
         <v>2.42</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO8" t="n">
         <v>1.23</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4085,13 +4085,13 @@
         <v>2.66</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CU8" t="n">
         <v>1.53</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CW8" t="n">
         <v>1.76</v>
@@ -4100,13 +4100,13 @@
         <v>1.55</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.38</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DB8" t="n">
         <v>1.25</v>
@@ -4115,7 +4115,7 @@
         <v>1.82</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="DE8" t="n">
         <v>0.12</v>
@@ -4124,10 +4124,10 @@
         <v>1.12</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="DH8" t="n">
-        <v>109.8</v>
+        <v>109.64</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
@@ -4136,28 +4136,28 @@
         <v>1.8</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.08</v>
+        <v>46.4</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.33</v>
+        <v>3.52</v>
       </c>
       <c r="DP8" t="n">
-        <v>11</v>
+        <v>11.08</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.25</v>
+        <v>10.16</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.62</v>
+        <v>6.64</v>
       </c>
       <c r="DS8" t="n">
         <v>0.12</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.21</v>
+        <v>51.24</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.45</v>
+        <v>15.96</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.789999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.66</v>
+        <v>5.8</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.46</v>
+        <v>20.52</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="9">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="F13" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="H13" t="n">
-        <v>89.27</v>
+        <v>88.75</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>4.17</v>
       </c>
       <c r="L13" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="M13" t="n">
-        <v>36.82</v>
+        <v>37.33</v>
       </c>
       <c r="N13" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>11.64</v>
+        <v>11.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.73</v>
+        <v>12.33</v>
       </c>
       <c r="R13" t="n">
-        <v>9.640000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="S13" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T13" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>41.82</v>
+        <v>41.67</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>9.73</v>
+        <v>9.67</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.18</v>
+        <v>6.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.27</v>
+        <v>17.08</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
         <v>0.15</v>
@@ -5983,70 +5983,70 @@
         <v>1.77</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.42</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.58</v>
+        <v>4.76</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.79</v>
+        <v>4.84</v>
       </c>
       <c r="BR13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="BS13" t="n">
-        <v>87.5</v>
+        <v>84</v>
       </c>
       <c r="BT13" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BU13" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BV13" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX13" t="n">
-        <v>70.83</v>
+        <v>68</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="CC13" t="n">
         <v>5.94</v>
@@ -6067,10 +6067,10 @@
         <v>1.58</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK13" t="n">
         <v>1.44</v>
@@ -6079,16 +6079,16 @@
         <v>1.83</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO13" t="n">
         <v>1.16</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CQ13" t="n">
         <v>2.43</v>
@@ -6106,73 +6106,73 @@
         <v>1.64</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY13" t="n">
         <v>1.8</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="DA13" t="n">
         <v>2.01</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DC13" t="n">
         <v>1.6</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DH13" t="n">
-        <v>82.83</v>
+        <v>82.84</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="DK13" t="n">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="DM13" t="n">
-        <v>33.96</v>
+        <v>34.32</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="DP13" t="n">
-        <v>11</v>
+        <v>11.04</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.25</v>
+        <v>12.08</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.33</v>
+        <v>10.24</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.46</v>
+        <v>44.28</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.210000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.67</v>
+        <v>5.72</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.46</v>
+        <v>16.4</v>
       </c>
       <c r="EB13" t="n">
         <v>1.08</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="14">
@@ -7416,10 +7416,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -7428,82 +7428,82 @@
         <v>0.08</v>
       </c>
       <c r="F17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="H17" t="n">
+        <v>120.62</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M17" t="n">
+        <v>65.69</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P17" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="S17" t="n">
         <v>0.92</v>
       </c>
-      <c r="G17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="H17" t="n">
-        <v>123.58</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M17" t="n">
-        <v>65.42</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="P17" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>57.54</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>57.92</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.08</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7587,70 +7587,70 @@
         <v>2</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.25</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL17" t="n">
         <v>0.96</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="BO17" t="n">
         <v>0.88</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.79</v>
+        <v>4.72</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS17" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT17" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BU17" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV17" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX17" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="CC17" t="n">
         <v>2.32</v>
@@ -7671,19 +7671,19 @@
         <v>1.57</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.65</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CN17" t="n">
         <v>1.95</v>
@@ -7701,22 +7701,22 @@
         <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CT17" t="n">
         <v>3.24</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CW17" t="n">
         <v>1.68</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY17" t="n">
         <v>1.81</v>
@@ -7740,76 +7740,76 @@
         <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DH17" t="n">
-        <v>110.29</v>
+        <v>109.28</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.42</v>
+        <v>5.36</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="DM17" t="n">
-        <v>59.5</v>
+        <v>59.88</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.25</v>
+        <v>11.32</v>
       </c>
       <c r="DQ17" t="n">
-        <v>9.880000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.96</v>
+        <v>6.92</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.71</v>
+        <v>54.64</v>
       </c>
       <c r="DW17" t="n">
         <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>18.54</v>
+        <v>18.56</v>
       </c>
       <c r="DY17" t="n">
-        <v>11.96</v>
+        <v>11.92</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.58</v>
+        <v>6.64</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.46</v>
+        <v>20.36</v>
       </c>
       <c r="EB17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="18">
@@ -7819,91 +7819,91 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="H18" t="n">
-        <v>95.75</v>
+        <v>94.23</v>
       </c>
       <c r="I18" t="n">
         <v>-0.08</v>
       </c>
       <c r="J18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="K18" t="n">
-        <v>5.25</v>
+        <v>5.23</v>
       </c>
       <c r="L18" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>40</v>
+        <v>39.69</v>
       </c>
       <c r="N18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>10.69</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.67</v>
+        <v>13.54</v>
       </c>
       <c r="R18" t="n">
         <v>7.08</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="T18" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>47</v>
+        <v>46.54</v>
       </c>
       <c r="Y18" t="n">
         <v>0.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.08</v>
+        <v>15.69</v>
       </c>
       <c r="AA18" t="n">
-        <v>11</v>
+        <v>10.77</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.08</v>
+        <v>4.92</v>
       </c>
       <c r="AC18" t="n">
-        <v>20.75</v>
+        <v>20.69</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AE18" t="n">
         <v>1.08</v>
@@ -7990,70 +7990,70 @@
         <v>1.75</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.539999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.83</v>
+        <v>4.8</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT18" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BU18" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BV18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>70.83</v>
+        <v>68</v>
       </c>
       <c r="BY18" t="n">
         <v>2.24</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CC18" t="n">
         <v>3.31</v>
@@ -8065,10 +8065,10 @@
         <v>1.32</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CH18" t="n">
         <v>1.5</v>
@@ -8077,19 +8077,19 @@
         <v>2.15</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM18" t="n">
         <v>2.65</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CO18" t="n">
         <v>1.21</v>
@@ -8098,7 +8098,7 @@
         <v>1.72</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CR18" t="n">
         <v>1.36</v>
@@ -8122,97 +8122,97 @@
         <v>1.5</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DA18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB18" t="n">
         <v>1.24</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DF18" t="n">
         <v>1.08</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="DH18" t="n">
-        <v>97.5</v>
+        <v>96.64</v>
       </c>
       <c r="DI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="DK18" t="n">
         <v>5.12</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="DM18" t="n">
-        <v>40</v>
+        <v>39.84</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.75</v>
+        <v>10.84</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.71</v>
+        <v>11.72</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.75</v>
+        <v>7.72</v>
       </c>
       <c r="DS18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DT18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.66</v>
+        <v>47.4</v>
       </c>
       <c r="DW18" t="n">
         <v>0.04</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.83</v>
+        <v>14.68</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.75</v>
+        <v>9.68</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.46</v>
+        <v>19.48</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="19">
@@ -8222,94 +8222,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F19" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="H19" t="n">
-        <v>83.42</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="K19" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="L19" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="M19" t="n">
-        <v>43.08</v>
+        <v>42.62</v>
       </c>
       <c r="N19" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="O19" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="P19" t="n">
-        <v>9.92</v>
+        <v>9.77</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.83</v>
+        <v>12.77</v>
       </c>
       <c r="R19" t="n">
-        <v>10.33</v>
+        <v>10.77</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T19" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="U19" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="V19" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>44.58</v>
+        <v>44.85</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>12.33</v>
+        <v>12.31</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.75</v>
+        <v>7.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="AC19" t="n">
-        <v>13.58</v>
+        <v>13.08</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8393,70 +8393,70 @@
         <v>1.08</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.5</v>
+        <v>10.56</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="BJ19" t="n">
         <v>1</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.79</v>
+        <v>5.96</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT19" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BU19" t="n">
-        <v>20.83</v>
+        <v>24</v>
       </c>
       <c r="BV19" t="n">
-        <v>4.17</v>
+        <v>8</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BY19" t="n">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
       <c r="BZ19" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.06</v>
+        <v>5.01</v>
       </c>
       <c r="CB19" t="n">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="CC19" t="n">
         <v>8.199999999999999</v>
@@ -8465,16 +8465,16 @@
         <v>9.050000000000001</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CI19" t="n">
         <v>2.24</v>
@@ -8489,7 +8489,7 @@
         <v>1.69</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CN19" t="n">
         <v>2.16</v>
@@ -8498,40 +8498,40 @@
         <v>1.15</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CT19" t="n">
         <v>3.36</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CV19" t="n">
         <v>2.32</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CX19" t="n">
         <v>1.51</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.44</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DB19" t="n">
         <v>1.17</v>
@@ -8540,82 +8540,82 @@
         <v>1.54</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DE19" t="n">
         <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="DH19" t="n">
-        <v>80.95999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="DI19" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM19" t="n">
-        <v>38.38</v>
+        <v>38.32</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="DP19" t="n">
-        <v>10.08</v>
+        <v>10</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.83</v>
+        <v>11.84</v>
       </c>
       <c r="DR19" t="n">
-        <v>10.17</v>
+        <v>10.4</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>44.25</v>
+        <v>44.4</v>
       </c>
       <c r="DW19" t="n">
         <v>0.04</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.46</v>
+        <v>10.52</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.92</v>
+        <v>6.96</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="EA19" t="n">
-        <v>15.29</v>
+        <v>14.96</v>
       </c>
       <c r="EB19" t="n">
         <v>1.19</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>0.15</v>
@@ -1875,49 +1875,49 @@
         <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AI3" t="n">
-        <v>100.42</v>
+        <v>100</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.33</v>
+        <v>4.62</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>49.42</v>
+        <v>49.62</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>9.77</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.33</v>
+        <v>10.85</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.92</v>
+        <v>6.85</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AV3" t="n">
         <v>0.08</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>58</v>
+        <v>58.15</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.08</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.33</v>
+        <v>13.31</v>
       </c>
       <c r="BB3" t="n">
         <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.33</v>
+        <v>5.31</v>
       </c>
       <c r="BD3" t="n">
         <v>17.08</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BF3" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.960000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="BJ3" t="n">
         <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.88</v>
+        <v>4.81</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.08</v>
+        <v>5.31</v>
       </c>
       <c r="BR3" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS3" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BU3" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BV3" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX3" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BY3" t="n">
         <v>1.61</v>
@@ -2013,34 +2013,34 @@
         <v>1.65</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="CC3" t="n">
         <v>2.29</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CE3" t="n">
         <v>1.24</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CK3" t="n">
         <v>1.47</v>
@@ -2061,19 +2061,19 @@
         <v>1.49</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CR3" t="n">
         <v>1.33</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CT3" t="n">
         <v>3.32</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CV3" t="n">
         <v>2.42</v>
@@ -2091,7 +2091,7 @@
         <v>2.43</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB3" t="n">
         <v>1.16</v>
@@ -2100,7 +2100,7 @@
         <v>1.52</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DE3" t="n">
         <v>0.12</v>
@@ -2109,40 +2109,40 @@
         <v>1.2</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.68</v>
+        <v>2.77</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.96</v>
+        <v>100.73</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DK3" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM3" t="n">
-        <v>52.68</v>
+        <v>52.66</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.24</v>
+        <v>10.12</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.44</v>
+        <v>12.16</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.56</v>
+        <v>6.54</v>
       </c>
       <c r="DS3" t="n">
         <v>0.04</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>57.04</v>
+        <v>57.15</v>
       </c>
       <c r="DW3" t="n">
         <v>0.04</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.92</v>
+        <v>14.84</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.12</v>
+        <v>6.08</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.4</v>
+        <v>16.42</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="4">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="F8" t="n">
         <v>1.08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.58</v>
+        <v>3.77</v>
       </c>
       <c r="H8" t="n">
-        <v>115.42</v>
+        <v>115.15</v>
       </c>
       <c r="I8" t="n">
         <v>0.08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="K8" t="n">
-        <v>7.58</v>
+        <v>7.46</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="M8" t="n">
-        <v>51.25</v>
+        <v>50.92</v>
       </c>
       <c r="N8" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>3.69</v>
       </c>
       <c r="P8" t="n">
-        <v>10.17</v>
+        <v>9.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.92</v>
+        <v>9.69</v>
       </c>
       <c r="R8" t="n">
-        <v>5.92</v>
+        <v>6</v>
       </c>
       <c r="S8" t="n">
         <v>1.08</v>
       </c>
       <c r="T8" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="U8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>54.67</v>
+        <v>53.54</v>
       </c>
       <c r="Y8" t="n">
         <v>0.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>17.33</v>
+        <v>17</v>
       </c>
       <c r="AA8" t="n">
-        <v>12</v>
+        <v>11.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.33</v>
+        <v>5.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.42</v>
+        <v>21.31</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AF8" t="n">
         <v>0.08</v>
@@ -3968,70 +3968,70 @@
         <v>1.85</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.8</v>
+        <v>10.92</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.64</v>
+        <v>5.54</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.16</v>
+        <v>5.38</v>
       </c>
       <c r="BR8" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BU8" t="n">
-        <v>20</v>
+        <v>23.08</v>
       </c>
       <c r="BV8" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW8" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX8" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="CC8" t="n">
         <v>4.44</v>
@@ -4043,7 +4043,7 @@
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CG8" t="n">
         <v>3.18</v>
@@ -4052,10 +4052,10 @@
         <v>1.49</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK8" t="n">
         <v>1.51</v>
@@ -4076,13 +4076,13 @@
         <v>1.76</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CT8" t="n">
         <v>3.21</v>
@@ -4091,10 +4091,10 @@
         <v>1.53</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX8" t="n">
         <v>1.55</v>
@@ -4103,7 +4103,7 @@
         <v>1.88</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA8" t="n">
         <v>1.93</v>
@@ -4112,52 +4112,52 @@
         <v>1.25</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DF8" t="n">
         <v>1.12</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="DH8" t="n">
-        <v>109.64</v>
+        <v>109.73</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.4</v>
+        <v>6.38</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.4</v>
+        <v>46.42</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="DP8" t="n">
-        <v>11.08</v>
+        <v>10.84</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.16</v>
+        <v>10.03</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.64</v>
+        <v>6.66</v>
       </c>
       <c r="DS8" t="n">
         <v>0.12</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.24</v>
+        <v>50.81</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.96</v>
+        <v>15.84</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.16</v>
+        <v>10.04</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.8</v>
+        <v>5.81</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.52</v>
+        <v>20.5</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="H10" t="n">
-        <v>94.42</v>
+        <v>94.23</v>
       </c>
       <c r="I10" t="n">
         <v>0.08</v>
       </c>
       <c r="J10" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="K10" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="L10" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>41.17</v>
+        <v>40.85</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="O10" t="n">
         <v>2.08</v>
       </c>
       <c r="P10" t="n">
-        <v>12.42</v>
+        <v>12.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.17</v>
+        <v>12.54</v>
       </c>
       <c r="R10" t="n">
-        <v>7.58</v>
+        <v>7.77</v>
       </c>
       <c r="S10" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="T10" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="U10" t="n">
         <v>0.08</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>44.33</v>
+        <v>44.54</v>
       </c>
       <c r="Y10" t="n">
         <v>0.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.75</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.25</v>
+        <v>5.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.08</v>
+        <v>17.23</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.46</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.88</v>
+        <v>3.73</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.24</v>
+        <v>10.46</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.88</v>
+        <v>3.73</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.2</v>
+        <v>5.38</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.04</v>
+        <v>5.08</v>
       </c>
       <c r="BR10" t="n">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS10" t="n">
-        <v>96</v>
+        <v>92.31</v>
       </c>
       <c r="BT10" t="n">
-        <v>76</v>
+        <v>73.08</v>
       </c>
       <c r="BU10" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BV10" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BW10" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BX10" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="CC10" t="n">
         <v>6.39</v>
@@ -4846,43 +4846,43 @@
         <v>7.21</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.64</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CO10" t="n">
         <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CR10" t="n">
         <v>1.36</v>
@@ -4906,64 +4906,64 @@
         <v>1.46</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.59</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DB10" t="n">
         <v>1.2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DH10" t="n">
-        <v>86.08</v>
+        <v>86.3</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.88</v>
+        <v>36.89</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO10" t="n">
         <v>2.16</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.4</v>
+        <v>13.38</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.08</v>
+        <v>11.31</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.96</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DS10" t="n">
         <v>0.12</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.36</v>
+        <v>43.5</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.24</v>
+        <v>11.19</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.32</v>
+        <v>7.31</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.96</v>
+        <v>18</v>
       </c>
       <c r="EB10" t="n">
         <v>1.25</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="11">
@@ -7819,13 +7819,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18" t="n">
         <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
         <v>0.08</v>
@@ -7912,49 +7912,49 @@
         <v>0.08</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="AI18" t="n">
-        <v>99.25</v>
+        <v>101.08</v>
       </c>
       <c r="AJ18" t="n">
         <v>0.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AL18" t="n">
-        <v>5</v>
+        <v>5.54</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AN18" t="n">
-        <v>40</v>
+        <v>39.77</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.33</v>
+        <v>2.77</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>11.46</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.42</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7966,82 +7966,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>48.33</v>
+        <v>48.69</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>13.58</v>
+        <v>13.77</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.5</v>
+        <v>8.85</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.08</v>
+        <v>4.92</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.17</v>
+        <v>18.15</v>
       </c>
       <c r="BE18" t="n">
         <v>1.51</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.52</v>
+        <v>9.77</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.72</v>
+        <v>4.92</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="BR18" t="n">
-        <v>100</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS18" t="n">
-        <v>80</v>
+        <v>76.92</v>
       </c>
       <c r="BT18" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BU18" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BV18" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>68</v>
+        <v>65.38</v>
       </c>
       <c r="BY18" t="n">
         <v>2.24</v>
@@ -8050,16 +8050,16 @@
         <v>2.24</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.31</v>
+        <v>3.22</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.63</v>
+        <v>3.52</v>
       </c>
       <c r="CE18" t="n">
         <v>1.32</v>
@@ -8068,10 +8068,10 @@
         <v>2.47</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI18" t="n">
         <v>2.15</v>
@@ -8086,7 +8086,7 @@
         <v>1.84</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CN18" t="n">
         <v>2.01</v>
@@ -8095,7 +8095,7 @@
         <v>1.21</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CQ18" t="n">
         <v>2.78</v>
@@ -8119,13 +8119,13 @@
         <v>1.7</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CY18" t="n">
         <v>1.78</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DA18" t="n">
         <v>2.04</v>
@@ -8134,10 +8134,10 @@
         <v>1.24</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DE18" t="n">
         <v>0.08</v>
@@ -8146,40 +8146,40 @@
         <v>1.08</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="DH18" t="n">
-        <v>96.64</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="DI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DK18" t="n">
-        <v>5.12</v>
+        <v>5.38</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.84</v>
+        <v>39.73</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.84</v>
+        <v>3.04</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.84</v>
+        <v>11.08</v>
       </c>
       <c r="DQ18" t="n">
-        <v>11.72</v>
+        <v>11.77</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.72</v>
+        <v>7.81</v>
       </c>
       <c r="DS18" t="n">
         <v>0.04</v>
@@ -8191,28 +8191,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>47.4</v>
+        <v>47.62</v>
       </c>
       <c r="DW18" t="n">
         <v>0.04</v>
       </c>
       <c r="DX18" t="n">
-        <v>14.68</v>
+        <v>14.73</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.68</v>
+        <v>9.81</v>
       </c>
       <c r="DZ18" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.48</v>
+        <v>19.42</v>
       </c>
       <c r="EB18" t="n">
         <v>1.57</v>
       </c>
       <c r="EC18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
         <v>0.25</v>
@@ -1469,115 +1469,115 @@
         <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="AI2" t="n">
-        <v>98.62</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.38</v>
+        <v>5.43</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AN2" t="n">
-        <v>45.23</v>
+        <v>42.79</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.85</v>
+        <v>11.29</v>
       </c>
       <c r="AR2" t="n">
-        <v>11.08</v>
+        <v>10.79</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.69</v>
+        <v>7.79</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>55</v>
+        <v>53.64</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA2" t="n">
-        <v>15.08</v>
+        <v>14.93</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.69</v>
+        <v>5.64</v>
       </c>
       <c r="BD2" t="n">
-        <v>15.92</v>
+        <v>16.07</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.880000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="BJ2" t="n">
         <v>1.08</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="BQ2" t="n">
         <v>5.12</v>
@@ -1586,22 +1586,22 @@
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT2" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BU2" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BV2" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BW2" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BX2" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BY2" t="n">
         <v>1.75</v>
@@ -1610,25 +1610,25 @@
         <v>1.83</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.21</v>
+        <v>2.54</v>
       </c>
       <c r="CE2" t="n">
         <v>1.24</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="CH2" t="n">
         <v>1.63</v>
@@ -1643,13 +1643,13 @@
         <v>1.43</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CO2" t="n">
         <v>1.14</v>
@@ -1658,7 +1658,7 @@
         <v>1.52</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CR2" t="n">
         <v>1.34</v>
@@ -1682,97 +1682,97 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.44</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="DB2" t="n">
         <v>1.17</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.56</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.44</v>
+        <v>5.46</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="DM2" t="n">
-        <v>47.28</v>
+        <v>45.89</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.68</v>
+        <v>10.43</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.04</v>
+        <v>10.89</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.4</v>
+        <v>7.46</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.12</v>
+        <v>52.46</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.44</v>
+        <v>15.35</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.640000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.8</v>
+        <v>5.77</v>
       </c>
       <c r="EA2" t="n">
-        <v>16.84</v>
+        <v>16.88</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="3">
@@ -2016,7 +2016,7 @@
         <v>4.54</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.72</v>
+        <v>4.71</v>
       </c>
       <c r="CC3" t="n">
         <v>2.29</v>
@@ -2091,13 +2091,13 @@
         <v>2.43</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB3" t="n">
         <v>1.16</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="DD3" t="n">
         <v>2.31</v>
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="H4" t="n">
-        <v>101.38</v>
+        <v>103.21</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="K4" t="n">
-        <v>4.23</v>
+        <v>4.36</v>
       </c>
       <c r="L4" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>39.54</v>
+        <v>42</v>
       </c>
       <c r="N4" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="O4" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="P4" t="n">
-        <v>12.23</v>
+        <v>11.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.77</v>
+        <v>8.57</v>
       </c>
       <c r="R4" t="n">
-        <v>9.08</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>47.15</v>
+        <v>47.43</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.54</v>
+        <v>13.14</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.460000000000001</v>
+        <v>9</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.08</v>
+        <v>4.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>18</v>
+        <v>18.86</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AF4" t="n">
         <v>0.08</v>
@@ -2356,70 +2356,70 @@
         <v>1.42</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.52</v>
+        <v>9.69</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.08</v>
+        <v>5.19</v>
       </c>
       <c r="BR4" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS4" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT4" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BU4" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV4" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW4" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX4" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.42</v>
+        <v>4.39</v>
       </c>
       <c r="CC4" t="n">
         <v>5.92</v>
@@ -2431,16 +2431,16 @@
         <v>1.27</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CH4" t="n">
         <v>1.58</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.6</v>
@@ -2449,7 +2449,7 @@
         <v>1.41</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM4" t="n">
         <v>2.71</v>
@@ -2476,7 +2476,7 @@
         <v>3.3</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CV4" t="n">
         <v>2.38</v>
@@ -2503,82 +2503,82 @@
         <v>1.63</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="DH4" t="n">
-        <v>97.84</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DM4" t="n">
-        <v>40.08</v>
+        <v>41.39</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.76</v>
+        <v>12.42</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.359999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.48</v>
+        <v>8.57</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.12</v>
+        <v>46.31</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX4" t="n">
-        <v>11.64</v>
+        <v>12</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.6</v>
+        <v>7.92</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.76</v>
+        <v>18.23</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -2678,52 +2678,52 @@
         <v>0.92</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AI5" t="n">
-        <v>103.5</v>
+        <v>104.77</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.42</v>
+        <v>6.62</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>53.5</v>
+        <v>54.62</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.33</v>
+        <v>9.23</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.67</v>
+        <v>10.77</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.25</v>
+        <v>6.92</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AV5" t="n">
         <v>0.08</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52.42</v>
+        <v>52.77</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.33</v>
+        <v>14.31</v>
       </c>
       <c r="BB5" t="n">
         <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.33</v>
+        <v>5.31</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.5</v>
+        <v>20.08</v>
       </c>
       <c r="BE5" t="n">
         <v>1.67</v>
       </c>
       <c r="BF5" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.92</v>
+        <v>11</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.72</v>
+        <v>0.77</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM5" t="n">
         <v>0.96</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.16</v>
+        <v>5.19</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.76</v>
+        <v>5.77</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT5" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BU5" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BV5" t="n">
-        <v>32</v>
+        <v>34.62</v>
       </c>
       <c r="BW5" t="n">
-        <v>24</v>
+        <v>26.92</v>
       </c>
       <c r="BX5" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BY5" t="n">
         <v>1.4</v>
@@ -2819,28 +2819,28 @@
         <v>1.45</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.26</v>
+        <v>5.2</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CE5" t="n">
         <v>1.23</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI5" t="n">
         <v>2.25</v>
@@ -2849,7 +2849,7 @@
         <v>1.64</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL5" t="n">
         <v>1.76</v>
@@ -2858,7 +2858,7 @@
         <v>2.73</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO5" t="n">
         <v>1.13</v>
@@ -2867,7 +2867,7 @@
         <v>1.49</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CR5" t="n">
         <v>1.33</v>
@@ -2897,58 +2897,58 @@
         <v>2.46</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="DE5" t="n">
         <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="DH5" t="n">
-        <v>104.44</v>
+        <v>105.04</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.48</v>
+        <v>7.54</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="DM5" t="n">
-        <v>58.12</v>
+        <v>58.5</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.72</v>
+        <v>3.77</v>
       </c>
       <c r="DP5" t="n">
-        <v>9.56</v>
+        <v>9.5</v>
       </c>
       <c r="DQ5" t="n">
-        <v>11.32</v>
+        <v>11.34</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.52</v>
+        <v>6.38</v>
       </c>
       <c r="DS5" t="n">
         <v>0.12</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>54.32</v>
+        <v>54.42</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX5" t="n">
-        <v>17.4</v>
+        <v>17.27</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.92</v>
+        <v>10.84</v>
       </c>
       <c r="DZ5" t="n">
-        <v>6.48</v>
+        <v>6.43</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.8</v>
+        <v>19.11</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="6">
@@ -2991,94 +2991,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="F6" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H6" t="n">
-        <v>88.17</v>
+        <v>89.77</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="K6" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="M6" t="n">
-        <v>40.25</v>
+        <v>41.54</v>
       </c>
       <c r="N6" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="P6" t="n">
-        <v>13.33</v>
+        <v>12.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.08</v>
+        <v>11.62</v>
       </c>
       <c r="R6" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>44.08</v>
+        <v>45.15</v>
       </c>
       <c r="Y6" t="n">
         <v>0.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.42</v>
+        <v>15.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.83</v>
+        <v>11.31</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="AC6" t="n">
-        <v>14.92</v>
+        <v>15.46</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AF6" t="n">
         <v>0.08</v>
@@ -3162,70 +3162,70 @@
         <v>1.92</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="BH6" t="n">
-        <v>11.4</v>
+        <v>11.27</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.76</v>
+        <v>5.73</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT6" t="n">
-        <v>68</v>
+        <v>69.23</v>
       </c>
       <c r="BU6" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BV6" t="n">
-        <v>24</v>
+        <v>26.92</v>
       </c>
       <c r="BW6" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX6" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="CC6" t="n">
         <v>5.91</v>
@@ -3249,16 +3249,16 @@
         <v>2.16</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL6" t="n">
         <v>1.74</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CN6" t="n">
         <v>2.07</v>
@@ -3270,7 +3270,7 @@
         <v>1.67</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3285,7 +3285,7 @@
         <v>1.59</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CW6" t="n">
         <v>1.68</v>
@@ -3306,52 +3306,52 @@
         <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="DE6" t="n">
         <v>0.2</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DG6" t="n">
         <v>2.08</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.92</v>
+        <v>88.73</v>
       </c>
       <c r="DI6" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.4</v>
+        <v>4.34</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.68</v>
+        <v>36.5</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.16</v>
+        <v>12.96</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.36</v>
+        <v>11.62</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.119999999999999</v>
+        <v>7.93</v>
       </c>
       <c r="DS6" t="n">
         <v>0.12</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.88</v>
+        <v>45.38</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.76</v>
+        <v>13.08</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.119999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.64</v>
+        <v>4.62</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.56</v>
+        <v>16.77</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="7">
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
         <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="G7" t="n">
         <v>3.92</v>
       </c>
       <c r="H7" t="n">
-        <v>94.42</v>
+        <v>95</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3421,34 +3421,34 @@
         <v>1.08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.92</v>
+        <v>6.85</v>
       </c>
       <c r="L7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="M7" t="n">
-        <v>51.75</v>
+        <v>51.69</v>
       </c>
       <c r="N7" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="P7" t="n">
-        <v>8.67</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.83</v>
+        <v>11.54</v>
       </c>
       <c r="R7" t="n">
-        <v>8.67</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="T7" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="U7" t="n">
         <v>0.08</v>
@@ -3460,25 +3460,25 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52.58</v>
+        <v>52.46</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.92</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.67</v>
+        <v>7.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.25</v>
+        <v>6.31</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.33</v>
+        <v>17.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE7" t="n">
         <v>1.08</v>
@@ -3565,31 +3565,31 @@
         <v>2.08</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.16</v>
+        <v>11.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="BL7" t="n">
         <v>0.92</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BP7" t="n">
         <v>4.96</v>
@@ -3601,28 +3601,28 @@
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BU7" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BV7" t="n">
-        <v>8</v>
+        <v>11.54</v>
       </c>
       <c r="BW7" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX7" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="CA7" t="n">
         <v>4.06</v>
@@ -3658,10 +3658,10 @@
         <v>1.34</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CN7" t="n">
         <v>2.22</v>
@@ -3709,52 +3709,52 @@
         <v>1.18</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF7" t="n">
         <v>0.92</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="DH7" t="n">
-        <v>93.31999999999999</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.44</v>
+        <v>5.46</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.32</v>
+        <v>45.54</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.640000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.36</v>
+        <v>10.27</v>
       </c>
       <c r="DR7" t="n">
-        <v>9.56</v>
+        <v>9.42</v>
       </c>
       <c r="DS7" t="n">
         <v>0.04</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>49.8</v>
+        <v>49.84</v>
       </c>
       <c r="DW7" t="n">
         <v>0.16</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.48</v>
+        <v>11.62</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.48</v>
+        <v>6.54</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.24</v>
+        <v>18.46</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="8">
@@ -4103,7 +4103,7 @@
         <v>1.88</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA8" t="n">
         <v>1.93</v>
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>0.08</v>
@@ -4296,94 +4296,94 @@
         <v>1.08</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="AI9" t="n">
-        <v>92.42</v>
+        <v>91.92</v>
       </c>
       <c r="AJ9" t="n">
         <v>0.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.33</v>
+        <v>5.54</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AN9" t="n">
-        <v>41.67</v>
+        <v>40.62</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.5</v>
+        <v>12.08</v>
       </c>
       <c r="AR9" t="n">
-        <v>10</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AS9" t="n">
         <v>8.92</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49.58</v>
+        <v>49.54</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.08</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.08</v>
+        <v>14.69</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.58</v>
+        <v>9.23</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.25</v>
+        <v>19</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.44</v>
+        <v>10.58</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BL9" t="n">
         <v>1</v>
@@ -4395,34 +4395,34 @@
         <v>1.96</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BP9" t="n">
-        <v>5</v>
+        <v>5.04</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BU9" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BW9" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX9" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BY9" t="n">
         <v>2.25</v>
@@ -4431,25 +4431,25 @@
         <v>2.21</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.27</v>
+        <v>4.12</v>
       </c>
       <c r="CE9" t="n">
         <v>1.27</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CH9" t="n">
         <v>1.6</v>
@@ -4458,7 +4458,7 @@
         <v>2.39</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK9" t="n">
         <v>1.42</v>
@@ -4476,7 +4476,7 @@
         <v>1.17</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ9" t="n">
         <v>2.46</v>
@@ -4491,7 +4491,7 @@
         <v>3.26</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV9" t="n">
         <v>2.51</v>
@@ -4515,7 +4515,7 @@
         <v>1.19</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DD9" t="n">
         <v>2.48</v>
@@ -4527,40 +4527,40 @@
         <v>1.12</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="DH9" t="n">
-        <v>98.8</v>
+        <v>98.3</v>
       </c>
       <c r="DI9" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="DM9" t="n">
-        <v>49.48</v>
+        <v>48.66</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.08</v>
+        <v>10.92</v>
       </c>
       <c r="DQ9" t="n">
-        <v>9.960000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.72</v>
+        <v>7.77</v>
       </c>
       <c r="DS9" t="n">
         <v>0.12</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.84</v>
+        <v>50.77</v>
       </c>
       <c r="DW9" t="n">
         <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.64</v>
+        <v>15.42</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.36</v>
+        <v>10.15</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.28</v>
+        <v>18.19</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
@@ -5018,82 +5018,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H11" t="n">
-        <v>98.45999999999999</v>
+        <v>98.14</v>
       </c>
       <c r="I11" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>5.38</v>
+        <v>5.29</v>
       </c>
       <c r="L11" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>46.08</v>
+        <v>45.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="O11" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="P11" t="n">
-        <v>10.08</v>
+        <v>10.21</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.38</v>
+        <v>13</v>
       </c>
       <c r="R11" t="n">
-        <v>6.31</v>
+        <v>6.43</v>
       </c>
       <c r="S11" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="U11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51.46</v>
+        <v>50.86</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.54</v>
+        <v>14.36</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.92</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.38</v>
+        <v>19</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AF11" t="n">
         <v>0.08</v>
@@ -5177,70 +5177,70 @@
         <v>1.92</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.44</v>
+        <v>9.58</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.08</v>
+        <v>5.12</v>
       </c>
       <c r="BR11" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS11" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BT11" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BU11" t="n">
-        <v>24</v>
+        <v>26.92</v>
       </c>
       <c r="BV11" t="n">
-        <v>8</v>
+        <v>11.54</v>
       </c>
       <c r="BW11" t="n">
-        <v>8</v>
+        <v>11.54</v>
       </c>
       <c r="BX11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="CC11" t="n">
         <v>4.95</v>
@@ -5252,7 +5252,7 @@
         <v>1.3</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CG11" t="n">
         <v>3.25</v>
@@ -5261,10 +5261,10 @@
         <v>1.51</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK11" t="n">
         <v>1.44</v>
@@ -5276,7 +5276,7 @@
         <v>2.57</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO11" t="n">
         <v>1.21</v>
@@ -5300,16 +5300,16 @@
         <v>1.52</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CX11" t="n">
         <v>1.51</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.46</v>
@@ -5324,49 +5324,49 @@
         <v>1.75</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="DE11" t="n">
         <v>0.04</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DH11" t="n">
-        <v>96.12</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.24</v>
+        <v>5.19</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.36</v>
+        <v>43.16</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="DP11" t="n">
-        <v>11.12</v>
+        <v>11.15</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.92</v>
+        <v>12.73</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.4</v>
+        <v>7.42</v>
       </c>
       <c r="DS11" t="n">
         <v>0.12</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.6</v>
+        <v>48.39</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.44</v>
+        <v>13.39</v>
       </c>
       <c r="DY11" t="n">
-        <v>9.44</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DZ11" t="n">
         <v>4</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.24</v>
+        <v>20</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="12">
@@ -5409,94 +5409,94 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F12" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>3.42</v>
+        <v>3.85</v>
       </c>
       <c r="H12" t="n">
-        <v>115.25</v>
+        <v>115.62</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="K12" t="n">
-        <v>5.92</v>
+        <v>6.38</v>
       </c>
       <c r="L12" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>54.75</v>
+        <v>57.69</v>
       </c>
       <c r="N12" t="n">
         <v>0.92</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="P12" t="n">
-        <v>10.25</v>
+        <v>10.23</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.58</v>
+        <v>14</v>
       </c>
       <c r="R12" t="n">
-        <v>5.17</v>
+        <v>5.31</v>
       </c>
       <c r="S12" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="T12" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="U12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="V12" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>56.33</v>
+        <v>56.38</v>
       </c>
       <c r="Y12" t="n">
         <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.83</v>
+        <v>16.69</v>
       </c>
       <c r="AA12" t="n">
-        <v>10</v>
+        <v>10.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.83</v>
+        <v>6.23</v>
       </c>
       <c r="AC12" t="n">
-        <v>21.08</v>
+        <v>20.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AF12" t="n">
         <v>0.23</v>
@@ -5580,70 +5580,70 @@
         <v>2.08</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.16</v>
+        <v>4.12</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="BI12" t="n">
-        <v>4.16</v>
+        <v>4.12</v>
       </c>
       <c r="BJ12" t="n">
         <v>0.96</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.96</v>
+        <v>4.88</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.92</v>
+        <v>5.12</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BU12" t="n">
-        <v>68</v>
+        <v>65.38</v>
       </c>
       <c r="BV12" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BW12" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BX12" t="n">
-        <v>84</v>
+        <v>80.77</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="CA12" t="n">
-        <v>4.06</v>
+        <v>4.13</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.17</v>
+        <v>4.24</v>
       </c>
       <c r="CC12" t="n">
         <v>2.98</v>
@@ -5655,70 +5655,70 @@
         <v>1.24</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="CH12" t="n">
         <v>1.64</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CK12" t="n">
         <v>1.39</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CR12" t="n">
         <v>1.34</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CT12" t="n">
         <v>3.34</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CX12" t="n">
         <v>1.5</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.47</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DB12" t="n">
         <v>1.16</v>
@@ -5727,49 +5727,49 @@
         <v>1.53</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="DH12" t="n">
-        <v>112.4</v>
+        <v>112.7</v>
       </c>
       <c r="DI12" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.48</v>
+        <v>5.73</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="DM12" t="n">
-        <v>55.24</v>
+        <v>56.69</v>
       </c>
       <c r="DN12" t="n">
         <v>0.84</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.04</v>
+        <v>11.96</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.8</v>
+        <v>12.58</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.48</v>
+        <v>5.54</v>
       </c>
       <c r="DS12" t="n">
         <v>0.16</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.56</v>
+        <v>57.54</v>
       </c>
       <c r="DW12" t="n">
         <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>15.84</v>
+        <v>16.27</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.279999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>6.56</v>
+        <v>6.73</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.24</v>
+        <v>21.12</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
         <v>0.33</v>
@@ -5902,52 +5902,52 @@
         <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AI13" t="n">
-        <v>77.38</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AN13" t="n">
-        <v>31.54</v>
+        <v>32.14</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.46</v>
+        <v>10.43</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.85</v>
+        <v>11.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.92</v>
+        <v>10.79</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,82 +5959,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>46.69</v>
+        <v>46.86</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.77</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.23</v>
+        <v>5.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.54</v>
+        <v>3.71</v>
       </c>
       <c r="BD13" t="n">
-        <v>15.77</v>
+        <v>15.64</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BF13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO13" t="n">
         <v>1.77</v>
       </c>
-      <c r="BG13" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1.84</v>
-      </c>
       <c r="BP13" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.84</v>
+        <v>4.81</v>
       </c>
       <c r="BR13" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS13" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT13" t="n">
-        <v>64</v>
+        <v>61.54</v>
       </c>
       <c r="BU13" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BV13" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW13" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BX13" t="n">
-        <v>68</v>
+        <v>69.23</v>
       </c>
       <c r="BY13" t="n">
         <v>3.44</v>
@@ -6043,46 +6043,46 @@
         <v>3.58</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.94</v>
+        <v>5.82</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.21</v>
+        <v>6.06</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.61</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CN13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CO13" t="n">
         <v>1.16</v>
@@ -6091,13 +6091,13 @@
         <v>1.58</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CT13" t="n">
         <v>3.34</v>
@@ -6106,7 +6106,7 @@
         <v>1.64</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CW13" t="n">
         <v>1.63</v>
@@ -6115,13 +6115,13 @@
         <v>1.51</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.46</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB13" t="n">
         <v>1.18</v>
@@ -6130,49 +6130,49 @@
         <v>1.6</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DH13" t="n">
-        <v>82.84</v>
+        <v>83.34</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM13" t="n">
-        <v>34.32</v>
+        <v>34.54</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.04</v>
+        <v>11</v>
       </c>
       <c r="DQ13" t="n">
-        <v>12.08</v>
+        <v>11.88</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.24</v>
+        <v>10.19</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.28</v>
+        <v>44.46</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.72</v>
+        <v>5.85</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
         <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="F14" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="G14" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="H14" t="n">
-        <v>121.67</v>
+        <v>120.85</v>
       </c>
       <c r="I14" t="n">
         <v>-0.08</v>
       </c>
       <c r="J14" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="K14" t="n">
-        <v>7.83</v>
+        <v>7.62</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="M14" t="n">
-        <v>67.92</v>
+        <v>64.31</v>
       </c>
       <c r="N14" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="P14" t="n">
-        <v>10.67</v>
+        <v>10.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.25</v>
+        <v>7.92</v>
       </c>
       <c r="R14" t="n">
-        <v>6.17</v>
+        <v>6.08</v>
       </c>
       <c r="S14" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>63.42</v>
+        <v>63.46</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.33</v>
+        <v>20.23</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.17</v>
+        <v>13</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.17</v>
+        <v>7.23</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.42</v>
+        <v>18</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF14" t="n">
         <v>0.31</v>
@@ -6386,13 +6386,13 @@
         <v>1.62</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.48</v>
+        <v>11.46</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="BJ14" t="n">
         <v>1.12</v>
@@ -6404,52 +6404,52 @@
         <v>0.96</v>
       </c>
       <c r="BM14" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.04</v>
+        <v>5.08</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6.44</v>
+        <v>6.38</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BT14" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BU14" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BW14" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BX14" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="CA14" t="n">
-        <v>6.24</v>
+        <v>6.21</v>
       </c>
       <c r="CB14" t="n">
-        <v>6.77</v>
+        <v>6.71</v>
       </c>
       <c r="CC14" t="n">
         <v>1.63</v>
@@ -6464,7 +6464,7 @@
         <v>1.91</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="CH14" t="n">
         <v>1.9</v>
@@ -6485,7 +6485,7 @@
         <v>2.95</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CO14" t="n">
         <v>1.07</v>
@@ -6505,7 +6505,7 @@
         <v>1.92</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CW14" t="n">
         <v>1.61</v>
@@ -6528,46 +6528,46 @@
         <v>1.83</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="DG14" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="DH14" t="n">
-        <v>111.8</v>
+        <v>111.77</v>
       </c>
       <c r="DI14" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DK14" t="n">
-        <v>7.32</v>
+        <v>7.24</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="DM14" t="n">
-        <v>62.6</v>
+        <v>61</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.96</v>
+        <v>10.8</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.24</v>
+        <v>7.16</v>
       </c>
       <c r="DS14" t="n">
         <v>0.12</v>
@@ -6579,28 +6579,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>61.12</v>
+        <v>61.23</v>
       </c>
       <c r="DW14" t="n">
         <v>0.04</v>
       </c>
       <c r="DX14" t="n">
-        <v>17.96</v>
+        <v>18</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.72</v>
+        <v>10.73</v>
       </c>
       <c r="DZ14" t="n">
-        <v>7.24</v>
+        <v>7.27</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.36</v>
+        <v>18.15</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="15">
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
         <v>13</v>
@@ -6622,82 +6622,82 @@
         <v>0.08</v>
       </c>
       <c r="F15" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="H15" t="n">
-        <v>92.58</v>
+        <v>93.69</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J15" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="K15" t="n">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="L15" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="M15" t="n">
-        <v>41.42</v>
+        <v>42.85</v>
       </c>
       <c r="N15" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="O15" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="P15" t="n">
-        <v>8.92</v>
+        <v>8.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.58</v>
+        <v>11.46</v>
       </c>
       <c r="R15" t="n">
-        <v>8.42</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="T15" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="U15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>45.25</v>
+        <v>45.69</v>
       </c>
       <c r="Y15" t="n">
         <v>0.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.25</v>
+        <v>12.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.67</v>
+        <v>8.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.58</v>
+        <v>4.77</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.58</v>
+        <v>17.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AF15" t="n">
         <v>0.08</v>
@@ -6781,70 +6781,70 @@
         <v>2.38</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BN15" t="n">
         <v>2</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.36</v>
+        <v>6.27</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BT15" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BV15" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW15" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BX15" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="CA15" t="n">
         <v>3.86</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="CC15" t="n">
         <v>4.17</v>
@@ -6856,25 +6856,25 @@
         <v>1.28</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CK15" t="n">
         <v>1.34</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CM15" t="n">
         <v>2.94</v>
@@ -6886,16 +6886,16 @@
         <v>1.18</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CR15" t="n">
         <v>1.36</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CT15" t="n">
         <v>3.26</v>
@@ -6913,7 +6913,7 @@
         <v>1.45</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.6</v>
@@ -6922,55 +6922,55 @@
         <v>2.26</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC15" t="n">
         <v>1.64</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="DE15" t="n">
         <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DH15" t="n">
-        <v>95.44</v>
+        <v>95.88</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.8</v>
+        <v>4.84</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="DM15" t="n">
-        <v>44.16</v>
+        <v>44.77</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.279999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.72</v>
+        <v>10.69</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.880000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="DS15" t="n">
         <v>0.12</v>
@@ -6982,28 +6982,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.12</v>
+        <v>47.27</v>
       </c>
       <c r="DW15" t="n">
         <v>0.08</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.88</v>
+        <v>13.16</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.32</v>
+        <v>8.5</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.56</v>
+        <v>4.66</v>
       </c>
       <c r="EA15" t="n">
-        <v>15.96</v>
+        <v>16.38</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="16">
@@ -7013,13 +7013,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" t="n">
         <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
         <v>0.15</v>
@@ -7103,52 +7103,52 @@
         <v>1.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AG16" t="n">
         <v>1.08</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AI16" t="n">
-        <v>79.75</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="AJ16" t="n">
         <v>-0.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.67</v>
+        <v>4.69</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AN16" t="n">
-        <v>36.58</v>
+        <v>36.92</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12.08</v>
+        <v>12.54</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.83</v>
+        <v>9.69</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.67</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.83</v>
+        <v>1.08</v>
       </c>
       <c r="AV16" t="n">
         <v>0</v>
@@ -7160,82 +7160,82 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>41.67</v>
+        <v>41.69</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.08</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="BB16" t="n">
-        <v>8</v>
+        <v>7.77</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.75</v>
+        <v>4.23</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.92</v>
+        <v>18.08</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.08</v>
+        <v>10.96</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="BP16" t="n">
-        <v>5.72</v>
+        <v>5.62</v>
       </c>
       <c r="BQ16" t="n">
         <v>5</v>
       </c>
       <c r="BR16" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS16" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT16" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BU16" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BV16" t="n">
-        <v>16</v>
+        <v>19.23</v>
       </c>
       <c r="BW16" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX16" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BY16" t="n">
         <v>3.33</v>
@@ -7244,25 +7244,25 @@
         <v>3.33</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.51</v>
+        <v>4.47</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.67</v>
+        <v>4.64</v>
       </c>
       <c r="CC16" t="n">
-        <v>7.74</v>
+        <v>7.36</v>
       </c>
       <c r="CD16" t="n">
-        <v>7.39</v>
+        <v>7.05</v>
       </c>
       <c r="CE16" t="n">
         <v>1.26</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CH16" t="n">
         <v>1.59</v>
@@ -7277,7 +7277,7 @@
         <v>1.36</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM16" t="n">
         <v>2.88</v>
@@ -7289,7 +7289,7 @@
         <v>1.17</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ16" t="n">
         <v>2.42</v>
@@ -7316,7 +7316,7 @@
         <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.37</v>
@@ -7331,46 +7331,46 @@
         <v>1.61</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DF16" t="n">
         <v>0.96</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="DH16" t="n">
-        <v>84.2</v>
+        <v>83.88</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DK16" t="n">
         <v>5.16</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="DM16" t="n">
-        <v>41.76</v>
+        <v>41.73</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.16</v>
+        <v>11.42</v>
       </c>
       <c r="DQ16" t="n">
-        <v>10.48</v>
+        <v>10.38</v>
       </c>
       <c r="DR16" t="n">
         <v>8.08</v>
@@ -7385,28 +7385,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.16</v>
+        <v>44.08</v>
       </c>
       <c r="DW16" t="n">
         <v>0.08</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.8</v>
+        <v>12.88</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.6</v>
+        <v>4.81</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.44</v>
+        <v>18.5</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="17">
@@ -7416,13 +7416,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17" t="n">
         <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
         <v>0.08</v>
@@ -7509,136 +7509,136 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AI17" t="n">
-        <v>97</v>
+        <v>98.38</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
         <v>5</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AN17" t="n">
-        <v>53.58</v>
+        <v>52.69</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.25</v>
+        <v>11.92</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.08</v>
+        <v>9.85</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.67</v>
+        <v>8</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>51.5</v>
+        <v>51.31</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.08</v>
       </c>
       <c r="BA17" t="n">
-        <v>18.25</v>
+        <v>17.69</v>
       </c>
       <c r="BB17" t="n">
-        <v>11.58</v>
+        <v>11.15</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.67</v>
+        <v>6.54</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.92</v>
+        <v>20.31</v>
       </c>
       <c r="BE17" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BF17" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.68</v>
+        <v>2.77</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.119999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.68</v>
+        <v>2.77</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="BL17" t="n">
         <v>0.96</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.72</v>
+        <v>4.73</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="BR17" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS17" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT17" t="n">
-        <v>40</v>
+        <v>42.31</v>
       </c>
       <c r="BU17" t="n">
-        <v>28</v>
+        <v>30.77</v>
       </c>
       <c r="BV17" t="n">
-        <v>20</v>
+        <v>23.08</v>
       </c>
       <c r="BW17" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX17" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BY17" t="n">
         <v>1.87</v>
@@ -7647,25 +7647,25 @@
         <v>1.89</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="CE17" t="n">
         <v>1.26</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CH17" t="n">
         <v>1.57</v>
@@ -7674,7 +7674,7 @@
         <v>2.2</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK17" t="n">
         <v>1.45</v>
@@ -7683,7 +7683,7 @@
         <v>1.81</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CN17" t="n">
         <v>1.95</v>
@@ -7695,7 +7695,7 @@
         <v>1.6</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
@@ -7710,10 +7710,10 @@
         <v>1.58</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX17" t="n">
         <v>1.51</v>
@@ -7731,85 +7731,85 @@
         <v>1.2</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="DE17" t="n">
         <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="DH17" t="n">
-        <v>109.28</v>
+        <v>109.5</v>
       </c>
       <c r="DI17" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.36</v>
+        <v>5.34</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM17" t="n">
-        <v>59.88</v>
+        <v>59.19</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DP17" t="n">
-        <v>11.32</v>
+        <v>11.19</v>
       </c>
       <c r="DQ17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.92</v>
+        <v>7.12</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.64</v>
+        <v>54.42</v>
       </c>
       <c r="DW17" t="n">
         <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>18.56</v>
+        <v>18.27</v>
       </c>
       <c r="DY17" t="n">
-        <v>11.92</v>
+        <v>11.69</v>
       </c>
       <c r="DZ17" t="n">
-        <v>6.64</v>
+        <v>6.58</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.36</v>
+        <v>20.54</v>
       </c>
       <c r="EB17" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="18">
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" t="n">
         <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
         <v>0.15</v>
@@ -8315,49 +8315,49 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AI19" t="n">
-        <v>78.5</v>
+        <v>77.62</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN19" t="n">
-        <v>33.67</v>
+        <v>32.69</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.25</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.83</v>
+        <v>10.77</v>
       </c>
       <c r="AS19" t="n">
-        <v>10</v>
+        <v>9.85</v>
       </c>
       <c r="AT19" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -8369,82 +8369,82 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>43.92</v>
+        <v>43.85</v>
       </c>
       <c r="AZ19" t="n">
         <v>0.08</v>
       </c>
       <c r="BA19" t="n">
-        <v>8.58</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.08</v>
+        <v>5.92</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BD19" t="n">
-        <v>17</v>
+        <v>17.15</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.56</v>
+        <v>10.65</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BJ19" t="n">
         <v>1</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.96</v>
+        <v>5.85</v>
       </c>
       <c r="BQ19" t="n">
-        <v>4.6</v>
+        <v>4.81</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT19" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BU19" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV19" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>64</v>
+        <v>61.54</v>
       </c>
       <c r="BY19" t="n">
         <v>4.37</v>
@@ -8453,16 +8453,16 @@
         <v>4.52</v>
       </c>
       <c r="CA19" t="n">
-        <v>5.01</v>
+        <v>5.05</v>
       </c>
       <c r="CB19" t="n">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="CC19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="CD19" t="n">
-        <v>9.050000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="CE19" t="n">
         <v>1.24</v>
@@ -8477,7 +8477,7 @@
         <v>1.66</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.63</v>
@@ -8486,10 +8486,10 @@
         <v>1.37</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CN19" t="n">
         <v>2.16</v>
@@ -8498,40 +8498,40 @@
         <v>1.15</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CT19" t="n">
         <v>3.36</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX19" t="n">
         <v>1.51</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.44</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DB19" t="n">
         <v>1.17</v>
@@ -8540,49 +8540,49 @@
         <v>1.54</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DE19" t="n">
         <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="DH19" t="n">
-        <v>80.59999999999999</v>
+        <v>80.08</v>
       </c>
       <c r="DI19" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM19" t="n">
-        <v>38.32</v>
+        <v>37.66</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="DP19" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.84</v>
+        <v>11.77</v>
       </c>
       <c r="DR19" t="n">
-        <v>10.4</v>
+        <v>10.31</v>
       </c>
       <c r="DS19" t="n">
         <v>0.08</v>
@@ -8594,28 +8594,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>44.4</v>
+        <v>44.35</v>
       </c>
       <c r="DW19" t="n">
         <v>0.04</v>
       </c>
       <c r="DX19" t="n">
-        <v>10.52</v>
+        <v>10.38</v>
       </c>
       <c r="DY19" t="n">
-        <v>6.96</v>
+        <v>6.84</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="EA19" t="n">
-        <v>14.96</v>
+        <v>15.12</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -3036,7 +3036,7 @@
         <v>12.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.62</v>
+        <v>11.54</v>
       </c>
       <c r="R6" t="n">
         <v>7</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>45.15</v>
+        <v>45.23</v>
       </c>
       <c r="Y6" t="n">
         <v>0.08</v>
@@ -3348,7 +3348,7 @@
         <v>12.96</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.62</v>
+        <v>11.58</v>
       </c>
       <c r="DR6" t="n">
         <v>7.93</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.38</v>
+        <v>45.42</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
@@ -5475,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>56.38</v>
+        <v>56.31</v>
       </c>
       <c r="Y12" t="n">
         <v>0.08</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>57.54</v>
+        <v>57.5</v>
       </c>
       <c r="DW12" t="n">
         <v>0.12</v>
@@ -7160,7 +7160,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>41.69</v>
+        <v>41.62</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.08</v>
@@ -7385,7 +7385,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>44.08</v>
+        <v>44.04</v>
       </c>
       <c r="DW16" t="n">
         <v>0.08</v>
@@ -8369,7 +8369,7 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>43.85</v>
+        <v>43.92</v>
       </c>
       <c r="AZ19" t="n">
         <v>0.08</v>
@@ -8594,7 +8594,7 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>44.35</v>
+        <v>44.39</v>
       </c>
       <c r="DW19" t="n">
         <v>0.04</v>

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
         <v>0.23</v>
@@ -3887,139 +3887,139 @@
         <v>1.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AI8" t="n">
-        <v>104.31</v>
+        <v>105.86</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AN8" t="n">
-        <v>41.92</v>
+        <v>42.29</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.92</v>
+        <v>11.79</v>
       </c>
       <c r="AR8" t="n">
-        <v>10.38</v>
+        <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.31</v>
+        <v>7.64</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.08</v>
+        <v>48.21</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>14.69</v>
+        <v>14.79</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.460000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.23</v>
+        <v>6.21</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.69</v>
+        <v>19.93</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.92</v>
+        <v>11</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.54</v>
+        <v>5.52</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.38</v>
+        <v>5.48</v>
       </c>
       <c r="BR8" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS8" t="n">
-        <v>88.45999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT8" t="n">
-        <v>53.85</v>
+        <v>51.85</v>
       </c>
       <c r="BU8" t="n">
-        <v>23.08</v>
+        <v>22.22</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BW8" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX8" t="n">
-        <v>53.85</v>
+        <v>55.56</v>
       </c>
       <c r="BY8" t="n">
         <v>2.15</v>
@@ -4028,31 +4028,31 @@
         <v>2.34</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.44</v>
+        <v>4.29</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.49</v>
+        <v>4.35</v>
       </c>
       <c r="CE8" t="n">
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CH8" t="n">
         <v>1.49</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.7</v>
@@ -4061,22 +4061,22 @@
         <v>1.51</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM8" t="n">
         <v>2.42</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4091,10 +4091,10 @@
         <v>1.53</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX8" t="n">
         <v>1.55</v>
@@ -4112,70 +4112,70 @@
         <v>1.25</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DG8" t="n">
         <v>3</v>
       </c>
       <c r="DH8" t="n">
-        <v>109.73</v>
+        <v>110.33</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="DK8" t="n">
-        <v>6.38</v>
+        <v>6.37</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.42</v>
+        <v>46.45</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="DP8" t="n">
-        <v>10.84</v>
+        <v>10.82</v>
       </c>
       <c r="DQ8" t="n">
-        <v>10.03</v>
+        <v>10.11</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.66</v>
+        <v>6.85</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.81</v>
+        <v>50.78</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.84</v>
+        <v>15.85</v>
       </c>
       <c r="DY8" t="n">
         <v>10.04</v>
@@ -4184,13 +4184,13 @@
         <v>5.81</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.5</v>
+        <v>20.59</v>
       </c>
       <c r="EB8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="EC8" t="n">
         <v>1.74</v>
-      </c>
-      <c r="EC8" t="n">
-        <v>1.7</v>
       </c>
     </row>
     <row r="9">
@@ -5812,61 +5812,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
         <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="G13" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="H13" t="n">
-        <v>88.75</v>
+        <v>89</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>4.17</v>
+        <v>4.38</v>
       </c>
       <c r="L13" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="M13" t="n">
-        <v>37.33</v>
+        <v>37.62</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="P13" t="n">
-        <v>11.67</v>
+        <v>11.69</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.33</v>
+        <v>12.15</v>
       </c>
       <c r="R13" t="n">
-        <v>9.5</v>
+        <v>9.23</v>
       </c>
       <c r="S13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5878,28 +5878,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>41.67</v>
+        <v>42.31</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>9.67</v>
+        <v>9.92</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.25</v>
+        <v>6.31</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.42</v>
+        <v>3.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.08</v>
+        <v>17.54</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AF13" t="n">
         <v>0.14</v>
@@ -5983,70 +5983,70 @@
         <v>1.71</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.619999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL13" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.81</v>
+        <v>4.93</v>
       </c>
       <c r="BR13" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS13" t="n">
-        <v>84.62</v>
+        <v>85.19</v>
       </c>
       <c r="BT13" t="n">
-        <v>61.54</v>
+        <v>59.26</v>
       </c>
       <c r="BU13" t="n">
-        <v>42.31</v>
+        <v>40.74</v>
       </c>
       <c r="BV13" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BW13" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BX13" t="n">
-        <v>69.23</v>
+        <v>70.37</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.44</v>
+        <v>3.39</v>
       </c>
       <c r="BZ13" t="n">
-        <v>3.58</v>
+        <v>3.51</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.45</v>
+        <v>4.41</v>
       </c>
       <c r="CC13" t="n">
         <v>5.82</v>
@@ -6055,22 +6055,22 @@
         <v>6.06</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF13" t="n">
         <v>2.29</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK13" t="n">
         <v>1.43</v>
@@ -6079,10 +6079,10 @@
         <v>1.82</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CO13" t="n">
         <v>1.16</v>
@@ -6106,7 +6106,7 @@
         <v>1.64</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CW13" t="n">
         <v>1.63</v>
@@ -6115,7 +6115,7 @@
         <v>1.51</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.46</v>
@@ -6130,49 +6130,49 @@
         <v>1.6</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="DH13" t="n">
-        <v>83.34</v>
+        <v>83.66</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DK13" t="n">
-        <v>3.31</v>
+        <v>3.44</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="DM13" t="n">
-        <v>34.54</v>
+        <v>34.78</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DP13" t="n">
-        <v>11</v>
+        <v>11.04</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.88</v>
+        <v>11.81</v>
       </c>
       <c r="DR13" t="n">
-        <v>10.19</v>
+        <v>10.04</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.46</v>
+        <v>44.67</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX13" t="n">
-        <v>9.42</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DY13" t="n">
-        <v>5.85</v>
+        <v>5.89</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.58</v>
+        <v>3.67</v>
       </c>
       <c r="EA13" t="n">
-        <v>16.3</v>
+        <v>16.55</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Netherlands_Eredivisie_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="F2" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="H2" t="n">
-        <v>102.67</v>
+        <v>103.69</v>
       </c>
       <c r="I2" t="n">
         <v>0.08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="L2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="M2" t="n">
-        <v>49.5</v>
+        <v>49.77</v>
       </c>
       <c r="N2" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="O2" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="P2" t="n">
-        <v>9.42</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>11.62</v>
       </c>
       <c r="R2" t="n">
-        <v>7.08</v>
+        <v>6.69</v>
       </c>
       <c r="S2" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="T2" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="U2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51.08</v>
+        <v>51.15</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.83</v>
+        <v>15.69</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.92</v>
+        <v>9.69</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.92</v>
+        <v>6</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.83</v>
+        <v>17.92</v>
       </c>
       <c r="AD2" t="n">
         <v>1.77</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AF2" t="n">
         <v>0.07000000000000001</v>
@@ -1550,70 +1550,70 @@
         <v>2.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.92</v>
+        <v>9.93</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.12</v>
+        <v>5.15</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>80.77</v>
+        <v>81.48</v>
       </c>
       <c r="BT2" t="n">
-        <v>65.38</v>
+        <v>66.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>46.15</v>
+        <v>48.15</v>
       </c>
       <c r="BV2" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BX2" t="n">
-        <v>73.08</v>
+        <v>70.37</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.58</v>
+        <v>4.62</v>
       </c>
       <c r="CC2" t="n">
         <v>2.43</v>
@@ -1625,37 +1625,37 @@
         <v>1.24</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CG2" t="n">
         <v>3.68</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="